--- a/Documentation/GanntChart/BattleNationsGanntChart.xlsx
+++ b/Documentation/GanntChart/BattleNationsGanntChart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jreig\git\BattleNations\Documentation\GanntChart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7B5CA29-5219-48F3-8FB1-CB715C0B9854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{34C683D4-32F6-4647-8681-0B1E686158EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="213">
   <si>
     <t/>
   </si>
@@ -416,9 +416,6 @@
     <t xml:space="preserve">Prepare for Customer Presentation </t>
   </si>
   <si>
-    <t>Update whatever requests we get from customer (17-Apr-26 - 24-Apr-26)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Add second game mode </t>
   </si>
   <si>
@@ -449,9 +446,6 @@
     <t>Add player owned chain check logic for fortify</t>
   </si>
   <si>
-    <t>Stil Need Info Button on general Game Rules on start screen. + terrain bonus explaination on game screen. Time To finish: 1.5 hours</t>
-  </si>
-  <si>
     <t>Allow users to choose what gamemode to play</t>
   </si>
   <si>
@@ -497,9 +491,6 @@
     <t>BOTH</t>
   </si>
   <si>
-    <t>Music logic is implemented, but need to select music to wire it to</t>
-  </si>
-  <si>
     <t>Ensure Game Is fully playable</t>
   </si>
   <si>
@@ -554,54 +545,21 @@
     <t>Java doc GameController + newly Created test files (03-Apr-26 - 10-Apr-26)</t>
   </si>
   <si>
-    <t>3/6 test methods implemented, but not on master branch yet. Estimated Time to complete: 1.25 hours</t>
-  </si>
-  <si>
-    <t>Code Is almost done, but not on master branch yet. Estimated Time to complete: .5 hours</t>
-  </si>
-  <si>
     <t>Display Player owed region percentages on region display</t>
   </si>
   <si>
-    <t>Time to complete: 30 minutes</t>
-  </si>
-  <si>
     <t>Display Simple Info on terrain bonuses + capital symbols</t>
   </si>
   <si>
-    <t>Test Game Logic</t>
-  </si>
-  <si>
-    <t>Relies on services that have already been tested. Only tests needed are on the GamePhase Enum and Player rotations.  Time to complete 1.5 hours</t>
-  </si>
-  <si>
-    <t>Test Map Loader service</t>
-  </si>
-  <si>
-    <t>Should be a really easy test since we already have txt files to test. Time to complete: 1 hour</t>
-  </si>
-  <si>
     <t>Look through all files javadocs + polish anywhere needed</t>
   </si>
   <si>
     <t>Time to complete: 2 hours</t>
   </si>
   <si>
-    <t>Get Game Manual Completed</t>
-  </si>
-  <si>
-    <t>Hours Alloted to complete: 26.75</t>
-  </si>
-  <si>
-    <t>Polish User Manual</t>
-  </si>
-  <si>
     <t>Prepare for final Presentation</t>
   </si>
   <si>
-    <t>Polish Game + Visuals  (27-Mar-26 - 03-Apr-26)</t>
-  </si>
-  <si>
     <t>Display Player owed region percentages on region display (10-Apr-26 - 17-Apr-26)</t>
   </si>
   <si>
@@ -617,23 +575,110 @@
     <t>Look through all files javadocs + polish anywhere needed (10-Apr-26 - 17-Apr-26)</t>
   </si>
   <si>
-    <t>Get Game Manual Completed (10-Apr-26 - 17-Apr-26)</t>
-  </si>
-  <si>
     <t>Prepare for Customer Presentation  (10-Apr-26 - 17-Apr-26)</t>
   </si>
   <si>
-    <t>Polish User Manual (17-Apr-26 - 24-Apr-26)</t>
-  </si>
-  <si>
     <t>Prepare for final Presentation (17-Apr-26 - 24-Apr-26)</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>Select Style For Game manual</t>
+  </si>
+  <si>
+    <t>Complete "User" Section of Game Manual</t>
+  </si>
+  <si>
+    <t>Complete Challenges Faced Section of Game Manual</t>
+  </si>
+  <si>
+    <t>Complete Future Plans Section Of game Manual</t>
+  </si>
+  <si>
+    <t>Break up SetUpGUI Class</t>
+  </si>
+  <si>
+    <t>Test GameLogic class</t>
+  </si>
+  <si>
+    <t>Test MapLoaderService class</t>
+  </si>
+  <si>
+    <t>Update GUI Displays for relative sizing</t>
+  </si>
+  <si>
+    <t>Write Final Test for NeigborService Class</t>
+  </si>
+  <si>
+    <t>Add GAANT Chart to Game Manual</t>
+  </si>
+  <si>
+    <t>Add UML Diagrams to game Manual</t>
+  </si>
+  <si>
+    <t>Add Test Section To game Manual</t>
+  </si>
+  <si>
+    <t>Update whatever requests we get from customer (17-Apr-26 - 22-Apr-26)</t>
+  </si>
+  <si>
+    <t>Polish Game + Visuals  (10-Apr-26 - 17-Apr-26)</t>
+  </si>
+  <si>
+    <t>Complete Future Plans Section Of game Manual (10-Apr-26 - 17-Apr-26)</t>
+  </si>
+  <si>
+    <t>Complete Challenges Faced Section of Game Manual (10-Apr-26 - 17-Apr-26)</t>
+  </si>
+  <si>
+    <t>Complete "User" Section of Game Manual (10-Apr-26 - 17-Apr-26)</t>
+  </si>
+  <si>
+    <t>Select Style For Game manual (10-Apr-26 - 17-Apr-26)</t>
+  </si>
+  <si>
+    <t>Break up SetUpGUI Class (10-Apr-26 - 17-Apr-26)</t>
+  </si>
+  <si>
+    <t>Update GUI Displays for relative sizing (10-Apr-26 - 17-Apr-26)</t>
+  </si>
+  <si>
+    <t>Add Flow Chart to game Manual (17-Apr-26 - 24-Apr-26)</t>
+  </si>
+  <si>
+    <t>Add Important Code Section To game Manual</t>
+  </si>
+  <si>
+    <t>Add Important Code Section To game Manual (17-Apr-26 - 24-Apr-26)</t>
+  </si>
+  <si>
+    <t>Add Test Section To game Manual (17-Apr-26 - 24-Apr-26)</t>
+  </si>
+  <si>
+    <t>Add UML Diagrams to game Manual (17-Apr-26 - 24-Apr-26)</t>
+  </si>
+  <si>
+    <t>Add GAANT Chart to Game Manual (17-Apr-26 - 24-Apr-26)</t>
+  </si>
+  <si>
+    <t>Add Flow Charts to game Manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add Images to Game Manual Where Appropriate </t>
+  </si>
+  <si>
+    <t>Add Images to Game Manual Where Appropriate (17-Apr-26 - 24-Apr-26)</t>
+  </si>
+  <si>
+    <t>Write Final Test for NeighborService Class (17-Apr-26 - 24-Apr-26)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="360" x14ac:knownFonts="1">
+  <fonts count="356" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2776,36 +2821,12 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="151">
+  <fills count="149">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3660,18 +3681,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4C4C4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF333333"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF333333"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -3719,7 +3728,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="450">
+  <cellXfs count="437">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3739,7 +3748,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4405,46 +4414,40 @@
     <xf numFmtId="0" fontId="294" fillId="139" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="304" fillId="140" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="314" fillId="141" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="323" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="310" fillId="140" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="319" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="325" fillId="142" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="328" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="321" fillId="141" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="324" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="336" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="332" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="333" fillId="142" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="344" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="336" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="344" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="337" fillId="144" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="348" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="345" fillId="143" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="350" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="348" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="350" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="349" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="354" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="354" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="355" fillId="146" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="351" fillId="144" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="133" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4501,13 +4504,13 @@
     <xf numFmtId="0" fontId="249" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="153" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="154" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="155" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="153" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="146" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -4561,59 +4564,56 @@
     <xf numFmtId="9" fontId="286" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="324" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="320" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="324" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="320" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="302" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="145" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="309" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="303" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="302" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="303" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="304" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="305" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="306" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="307" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="308" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="323" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="312" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="343" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="313" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="147" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="303" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="313" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="305" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="306" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="307" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="308" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="309" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="310" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="311" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="327" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="347" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="312" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="313" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="314" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="315" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="316" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4624,16 +4624,16 @@
     <xf numFmtId="0" fontId="318" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="319" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="320" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="321" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="322" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="325" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="326" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="327" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="328" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="329" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4642,18 +4642,18 @@
     <xf numFmtId="0" fontId="330" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="331" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="332" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="333" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="334" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="335" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="336" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="337" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="338" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4669,22 +4669,16 @@
     <xf numFmtId="0" fontId="342" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="343" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="344" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="345" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="346" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="350" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="351" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="347" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="348" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="349" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="352" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4693,13 +4687,7 @@
     <xf numFmtId="0" fontId="353" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="356" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="357" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="358" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="354" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="291" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4708,115 +4696,288 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="146" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="290" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="291" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="355" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="148" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="146" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="322" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="295" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="296" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="297" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="298" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="299" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="300" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="301" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="183" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="185" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="189" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="190" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="191" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="199" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="200" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="201" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="202" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="203" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="204" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="205" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="209" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="211" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="212" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="213" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="214" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="215" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="277" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="278" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="279" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="280" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="281" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="282" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="283" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="284" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="145" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="219" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="220" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="221" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="222" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="223" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="224" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="225" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="145" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="253" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="253" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="229" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="231" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="232" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="233" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="234" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="235" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="236" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="240" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="241" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="242" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="243" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="244" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="245" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="246" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="145" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="147" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="229" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="230" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="231" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="232" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="233" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="234" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="235" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="236" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="240" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="241" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="242" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="243" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="244" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="245" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="246" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="147" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="229" fillId="145" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="229" fillId="147" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="249" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="250" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="251" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="252" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="253" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="254" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="255" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="256" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="257" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="258" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="259" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="260" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="249" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="250" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="251" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="252" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="253" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="254" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="255" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="256" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="257" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="258" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="259" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="260" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="141" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4825,231 +4986,40 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="160" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="173" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="174" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="160" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="344" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="311" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="331" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="219" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="220" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="221" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="222" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="223" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="224" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="225" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="295" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="296" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="297" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="298" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="299" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="300" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="301" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="178" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="179" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="180" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="183" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="185" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="189" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="190" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="191" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="199" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="200" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="201" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="202" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="203" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="204" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="205" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="209" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="210" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="211" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="212" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="213" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="214" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="215" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="277" fillId="149" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="278" fillId="149" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="279" fillId="149" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="280" fillId="149" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="281" fillId="149" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="282" fillId="149" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="283" fillId="149" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="284" fillId="149" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="147" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="150" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="143" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="335" fillId="143" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="150" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="295" fillId="150" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="296" fillId="150" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="297" fillId="150" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="298" fillId="150" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="299" fillId="150" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="300" fillId="150" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="301" fillId="150" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="326" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="148" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="290" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="291" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="148" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="315" fillId="148" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="359" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="331" fillId="146" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5391,17 +5361,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DF67"/>
+  <dimension ref="A1:DF78"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="1" width="52.83203125" customWidth="1"/>
-    <col min="2" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="29.4140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="1" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" customWidth="1"/>
-    <col min="11" max="11" width="19.125" customWidth="1"/>
+    <col min="2" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" customWidth="1"/>
+    <col min="5" max="5" width="17.70703125" customWidth="1"/>
+    <col min="6" max="6" width="10.95703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="3.33203125" customWidth="1"/>
+    <col min="9" max="9" width="8.5" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="31.1640625" customWidth="1"/>
     <col min="16" max="16" width="31.5390625" customWidth="1"/>
     <col min="22" max="22" width="15.0390625" customWidth="1"/>
+    <col min="71" max="71" width="29.20703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:110" ht="31.25" x14ac:dyDescent="0.8">
@@ -5521,13 +5495,13 @@
       <c r="DF1" s="2"/>
     </row>
     <row r="2" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A2" s="378" t="s">
+      <c r="A2" s="376" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="331" t="s">
+      <c r="B2" s="377" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="331" t="s">
+      <c r="C2" s="377" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="11"/>
@@ -5536,313 +5510,313 @@
       <c r="G2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="379" t="s">
+      <c r="H2" s="378" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="331" t="s">
+      <c r="I2" s="377" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="331" t="s">
+      <c r="J2" s="377" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="331" t="s">
+      <c r="K2" s="377" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="331" t="s">
+      <c r="L2" s="377" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="331" t="s">
+      <c r="M2" s="377" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="331" t="s">
+      <c r="N2" s="377" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="331" t="s">
+      <c r="O2" s="377" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="331" t="s">
+      <c r="P2" s="377" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="331" t="s">
+      <c r="Q2" s="377" t="s">
         <v>2</v>
       </c>
-      <c r="R2" s="331" t="s">
+      <c r="R2" s="377" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="331" t="s">
+      <c r="S2" s="377" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="367" t="s">
+      <c r="T2" s="423" t="s">
         <v>3</v>
       </c>
-      <c r="U2" s="331" t="s">
+      <c r="U2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="V2" s="331" t="s">
+      <c r="V2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="W2" s="331" t="s">
+      <c r="W2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="X2" s="331" t="s">
+      <c r="X2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="Y2" s="331" t="s">
+      <c r="Y2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="Z2" s="331" t="s">
+      <c r="Z2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AA2" s="331" t="s">
+      <c r="AA2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AB2" s="331" t="s">
+      <c r="AB2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="331" t="s">
+      <c r="AC2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AD2" s="331" t="s">
+      <c r="AD2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AE2" s="331" t="s">
+      <c r="AE2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AF2" s="331" t="s">
+      <c r="AF2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AG2" s="331" t="s">
+      <c r="AG2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AH2" s="331" t="s">
+      <c r="AH2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AI2" s="331" t="s">
+      <c r="AI2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AJ2" s="331" t="s">
+      <c r="AJ2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AK2" s="331" t="s">
+      <c r="AK2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AL2" s="331" t="s">
+      <c r="AL2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AM2" s="331" t="s">
+      <c r="AM2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AN2" s="331" t="s">
+      <c r="AN2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AO2" s="331" t="s">
+      <c r="AO2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AP2" s="331" t="s">
+      <c r="AP2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AQ2" s="331" t="s">
+      <c r="AQ2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AR2" s="331" t="s">
+      <c r="AR2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AS2" s="331" t="s">
+      <c r="AS2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AT2" s="331" t="s">
+      <c r="AT2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AU2" s="331" t="s">
+      <c r="AU2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AV2" s="331" t="s">
+      <c r="AV2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AW2" s="331" t="s">
+      <c r="AW2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AX2" s="331" t="s">
+      <c r="AX2" s="377" t="s">
         <v>3</v>
       </c>
-      <c r="AY2" s="368" t="s">
+      <c r="AY2" s="424" t="s">
         <v>4</v>
       </c>
-      <c r="AZ2" s="331" t="s">
+      <c r="AZ2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BA2" s="331" t="s">
+      <c r="BA2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BB2" s="331" t="s">
+      <c r="BB2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BC2" s="331" t="s">
+      <c r="BC2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BD2" s="331" t="s">
+      <c r="BD2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BE2" s="331" t="s">
+      <c r="BE2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BF2" s="331" t="s">
+      <c r="BF2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BG2" s="331" t="s">
+      <c r="BG2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BH2" s="331" t="s">
+      <c r="BH2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BI2" s="331" t="s">
+      <c r="BI2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BJ2" s="331" t="s">
+      <c r="BJ2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BK2" s="331" t="s">
+      <c r="BK2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BL2" s="331" t="s">
+      <c r="BL2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BM2" s="331" t="s">
+      <c r="BM2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BN2" s="331" t="s">
+      <c r="BN2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BO2" s="331" t="s">
+      <c r="BO2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BP2" s="331" t="s">
+      <c r="BP2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BQ2" s="331" t="s">
+      <c r="BQ2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BR2" s="331" t="s">
+      <c r="BR2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BS2" s="331" t="s">
+      <c r="BS2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BT2" s="331" t="s">
+      <c r="BT2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BU2" s="331" t="s">
+      <c r="BU2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BV2" s="331" t="s">
+      <c r="BV2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BW2" s="331" t="s">
+      <c r="BW2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BX2" s="331" t="s">
+      <c r="BX2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BY2" s="331" t="s">
+      <c r="BY2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="BZ2" s="331" t="s">
+      <c r="BZ2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="CA2" s="331" t="s">
+      <c r="CA2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="CB2" s="331" t="s">
+      <c r="CB2" s="377" t="s">
         <v>4</v>
       </c>
-      <c r="CC2" s="330" t="s">
+      <c r="CC2" s="390" t="s">
         <v>5</v>
       </c>
-      <c r="CD2" s="331" t="s">
+      <c r="CD2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CE2" s="331" t="s">
+      <c r="CE2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CF2" s="331" t="s">
+      <c r="CF2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CG2" s="331" t="s">
+      <c r="CG2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CH2" s="331" t="s">
+      <c r="CH2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CI2" s="331" t="s">
+      <c r="CI2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CJ2" s="331" t="s">
+      <c r="CJ2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CK2" s="331" t="s">
+      <c r="CK2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CL2" s="331" t="s">
+      <c r="CL2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CM2" s="331" t="s">
+      <c r="CM2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CN2" s="331" t="s">
+      <c r="CN2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CO2" s="331" t="s">
+      <c r="CO2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CP2" s="331" t="s">
+      <c r="CP2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CQ2" s="331" t="s">
+      <c r="CQ2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CR2" s="331" t="s">
+      <c r="CR2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CS2" s="331" t="s">
+      <c r="CS2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CT2" s="331" t="s">
+      <c r="CT2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CU2" s="331" t="s">
+      <c r="CU2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CV2" s="331" t="s">
+      <c r="CV2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CW2" s="331" t="s">
+      <c r="CW2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CX2" s="331" t="s">
+      <c r="CX2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CY2" s="331" t="s">
+      <c r="CY2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="CZ2" s="331" t="s">
+      <c r="CZ2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="DA2" s="331" t="s">
+      <c r="DA2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="DB2" s="331" t="s">
+      <c r="DB2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="DC2" s="331" t="s">
+      <c r="DC2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="DD2" s="331" t="s">
+      <c r="DD2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="DE2" s="331" t="s">
+      <c r="DE2" s="377" t="s">
         <v>5</v>
       </c>
-      <c r="DF2" s="331" t="s">
+      <c r="DF2" s="377" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5860,7 +5834,7 @@
         <v>86</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>87</v>
@@ -6301,7 +6275,7 @@
       <c r="DF4" s="2"/>
     </row>
     <row r="5" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A5" s="287" t="s">
+      <c r="A5" s="281" t="s">
         <v>91</v>
       </c>
       <c r="B5" s="129" t="s">
@@ -6313,23 +6287,23 @@
       <c r="D5" s="131">
         <v>1</v>
       </c>
-      <c r="E5" s="446" t="s">
-        <v>151</v>
+      <c r="E5" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F5" s="132"/>
       <c r="G5" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="H5" s="343" t="s">
+      <c r="H5" s="333" t="s">
         <v>88</v>
       </c>
-      <c r="I5" s="380" t="s">
+      <c r="I5" s="379" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="381" t="s">
+      <c r="J5" s="380" t="s">
         <v>42</v>
       </c>
-      <c r="K5" s="382" t="s">
+      <c r="K5" s="381" t="s">
         <v>42</v>
       </c>
       <c r="L5" s="2"/>
@@ -6433,10 +6407,10 @@
       <c r="DF5" s="2"/>
     </row>
     <row r="6" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A6" s="287" t="s">
+      <c r="A6" s="281" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="252">
+      <c r="B6" s="250">
         <v>46073</v>
       </c>
       <c r="C6" s="134" t="s">
@@ -6445,8 +6419,8 @@
       <c r="D6" s="135">
         <v>1</v>
       </c>
-      <c r="E6" s="446" t="s">
-        <v>152</v>
+      <c r="E6" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F6" s="136"/>
       <c r="G6" s="137" t="s">
@@ -6455,16 +6429,16 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="150"/>
-      <c r="K6" s="332" t="s">
+      <c r="K6" s="330" t="s">
         <v>96</v>
       </c>
-      <c r="L6" s="365"/>
-      <c r="M6" s="365"/>
-      <c r="N6" s="365"/>
-      <c r="O6" s="365"/>
-      <c r="P6" s="365"/>
-      <c r="Q6" s="365"/>
-      <c r="R6" s="365"/>
+      <c r="L6" s="421"/>
+      <c r="M6" s="421"/>
+      <c r="N6" s="421"/>
+      <c r="O6" s="421"/>
+      <c r="P6" s="421"/>
+      <c r="Q6" s="421"/>
+      <c r="R6" s="421"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
@@ -6559,20 +6533,20 @@
       <c r="DF6" s="2"/>
     </row>
     <row r="7" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A7" s="287" t="s">
+      <c r="A7" s="281" t="s">
         <v>89</v>
       </c>
       <c r="B7" s="142" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="251">
+      <c r="C7" s="249">
         <v>46108</v>
       </c>
       <c r="D7" s="143">
         <v>1</v>
       </c>
-      <c r="E7" s="446" t="s">
-        <v>152</v>
+      <c r="E7" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F7" s="144"/>
       <c r="G7" s="145" t="s">
@@ -6581,16 +6555,16 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
-      <c r="K7" s="332" t="s">
+      <c r="K7" s="330" t="s">
         <v>97</v>
       </c>
-      <c r="L7" s="332"/>
-      <c r="M7" s="332"/>
-      <c r="N7" s="332"/>
-      <c r="O7" s="332"/>
-      <c r="P7" s="332"/>
-      <c r="Q7" s="332"/>
-      <c r="R7" s="332"/>
+      <c r="L7" s="330"/>
+      <c r="M7" s="330"/>
+      <c r="N7" s="330"/>
+      <c r="O7" s="330"/>
+      <c r="P7" s="330"/>
+      <c r="Q7" s="330"/>
+      <c r="R7" s="330"/>
       <c r="S7" s="150"/>
       <c r="T7" s="150"/>
       <c r="U7" s="2"/>
@@ -6685,7 +6659,7 @@
       <c r="DF7" s="2"/>
     </row>
     <row r="8" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A8" s="287" t="s">
+      <c r="A8" s="281" t="s">
         <v>47</v>
       </c>
       <c r="B8" s="157" t="s">
@@ -6697,8 +6671,8 @@
       <c r="D8" s="159">
         <v>1</v>
       </c>
-      <c r="E8" s="446" t="s">
-        <v>152</v>
+      <c r="E8" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F8" s="160"/>
       <c r="G8" s="161" t="s">
@@ -6712,13 +6686,13 @@
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="369" t="s">
+      <c r="P8" s="425" t="s">
         <v>49</v>
       </c>
-      <c r="Q8" s="370" t="s">
+      <c r="Q8" s="426" t="s">
         <v>49</v>
       </c>
-      <c r="R8" s="371" t="s">
+      <c r="R8" s="427" t="s">
         <v>49</v>
       </c>
       <c r="S8" s="2"/>
@@ -6815,7 +6789,7 @@
       <c r="DF8" s="2"/>
     </row>
     <row r="9" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A9" s="287" t="s">
+      <c r="A9" s="281" t="s">
         <v>50</v>
       </c>
       <c r="B9" s="162" t="s">
@@ -6827,8 +6801,8 @@
       <c r="D9" s="164">
         <v>1</v>
       </c>
-      <c r="E9" s="446" t="s">
-        <v>152</v>
+      <c r="E9" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F9" s="165"/>
       <c r="G9" s="166" t="s">
@@ -6842,13 +6816,13 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="372" t="s">
+      <c r="P9" s="428" t="s">
         <v>51</v>
       </c>
-      <c r="Q9" s="373" t="s">
+      <c r="Q9" s="429" t="s">
         <v>51</v>
       </c>
-      <c r="R9" s="374" t="s">
+      <c r="R9" s="430" t="s">
         <v>51</v>
       </c>
       <c r="S9" s="2"/>
@@ -6945,7 +6919,7 @@
       <c r="DF9" s="2"/>
     </row>
     <row r="10" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A10" s="287" t="s">
+      <c r="A10" s="281" t="s">
         <v>52</v>
       </c>
       <c r="B10" s="167" t="s">
@@ -6957,8 +6931,8 @@
       <c r="D10" s="169">
         <v>1</v>
       </c>
-      <c r="E10" s="446" t="s">
-        <v>152</v>
+      <c r="E10" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F10" s="170"/>
       <c r="G10" s="171" t="s">
@@ -6972,13 +6946,13 @@
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="375" t="s">
+      <c r="P10" s="373" t="s">
         <v>53</v>
       </c>
-      <c r="Q10" s="376" t="s">
+      <c r="Q10" s="374" t="s">
         <v>53</v>
       </c>
-      <c r="R10" s="377" t="s">
+      <c r="R10" s="375" t="s">
         <v>53</v>
       </c>
       <c r="S10" s="2"/>
@@ -7075,7 +7049,7 @@
       <c r="DF10" s="2"/>
     </row>
     <row r="11" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A11" s="287" t="s">
+      <c r="A11" s="281" t="s">
         <v>55</v>
       </c>
       <c r="B11" s="172" t="s">
@@ -7087,8 +7061,8 @@
       <c r="D11" s="173">
         <v>1</v>
       </c>
-      <c r="E11" s="446" t="s">
-        <v>152</v>
+      <c r="E11" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F11" s="174"/>
       <c r="G11" s="175" t="s">
@@ -7102,13 +7076,13 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="397" t="s">
+      <c r="P11" s="341" t="s">
         <v>56</v>
       </c>
-      <c r="Q11" s="398" t="s">
+      <c r="Q11" s="342" t="s">
         <v>56</v>
       </c>
-      <c r="R11" s="399" t="s">
+      <c r="R11" s="343" t="s">
         <v>56</v>
       </c>
       <c r="S11" s="2"/>
@@ -7205,7 +7179,7 @@
       <c r="DF11" s="2"/>
     </row>
     <row r="12" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A12" s="287" t="s">
+      <c r="A12" s="281" t="s">
         <v>57</v>
       </c>
       <c r="B12" s="176" t="s">
@@ -7217,8 +7191,8 @@
       <c r="D12" s="178">
         <v>1</v>
       </c>
-      <c r="E12" s="446" t="s">
-        <v>152</v>
+      <c r="E12" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F12" s="179"/>
       <c r="G12" s="180" t="s">
@@ -7232,13 +7206,13 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="400" t="s">
+      <c r="P12" s="344" t="s">
         <v>58</v>
       </c>
-      <c r="Q12" s="401" t="s">
+      <c r="Q12" s="345" t="s">
         <v>58</v>
       </c>
-      <c r="R12" s="402" t="s">
+      <c r="R12" s="346" t="s">
         <v>58</v>
       </c>
       <c r="S12" s="2"/>
@@ -7335,7 +7309,7 @@
       <c r="DF12" s="2"/>
     </row>
     <row r="13" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A13" s="287" t="s">
+      <c r="A13" s="281" t="s">
         <v>59</v>
       </c>
       <c r="B13" s="181" t="s">
@@ -7347,8 +7321,8 @@
       <c r="D13" s="183">
         <v>1</v>
       </c>
-      <c r="E13" s="446" t="s">
-        <v>152</v>
+      <c r="E13" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F13" s="184"/>
       <c r="G13" s="185" t="s">
@@ -7362,13 +7336,13 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="403" t="s">
+      <c r="P13" s="347" t="s">
         <v>60</v>
       </c>
-      <c r="Q13" s="404" t="s">
+      <c r="Q13" s="348" t="s">
         <v>60</v>
       </c>
-      <c r="R13" s="405" t="s">
+      <c r="R13" s="349" t="s">
         <v>60</v>
       </c>
       <c r="S13" s="2"/>
@@ -7465,7 +7439,7 @@
       <c r="DF13" s="2"/>
     </row>
     <row r="14" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A14" s="287" t="s">
+      <c r="A14" s="281" t="s">
         <v>61</v>
       </c>
       <c r="B14" s="186" t="s">
@@ -7477,8 +7451,8 @@
       <c r="D14" s="188">
         <v>1</v>
       </c>
-      <c r="E14" s="446" t="s">
-        <v>152</v>
+      <c r="E14" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="189" t="s">
@@ -7497,13 +7471,13 @@
       <c r="R14" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="S14" s="287"/>
-      <c r="T14" s="287"/>
-      <c r="U14" s="287"/>
-      <c r="V14" s="287"/>
-      <c r="W14" s="287"/>
-      <c r="X14" s="287"/>
-      <c r="Y14" s="287"/>
+      <c r="S14" s="281"/>
+      <c r="T14" s="281"/>
+      <c r="U14" s="281"/>
+      <c r="V14" s="281"/>
+      <c r="W14" s="281"/>
+      <c r="X14" s="281"/>
+      <c r="Y14" s="281"/>
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
       <c r="AB14" s="2"/>
@@ -7591,7 +7565,7 @@
       <c r="DF14" s="2"/>
     </row>
     <row r="15" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A15" s="287" t="s">
+      <c r="A15" s="281" t="s">
         <v>118</v>
       </c>
       <c r="B15" s="192" t="s">
@@ -7603,8 +7577,8 @@
       <c r="D15" s="194">
         <v>1</v>
       </c>
-      <c r="E15" s="446" t="s">
-        <v>151</v>
+      <c r="E15" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F15" s="195"/>
       <c r="G15" s="196" t="s">
@@ -7620,28 +7594,28 @@
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
-      <c r="R15" s="343" t="s">
+      <c r="R15" s="333" t="s">
         <v>92</v>
       </c>
-      <c r="S15" s="406" t="s">
+      <c r="S15" s="350" t="s">
         <v>63</v>
       </c>
-      <c r="T15" s="407" t="s">
+      <c r="T15" s="351" t="s">
         <v>63</v>
       </c>
-      <c r="U15" s="408" t="s">
+      <c r="U15" s="352" t="s">
         <v>63</v>
       </c>
-      <c r="V15" s="409" t="s">
+      <c r="V15" s="353" t="s">
         <v>63</v>
       </c>
-      <c r="W15" s="410" t="s">
+      <c r="W15" s="354" t="s">
         <v>63</v>
       </c>
-      <c r="X15" s="411" t="s">
+      <c r="X15" s="355" t="s">
         <v>63</v>
       </c>
-      <c r="Y15" s="412" t="s">
+      <c r="Y15" s="356" t="s">
         <v>63</v>
       </c>
       <c r="Z15" s="2"/>
@@ -7731,7 +7705,7 @@
       <c r="DF15" s="2"/>
     </row>
     <row r="16" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A16" s="287" t="s">
+      <c r="A16" s="281" t="s">
         <v>64</v>
       </c>
       <c r="B16" s="197" t="s">
@@ -7743,8 +7717,8 @@
       <c r="D16" s="198">
         <v>1</v>
       </c>
-      <c r="E16" s="446" t="s">
-        <v>151</v>
+      <c r="E16" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F16" s="199"/>
       <c r="G16" s="200" t="s">
@@ -7760,28 +7734,28 @@
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
-      <c r="R16" s="343" t="s">
+      <c r="R16" s="333" t="s">
         <v>92</v>
       </c>
-      <c r="S16" s="413" t="s">
+      <c r="S16" s="357" t="s">
         <v>65</v>
       </c>
-      <c r="T16" s="414" t="s">
+      <c r="T16" s="358" t="s">
         <v>65</v>
       </c>
-      <c r="U16" s="415" t="s">
+      <c r="U16" s="359" t="s">
         <v>65</v>
       </c>
-      <c r="V16" s="416" t="s">
+      <c r="V16" s="360" t="s">
         <v>65</v>
       </c>
-      <c r="W16" s="417" t="s">
+      <c r="W16" s="361" t="s">
         <v>65</v>
       </c>
-      <c r="X16" s="418" t="s">
+      <c r="X16" s="362" t="s">
         <v>65</v>
       </c>
-      <c r="Y16" s="419" t="s">
+      <c r="Y16" s="363" t="s">
         <v>65</v>
       </c>
       <c r="Z16" s="2"/>
@@ -7871,7 +7845,7 @@
       <c r="DF16" s="2"/>
     </row>
     <row r="17" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A17" s="287" t="s">
+      <c r="A17" s="281" t="s">
         <v>66</v>
       </c>
       <c r="B17" s="201" t="s">
@@ -7883,8 +7857,8 @@
       <c r="D17" s="202">
         <v>1</v>
       </c>
-      <c r="E17" s="446" t="s">
-        <v>151</v>
+      <c r="E17" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F17" s="203"/>
       <c r="G17" s="204" t="s">
@@ -7900,28 +7874,28 @@
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
-      <c r="R17" s="343" t="s">
+      <c r="R17" s="333" t="s">
         <v>67</v>
       </c>
-      <c r="S17" s="383" t="s">
+      <c r="S17" s="382" t="s">
         <v>67</v>
       </c>
-      <c r="T17" s="384" t="s">
+      <c r="T17" s="383" t="s">
         <v>67</v>
       </c>
-      <c r="U17" s="385" t="s">
+      <c r="U17" s="384" t="s">
         <v>67</v>
       </c>
-      <c r="V17" s="386" t="s">
+      <c r="V17" s="385" t="s">
         <v>67</v>
       </c>
-      <c r="W17" s="387" t="s">
+      <c r="W17" s="386" t="s">
         <v>67</v>
       </c>
-      <c r="X17" s="388" t="s">
+      <c r="X17" s="387" t="s">
         <v>67</v>
       </c>
-      <c r="Y17" s="389" t="s">
+      <c r="Y17" s="388" t="s">
         <v>67</v>
       </c>
       <c r="Z17" s="2"/>
@@ -8011,7 +7985,7 @@
       <c r="DF17" s="2"/>
     </row>
     <row r="18" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A18" s="287" t="s">
+      <c r="A18" s="281" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="205" t="s">
@@ -8023,8 +7997,8 @@
       <c r="D18" s="207">
         <v>1</v>
       </c>
-      <c r="E18" s="446" t="s">
-        <v>151</v>
+      <c r="E18" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F18" s="208"/>
       <c r="G18" s="209" t="s">
@@ -8040,28 +8014,28 @@
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
-      <c r="R18" s="335" t="s">
+      <c r="R18" s="392" t="s">
         <v>69</v>
       </c>
-      <c r="S18" s="336" t="s">
+      <c r="S18" s="393" t="s">
         <v>69</v>
       </c>
-      <c r="T18" s="337" t="s">
+      <c r="T18" s="394" t="s">
         <v>69</v>
       </c>
-      <c r="U18" s="338" t="s">
+      <c r="U18" s="395" t="s">
         <v>69</v>
       </c>
-      <c r="V18" s="339" t="s">
+      <c r="V18" s="396" t="s">
         <v>69</v>
       </c>
-      <c r="W18" s="340" t="s">
+      <c r="W18" s="397" t="s">
         <v>69</v>
       </c>
-      <c r="X18" s="341" t="s">
+      <c r="X18" s="398" t="s">
         <v>69</v>
       </c>
-      <c r="Y18" s="342" t="s">
+      <c r="Y18" s="399" t="s">
         <v>69</v>
       </c>
       <c r="Z18" s="2"/>
@@ -8151,20 +8125,20 @@
       <c r="DF18" s="2"/>
     </row>
     <row r="19" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A19" s="287" t="s">
+      <c r="A19" s="281" t="s">
         <v>46</v>
       </c>
       <c r="B19" s="146">
         <v>46080</v>
       </c>
-      <c r="C19" s="264">
+      <c r="C19" s="262">
         <v>46087</v>
       </c>
       <c r="D19" s="147">
         <v>1</v>
       </c>
-      <c r="E19" s="446" t="s">
-        <v>151</v>
+      <c r="E19" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F19" s="148"/>
       <c r="G19" s="149" t="s">
@@ -8182,13 +8156,13 @@
       <c r="R19" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="S19" s="261"/>
-      <c r="T19" s="261"/>
-      <c r="U19" s="261"/>
-      <c r="V19" s="261"/>
-      <c r="W19" s="261"/>
-      <c r="X19" s="262"/>
-      <c r="Y19" s="263"/>
+      <c r="S19" s="259"/>
+      <c r="T19" s="259"/>
+      <c r="U19" s="259"/>
+      <c r="V19" s="259"/>
+      <c r="W19" s="259"/>
+      <c r="X19" s="260"/>
+      <c r="Y19" s="261"/>
       <c r="Z19" s="156"/>
       <c r="AA19" s="2"/>
       <c r="AB19" s="2"/>
@@ -8276,7 +8250,7 @@
       <c r="DF19" s="2"/>
     </row>
     <row r="20" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A20" s="287" t="s">
+      <c r="A20" s="281" t="s">
         <v>94</v>
       </c>
       <c r="B20" s="205" t="s">
@@ -8288,8 +8262,8 @@
       <c r="D20" s="207">
         <v>1</v>
       </c>
-      <c r="E20" s="446" t="s">
-        <v>151</v>
+      <c r="E20" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F20" s="208"/>
       <c r="G20" s="209"/>
@@ -8303,16 +8277,16 @@
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
-      <c r="R20" s="351" t="s">
+      <c r="R20" s="407" t="s">
         <v>95</v>
       </c>
-      <c r="S20" s="352"/>
-      <c r="T20" s="352"/>
-      <c r="U20" s="352"/>
-      <c r="V20" s="352"/>
-      <c r="W20" s="352"/>
-      <c r="X20" s="352"/>
-      <c r="Y20" s="352"/>
+      <c r="S20" s="408"/>
+      <c r="T20" s="408"/>
+      <c r="U20" s="408"/>
+      <c r="V20" s="408"/>
+      <c r="W20" s="408"/>
+      <c r="X20" s="408"/>
+      <c r="Y20" s="408"/>
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
       <c r="AB20" s="2"/>
@@ -8400,7 +8374,7 @@
       <c r="DF20" s="2"/>
     </row>
     <row r="21" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A21" s="287" t="s">
+      <c r="A21" s="281" t="s">
         <v>70</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -8412,8 +8386,8 @@
       <c r="D21" s="5">
         <v>1</v>
       </c>
-      <c r="E21" s="446" t="s">
-        <v>151</v>
+      <c r="E21" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="210" t="s">
@@ -8429,28 +8403,28 @@
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
-      <c r="R21" s="343" t="s">
+      <c r="R21" s="333" t="s">
         <v>71</v>
       </c>
-      <c r="S21" s="344" t="s">
+      <c r="S21" s="400" t="s">
         <v>71</v>
       </c>
-      <c r="T21" s="345" t="s">
+      <c r="T21" s="401" t="s">
         <v>71</v>
       </c>
-      <c r="U21" s="346" t="s">
+      <c r="U21" s="402" t="s">
         <v>71</v>
       </c>
-      <c r="V21" s="347" t="s">
+      <c r="V21" s="403" t="s">
         <v>71</v>
       </c>
-      <c r="W21" s="348" t="s">
+      <c r="W21" s="404" t="s">
         <v>71</v>
       </c>
-      <c r="X21" s="349" t="s">
+      <c r="X21" s="405" t="s">
         <v>71</v>
       </c>
-      <c r="Y21" s="350" t="s">
+      <c r="Y21" s="406" t="s">
         <v>71</v>
       </c>
       <c r="Z21" s="2"/>
@@ -8540,10 +8514,10 @@
       <c r="DF21" s="2"/>
     </row>
     <row r="22" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A22" s="287" t="s">
+      <c r="A22" s="281" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="255">
+      <c r="B22" s="253">
         <v>46080</v>
       </c>
       <c r="C22" s="138" t="s">
@@ -8552,8 +8526,8 @@
       <c r="D22" s="139">
         <v>1</v>
       </c>
-      <c r="E22" s="446" t="s">
-        <v>151</v>
+      <c r="E22" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F22" s="140"/>
       <c r="G22" s="141" t="s">
@@ -8562,21 +8536,21 @@
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="150"/>
-      <c r="K22" s="243"/>
-      <c r="L22" s="244"/>
-      <c r="M22" s="245"/>
-      <c r="N22" s="246"/>
-      <c r="O22" s="247"/>
-      <c r="P22" s="248"/>
-      <c r="Q22" s="249"/>
-      <c r="R22" s="250"/>
-      <c r="S22" s="332" t="s">
+      <c r="K22" s="241"/>
+      <c r="L22" s="242"/>
+      <c r="M22" s="243"/>
+      <c r="N22" s="244"/>
+      <c r="O22" s="245"/>
+      <c r="P22" s="246"/>
+      <c r="Q22" s="247"/>
+      <c r="R22" s="248"/>
+      <c r="S22" s="330" t="s">
         <v>104</v>
       </c>
-      <c r="T22" s="366"/>
-      <c r="U22" s="366"/>
-      <c r="V22" s="366"/>
-      <c r="W22" s="366"/>
+      <c r="T22" s="422"/>
+      <c r="U22" s="422"/>
+      <c r="V22" s="422"/>
+      <c r="W22" s="422"/>
       <c r="X22" s="2"/>
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
@@ -8666,20 +8640,20 @@
       <c r="DF22" s="2"/>
     </row>
     <row r="23" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A23" s="287" t="s">
+      <c r="A23" s="281" t="s">
         <v>72</v>
       </c>
       <c r="B23" s="213" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="254">
+      <c r="C23" s="252">
         <v>46094</v>
       </c>
-      <c r="D23" s="253">
+      <c r="D23" s="251">
         <v>1</v>
       </c>
-      <c r="E23" s="446" t="s">
-        <v>152</v>
+      <c r="E23" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="212" t="s">
@@ -8698,40 +8672,40 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
-      <c r="U23" s="353" t="s">
+      <c r="U23" s="409" t="s">
         <v>74</v>
       </c>
-      <c r="V23" s="354" t="s">
+      <c r="V23" s="410" t="s">
         <v>74</v>
       </c>
-      <c r="W23" s="355" t="s">
+      <c r="W23" s="411" t="s">
         <v>74</v>
       </c>
-      <c r="X23" s="356" t="s">
+      <c r="X23" s="412" t="s">
         <v>74</v>
       </c>
-      <c r="Y23" s="357" t="s">
+      <c r="Y23" s="413" t="s">
         <v>74</v>
       </c>
-      <c r="Z23" s="358" t="s">
+      <c r="Z23" s="414" t="s">
         <v>74</v>
       </c>
-      <c r="AA23" s="359" t="s">
+      <c r="AA23" s="415" t="s">
         <v>74</v>
       </c>
-      <c r="AB23" s="360" t="s">
+      <c r="AB23" s="416" t="s">
         <v>74</v>
       </c>
-      <c r="AC23" s="361" t="s">
+      <c r="AC23" s="417" t="s">
         <v>74</v>
       </c>
-      <c r="AD23" s="362" t="s">
+      <c r="AD23" s="418" t="s">
         <v>74</v>
       </c>
-      <c r="AE23" s="363" t="s">
+      <c r="AE23" s="419" t="s">
         <v>74</v>
       </c>
-      <c r="AF23" s="364" t="s">
+      <c r="AF23" s="420" t="s">
         <v>74</v>
       </c>
       <c r="AG23" s="2"/>
@@ -8814,7 +8788,7 @@
       <c r="DF23" s="2"/>
     </row>
     <row r="24" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A24" s="287" t="s">
+      <c r="A24" s="281" t="s">
         <v>102</v>
       </c>
       <c r="B24" s="213" t="s">
@@ -8823,11 +8797,11 @@
       <c r="C24" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="253">
+      <c r="D24" s="251">
         <v>1</v>
       </c>
-      <c r="E24" s="446" t="s">
-        <v>152</v>
+      <c r="E24" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="212"/>
@@ -8845,19 +8819,19 @@
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
       <c r="U24" s="150"/>
-      <c r="V24" s="256"/>
-      <c r="W24" s="257"/>
-      <c r="X24" s="258"/>
-      <c r="Y24" s="332" t="s">
+      <c r="V24" s="254"/>
+      <c r="W24" s="255"/>
+      <c r="X24" s="256"/>
+      <c r="Y24" s="330" t="s">
         <v>103</v>
       </c>
-      <c r="Z24" s="333"/>
-      <c r="AA24" s="333"/>
-      <c r="AB24" s="333"/>
-      <c r="AC24" s="333"/>
-      <c r="AD24" s="333"/>
-      <c r="AE24" s="333"/>
-      <c r="AF24" s="333"/>
+      <c r="Z24" s="391"/>
+      <c r="AA24" s="391"/>
+      <c r="AB24" s="391"/>
+      <c r="AC24" s="391"/>
+      <c r="AD24" s="391"/>
+      <c r="AE24" s="391"/>
+      <c r="AF24" s="391"/>
       <c r="AG24" s="2"/>
       <c r="AH24" s="2"/>
       <c r="AI24" s="2"/>
@@ -8938,7 +8912,7 @@
       <c r="DF24" s="2"/>
     </row>
     <row r="25" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A25" s="287" t="s">
+      <c r="A25" s="281" t="s">
         <v>101</v>
       </c>
       <c r="B25" s="213" t="s">
@@ -8947,11 +8921,11 @@
       <c r="C25" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="D25" s="253">
+      <c r="D25" s="251">
         <v>1</v>
       </c>
-      <c r="E25" s="446" t="s">
-        <v>151</v>
+      <c r="E25" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F25" s="211"/>
       <c r="G25" s="212"/>
@@ -8968,20 +8942,20 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
-      <c r="U25" s="260"/>
-      <c r="V25" s="256"/>
-      <c r="W25" s="257"/>
-      <c r="X25" s="258"/>
-      <c r="Y25" s="332" t="s">
+      <c r="U25" s="258"/>
+      <c r="V25" s="254"/>
+      <c r="W25" s="255"/>
+      <c r="X25" s="256"/>
+      <c r="Y25" s="330" t="s">
         <v>105</v>
       </c>
-      <c r="Z25" s="333"/>
-      <c r="AA25" s="333"/>
-      <c r="AB25" s="333"/>
-      <c r="AC25" s="333"/>
-      <c r="AD25" s="333"/>
-      <c r="AE25" s="333"/>
-      <c r="AF25" s="333"/>
+      <c r="Z25" s="391"/>
+      <c r="AA25" s="391"/>
+      <c r="AB25" s="391"/>
+      <c r="AC25" s="391"/>
+      <c r="AD25" s="391"/>
+      <c r="AE25" s="391"/>
+      <c r="AF25" s="391"/>
       <c r="AG25" s="2"/>
       <c r="AH25" s="2"/>
       <c r="AI25" s="2"/>
@@ -9062,7 +9036,7 @@
       <c r="DF25" s="2"/>
     </row>
     <row r="26" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A26" s="287" t="s">
+      <c r="A26" s="281" t="s">
         <v>99</v>
       </c>
       <c r="B26" s="213" t="s">
@@ -9071,11 +9045,11 @@
       <c r="C26" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="D26" s="253">
+      <c r="D26" s="251">
         <v>1</v>
       </c>
-      <c r="E26" s="446" t="s">
-        <v>152</v>
+      <c r="E26" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F26" s="215"/>
       <c r="G26" s="216" t="s">
@@ -9098,16 +9072,16 @@
       <c r="V26" s="2"/>
       <c r="W26" s="2"/>
       <c r="X26" s="2"/>
-      <c r="Y26" s="332" t="s">
+      <c r="Y26" s="330" t="s">
         <v>108</v>
       </c>
-      <c r="Z26" s="333"/>
-      <c r="AA26" s="333"/>
-      <c r="AB26" s="333"/>
-      <c r="AC26" s="333"/>
-      <c r="AD26" s="333"/>
-      <c r="AE26" s="333"/>
-      <c r="AF26" s="333"/>
+      <c r="Z26" s="391"/>
+      <c r="AA26" s="391"/>
+      <c r="AB26" s="391"/>
+      <c r="AC26" s="391"/>
+      <c r="AD26" s="391"/>
+      <c r="AE26" s="391"/>
+      <c r="AF26" s="391"/>
       <c r="AG26" s="2"/>
       <c r="AH26" s="2"/>
       <c r="AI26" s="2"/>
@@ -9188,7 +9162,7 @@
       <c r="DF26" s="2"/>
     </row>
     <row r="27" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A27" s="287" t="s">
+      <c r="A27" s="281" t="s">
         <v>100</v>
       </c>
       <c r="B27" s="213" t="s">
@@ -9197,11 +9171,11 @@
       <c r="C27" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="D27" s="253">
+      <c r="D27" s="251">
         <v>1</v>
       </c>
-      <c r="E27" s="446" t="s">
-        <v>152</v>
+      <c r="E27" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F27" s="215"/>
       <c r="G27" s="216" t="s">
@@ -9224,17 +9198,17 @@
       <c r="V27" s="2"/>
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
-      <c r="AF27" s="334" t="s">
+      <c r="AF27" s="389" t="s">
         <v>109</v>
       </c>
-      <c r="AG27" s="334"/>
-      <c r="AH27" s="334"/>
-      <c r="AI27" s="334"/>
-      <c r="AJ27" s="334"/>
-      <c r="AK27" s="334"/>
-      <c r="AL27" s="334"/>
-      <c r="AM27" s="334"/>
-      <c r="AN27" s="265"/>
+      <c r="AG27" s="389"/>
+      <c r="AH27" s="389"/>
+      <c r="AI27" s="389"/>
+      <c r="AJ27" s="389"/>
+      <c r="AK27" s="389"/>
+      <c r="AL27" s="389"/>
+      <c r="AM27" s="389"/>
+      <c r="AN27" s="263"/>
       <c r="AO27" s="2"/>
       <c r="AP27" s="2"/>
       <c r="AQ27" s="2"/>
@@ -9307,20 +9281,20 @@
       <c r="DF27" s="2"/>
     </row>
     <row r="28" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A28" s="287" t="s">
+      <c r="A28" s="281" t="s">
         <v>106</v>
       </c>
       <c r="B28" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="259">
+      <c r="C28" s="257">
         <v>46101</v>
       </c>
-      <c r="D28" s="253">
+      <c r="D28" s="251">
         <v>1</v>
       </c>
-      <c r="E28" s="446" t="s">
-        <v>152</v>
+      <c r="E28" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F28" s="215"/>
       <c r="G28" s="216"/>
@@ -9342,22 +9316,22 @@
       <c r="W28" s="2"/>
       <c r="X28" s="2"/>
       <c r="Y28" s="150"/>
-      <c r="Z28" s="265"/>
-      <c r="AA28" s="265"/>
-      <c r="AB28" s="265"/>
-      <c r="AC28" s="265"/>
-      <c r="AD28" s="265"/>
-      <c r="AE28" s="265"/>
-      <c r="AF28" s="334" t="s">
+      <c r="Z28" s="263"/>
+      <c r="AA28" s="263"/>
+      <c r="AB28" s="263"/>
+      <c r="AC28" s="263"/>
+      <c r="AD28" s="263"/>
+      <c r="AE28" s="263"/>
+      <c r="AF28" s="389" t="s">
         <v>110</v>
       </c>
-      <c r="AG28" s="334"/>
-      <c r="AH28" s="334"/>
-      <c r="AI28" s="334"/>
-      <c r="AJ28" s="334"/>
-      <c r="AK28" s="334"/>
-      <c r="AL28" s="334"/>
-      <c r="AM28" s="334"/>
+      <c r="AG28" s="389"/>
+      <c r="AH28" s="389"/>
+      <c r="AI28" s="389"/>
+      <c r="AJ28" s="389"/>
+      <c r="AK28" s="389"/>
+      <c r="AL28" s="389"/>
+      <c r="AM28" s="389"/>
       <c r="AN28" s="2"/>
       <c r="AO28" s="2"/>
       <c r="AP28" s="2"/>
@@ -9431,20 +9405,20 @@
       <c r="DF28" s="2"/>
     </row>
     <row r="29" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A29" s="287" t="s">
+      <c r="A29" s="281" t="s">
         <v>107</v>
       </c>
       <c r="B29" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="259">
+      <c r="C29" s="257">
         <v>46101</v>
       </c>
-      <c r="D29" s="253">
+      <c r="D29" s="251">
         <v>1</v>
       </c>
-      <c r="E29" s="446" t="s">
-        <v>152</v>
+      <c r="E29" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F29" s="215"/>
       <c r="G29" s="216"/>
@@ -9466,22 +9440,22 @@
       <c r="W29" s="2"/>
       <c r="X29" s="2"/>
       <c r="Y29" s="150"/>
-      <c r="Z29" s="266"/>
-      <c r="AA29" s="267"/>
-      <c r="AB29" s="268"/>
-      <c r="AC29" s="269"/>
-      <c r="AD29" s="270"/>
-      <c r="AE29" s="271"/>
-      <c r="AF29" s="334" t="s">
+      <c r="Z29" s="264"/>
+      <c r="AA29" s="265"/>
+      <c r="AB29" s="266"/>
+      <c r="AC29" s="267"/>
+      <c r="AD29" s="268"/>
+      <c r="AE29" s="269"/>
+      <c r="AF29" s="389" t="s">
         <v>111</v>
       </c>
-      <c r="AG29" s="334"/>
-      <c r="AH29" s="334"/>
-      <c r="AI29" s="334"/>
-      <c r="AJ29" s="334"/>
-      <c r="AK29" s="334"/>
-      <c r="AL29" s="334"/>
-      <c r="AM29" s="334"/>
+      <c r="AG29" s="389"/>
+      <c r="AH29" s="389"/>
+      <c r="AI29" s="389"/>
+      <c r="AJ29" s="389"/>
+      <c r="AK29" s="389"/>
+      <c r="AL29" s="389"/>
+      <c r="AM29" s="389"/>
       <c r="AN29" s="2"/>
       <c r="AO29" s="2"/>
       <c r="AP29" s="2"/>
@@ -9555,20 +9529,20 @@
       <c r="DF29" s="2"/>
     </row>
     <row r="30" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A30" s="287" t="s">
+      <c r="A30" s="281" t="s">
         <v>112</v>
       </c>
       <c r="B30" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="C30" s="259">
+      <c r="C30" s="257">
         <v>46101</v>
       </c>
-      <c r="D30" s="253">
+      <c r="D30" s="251">
         <v>1</v>
       </c>
-      <c r="E30" s="446" t="s">
-        <v>151</v>
+      <c r="E30" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F30" s="215"/>
       <c r="G30" s="216"/>
@@ -9590,22 +9564,22 @@
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
       <c r="Y30" s="150"/>
-      <c r="Z30" s="266"/>
-      <c r="AA30" s="267"/>
-      <c r="AB30" s="268"/>
-      <c r="AC30" s="269"/>
-      <c r="AD30" s="270"/>
-      <c r="AE30" s="271"/>
-      <c r="AF30" s="334" t="s">
+      <c r="Z30" s="264"/>
+      <c r="AA30" s="265"/>
+      <c r="AB30" s="266"/>
+      <c r="AC30" s="267"/>
+      <c r="AD30" s="268"/>
+      <c r="AE30" s="269"/>
+      <c r="AF30" s="389" t="s">
         <v>114</v>
       </c>
-      <c r="AG30" s="334"/>
-      <c r="AH30" s="334"/>
-      <c r="AI30" s="334"/>
-      <c r="AJ30" s="334"/>
-      <c r="AK30" s="334"/>
-      <c r="AL30" s="334"/>
-      <c r="AM30" s="334"/>
+      <c r="AG30" s="389"/>
+      <c r="AH30" s="389"/>
+      <c r="AI30" s="389"/>
+      <c r="AJ30" s="389"/>
+      <c r="AK30" s="389"/>
+      <c r="AL30" s="389"/>
+      <c r="AM30" s="389"/>
       <c r="AN30" s="2"/>
       <c r="AO30" s="2"/>
       <c r="AP30" s="2"/>
@@ -9679,20 +9653,20 @@
       <c r="DF30" s="2"/>
     </row>
     <row r="31" spans="1:110" ht="17.5" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A31" s="287" t="s">
+      <c r="A31" s="281" t="s">
         <v>113</v>
       </c>
       <c r="B31" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="C31" s="259">
+      <c r="C31" s="257">
         <v>46101</v>
       </c>
-      <c r="D31" s="253">
+      <c r="D31" s="251">
         <v>1</v>
       </c>
-      <c r="E31" s="446" t="s">
-        <v>151</v>
+      <c r="E31" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F31" s="217"/>
       <c r="G31" s="218" t="s">
@@ -9720,18 +9694,18 @@
       <c r="AA31" s="2"/>
       <c r="AB31" s="2"/>
       <c r="AC31" s="2"/>
-      <c r="AD31" s="274"/>
-      <c r="AE31" s="275"/>
-      <c r="AF31" s="334" t="s">
+      <c r="AD31" s="272"/>
+      <c r="AE31" s="273"/>
+      <c r="AF31" s="389" t="s">
         <v>115</v>
       </c>
-      <c r="AG31" s="334"/>
-      <c r="AH31" s="334"/>
-      <c r="AI31" s="334"/>
-      <c r="AJ31" s="334"/>
-      <c r="AK31" s="334"/>
-      <c r="AL31" s="334"/>
-      <c r="AM31" s="334"/>
+      <c r="AG31" s="389"/>
+      <c r="AH31" s="389"/>
+      <c r="AI31" s="389"/>
+      <c r="AJ31" s="389"/>
+      <c r="AK31" s="389"/>
+      <c r="AL31" s="389"/>
+      <c r="AM31" s="389"/>
       <c r="AN31" s="2"/>
       <c r="AO31" s="2"/>
       <c r="AP31" s="2"/>
@@ -9805,20 +9779,20 @@
       <c r="DF31" s="2"/>
     </row>
     <row r="32" spans="1:110" ht="17.5" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A32" s="287" t="s">
+      <c r="A32" s="281" t="s">
         <v>116</v>
       </c>
       <c r="B32" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="259">
+      <c r="C32" s="257">
         <v>46101</v>
       </c>
-      <c r="D32" s="253">
+      <c r="D32" s="251">
         <v>1</v>
       </c>
-      <c r="E32" s="446" t="s">
-        <v>151</v>
+      <c r="E32" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F32" s="217"/>
       <c r="G32" s="218" t="s">
@@ -9846,18 +9820,18 @@
       <c r="AA32" s="2"/>
       <c r="AB32" s="2"/>
       <c r="AC32" s="2"/>
-      <c r="AD32" s="274"/>
-      <c r="AE32" s="275"/>
-      <c r="AF32" s="334" t="s">
+      <c r="AD32" s="272"/>
+      <c r="AE32" s="273"/>
+      <c r="AF32" s="389" t="s">
         <v>117</v>
       </c>
-      <c r="AG32" s="334"/>
-      <c r="AH32" s="334"/>
-      <c r="AI32" s="334"/>
-      <c r="AJ32" s="334"/>
-      <c r="AK32" s="334"/>
-      <c r="AL32" s="334"/>
-      <c r="AM32" s="334"/>
+      <c r="AG32" s="389"/>
+      <c r="AH32" s="389"/>
+      <c r="AI32" s="389"/>
+      <c r="AJ32" s="389"/>
+      <c r="AK32" s="389"/>
+      <c r="AL32" s="389"/>
+      <c r="AM32" s="389"/>
       <c r="AN32" s="2"/>
       <c r="AO32" s="2"/>
       <c r="AP32" s="2"/>
@@ -9931,20 +9905,20 @@
       <c r="DF32" s="2"/>
     </row>
     <row r="33" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A33" s="287" t="s">
+      <c r="A33" s="281" t="s">
         <v>76</v>
       </c>
-      <c r="B33" s="272">
+      <c r="B33" s="270">
         <v>46101</v>
       </c>
-      <c r="C33" s="273">
+      <c r="C33" s="271">
         <v>46108</v>
       </c>
-      <c r="D33" s="276">
+      <c r="D33" s="274">
         <v>1</v>
       </c>
-      <c r="E33" s="446" t="s">
-        <v>153</v>
+      <c r="E33" s="326" t="s">
+        <v>151</v>
       </c>
       <c r="F33" s="219"/>
       <c r="G33" s="220" t="s">
@@ -9973,38 +9947,38 @@
       <c r="AB33" s="2"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="2"/>
-      <c r="AE33" s="420"/>
-      <c r="AF33" s="421" t="s">
+      <c r="AE33" s="364"/>
+      <c r="AF33" s="365" t="s">
         <v>77</v>
       </c>
-      <c r="AG33" s="422" t="s">
+      <c r="AG33" s="366" t="s">
         <v>77</v>
       </c>
-      <c r="AH33" s="423" t="s">
+      <c r="AH33" s="367" t="s">
         <v>77</v>
       </c>
-      <c r="AI33" s="424" t="s">
+      <c r="AI33" s="368" t="s">
         <v>77</v>
       </c>
-      <c r="AJ33" s="425" t="s">
+      <c r="AJ33" s="369" t="s">
         <v>77</v>
       </c>
-      <c r="AK33" s="426" t="s">
+      <c r="AK33" s="370" t="s">
         <v>77</v>
       </c>
-      <c r="AL33" s="427" t="s">
+      <c r="AL33" s="371" t="s">
         <v>77</v>
       </c>
-      <c r="AM33" s="287"/>
-      <c r="AN33" s="287"/>
-      <c r="AO33" s="428" t="s">
+      <c r="AM33" s="281"/>
+      <c r="AN33" s="281"/>
+      <c r="AO33" s="372" t="s">
         <v>119</v>
       </c>
-      <c r="AP33" s="428"/>
-      <c r="AQ33" s="428"/>
-      <c r="AR33" s="428"/>
-      <c r="AS33" s="428"/>
-      <c r="AT33" s="428"/>
+      <c r="AP33" s="372"/>
+      <c r="AQ33" s="372"/>
+      <c r="AR33" s="372"/>
+      <c r="AS33" s="372"/>
+      <c r="AT33" s="372"/>
       <c r="AU33" s="2"/>
       <c r="AV33" s="2"/>
       <c r="AW33" s="2"/>
@@ -10071,8 +10045,8 @@
       <c r="DF33" s="2"/>
     </row>
     <row r="34" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A34" s="287" t="s">
-        <v>128</v>
+      <c r="A34" s="281" t="s">
+        <v>127</v>
       </c>
       <c r="B34" s="221" t="s">
         <v>75</v>
@@ -10080,11 +10054,11 @@
       <c r="C34" s="222" t="s">
         <v>78</v>
       </c>
-      <c r="D34" s="280">
+      <c r="D34" s="278">
         <v>1</v>
       </c>
-      <c r="E34" s="446" t="s">
-        <v>153</v>
+      <c r="E34" s="326" t="s">
+        <v>151</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="224" t="s">
@@ -10119,18 +10093,18 @@
       <c r="AH34" s="2"/>
       <c r="AI34" s="2"/>
       <c r="AJ34" s="2"/>
-      <c r="AK34" s="277"/>
-      <c r="AL34" s="278"/>
-      <c r="AM34" s="442"/>
-      <c r="AN34" s="443"/>
-      <c r="AO34" s="428" t="s">
-        <v>129</v>
-      </c>
-      <c r="AP34" s="428"/>
-      <c r="AQ34" s="428"/>
-      <c r="AR34" s="428"/>
-      <c r="AS34" s="428"/>
-      <c r="AT34" s="428"/>
+      <c r="AK34" s="275"/>
+      <c r="AL34" s="276"/>
+      <c r="AM34" s="324"/>
+      <c r="AN34" s="325"/>
+      <c r="AO34" s="372" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP34" s="372"/>
+      <c r="AQ34" s="372"/>
+      <c r="AR34" s="372"/>
+      <c r="AS34" s="372"/>
+      <c r="AT34" s="372"/>
       <c r="AU34" s="2"/>
       <c r="AV34" s="2"/>
       <c r="AW34" s="2"/>
@@ -10197,7 +10171,7 @@
       <c r="DF34" s="2"/>
     </row>
     <row r="35" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A35" s="287" t="s">
+      <c r="A35" s="281" t="s">
         <v>54</v>
       </c>
       <c r="B35" s="225" t="s">
@@ -10206,11 +10180,11 @@
       <c r="C35" s="226" t="s">
         <v>80</v>
       </c>
-      <c r="D35" s="280">
+      <c r="D35" s="278">
         <v>1</v>
       </c>
-      <c r="E35" s="446" t="s">
-        <v>152</v>
+      <c r="E35" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F35" s="223"/>
       <c r="G35" s="224"/>
@@ -10243,37 +10217,37 @@
       <c r="AH35" s="2"/>
       <c r="AI35" s="2"/>
       <c r="AJ35" s="2"/>
-      <c r="AK35" s="277"/>
-      <c r="AL35" s="278"/>
-      <c r="AM35" s="279"/>
-      <c r="AN35" s="328"/>
-      <c r="AO35" s="329"/>
-      <c r="AP35" s="329"/>
-      <c r="AQ35" s="329"/>
-      <c r="AR35" s="329"/>
-      <c r="AS35" s="329"/>
-      <c r="AT35" s="343" t="s">
+      <c r="AK35" s="275"/>
+      <c r="AL35" s="276"/>
+      <c r="AM35" s="277"/>
+      <c r="AN35" s="321"/>
+      <c r="AO35" s="322"/>
+      <c r="AP35" s="322"/>
+      <c r="AQ35" s="322"/>
+      <c r="AR35" s="322"/>
+      <c r="AS35" s="322"/>
+      <c r="AT35" s="333" t="s">
         <v>120</v>
       </c>
-      <c r="AU35" s="390" t="s">
+      <c r="AU35" s="334" t="s">
         <v>81</v>
       </c>
-      <c r="AV35" s="391" t="s">
+      <c r="AV35" s="335" t="s">
         <v>81</v>
       </c>
-      <c r="AW35" s="392" t="s">
+      <c r="AW35" s="336" t="s">
         <v>81</v>
       </c>
-      <c r="AX35" s="393" t="s">
+      <c r="AX35" s="337" t="s">
         <v>81</v>
       </c>
-      <c r="AY35" s="394" t="s">
+      <c r="AY35" s="338" t="s">
         <v>81</v>
       </c>
-      <c r="AZ35" s="395" t="s">
+      <c r="AZ35" s="339" t="s">
         <v>81</v>
       </c>
-      <c r="BA35" s="396" t="s">
+      <c r="BA35" s="340" t="s">
         <v>81</v>
       </c>
       <c r="BB35" s="2"/>
@@ -10335,7 +10309,7 @@
       <c r="DF35" s="2"/>
     </row>
     <row r="36" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A36" s="287" t="s">
+      <c r="A36" s="281" t="s">
         <v>121</v>
       </c>
       <c r="B36" s="225" t="s">
@@ -10344,11 +10318,11 @@
       <c r="C36" s="226" t="s">
         <v>80</v>
       </c>
-      <c r="D36" s="280">
+      <c r="D36" s="278">
         <v>1</v>
       </c>
-      <c r="E36" s="446" t="s">
-        <v>152</v>
+      <c r="E36" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F36" s="227"/>
       <c r="G36" s="228"/>
@@ -10390,28 +10364,28 @@
       <c r="AQ36" s="2"/>
       <c r="AR36" s="2"/>
       <c r="AS36" s="2"/>
-      <c r="AT36" s="343" t="s">
+      <c r="AT36" s="333" t="s">
         <v>124</v>
       </c>
-      <c r="AU36" s="390" t="s">
+      <c r="AU36" s="334" t="s">
         <v>81</v>
       </c>
-      <c r="AV36" s="391" t="s">
+      <c r="AV36" s="335" t="s">
         <v>81</v>
       </c>
-      <c r="AW36" s="392" t="s">
+      <c r="AW36" s="336" t="s">
         <v>81</v>
       </c>
-      <c r="AX36" s="393" t="s">
+      <c r="AX36" s="337" t="s">
         <v>81</v>
       </c>
-      <c r="AY36" s="394" t="s">
+      <c r="AY36" s="338" t="s">
         <v>81</v>
       </c>
-      <c r="AZ36" s="395" t="s">
+      <c r="AZ36" s="339" t="s">
         <v>81</v>
       </c>
-      <c r="BA36" s="396" t="s">
+      <c r="BA36" s="340" t="s">
         <v>81</v>
       </c>
       <c r="BB36" s="2"/>
@@ -10473,7 +10447,7 @@
       <c r="DF36" s="2"/>
     </row>
     <row r="37" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A37" s="287" t="s">
+      <c r="A37" s="281" t="s">
         <v>122</v>
       </c>
       <c r="B37" s="225" t="s">
@@ -10482,11 +10456,11 @@
       <c r="C37" s="226" t="s">
         <v>80</v>
       </c>
-      <c r="D37" s="280">
+      <c r="D37" s="278">
         <v>1</v>
       </c>
-      <c r="E37" s="446" t="s">
-        <v>151</v>
+      <c r="E37" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F37" s="227"/>
       <c r="G37" s="228"/>
@@ -10528,28 +10502,28 @@
       <c r="AQ37" s="2"/>
       <c r="AR37" s="2"/>
       <c r="AS37" s="2"/>
-      <c r="AT37" s="343" t="s">
+      <c r="AT37" s="333" t="s">
         <v>123</v>
       </c>
-      <c r="AU37" s="390" t="s">
+      <c r="AU37" s="334" t="s">
         <v>81</v>
       </c>
-      <c r="AV37" s="391" t="s">
+      <c r="AV37" s="335" t="s">
         <v>81</v>
       </c>
-      <c r="AW37" s="392" t="s">
+      <c r="AW37" s="336" t="s">
         <v>81</v>
       </c>
-      <c r="AX37" s="393" t="s">
+      <c r="AX37" s="337" t="s">
         <v>81</v>
       </c>
-      <c r="AY37" s="394" t="s">
+      <c r="AY37" s="338" t="s">
         <v>81</v>
       </c>
-      <c r="AZ37" s="395" t="s">
+      <c r="AZ37" s="339" t="s">
         <v>81</v>
       </c>
-      <c r="BA37" s="396" t="s">
+      <c r="BA37" s="340" t="s">
         <v>81</v>
       </c>
       <c r="BB37" s="2"/>
@@ -10610,25 +10584,23 @@
       <c r="DE37" s="2"/>
       <c r="DF37" s="2"/>
     </row>
-    <row r="38" spans="1:110" ht="80" x14ac:dyDescent="0.8">
-      <c r="A38" s="441" t="s">
-        <v>82</v>
-      </c>
-      <c r="B38" s="283">
-        <v>46108</v>
-      </c>
-      <c r="C38" s="284">
-        <v>46115</v>
-      </c>
-      <c r="D38" s="288">
-        <v>0.85</v>
-      </c>
-      <c r="E38" s="446" t="s">
-        <v>153</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>138</v>
-      </c>
+    <row r="38" spans="1:110" ht="19.5" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A38" s="281" t="s">
+        <v>140</v>
+      </c>
+      <c r="B38" s="230" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="279">
+        <v>46122</v>
+      </c>
+      <c r="D38" s="282">
+        <v>0.75</v>
+      </c>
+      <c r="E38" s="326" t="s">
+        <v>149</v>
+      </c>
+      <c r="F38" s="6"/>
       <c r="G38" s="229" t="s">
         <v>0</v>
       </c>
@@ -10670,44 +10642,30 @@
       <c r="AQ38" s="2"/>
       <c r="AR38" s="2"/>
       <c r="AS38" s="2"/>
-      <c r="AT38" s="432" t="s">
-        <v>188</v>
-      </c>
-      <c r="AU38" s="433" t="s">
-        <v>81</v>
-      </c>
-      <c r="AV38" s="434" t="s">
-        <v>81</v>
-      </c>
-      <c r="AW38" s="435" t="s">
-        <v>81</v>
-      </c>
-      <c r="AX38" s="436" t="s">
-        <v>81</v>
-      </c>
-      <c r="AY38" s="437" t="s">
-        <v>81</v>
-      </c>
-      <c r="AZ38" s="438" t="s">
-        <v>81</v>
-      </c>
-      <c r="BA38" s="439" t="s">
-        <v>81</v>
-      </c>
-      <c r="BB38" s="2"/>
-      <c r="BC38" s="2"/>
-      <c r="BD38" s="2"/>
-      <c r="BE38" s="2"/>
-      <c r="BF38" s="2"/>
-      <c r="BG38" s="2"/>
-      <c r="BH38" s="2"/>
-      <c r="BI38" s="2"/>
-      <c r="BJ38" s="2"/>
-      <c r="BK38" s="2"/>
-      <c r="BL38" s="2"/>
-      <c r="BM38" s="2"/>
-      <c r="BN38" s="2"/>
-      <c r="BO38" s="2"/>
+      <c r="AT38" s="2"/>
+      <c r="AU38" s="2"/>
+      <c r="AV38" s="2"/>
+      <c r="AW38" s="2"/>
+      <c r="AX38" s="2"/>
+      <c r="AY38" s="2"/>
+      <c r="AZ38" s="2"/>
+      <c r="BA38" s="330" t="s">
+        <v>147</v>
+      </c>
+      <c r="BB38" s="432"/>
+      <c r="BC38" s="432"/>
+      <c r="BD38" s="432"/>
+      <c r="BE38" s="432"/>
+      <c r="BF38" s="432"/>
+      <c r="BG38" s="432"/>
+      <c r="BH38" s="432"/>
+      <c r="BI38" s="283"/>
+      <c r="BJ38" s="284"/>
+      <c r="BK38" s="285"/>
+      <c r="BL38" s="286"/>
+      <c r="BM38" s="287"/>
+      <c r="BN38" s="288"/>
+      <c r="BO38" s="289"/>
       <c r="BP38" s="2"/>
       <c r="BQ38" s="2"/>
       <c r="BR38" s="2"/>
@@ -10752,26 +10710,24 @@
       <c r="DE38" s="2"/>
       <c r="DF38" s="2"/>
     </row>
-    <row r="39" spans="1:110" ht="32" x14ac:dyDescent="0.8">
-      <c r="A39" s="441" t="s">
-        <v>142</v>
-      </c>
-      <c r="B39" s="285">
-        <v>46108</v>
-      </c>
-      <c r="C39" s="286">
-        <v>46115</v>
-      </c>
-      <c r="D39" s="289">
-        <v>0.75</v>
-      </c>
-      <c r="E39" s="446" t="s">
-        <v>151</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G39" s="230" t="s">
+    <row r="39" spans="1:110" x14ac:dyDescent="0.8">
+      <c r="A39" s="281" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39" s="230" t="s">
+        <v>80</v>
+      </c>
+      <c r="C39" s="279">
+        <v>46122</v>
+      </c>
+      <c r="D39" s="280">
+        <v>1</v>
+      </c>
+      <c r="E39" s="326" t="s">
+        <v>149</v>
+      </c>
+      <c r="F39" s="6"/>
+      <c r="G39" s="231" t="s">
         <v>0</v>
       </c>
       <c r="H39" s="2"/>
@@ -10819,23 +10775,23 @@
       <c r="AX39" s="2"/>
       <c r="AY39" s="2"/>
       <c r="AZ39" s="2"/>
-      <c r="BA39" s="444" t="s">
-        <v>149</v>
-      </c>
-      <c r="BB39" s="445"/>
-      <c r="BC39" s="445"/>
-      <c r="BD39" s="445"/>
-      <c r="BE39" s="445"/>
-      <c r="BF39" s="445"/>
-      <c r="BG39" s="445"/>
-      <c r="BH39" s="445"/>
-      <c r="BI39" s="290"/>
-      <c r="BJ39" s="291"/>
-      <c r="BK39" s="292"/>
-      <c r="BL39" s="293"/>
-      <c r="BM39" s="294"/>
-      <c r="BN39" s="295"/>
-      <c r="BO39" s="296"/>
+      <c r="BA39" s="330" t="s">
+        <v>125</v>
+      </c>
+      <c r="BB39" s="332"/>
+      <c r="BC39" s="332"/>
+      <c r="BD39" s="332"/>
+      <c r="BE39" s="332"/>
+      <c r="BF39" s="332"/>
+      <c r="BG39" s="332"/>
+      <c r="BH39" s="332"/>
+      <c r="BI39" s="292"/>
+      <c r="BJ39" s="293"/>
+      <c r="BK39" s="294"/>
+      <c r="BL39" s="295"/>
+      <c r="BM39" s="296"/>
+      <c r="BN39" s="297"/>
+      <c r="BO39" s="298"/>
       <c r="BP39" s="2"/>
       <c r="BQ39" s="2"/>
       <c r="BR39" s="2"/>
@@ -10881,25 +10837,23 @@
       <c r="DF39" s="2"/>
     </row>
     <row r="40" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A40" s="287" t="s">
-        <v>147</v>
-      </c>
-      <c r="B40" s="231" t="s">
+      <c r="A40" s="281" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="281">
+      <c r="C40" s="279">
         <v>46122</v>
       </c>
-      <c r="D40" s="282">
+      <c r="D40" s="280">
         <v>1</v>
       </c>
-      <c r="E40" s="446" t="s">
-        <v>151</v>
+      <c r="E40" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F40" s="6"/>
-      <c r="G40" s="232" t="s">
-        <v>0</v>
-      </c>
+      <c r="G40" s="231"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
@@ -10945,23 +10899,23 @@
       <c r="AX40" s="2"/>
       <c r="AY40" s="2"/>
       <c r="AZ40" s="2"/>
-      <c r="BA40" s="332" t="s">
-        <v>125</v>
-      </c>
-      <c r="BB40" s="440"/>
-      <c r="BC40" s="440"/>
-      <c r="BD40" s="440"/>
-      <c r="BE40" s="440"/>
-      <c r="BF40" s="440"/>
-      <c r="BG40" s="440"/>
-      <c r="BH40" s="440"/>
-      <c r="BI40" s="299"/>
-      <c r="BJ40" s="300"/>
-      <c r="BK40" s="301"/>
-      <c r="BL40" s="302"/>
-      <c r="BM40" s="303"/>
-      <c r="BN40" s="304"/>
-      <c r="BO40" s="305"/>
+      <c r="BA40" s="330" t="s">
+        <v>153</v>
+      </c>
+      <c r="BB40" s="330"/>
+      <c r="BC40" s="330"/>
+      <c r="BD40" s="330"/>
+      <c r="BE40" s="330"/>
+      <c r="BF40" s="330"/>
+      <c r="BG40" s="330"/>
+      <c r="BH40" s="330"/>
+      <c r="BI40" s="292"/>
+      <c r="BJ40" s="293"/>
+      <c r="BK40" s="294"/>
+      <c r="BL40" s="295"/>
+      <c r="BM40" s="296"/>
+      <c r="BN40" s="297"/>
+      <c r="BO40" s="298"/>
       <c r="BP40" s="2"/>
       <c r="BQ40" s="2"/>
       <c r="BR40" s="2"/>
@@ -11007,23 +10961,23 @@
       <c r="DF40" s="2"/>
     </row>
     <row r="41" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A41" s="287" t="s">
+      <c r="A41" s="281" t="s">
         <v>130</v>
       </c>
-      <c r="B41" s="231" t="s">
+      <c r="B41" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="281">
+      <c r="C41" s="279">
         <v>46122</v>
       </c>
-      <c r="D41" s="282">
+      <c r="D41" s="280">
         <v>1</v>
       </c>
-      <c r="E41" s="446" t="s">
-        <v>152</v>
+      <c r="E41" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F41" s="6"/>
-      <c r="G41" s="232"/>
+      <c r="G41" s="231"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
@@ -11069,23 +11023,23 @@
       <c r="AX41" s="2"/>
       <c r="AY41" s="2"/>
       <c r="AZ41" s="2"/>
-      <c r="BA41" s="332" t="s">
-        <v>156</v>
-      </c>
-      <c r="BB41" s="332"/>
-      <c r="BC41" s="332"/>
-      <c r="BD41" s="332"/>
-      <c r="BE41" s="332"/>
-      <c r="BF41" s="332"/>
-      <c r="BG41" s="332"/>
-      <c r="BH41" s="332"/>
-      <c r="BI41" s="299"/>
-      <c r="BJ41" s="300"/>
-      <c r="BK41" s="301"/>
-      <c r="BL41" s="302"/>
-      <c r="BM41" s="303"/>
-      <c r="BN41" s="304"/>
-      <c r="BO41" s="305"/>
+      <c r="BA41" s="330" t="s">
+        <v>154</v>
+      </c>
+      <c r="BB41" s="330"/>
+      <c r="BC41" s="330"/>
+      <c r="BD41" s="330"/>
+      <c r="BE41" s="330"/>
+      <c r="BF41" s="330"/>
+      <c r="BG41" s="330"/>
+      <c r="BH41" s="330"/>
+      <c r="BI41" s="292"/>
+      <c r="BJ41" s="293"/>
+      <c r="BK41" s="294"/>
+      <c r="BL41" s="295"/>
+      <c r="BM41" s="296"/>
+      <c r="BN41" s="297"/>
+      <c r="BO41" s="298"/>
       <c r="BP41" s="2"/>
       <c r="BQ41" s="2"/>
       <c r="BR41" s="2"/>
@@ -11131,23 +11085,23 @@
       <c r="DF41" s="2"/>
     </row>
     <row r="42" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A42" s="287" t="s">
+      <c r="A42" s="281" t="s">
         <v>131</v>
       </c>
-      <c r="B42" s="231" t="s">
+      <c r="B42" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C42" s="281">
+      <c r="C42" s="279">
         <v>46122</v>
       </c>
-      <c r="D42" s="282">
+      <c r="D42" s="280">
         <v>1</v>
       </c>
-      <c r="E42" s="446" t="s">
-        <v>152</v>
+      <c r="E42" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F42" s="6"/>
-      <c r="G42" s="232"/>
+      <c r="G42" s="231"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
@@ -11193,23 +11147,23 @@
       <c r="AX42" s="2"/>
       <c r="AY42" s="2"/>
       <c r="AZ42" s="2"/>
-      <c r="BA42" s="332" t="s">
-        <v>157</v>
-      </c>
-      <c r="BB42" s="332"/>
-      <c r="BC42" s="332"/>
-      <c r="BD42" s="332"/>
-      <c r="BE42" s="332"/>
-      <c r="BF42" s="332"/>
-      <c r="BG42" s="332"/>
-      <c r="BH42" s="332"/>
-      <c r="BI42" s="299"/>
-      <c r="BJ42" s="300"/>
-      <c r="BK42" s="301"/>
-      <c r="BL42" s="302"/>
-      <c r="BM42" s="303"/>
-      <c r="BN42" s="304"/>
-      <c r="BO42" s="305"/>
+      <c r="BA42" s="330" t="s">
+        <v>155</v>
+      </c>
+      <c r="BB42" s="330"/>
+      <c r="BC42" s="330"/>
+      <c r="BD42" s="330"/>
+      <c r="BE42" s="330"/>
+      <c r="BF42" s="330"/>
+      <c r="BG42" s="330"/>
+      <c r="BH42" s="330"/>
+      <c r="BI42" s="292"/>
+      <c r="BJ42" s="293"/>
+      <c r="BK42" s="294"/>
+      <c r="BL42" s="295"/>
+      <c r="BM42" s="296"/>
+      <c r="BN42" s="297"/>
+      <c r="BO42" s="298"/>
       <c r="BP42" s="2"/>
       <c r="BQ42" s="2"/>
       <c r="BR42" s="2"/>
@@ -11254,26 +11208,24 @@
       <c r="DE42" s="2"/>
       <c r="DF42" s="2"/>
     </row>
-    <row r="43" spans="1:110" ht="48" x14ac:dyDescent="0.8">
-      <c r="A43" s="441" t="s">
+    <row r="43" spans="1:110" x14ac:dyDescent="0.8">
+      <c r="A43" s="281" t="s">
         <v>132</v>
       </c>
-      <c r="B43" s="231" t="s">
+      <c r="B43" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C43" s="281">
+      <c r="C43" s="279">
         <v>46122</v>
       </c>
-      <c r="D43" s="282">
-        <v>0.85</v>
-      </c>
-      <c r="E43" s="446" t="s">
-        <v>152</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="G43" s="232"/>
+      <c r="D43" s="280">
+        <v>1</v>
+      </c>
+      <c r="E43" s="326" t="s">
+        <v>150</v>
+      </c>
+      <c r="F43" s="6"/>
+      <c r="G43" s="231"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
@@ -11319,23 +11271,23 @@
       <c r="AX43" s="2"/>
       <c r="AY43" s="2"/>
       <c r="AZ43" s="2"/>
-      <c r="BA43" s="444" t="s">
-        <v>158</v>
-      </c>
-      <c r="BB43" s="444"/>
-      <c r="BC43" s="444"/>
-      <c r="BD43" s="444"/>
-      <c r="BE43" s="444"/>
-      <c r="BF43" s="444"/>
-      <c r="BG43" s="444"/>
-      <c r="BH43" s="444"/>
-      <c r="BI43" s="299"/>
-      <c r="BJ43" s="300"/>
-      <c r="BK43" s="301"/>
-      <c r="BL43" s="302"/>
-      <c r="BM43" s="303"/>
-      <c r="BN43" s="304"/>
-      <c r="BO43" s="305"/>
+      <c r="BA43" s="330" t="s">
+        <v>156</v>
+      </c>
+      <c r="BB43" s="330"/>
+      <c r="BC43" s="330"/>
+      <c r="BD43" s="330"/>
+      <c r="BE43" s="330"/>
+      <c r="BF43" s="330"/>
+      <c r="BG43" s="330"/>
+      <c r="BH43" s="330"/>
+      <c r="BI43" s="292"/>
+      <c r="BJ43" s="293"/>
+      <c r="BK43" s="294"/>
+      <c r="BL43" s="295"/>
+      <c r="BM43" s="296"/>
+      <c r="BN43" s="297"/>
+      <c r="BO43" s="298"/>
       <c r="BP43" s="2"/>
       <c r="BQ43" s="2"/>
       <c r="BR43" s="2"/>
@@ -11380,26 +11332,24 @@
       <c r="DE43" s="2"/>
       <c r="DF43" s="2"/>
     </row>
-    <row r="44" spans="1:110" ht="64" x14ac:dyDescent="0.8">
-      <c r="A44" s="441" t="s">
+    <row r="44" spans="1:110" x14ac:dyDescent="0.8">
+      <c r="A44" s="281" t="s">
         <v>133</v>
       </c>
-      <c r="B44" s="231" t="s">
+      <c r="B44" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C44" s="281">
+      <c r="C44" s="279">
         <v>46122</v>
       </c>
-      <c r="D44" s="282">
-        <v>0.5</v>
-      </c>
-      <c r="E44" s="446" t="s">
-        <v>152</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G44" s="232"/>
+      <c r="D44" s="280">
+        <v>1</v>
+      </c>
+      <c r="E44" s="326" t="s">
+        <v>149</v>
+      </c>
+      <c r="F44" s="6"/>
+      <c r="G44" s="231"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
@@ -11445,23 +11395,23 @@
       <c r="AX44" s="2"/>
       <c r="AY44" s="2"/>
       <c r="AZ44" s="2"/>
-      <c r="BA44" s="444" t="s">
-        <v>159</v>
-      </c>
-      <c r="BB44" s="444"/>
-      <c r="BC44" s="444"/>
-      <c r="BD44" s="444"/>
-      <c r="BE44" s="444"/>
-      <c r="BF44" s="444"/>
-      <c r="BG44" s="444"/>
-      <c r="BH44" s="444"/>
-      <c r="BI44" s="299"/>
-      <c r="BJ44" s="300"/>
-      <c r="BK44" s="301"/>
-      <c r="BL44" s="302"/>
-      <c r="BM44" s="303"/>
-      <c r="BN44" s="304"/>
-      <c r="BO44" s="305"/>
+      <c r="BA44" s="330" t="s">
+        <v>157</v>
+      </c>
+      <c r="BB44" s="330"/>
+      <c r="BC44" s="330"/>
+      <c r="BD44" s="330"/>
+      <c r="BE44" s="330"/>
+      <c r="BF44" s="330"/>
+      <c r="BG44" s="330"/>
+      <c r="BH44" s="330"/>
+      <c r="BI44" s="292"/>
+      <c r="BJ44" s="293"/>
+      <c r="BK44" s="294"/>
+      <c r="BL44" s="295"/>
+      <c r="BM44" s="296"/>
+      <c r="BN44" s="297"/>
+      <c r="BO44" s="298"/>
       <c r="BP44" s="2"/>
       <c r="BQ44" s="2"/>
       <c r="BR44" s="2"/>
@@ -11507,23 +11457,23 @@
       <c r="DF44" s="2"/>
     </row>
     <row r="45" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A45" s="287" t="s">
+      <c r="A45" s="281" t="s">
         <v>134</v>
       </c>
-      <c r="B45" s="231" t="s">
+      <c r="B45" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C45" s="281">
+      <c r="C45" s="279">
         <v>46122</v>
       </c>
-      <c r="D45" s="282">
+      <c r="D45" s="280">
         <v>1</v>
       </c>
-      <c r="E45" s="446" t="s">
-        <v>151</v>
+      <c r="E45" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F45" s="6"/>
-      <c r="G45" s="232"/>
+      <c r="G45" s="231"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
@@ -11569,23 +11519,23 @@
       <c r="AX45" s="2"/>
       <c r="AY45" s="2"/>
       <c r="AZ45" s="2"/>
-      <c r="BA45" s="332" t="s">
-        <v>160</v>
-      </c>
-      <c r="BB45" s="332"/>
-      <c r="BC45" s="332"/>
-      <c r="BD45" s="332"/>
-      <c r="BE45" s="332"/>
-      <c r="BF45" s="332"/>
-      <c r="BG45" s="332"/>
-      <c r="BH45" s="332"/>
-      <c r="BI45" s="299"/>
-      <c r="BJ45" s="300"/>
-      <c r="BK45" s="301"/>
-      <c r="BL45" s="302"/>
-      <c r="BM45" s="303"/>
-      <c r="BN45" s="304"/>
-      <c r="BO45" s="305"/>
+      <c r="BA45" s="330" t="s">
+        <v>158</v>
+      </c>
+      <c r="BB45" s="330"/>
+      <c r="BC45" s="330"/>
+      <c r="BD45" s="330"/>
+      <c r="BE45" s="330"/>
+      <c r="BF45" s="330"/>
+      <c r="BG45" s="330"/>
+      <c r="BH45" s="330"/>
+      <c r="BI45" s="292"/>
+      <c r="BJ45" s="293"/>
+      <c r="BK45" s="294"/>
+      <c r="BL45" s="295"/>
+      <c r="BM45" s="296"/>
+      <c r="BN45" s="297"/>
+      <c r="BO45" s="298"/>
       <c r="BP45" s="2"/>
       <c r="BQ45" s="2"/>
       <c r="BR45" s="2"/>
@@ -11631,23 +11581,23 @@
       <c r="DF45" s="2"/>
     </row>
     <row r="46" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A46" s="287" t="s">
-        <v>135</v>
-      </c>
-      <c r="B46" s="231" t="s">
+      <c r="A46" s="281" t="s">
+        <v>139</v>
+      </c>
+      <c r="B46" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C46" s="281">
+      <c r="C46" s="279">
         <v>46122</v>
       </c>
-      <c r="D46" s="282">
+      <c r="D46" s="280">
         <v>1</v>
       </c>
-      <c r="E46" s="446" t="s">
-        <v>152</v>
+      <c r="E46" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F46" s="6"/>
-      <c r="G46" s="232"/>
+      <c r="G46" s="231"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
@@ -11693,23 +11643,23 @@
       <c r="AX46" s="2"/>
       <c r="AY46" s="2"/>
       <c r="AZ46" s="2"/>
-      <c r="BA46" s="332" t="s">
-        <v>161</v>
-      </c>
-      <c r="BB46" s="332"/>
-      <c r="BC46" s="332"/>
-      <c r="BD46" s="332"/>
-      <c r="BE46" s="332"/>
-      <c r="BF46" s="332"/>
-      <c r="BG46" s="332"/>
-      <c r="BH46" s="332"/>
-      <c r="BI46" s="299"/>
-      <c r="BJ46" s="300"/>
-      <c r="BK46" s="301"/>
-      <c r="BL46" s="302"/>
-      <c r="BM46" s="303"/>
-      <c r="BN46" s="304"/>
-      <c r="BO46" s="305"/>
+      <c r="BA46" s="330" t="s">
+        <v>159</v>
+      </c>
+      <c r="BB46" s="330"/>
+      <c r="BC46" s="330"/>
+      <c r="BD46" s="330"/>
+      <c r="BE46" s="330"/>
+      <c r="BF46" s="330"/>
+      <c r="BG46" s="330"/>
+      <c r="BH46" s="330"/>
+      <c r="BI46" s="292"/>
+      <c r="BJ46" s="293"/>
+      <c r="BK46" s="294"/>
+      <c r="BL46" s="295"/>
+      <c r="BM46" s="296"/>
+      <c r="BN46" s="297"/>
+      <c r="BO46" s="298"/>
       <c r="BP46" s="2"/>
       <c r="BQ46" s="2"/>
       <c r="BR46" s="2"/>
@@ -11755,23 +11705,23 @@
       <c r="DF46" s="2"/>
     </row>
     <row r="47" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A47" s="287" t="s">
-        <v>141</v>
-      </c>
-      <c r="B47" s="231" t="s">
+      <c r="A47" s="281" t="s">
+        <v>135</v>
+      </c>
+      <c r="B47" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C47" s="281">
+      <c r="C47" s="279">
         <v>46122</v>
       </c>
-      <c r="D47" s="282">
+      <c r="D47" s="280">
         <v>1</v>
       </c>
-      <c r="E47" s="446" t="s">
-        <v>151</v>
+      <c r="E47" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F47" s="6"/>
-      <c r="G47" s="232"/>
+      <c r="G47" s="231"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
@@ -11817,23 +11767,23 @@
       <c r="AX47" s="2"/>
       <c r="AY47" s="2"/>
       <c r="AZ47" s="2"/>
-      <c r="BA47" s="332" t="s">
-        <v>162</v>
-      </c>
-      <c r="BB47" s="332"/>
-      <c r="BC47" s="332"/>
-      <c r="BD47" s="332"/>
-      <c r="BE47" s="332"/>
-      <c r="BF47" s="332"/>
-      <c r="BG47" s="332"/>
-      <c r="BH47" s="332"/>
-      <c r="BI47" s="299"/>
-      <c r="BJ47" s="300"/>
-      <c r="BK47" s="301"/>
-      <c r="BL47" s="302"/>
-      <c r="BM47" s="303"/>
-      <c r="BN47" s="304"/>
-      <c r="BO47" s="305"/>
+      <c r="BA47" s="330" t="s">
+        <v>160</v>
+      </c>
+      <c r="BB47" s="330"/>
+      <c r="BC47" s="330"/>
+      <c r="BD47" s="330"/>
+      <c r="BE47" s="330"/>
+      <c r="BF47" s="330"/>
+      <c r="BG47" s="330"/>
+      <c r="BH47" s="330"/>
+      <c r="BI47" s="292"/>
+      <c r="BJ47" s="293"/>
+      <c r="BK47" s="294"/>
+      <c r="BL47" s="295"/>
+      <c r="BM47" s="296"/>
+      <c r="BN47" s="297"/>
+      <c r="BO47" s="298"/>
       <c r="BP47" s="2"/>
       <c r="BQ47" s="2"/>
       <c r="BR47" s="2"/>
@@ -11879,23 +11829,23 @@
       <c r="DF47" s="2"/>
     </row>
     <row r="48" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A48" s="287" t="s">
+      <c r="A48" s="281" t="s">
         <v>136</v>
       </c>
-      <c r="B48" s="231" t="s">
+      <c r="B48" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C48" s="281">
+      <c r="C48" s="279">
         <v>46122</v>
       </c>
-      <c r="D48" s="282">
+      <c r="D48" s="280">
         <v>1</v>
       </c>
-      <c r="E48" s="446" t="s">
-        <v>152</v>
+      <c r="E48" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F48" s="6"/>
-      <c r="G48" s="232"/>
+      <c r="G48" s="231"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
@@ -11941,23 +11891,23 @@
       <c r="AX48" s="2"/>
       <c r="AY48" s="2"/>
       <c r="AZ48" s="2"/>
-      <c r="BA48" s="332" t="s">
-        <v>163</v>
-      </c>
-      <c r="BB48" s="332"/>
-      <c r="BC48" s="332"/>
-      <c r="BD48" s="332"/>
-      <c r="BE48" s="332"/>
-      <c r="BF48" s="332"/>
-      <c r="BG48" s="332"/>
-      <c r="BH48" s="332"/>
-      <c r="BI48" s="299"/>
-      <c r="BJ48" s="300"/>
-      <c r="BK48" s="301"/>
-      <c r="BL48" s="302"/>
-      <c r="BM48" s="303"/>
-      <c r="BN48" s="304"/>
-      <c r="BO48" s="305"/>
+      <c r="BA48" s="330" t="s">
+        <v>161</v>
+      </c>
+      <c r="BB48" s="330"/>
+      <c r="BC48" s="330"/>
+      <c r="BD48" s="330"/>
+      <c r="BE48" s="330"/>
+      <c r="BF48" s="330"/>
+      <c r="BG48" s="330"/>
+      <c r="BH48" s="330"/>
+      <c r="BI48" s="292"/>
+      <c r="BJ48" s="293"/>
+      <c r="BK48" s="294"/>
+      <c r="BL48" s="295"/>
+      <c r="BM48" s="296"/>
+      <c r="BN48" s="297"/>
+      <c r="BO48" s="298"/>
       <c r="BP48" s="2"/>
       <c r="BQ48" s="2"/>
       <c r="BR48" s="2"/>
@@ -12003,23 +11953,23 @@
       <c r="DF48" s="2"/>
     </row>
     <row r="49" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A49" s="287" t="s">
+      <c r="A49" s="281" t="s">
         <v>137</v>
       </c>
-      <c r="B49" s="231" t="s">
+      <c r="B49" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C49" s="281">
+      <c r="C49" s="279">
         <v>46122</v>
       </c>
-      <c r="D49" s="282">
+      <c r="D49" s="280">
         <v>1</v>
       </c>
-      <c r="E49" s="446" t="s">
-        <v>152</v>
+      <c r="E49" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F49" s="6"/>
-      <c r="G49" s="232"/>
+      <c r="G49" s="231"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
@@ -12065,23 +12015,23 @@
       <c r="AX49" s="2"/>
       <c r="AY49" s="2"/>
       <c r="AZ49" s="2"/>
-      <c r="BA49" s="332" t="s">
-        <v>164</v>
-      </c>
-      <c r="BB49" s="332"/>
-      <c r="BC49" s="332"/>
-      <c r="BD49" s="332"/>
-      <c r="BE49" s="332"/>
-      <c r="BF49" s="332"/>
-      <c r="BG49" s="332"/>
-      <c r="BH49" s="332"/>
-      <c r="BI49" s="299"/>
-      <c r="BJ49" s="300"/>
-      <c r="BK49" s="301"/>
-      <c r="BL49" s="302"/>
-      <c r="BM49" s="303"/>
-      <c r="BN49" s="304"/>
-      <c r="BO49" s="305"/>
+      <c r="BA49" s="330" t="s">
+        <v>162</v>
+      </c>
+      <c r="BB49" s="330"/>
+      <c r="BC49" s="330"/>
+      <c r="BD49" s="330"/>
+      <c r="BE49" s="330"/>
+      <c r="BF49" s="330"/>
+      <c r="BG49" s="330"/>
+      <c r="BH49" s="330"/>
+      <c r="BI49" s="292"/>
+      <c r="BJ49" s="293"/>
+      <c r="BK49" s="294"/>
+      <c r="BL49" s="295"/>
+      <c r="BM49" s="296"/>
+      <c r="BN49" s="297"/>
+      <c r="BO49" s="298"/>
       <c r="BP49" s="2"/>
       <c r="BQ49" s="2"/>
       <c r="BR49" s="2"/>
@@ -12127,23 +12077,23 @@
       <c r="DF49" s="2"/>
     </row>
     <row r="50" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A50" s="287" t="s">
-        <v>139</v>
-      </c>
-      <c r="B50" s="231" t="s">
+      <c r="A50" s="281" t="s">
+        <v>138</v>
+      </c>
+      <c r="B50" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C50" s="281">
+      <c r="C50" s="279">
         <v>46122</v>
       </c>
-      <c r="D50" s="282">
+      <c r="D50" s="280">
         <v>1</v>
       </c>
-      <c r="E50" s="446" t="s">
-        <v>151</v>
+      <c r="E50" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F50" s="6"/>
-      <c r="G50" s="232"/>
+      <c r="G50" s="231"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
@@ -12189,23 +12139,23 @@
       <c r="AX50" s="2"/>
       <c r="AY50" s="2"/>
       <c r="AZ50" s="2"/>
-      <c r="BA50" s="332" t="s">
-        <v>165</v>
-      </c>
-      <c r="BB50" s="332"/>
-      <c r="BC50" s="332"/>
-      <c r="BD50" s="332"/>
-      <c r="BE50" s="332"/>
-      <c r="BF50" s="332"/>
-      <c r="BG50" s="332"/>
-      <c r="BH50" s="332"/>
-      <c r="BI50" s="299"/>
-      <c r="BJ50" s="300"/>
-      <c r="BK50" s="301"/>
-      <c r="BL50" s="302"/>
-      <c r="BM50" s="303"/>
-      <c r="BN50" s="304"/>
-      <c r="BO50" s="305"/>
+      <c r="BA50" s="330" t="s">
+        <v>163</v>
+      </c>
+      <c r="BB50" s="330"/>
+      <c r="BC50" s="330"/>
+      <c r="BD50" s="330"/>
+      <c r="BE50" s="330"/>
+      <c r="BF50" s="330"/>
+      <c r="BG50" s="330"/>
+      <c r="BH50" s="330"/>
+      <c r="BI50" s="292"/>
+      <c r="BJ50" s="293"/>
+      <c r="BK50" s="294"/>
+      <c r="BL50" s="295"/>
+      <c r="BM50" s="296"/>
+      <c r="BN50" s="297"/>
+      <c r="BO50" s="298"/>
       <c r="BP50" s="2"/>
       <c r="BQ50" s="2"/>
       <c r="BR50" s="2"/>
@@ -12251,23 +12201,23 @@
       <c r="DF50" s="2"/>
     </row>
     <row r="51" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A51" s="287" t="s">
-        <v>140</v>
-      </c>
-      <c r="B51" s="231" t="s">
+      <c r="A51" s="281" t="s">
+        <v>141</v>
+      </c>
+      <c r="B51" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C51" s="281">
+      <c r="C51" s="279">
         <v>46122</v>
       </c>
-      <c r="D51" s="282">
+      <c r="D51" s="280">
         <v>1</v>
       </c>
-      <c r="E51" s="446" t="s">
-        <v>152</v>
+      <c r="E51" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F51" s="6"/>
-      <c r="G51" s="232"/>
+      <c r="G51" s="231"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
@@ -12313,23 +12263,23 @@
       <c r="AX51" s="2"/>
       <c r="AY51" s="2"/>
       <c r="AZ51" s="2"/>
-      <c r="BA51" s="332" t="s">
-        <v>166</v>
-      </c>
-      <c r="BB51" s="332"/>
-      <c r="BC51" s="332"/>
-      <c r="BD51" s="332"/>
-      <c r="BE51" s="332"/>
-      <c r="BF51" s="332"/>
-      <c r="BG51" s="332"/>
-      <c r="BH51" s="332"/>
-      <c r="BI51" s="299"/>
-      <c r="BJ51" s="300"/>
-      <c r="BK51" s="301"/>
-      <c r="BL51" s="302"/>
-      <c r="BM51" s="303"/>
-      <c r="BN51" s="304"/>
-      <c r="BO51" s="305"/>
+      <c r="BA51" s="330" t="s">
+        <v>164</v>
+      </c>
+      <c r="BB51" s="330"/>
+      <c r="BC51" s="330"/>
+      <c r="BD51" s="330"/>
+      <c r="BE51" s="330"/>
+      <c r="BF51" s="330"/>
+      <c r="BG51" s="330"/>
+      <c r="BH51" s="330"/>
+      <c r="BI51" s="292"/>
+      <c r="BJ51" s="293"/>
+      <c r="BK51" s="294"/>
+      <c r="BL51" s="295"/>
+      <c r="BM51" s="296"/>
+      <c r="BN51" s="297"/>
+      <c r="BO51" s="298"/>
       <c r="BP51" s="2"/>
       <c r="BQ51" s="2"/>
       <c r="BR51" s="2"/>
@@ -12375,23 +12325,23 @@
       <c r="DF51" s="2"/>
     </row>
     <row r="52" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A52" s="287" t="s">
-        <v>143</v>
-      </c>
-      <c r="B52" s="231" t="s">
+      <c r="A52" s="281" t="s">
+        <v>142</v>
+      </c>
+      <c r="B52" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C52" s="281">
+      <c r="C52" s="279">
         <v>46122</v>
       </c>
-      <c r="D52" s="282">
+      <c r="D52" s="280">
         <v>1</v>
       </c>
-      <c r="E52" s="446" t="s">
-        <v>151</v>
+      <c r="E52" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F52" s="6"/>
-      <c r="G52" s="232"/>
+      <c r="G52" s="231"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
@@ -12437,23 +12387,23 @@
       <c r="AX52" s="2"/>
       <c r="AY52" s="2"/>
       <c r="AZ52" s="2"/>
-      <c r="BA52" s="332" t="s">
-        <v>167</v>
-      </c>
-      <c r="BB52" s="332"/>
-      <c r="BC52" s="332"/>
-      <c r="BD52" s="332"/>
-      <c r="BE52" s="332"/>
-      <c r="BF52" s="332"/>
-      <c r="BG52" s="332"/>
-      <c r="BH52" s="332"/>
-      <c r="BI52" s="299"/>
-      <c r="BJ52" s="300"/>
-      <c r="BK52" s="301"/>
-      <c r="BL52" s="302"/>
-      <c r="BM52" s="303"/>
-      <c r="BN52" s="304"/>
-      <c r="BO52" s="305"/>
+      <c r="BA52" s="330" t="s">
+        <v>165</v>
+      </c>
+      <c r="BB52" s="330"/>
+      <c r="BC52" s="330"/>
+      <c r="BD52" s="330"/>
+      <c r="BE52" s="330"/>
+      <c r="BF52" s="330"/>
+      <c r="BG52" s="330"/>
+      <c r="BH52" s="330"/>
+      <c r="BI52" s="292"/>
+      <c r="BJ52" s="293"/>
+      <c r="BK52" s="294"/>
+      <c r="BL52" s="295"/>
+      <c r="BM52" s="296"/>
+      <c r="BN52" s="297"/>
+      <c r="BO52" s="298"/>
       <c r="BP52" s="2"/>
       <c r="BQ52" s="2"/>
       <c r="BR52" s="2"/>
@@ -12499,23 +12449,23 @@
       <c r="DF52" s="2"/>
     </row>
     <row r="53" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A53" s="287" t="s">
-        <v>144</v>
-      </c>
-      <c r="B53" s="231" t="s">
+      <c r="A53" s="281" t="s">
+        <v>143</v>
+      </c>
+      <c r="B53" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C53" s="281">
+      <c r="C53" s="279">
         <v>46122</v>
       </c>
-      <c r="D53" s="282">
+      <c r="D53" s="280">
         <v>1</v>
       </c>
-      <c r="E53" s="446" t="s">
-        <v>151</v>
+      <c r="E53" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F53" s="6"/>
-      <c r="G53" s="232"/>
+      <c r="G53" s="231"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
@@ -12561,23 +12511,23 @@
       <c r="AX53" s="2"/>
       <c r="AY53" s="2"/>
       <c r="AZ53" s="2"/>
-      <c r="BA53" s="332" t="s">
-        <v>168</v>
-      </c>
-      <c r="BB53" s="332"/>
-      <c r="BC53" s="332"/>
-      <c r="BD53" s="332"/>
-      <c r="BE53" s="332"/>
-      <c r="BF53" s="332"/>
-      <c r="BG53" s="332"/>
-      <c r="BH53" s="332"/>
-      <c r="BI53" s="299"/>
-      <c r="BJ53" s="300"/>
-      <c r="BK53" s="301"/>
-      <c r="BL53" s="302"/>
-      <c r="BM53" s="303"/>
-      <c r="BN53" s="304"/>
-      <c r="BO53" s="305"/>
+      <c r="BA53" s="330" t="s">
+        <v>166</v>
+      </c>
+      <c r="BB53" s="330"/>
+      <c r="BC53" s="330"/>
+      <c r="BD53" s="330"/>
+      <c r="BE53" s="330"/>
+      <c r="BF53" s="330"/>
+      <c r="BG53" s="330"/>
+      <c r="BH53" s="330"/>
+      <c r="BI53" s="292"/>
+      <c r="BJ53" s="293"/>
+      <c r="BK53" s="294"/>
+      <c r="BL53" s="295"/>
+      <c r="BM53" s="296"/>
+      <c r="BN53" s="297"/>
+      <c r="BO53" s="298"/>
       <c r="BP53" s="2"/>
       <c r="BQ53" s="2"/>
       <c r="BR53" s="2"/>
@@ -12623,23 +12573,23 @@
       <c r="DF53" s="2"/>
     </row>
     <row r="54" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A54" s="287" t="s">
-        <v>145</v>
-      </c>
-      <c r="B54" s="231" t="s">
+      <c r="A54" s="281" t="s">
+        <v>144</v>
+      </c>
+      <c r="B54" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C54" s="281">
+      <c r="C54" s="279">
         <v>46122</v>
       </c>
-      <c r="D54" s="282">
+      <c r="D54" s="280">
         <v>1</v>
       </c>
-      <c r="E54" s="446" t="s">
-        <v>152</v>
+      <c r="E54" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F54" s="6"/>
-      <c r="G54" s="232"/>
+      <c r="G54" s="231"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
@@ -12685,23 +12635,23 @@
       <c r="AX54" s="2"/>
       <c r="AY54" s="2"/>
       <c r="AZ54" s="2"/>
-      <c r="BA54" s="332" t="s">
-        <v>169</v>
-      </c>
-      <c r="BB54" s="332"/>
-      <c r="BC54" s="332"/>
-      <c r="BD54" s="332"/>
-      <c r="BE54" s="332"/>
-      <c r="BF54" s="332"/>
-      <c r="BG54" s="332"/>
-      <c r="BH54" s="332"/>
-      <c r="BI54" s="299"/>
-      <c r="BJ54" s="300"/>
-      <c r="BK54" s="301"/>
-      <c r="BL54" s="302"/>
-      <c r="BM54" s="303"/>
-      <c r="BN54" s="304"/>
-      <c r="BO54" s="305"/>
+      <c r="BA54" s="330" t="s">
+        <v>167</v>
+      </c>
+      <c r="BB54" s="330"/>
+      <c r="BC54" s="330"/>
+      <c r="BD54" s="330"/>
+      <c r="BE54" s="330"/>
+      <c r="BF54" s="330"/>
+      <c r="BG54" s="330"/>
+      <c r="BH54" s="330"/>
+      <c r="BI54" s="292"/>
+      <c r="BJ54" s="293"/>
+      <c r="BK54" s="294"/>
+      <c r="BL54" s="295"/>
+      <c r="BM54" s="296"/>
+      <c r="BN54" s="297"/>
+      <c r="BO54" s="298"/>
       <c r="BP54" s="2"/>
       <c r="BQ54" s="2"/>
       <c r="BR54" s="2"/>
@@ -12747,23 +12697,23 @@
       <c r="DF54" s="2"/>
     </row>
     <row r="55" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A55" s="287" t="s">
-        <v>146</v>
-      </c>
-      <c r="B55" s="231" t="s">
+      <c r="A55" s="281" t="s">
+        <v>152</v>
+      </c>
+      <c r="B55" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C55" s="281">
+      <c r="C55" s="279">
         <v>46122</v>
       </c>
-      <c r="D55" s="282">
+      <c r="D55" s="280">
         <v>1</v>
       </c>
-      <c r="E55" s="446" t="s">
-        <v>152</v>
+      <c r="E55" s="326" t="s">
+        <v>151</v>
       </c>
       <c r="F55" s="6"/>
-      <c r="G55" s="232"/>
+      <c r="G55" s="231"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
@@ -12809,23 +12759,23 @@
       <c r="AX55" s="2"/>
       <c r="AY55" s="2"/>
       <c r="AZ55" s="2"/>
-      <c r="BA55" s="332" t="s">
-        <v>170</v>
-      </c>
-      <c r="BB55" s="332"/>
-      <c r="BC55" s="332"/>
-      <c r="BD55" s="332"/>
-      <c r="BE55" s="332"/>
-      <c r="BF55" s="332"/>
-      <c r="BG55" s="332"/>
-      <c r="BH55" s="332"/>
-      <c r="BI55" s="299"/>
-      <c r="BJ55" s="300"/>
-      <c r="BK55" s="301"/>
-      <c r="BL55" s="302"/>
-      <c r="BM55" s="303"/>
-      <c r="BN55" s="304"/>
-      <c r="BO55" s="305"/>
+      <c r="BA55" s="330" t="s">
+        <v>168</v>
+      </c>
+      <c r="BB55" s="330"/>
+      <c r="BC55" s="330"/>
+      <c r="BD55" s="330"/>
+      <c r="BE55" s="330"/>
+      <c r="BF55" s="330"/>
+      <c r="BG55" s="330"/>
+      <c r="BH55" s="330"/>
+      <c r="BI55" s="292"/>
+      <c r="BJ55" s="293"/>
+      <c r="BK55" s="294"/>
+      <c r="BL55" s="295"/>
+      <c r="BM55" s="296"/>
+      <c r="BN55" s="297"/>
+      <c r="BO55" s="298"/>
       <c r="BP55" s="2"/>
       <c r="BQ55" s="2"/>
       <c r="BR55" s="2"/>
@@ -12871,23 +12821,23 @@
       <c r="DF55" s="2"/>
     </row>
     <row r="56" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A56" s="287" t="s">
-        <v>155</v>
-      </c>
-      <c r="B56" s="231" t="s">
+      <c r="A56" s="281" t="s">
+        <v>146</v>
+      </c>
+      <c r="B56" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C56" s="281">
+      <c r="C56" s="279">
         <v>46122</v>
       </c>
-      <c r="D56" s="282">
+      <c r="D56" s="280">
         <v>1</v>
       </c>
-      <c r="E56" s="446" t="s">
-        <v>153</v>
+      <c r="E56" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F56" s="6"/>
-      <c r="G56" s="232"/>
+      <c r="G56" s="231"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
@@ -12933,23 +12883,23 @@
       <c r="AX56" s="2"/>
       <c r="AY56" s="2"/>
       <c r="AZ56" s="2"/>
-      <c r="BA56" s="332" t="s">
-        <v>171</v>
-      </c>
-      <c r="BB56" s="332"/>
-      <c r="BC56" s="332"/>
-      <c r="BD56" s="332"/>
-      <c r="BE56" s="332"/>
-      <c r="BF56" s="332"/>
-      <c r="BG56" s="332"/>
-      <c r="BH56" s="332"/>
-      <c r="BI56" s="299"/>
-      <c r="BJ56" s="300"/>
-      <c r="BK56" s="301"/>
-      <c r="BL56" s="302"/>
-      <c r="BM56" s="303"/>
-      <c r="BN56" s="304"/>
-      <c r="BO56" s="305"/>
+      <c r="BA56" s="330" t="s">
+        <v>169</v>
+      </c>
+      <c r="BB56" s="330"/>
+      <c r="BC56" s="330"/>
+      <c r="BD56" s="330"/>
+      <c r="BE56" s="330"/>
+      <c r="BF56" s="330"/>
+      <c r="BG56" s="330"/>
+      <c r="BH56" s="330"/>
+      <c r="BI56" s="292"/>
+      <c r="BJ56" s="293"/>
+      <c r="BK56" s="294"/>
+      <c r="BL56" s="295"/>
+      <c r="BM56" s="296"/>
+      <c r="BN56" s="297"/>
+      <c r="BO56" s="298"/>
       <c r="BP56" s="2"/>
       <c r="BQ56" s="2"/>
       <c r="BR56" s="2"/>
@@ -12995,23 +12945,23 @@
       <c r="DF56" s="2"/>
     </row>
     <row r="57" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A57" s="287" t="s">
-        <v>148</v>
-      </c>
-      <c r="B57" s="231" t="s">
-        <v>80</v>
-      </c>
-      <c r="C57" s="281">
+      <c r="A57" s="281" t="s">
+        <v>170</v>
+      </c>
+      <c r="B57" s="290">
         <v>46122</v>
       </c>
-      <c r="D57" s="282">
+      <c r="C57" s="232" t="s">
+        <v>83</v>
+      </c>
+      <c r="D57" s="280">
         <v>1</v>
       </c>
-      <c r="E57" s="446" t="s">
-        <v>152</v>
+      <c r="E57" s="326" t="s">
+        <v>150</v>
       </c>
       <c r="F57" s="6"/>
-      <c r="G57" s="232"/>
+      <c r="G57" s="231"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
@@ -13057,24 +13007,24 @@
       <c r="AX57" s="2"/>
       <c r="AY57" s="2"/>
       <c r="AZ57" s="2"/>
-      <c r="BA57" s="332" t="s">
-        <v>172</v>
-      </c>
-      <c r="BB57" s="332"/>
-      <c r="BC57" s="332"/>
-      <c r="BD57" s="332"/>
-      <c r="BE57" s="332"/>
-      <c r="BF57" s="332"/>
-      <c r="BG57" s="332"/>
-      <c r="BH57" s="332"/>
-      <c r="BI57" s="299"/>
-      <c r="BJ57" s="300"/>
-      <c r="BK57" s="301"/>
-      <c r="BL57" s="302"/>
-      <c r="BM57" s="303"/>
-      <c r="BN57" s="304"/>
-      <c r="BO57" s="305"/>
-      <c r="BP57" s="2"/>
+      <c r="BA57" s="327"/>
+      <c r="BB57" s="327"/>
+      <c r="BC57" s="327"/>
+      <c r="BD57" s="327"/>
+      <c r="BE57" s="327"/>
+      <c r="BF57" s="327"/>
+      <c r="BG57" s="327"/>
+      <c r="BH57" s="330" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI57" s="433"/>
+      <c r="BJ57" s="433"/>
+      <c r="BK57" s="433"/>
+      <c r="BL57" s="433"/>
+      <c r="BM57" s="433"/>
+      <c r="BN57" s="433"/>
+      <c r="BO57" s="433"/>
+      <c r="BP57" s="328"/>
       <c r="BQ57" s="2"/>
       <c r="BR57" s="2"/>
       <c r="BS57" s="2"/>
@@ -13119,21 +13069,23 @@
       <c r="DF57" s="2"/>
     </row>
     <row r="58" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A58" s="447" t="s">
-        <v>175</v>
-      </c>
-      <c r="B58" s="297">
+      <c r="A58" s="281" t="s">
+        <v>171</v>
+      </c>
+      <c r="B58" s="290">
         <v>46122</v>
       </c>
-      <c r="C58" s="233" t="s">
+      <c r="C58" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D58" s="282"/>
-      <c r="E58" s="446"/>
-      <c r="F58" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="G58" s="232"/>
+      <c r="D58" s="280">
+        <v>1</v>
+      </c>
+      <c r="E58" s="326" t="s">
+        <v>150</v>
+      </c>
+      <c r="F58" s="6"/>
+      <c r="G58" s="231"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
@@ -13179,24 +13131,24 @@
       <c r="AX58" s="2"/>
       <c r="AY58" s="2"/>
       <c r="AZ58" s="2"/>
-      <c r="BA58" s="448"/>
-      <c r="BB58" s="448"/>
-      <c r="BC58" s="448"/>
-      <c r="BD58" s="448"/>
-      <c r="BE58" s="448"/>
-      <c r="BF58" s="448"/>
-      <c r="BG58" s="448"/>
-      <c r="BH58" s="430" t="s">
-        <v>189</v>
-      </c>
-      <c r="BI58" s="431"/>
-      <c r="BJ58" s="431"/>
-      <c r="BK58" s="431"/>
-      <c r="BL58" s="431"/>
-      <c r="BM58" s="431"/>
-      <c r="BN58" s="431"/>
-      <c r="BO58" s="431"/>
-      <c r="BP58" s="449"/>
+      <c r="BA58" s="327"/>
+      <c r="BB58" s="327"/>
+      <c r="BC58" s="327"/>
+      <c r="BD58" s="327"/>
+      <c r="BE58" s="327"/>
+      <c r="BF58" s="327"/>
+      <c r="BG58" s="327"/>
+      <c r="BH58" s="330" t="s">
+        <v>176</v>
+      </c>
+      <c r="BI58" s="433"/>
+      <c r="BJ58" s="433"/>
+      <c r="BK58" s="433"/>
+      <c r="BL58" s="433"/>
+      <c r="BM58" s="433"/>
+      <c r="BN58" s="433"/>
+      <c r="BO58" s="433"/>
+      <c r="BP58" s="2"/>
       <c r="BQ58" s="2"/>
       <c r="BR58" s="2"/>
       <c r="BS58" s="2"/>
@@ -13241,21 +13193,23 @@
       <c r="DF58" s="2"/>
     </row>
     <row r="59" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A59" s="447" t="s">
-        <v>177</v>
-      </c>
-      <c r="B59" s="297">
+      <c r="A59" s="281" t="s">
+        <v>188</v>
+      </c>
+      <c r="B59" s="290">
         <v>46122</v>
       </c>
-      <c r="C59" s="233" t="s">
+      <c r="C59" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D59" s="282"/>
-      <c r="E59" s="446"/>
-      <c r="F59" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="G59" s="232"/>
+      <c r="D59" s="280">
+        <v>1</v>
+      </c>
+      <c r="E59" s="326" t="s">
+        <v>150</v>
+      </c>
+      <c r="F59" s="6"/>
+      <c r="G59" s="231"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
@@ -13301,23 +13255,23 @@
       <c r="AX59" s="2"/>
       <c r="AY59" s="2"/>
       <c r="AZ59" s="2"/>
-      <c r="BA59" s="448"/>
-      <c r="BB59" s="448"/>
-      <c r="BC59" s="448"/>
-      <c r="BD59" s="448"/>
-      <c r="BE59" s="448"/>
-      <c r="BF59" s="448"/>
-      <c r="BG59" s="448"/>
-      <c r="BH59" s="430" t="s">
-        <v>190</v>
-      </c>
-      <c r="BI59" s="431"/>
-      <c r="BJ59" s="431"/>
-      <c r="BK59" s="431"/>
-      <c r="BL59" s="431"/>
-      <c r="BM59" s="431"/>
-      <c r="BN59" s="431"/>
-      <c r="BO59" s="431"/>
+      <c r="BA59" s="327"/>
+      <c r="BB59" s="327"/>
+      <c r="BC59" s="327"/>
+      <c r="BD59" s="327"/>
+      <c r="BE59" s="327"/>
+      <c r="BF59" s="327"/>
+      <c r="BG59" s="327"/>
+      <c r="BH59" s="330" t="s">
+        <v>177</v>
+      </c>
+      <c r="BI59" s="433"/>
+      <c r="BJ59" s="433"/>
+      <c r="BK59" s="433"/>
+      <c r="BL59" s="433"/>
+      <c r="BM59" s="433"/>
+      <c r="BN59" s="433"/>
+      <c r="BO59" s="433"/>
       <c r="BP59" s="2"/>
       <c r="BQ59" s="2"/>
       <c r="BR59" s="2"/>
@@ -13362,22 +13316,24 @@
       <c r="DE59" s="2"/>
       <c r="DF59" s="2"/>
     </row>
-    <row r="60" spans="1:110" ht="80" x14ac:dyDescent="0.8">
-      <c r="A60" s="447" t="s">
-        <v>178</v>
-      </c>
-      <c r="B60" s="297">
+    <row r="60" spans="1:110" x14ac:dyDescent="0.8">
+      <c r="A60" s="281" t="s">
+        <v>189</v>
+      </c>
+      <c r="B60" s="290">
         <v>46122</v>
       </c>
-      <c r="C60" s="233" t="s">
+      <c r="C60" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D60" s="282"/>
-      <c r="E60" s="446"/>
-      <c r="F60" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="G60" s="232"/>
+      <c r="D60" s="280">
+        <v>1</v>
+      </c>
+      <c r="E60" s="326" t="s">
+        <v>182</v>
+      </c>
+      <c r="F60" s="6"/>
+      <c r="G60" s="231"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
@@ -13423,23 +13379,23 @@
       <c r="AX60" s="2"/>
       <c r="AY60" s="2"/>
       <c r="AZ60" s="2"/>
-      <c r="BA60" s="448"/>
-      <c r="BB60" s="448"/>
-      <c r="BC60" s="448"/>
-      <c r="BD60" s="448"/>
-      <c r="BE60" s="448"/>
-      <c r="BF60" s="448"/>
-      <c r="BG60" s="448"/>
-      <c r="BH60" s="430" t="s">
-        <v>191</v>
-      </c>
-      <c r="BI60" s="431"/>
-      <c r="BJ60" s="431"/>
-      <c r="BK60" s="431"/>
-      <c r="BL60" s="431"/>
-      <c r="BM60" s="431"/>
-      <c r="BN60" s="431"/>
-      <c r="BO60" s="431"/>
+      <c r="BA60" s="327"/>
+      <c r="BB60" s="327"/>
+      <c r="BC60" s="327"/>
+      <c r="BD60" s="327"/>
+      <c r="BE60" s="327"/>
+      <c r="BF60" s="327"/>
+      <c r="BG60" s="327"/>
+      <c r="BH60" s="330" t="s">
+        <v>178</v>
+      </c>
+      <c r="BI60" s="433"/>
+      <c r="BJ60" s="433"/>
+      <c r="BK60" s="433"/>
+      <c r="BL60" s="433"/>
+      <c r="BM60" s="433"/>
+      <c r="BN60" s="433"/>
+      <c r="BO60" s="433"/>
       <c r="BP60" s="2"/>
       <c r="BQ60" s="2"/>
       <c r="BR60" s="2"/>
@@ -13484,22 +13440,24 @@
       <c r="DE60" s="2"/>
       <c r="DF60" s="2"/>
     </row>
-    <row r="61" spans="1:110" ht="48" x14ac:dyDescent="0.8">
-      <c r="A61" s="447" t="s">
-        <v>180</v>
-      </c>
-      <c r="B61" s="297">
+    <row r="61" spans="1:110" ht="53.25" customHeight="1" x14ac:dyDescent="0.8">
+      <c r="A61" s="323" t="s">
+        <v>172</v>
+      </c>
+      <c r="B61" s="290">
         <v>46122</v>
       </c>
-      <c r="C61" s="233" t="s">
+      <c r="C61" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D61" s="282"/>
-      <c r="E61" s="446"/>
+      <c r="D61" s="280">
+        <v>0.95</v>
+      </c>
+      <c r="E61" s="326"/>
       <c r="F61" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="G61" s="232"/>
+        <v>173</v>
+      </c>
+      <c r="G61" s="231"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
@@ -13545,23 +13503,23 @@
       <c r="AX61" s="2"/>
       <c r="AY61" s="2"/>
       <c r="AZ61" s="2"/>
-      <c r="BA61" s="448"/>
-      <c r="BB61" s="448"/>
-      <c r="BC61" s="448"/>
-      <c r="BD61" s="448"/>
-      <c r="BE61" s="448"/>
-      <c r="BF61" s="448"/>
-      <c r="BG61" s="448"/>
-      <c r="BH61" s="430" t="s">
-        <v>192</v>
-      </c>
-      <c r="BI61" s="431"/>
-      <c r="BJ61" s="431"/>
-      <c r="BK61" s="431"/>
-      <c r="BL61" s="431"/>
-      <c r="BM61" s="431"/>
-      <c r="BN61" s="431"/>
-      <c r="BO61" s="431"/>
+      <c r="BA61" s="327"/>
+      <c r="BB61" s="327"/>
+      <c r="BC61" s="327"/>
+      <c r="BD61" s="327"/>
+      <c r="BE61" s="327"/>
+      <c r="BF61" s="327"/>
+      <c r="BG61" s="327"/>
+      <c r="BH61" s="331" t="s">
+        <v>179</v>
+      </c>
+      <c r="BI61" s="436"/>
+      <c r="BJ61" s="436"/>
+      <c r="BK61" s="436"/>
+      <c r="BL61" s="436"/>
+      <c r="BM61" s="436"/>
+      <c r="BN61" s="436"/>
+      <c r="BO61" s="436"/>
       <c r="BP61" s="2"/>
       <c r="BQ61" s="2"/>
       <c r="BR61" s="2"/>
@@ -13607,21 +13565,23 @@
       <c r="DF61" s="2"/>
     </row>
     <row r="62" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A62" s="447" t="s">
-        <v>182</v>
-      </c>
-      <c r="B62" s="297">
+      <c r="A62" s="281" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" s="290">
         <v>46122</v>
       </c>
-      <c r="C62" s="233" t="s">
+      <c r="C62" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D62" s="282"/>
-      <c r="E62" s="446"/>
-      <c r="F62" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="G62" s="232"/>
+      <c r="D62" s="280">
+        <v>1</v>
+      </c>
+      <c r="E62" s="326" t="s">
+        <v>151</v>
+      </c>
+      <c r="F62" s="6"/>
+      <c r="G62" s="231"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
@@ -13667,23 +13627,23 @@
       <c r="AX62" s="2"/>
       <c r="AY62" s="2"/>
       <c r="AZ62" s="2"/>
-      <c r="BA62" s="448"/>
-      <c r="BB62" s="448"/>
-      <c r="BC62" s="448"/>
-      <c r="BD62" s="448"/>
-      <c r="BE62" s="448"/>
-      <c r="BF62" s="448"/>
-      <c r="BG62" s="448"/>
-      <c r="BH62" s="430" t="s">
-        <v>193</v>
-      </c>
-      <c r="BI62" s="431"/>
-      <c r="BJ62" s="431"/>
-      <c r="BK62" s="431"/>
-      <c r="BL62" s="431"/>
-      <c r="BM62" s="431"/>
-      <c r="BN62" s="431"/>
-      <c r="BO62" s="431"/>
+      <c r="BA62" s="327"/>
+      <c r="BB62" s="327"/>
+      <c r="BC62" s="327"/>
+      <c r="BD62" s="327"/>
+      <c r="BE62" s="327"/>
+      <c r="BF62" s="327"/>
+      <c r="BG62" s="327"/>
+      <c r="BH62" s="330" t="s">
+        <v>196</v>
+      </c>
+      <c r="BI62" s="330"/>
+      <c r="BJ62" s="330"/>
+      <c r="BK62" s="330"/>
+      <c r="BL62" s="330"/>
+      <c r="BM62" s="330"/>
+      <c r="BN62" s="330"/>
+      <c r="BO62" s="330"/>
       <c r="BP62" s="2"/>
       <c r="BQ62" s="2"/>
       <c r="BR62" s="2"/>
@@ -13729,21 +13689,23 @@
       <c r="DF62" s="2"/>
     </row>
     <row r="63" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A63" s="447" t="s">
-        <v>184</v>
-      </c>
-      <c r="B63" s="297">
+      <c r="A63" s="281" t="s">
+        <v>186</v>
+      </c>
+      <c r="B63" s="290">
         <v>46122</v>
       </c>
-      <c r="C63" s="233" t="s">
+      <c r="C63" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D63" s="282"/>
-      <c r="E63" s="446"/>
-      <c r="F63" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="G63" s="232"/>
+      <c r="D63" s="280">
+        <v>1</v>
+      </c>
+      <c r="E63" s="326" t="s">
+        <v>150</v>
+      </c>
+      <c r="F63" s="6"/>
+      <c r="G63" s="231"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
@@ -13789,23 +13751,23 @@
       <c r="AX63" s="2"/>
       <c r="AY63" s="2"/>
       <c r="AZ63" s="2"/>
-      <c r="BA63" s="448"/>
-      <c r="BB63" s="448"/>
-      <c r="BC63" s="448"/>
-      <c r="BD63" s="448"/>
-      <c r="BE63" s="448"/>
-      <c r="BF63" s="448"/>
-      <c r="BG63" s="448"/>
-      <c r="BH63" s="430" t="s">
-        <v>194</v>
-      </c>
-      <c r="BI63" s="431"/>
-      <c r="BJ63" s="431"/>
-      <c r="BK63" s="431"/>
-      <c r="BL63" s="431"/>
-      <c r="BM63" s="431"/>
-      <c r="BN63" s="431"/>
-      <c r="BO63" s="431"/>
+      <c r="BA63" s="327"/>
+      <c r="BB63" s="327"/>
+      <c r="BC63" s="327"/>
+      <c r="BD63" s="327"/>
+      <c r="BE63" s="327"/>
+      <c r="BF63" s="327"/>
+      <c r="BG63" s="327"/>
+      <c r="BH63" s="330" t="s">
+        <v>197</v>
+      </c>
+      <c r="BI63" s="330"/>
+      <c r="BJ63" s="330"/>
+      <c r="BK63" s="330"/>
+      <c r="BL63" s="330"/>
+      <c r="BM63" s="330"/>
+      <c r="BN63" s="330"/>
+      <c r="BO63" s="330"/>
       <c r="BP63" s="2"/>
       <c r="BQ63" s="2"/>
       <c r="BR63" s="2"/>
@@ -13851,21 +13813,23 @@
       <c r="DF63" s="2"/>
     </row>
     <row r="64" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A64" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B64" s="297">
+      <c r="A64" s="281" t="s">
+        <v>185</v>
+      </c>
+      <c r="B64" s="290">
         <v>46122</v>
       </c>
-      <c r="C64" s="233" t="s">
+      <c r="C64" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D64" s="234"/>
-      <c r="E64" s="234"/>
-      <c r="F64" s="235"/>
-      <c r="G64" s="236" t="s">
-        <v>0</v>
-      </c>
+      <c r="D64" s="280">
+        <v>1</v>
+      </c>
+      <c r="E64" s="326" t="s">
+        <v>150</v>
+      </c>
+      <c r="F64" s="6"/>
+      <c r="G64" s="231"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
@@ -13911,23 +13875,23 @@
       <c r="AX64" s="2"/>
       <c r="AY64" s="2"/>
       <c r="AZ64" s="2"/>
-      <c r="BA64" s="150"/>
-      <c r="BB64" s="306"/>
-      <c r="BC64" s="307"/>
-      <c r="BD64" s="308"/>
-      <c r="BE64" s="309"/>
-      <c r="BF64" s="310"/>
-      <c r="BG64" s="311"/>
-      <c r="BH64" s="430" t="s">
-        <v>195</v>
-      </c>
-      <c r="BI64" s="431"/>
-      <c r="BJ64" s="431"/>
-      <c r="BK64" s="431"/>
-      <c r="BL64" s="431"/>
-      <c r="BM64" s="431"/>
-      <c r="BN64" s="431"/>
-      <c r="BO64" s="431"/>
+      <c r="BA64" s="327"/>
+      <c r="BB64" s="327"/>
+      <c r="BC64" s="327"/>
+      <c r="BD64" s="327"/>
+      <c r="BE64" s="327"/>
+      <c r="BF64" s="327"/>
+      <c r="BG64" s="327"/>
+      <c r="BH64" s="330" t="s">
+        <v>198</v>
+      </c>
+      <c r="BI64" s="330"/>
+      <c r="BJ64" s="330"/>
+      <c r="BK64" s="330"/>
+      <c r="BL64" s="330"/>
+      <c r="BM64" s="330"/>
+      <c r="BN64" s="330"/>
+      <c r="BO64" s="330"/>
       <c r="BP64" s="2"/>
       <c r="BQ64" s="2"/>
       <c r="BR64" s="2"/>
@@ -13973,21 +13937,23 @@
       <c r="DF64" s="2"/>
     </row>
     <row r="65" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A65" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B65" s="298">
-        <v>46129</v>
-      </c>
-      <c r="C65" s="237" t="s">
-        <v>85</v>
-      </c>
-      <c r="D65" s="237"/>
-      <c r="E65" s="237"/>
-      <c r="F65" s="238"/>
-      <c r="G65" s="239" t="s">
-        <v>0</v>
-      </c>
+      <c r="A65" s="281" t="s">
+        <v>184</v>
+      </c>
+      <c r="B65" s="290">
+        <v>46122</v>
+      </c>
+      <c r="C65" s="232" t="s">
+        <v>83</v>
+      </c>
+      <c r="D65" s="280">
+        <v>1</v>
+      </c>
+      <c r="E65" s="326" t="s">
+        <v>150</v>
+      </c>
+      <c r="F65" s="6"/>
+      <c r="G65" s="231"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
@@ -14033,29 +13999,29 @@
       <c r="AX65" s="2"/>
       <c r="AY65" s="2"/>
       <c r="AZ65" s="2"/>
-      <c r="BA65" s="2"/>
-      <c r="BB65" s="2"/>
-      <c r="BC65" s="2"/>
-      <c r="BD65" s="2"/>
-      <c r="BE65" s="312"/>
-      <c r="BF65" s="313"/>
-      <c r="BG65" s="314"/>
-      <c r="BH65" s="315"/>
-      <c r="BI65" s="316"/>
-      <c r="BJ65" s="317"/>
-      <c r="BK65" s="318"/>
-      <c r="BL65" s="319"/>
-      <c r="BM65" s="320"/>
-      <c r="BN65" s="2"/>
-      <c r="BO65" s="429" t="s">
-        <v>127</v>
-      </c>
-      <c r="BP65" s="429"/>
-      <c r="BQ65" s="429"/>
-      <c r="BR65" s="429"/>
-      <c r="BS65" s="429"/>
-      <c r="BT65" s="429"/>
-      <c r="BU65" s="429"/>
+      <c r="BA65" s="327"/>
+      <c r="BB65" s="327"/>
+      <c r="BC65" s="327"/>
+      <c r="BD65" s="327"/>
+      <c r="BE65" s="327"/>
+      <c r="BF65" s="327"/>
+      <c r="BG65" s="327"/>
+      <c r="BH65" s="330" t="s">
+        <v>199</v>
+      </c>
+      <c r="BI65" s="330"/>
+      <c r="BJ65" s="330"/>
+      <c r="BK65" s="330"/>
+      <c r="BL65" s="330"/>
+      <c r="BM65" s="330"/>
+      <c r="BN65" s="330"/>
+      <c r="BO65" s="330"/>
+      <c r="BP65" s="2"/>
+      <c r="BQ65" s="2"/>
+      <c r="BR65" s="2"/>
+      <c r="BS65" s="2"/>
+      <c r="BT65" s="2"/>
+      <c r="BU65" s="2"/>
       <c r="BV65" s="2"/>
       <c r="BW65" s="2"/>
       <c r="BX65" s="2"/>
@@ -14095,21 +14061,23 @@
       <c r="DF65" s="2"/>
     </row>
     <row r="66" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A66" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B66" s="298">
-        <v>46129</v>
-      </c>
-      <c r="C66" s="237" t="s">
-        <v>85</v>
-      </c>
-      <c r="D66" s="240"/>
-      <c r="E66" s="240"/>
-      <c r="F66" s="241"/>
-      <c r="G66" s="242" t="s">
-        <v>0</v>
-      </c>
+      <c r="A66" s="281" t="s">
+        <v>183</v>
+      </c>
+      <c r="B66" s="290">
+        <v>46122</v>
+      </c>
+      <c r="C66" s="232" t="s">
+        <v>83</v>
+      </c>
+      <c r="D66" s="280">
+        <v>1</v>
+      </c>
+      <c r="E66" s="326" t="s">
+        <v>150</v>
+      </c>
+      <c r="F66" s="6"/>
+      <c r="G66" s="231"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
@@ -14155,30 +14123,30 @@
       <c r="AX66" s="2"/>
       <c r="AY66" s="2"/>
       <c r="AZ66" s="2"/>
-      <c r="BA66" s="2"/>
-      <c r="BB66" s="2"/>
-      <c r="BC66" s="2"/>
-      <c r="BD66" s="2"/>
-      <c r="BE66" s="2"/>
-      <c r="BF66" s="2"/>
-      <c r="BG66" s="2"/>
-      <c r="BH66" s="2"/>
-      <c r="BI66" s="2"/>
-      <c r="BJ66" s="2"/>
-      <c r="BK66" s="2"/>
-      <c r="BL66" s="321"/>
-      <c r="BM66" s="322"/>
-      <c r="BN66" s="323"/>
-      <c r="BO66" s="429" t="s">
-        <v>196</v>
-      </c>
-      <c r="BP66" s="429"/>
-      <c r="BQ66" s="429"/>
-      <c r="BR66" s="429"/>
-      <c r="BS66" s="429"/>
-      <c r="BT66" s="429"/>
-      <c r="BU66" s="429"/>
-      <c r="BV66" s="324"/>
+      <c r="BA66" s="327"/>
+      <c r="BB66" s="327"/>
+      <c r="BC66" s="327"/>
+      <c r="BD66" s="327"/>
+      <c r="BE66" s="327"/>
+      <c r="BF66" s="327"/>
+      <c r="BG66" s="327"/>
+      <c r="BH66" s="330" t="s">
+        <v>200</v>
+      </c>
+      <c r="BI66" s="330"/>
+      <c r="BJ66" s="330"/>
+      <c r="BK66" s="330"/>
+      <c r="BL66" s="330"/>
+      <c r="BM66" s="330"/>
+      <c r="BN66" s="330"/>
+      <c r="BO66" s="330"/>
+      <c r="BP66" s="2"/>
+      <c r="BQ66" s="2"/>
+      <c r="BR66" s="2"/>
+      <c r="BS66" s="2"/>
+      <c r="BT66" s="2"/>
+      <c r="BU66" s="2"/>
+      <c r="BV66" s="2"/>
       <c r="BW66" s="2"/>
       <c r="BX66" s="2"/>
       <c r="BY66" s="2"/>
@@ -14217,15 +14185,61 @@
       <c r="DF66" s="2"/>
     </row>
     <row r="67" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="281" t="s">
         <v>187</v>
       </c>
-      <c r="B67" s="298">
-        <v>46129</v>
-      </c>
-      <c r="C67" s="237" t="s">
-        <v>85</v>
-      </c>
+      <c r="B67" s="290">
+        <v>46122</v>
+      </c>
+      <c r="C67" s="232" t="s">
+        <v>83</v>
+      </c>
+      <c r="D67" s="280">
+        <v>1</v>
+      </c>
+      <c r="E67" s="326" t="s">
+        <v>182</v>
+      </c>
+      <c r="F67" s="6"/>
+      <c r="G67" s="231"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2"/>
+      <c r="R67" s="2"/>
+      <c r="S67" s="2"/>
+      <c r="T67" s="2"/>
+      <c r="U67" s="2"/>
+      <c r="V67" s="2"/>
+      <c r="W67" s="2"/>
+      <c r="X67" s="2"/>
+      <c r="Y67" s="2"/>
+      <c r="Z67" s="2"/>
+      <c r="AA67" s="2"/>
+      <c r="AB67" s="2"/>
+      <c r="AC67" s="2"/>
+      <c r="AD67" s="2"/>
+      <c r="AE67" s="2"/>
+      <c r="AF67" s="2"/>
+      <c r="AG67" s="2"/>
+      <c r="AH67" s="2"/>
+      <c r="AI67" s="2"/>
+      <c r="AJ67" s="2"/>
+      <c r="AK67" s="2"/>
+      <c r="AL67" s="2"/>
+      <c r="AM67" s="2"/>
+      <c r="AN67" s="2"/>
+      <c r="AO67" s="2"/>
+      <c r="AP67" s="2"/>
+      <c r="AQ67" s="2"/>
+      <c r="AR67" s="2"/>
+      <c r="AS67" s="2"/>
       <c r="AT67" s="2"/>
       <c r="AU67" s="2"/>
       <c r="AV67" s="2"/>
@@ -14233,30 +14247,30 @@
       <c r="AX67" s="2"/>
       <c r="AY67" s="2"/>
       <c r="AZ67" s="2"/>
-      <c r="BA67" s="2"/>
-      <c r="BB67" s="2"/>
-      <c r="BC67" s="2"/>
-      <c r="BD67" s="2"/>
-      <c r="BE67" s="2"/>
-      <c r="BF67" s="2"/>
-      <c r="BG67" s="2"/>
-      <c r="BH67" s="2"/>
-      <c r="BI67" s="2"/>
-      <c r="BJ67" s="2"/>
-      <c r="BK67" s="2"/>
-      <c r="BL67" s="150"/>
-      <c r="BM67" s="325"/>
-      <c r="BN67" s="326"/>
-      <c r="BO67" s="429" t="s">
-        <v>197</v>
-      </c>
-      <c r="BP67" s="429"/>
-      <c r="BQ67" s="429"/>
-      <c r="BR67" s="429"/>
-      <c r="BS67" s="429"/>
-      <c r="BT67" s="429"/>
-      <c r="BU67" s="429"/>
-      <c r="BV67" s="327"/>
+      <c r="BA67" s="327"/>
+      <c r="BB67" s="327"/>
+      <c r="BC67" s="327"/>
+      <c r="BD67" s="327"/>
+      <c r="BE67" s="327"/>
+      <c r="BF67" s="327"/>
+      <c r="BG67" s="327"/>
+      <c r="BH67" s="330" t="s">
+        <v>201</v>
+      </c>
+      <c r="BI67" s="330"/>
+      <c r="BJ67" s="330"/>
+      <c r="BK67" s="330"/>
+      <c r="BL67" s="330"/>
+      <c r="BM67" s="330"/>
+      <c r="BN67" s="330"/>
+      <c r="BO67" s="330"/>
+      <c r="BP67" s="2"/>
+      <c r="BQ67" s="2"/>
+      <c r="BR67" s="2"/>
+      <c r="BS67" s="2"/>
+      <c r="BT67" s="2"/>
+      <c r="BU67" s="2"/>
+      <c r="BV67" s="2"/>
       <c r="BW67" s="2"/>
       <c r="BX67" s="2"/>
       <c r="BY67" s="2"/>
@@ -14294,58 +14308,1204 @@
       <c r="DE67" s="2"/>
       <c r="DF67" s="2"/>
     </row>
+    <row r="68" spans="1:110" x14ac:dyDescent="0.8">
+      <c r="A68" s="281" t="s">
+        <v>190</v>
+      </c>
+      <c r="B68" s="290">
+        <v>46122</v>
+      </c>
+      <c r="C68" s="232" t="s">
+        <v>83</v>
+      </c>
+      <c r="D68" s="280">
+        <v>1</v>
+      </c>
+      <c r="E68" s="326" t="s">
+        <v>182</v>
+      </c>
+      <c r="F68" s="6"/>
+      <c r="G68" s="231"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="2"/>
+      <c r="T68" s="2"/>
+      <c r="U68" s="2"/>
+      <c r="V68" s="2"/>
+      <c r="W68" s="2"/>
+      <c r="X68" s="2"/>
+      <c r="Y68" s="2"/>
+      <c r="Z68" s="2"/>
+      <c r="AA68" s="2"/>
+      <c r="AB68" s="2"/>
+      <c r="AC68" s="2"/>
+      <c r="AD68" s="2"/>
+      <c r="AE68" s="2"/>
+      <c r="AF68" s="2"/>
+      <c r="AG68" s="2"/>
+      <c r="AH68" s="2"/>
+      <c r="AI68" s="2"/>
+      <c r="AJ68" s="2"/>
+      <c r="AK68" s="2"/>
+      <c r="AL68" s="2"/>
+      <c r="AM68" s="2"/>
+      <c r="AN68" s="2"/>
+      <c r="AO68" s="2"/>
+      <c r="AP68" s="2"/>
+      <c r="AQ68" s="2"/>
+      <c r="AR68" s="2"/>
+      <c r="AS68" s="2"/>
+      <c r="AT68" s="2"/>
+      <c r="AU68" s="2"/>
+      <c r="AV68" s="2"/>
+      <c r="AW68" s="2"/>
+      <c r="AX68" s="2"/>
+      <c r="AY68" s="2"/>
+      <c r="AZ68" s="2"/>
+      <c r="BA68" s="327"/>
+      <c r="BB68" s="327"/>
+      <c r="BC68" s="327"/>
+      <c r="BD68" s="327"/>
+      <c r="BE68" s="327"/>
+      <c r="BF68" s="327"/>
+      <c r="BG68" s="327"/>
+      <c r="BH68" s="330" t="s">
+        <v>202</v>
+      </c>
+      <c r="BI68" s="330"/>
+      <c r="BJ68" s="330"/>
+      <c r="BK68" s="330"/>
+      <c r="BL68" s="330"/>
+      <c r="BM68" s="330"/>
+      <c r="BN68" s="330"/>
+      <c r="BO68" s="330"/>
+      <c r="BP68" s="2"/>
+      <c r="BQ68" s="2"/>
+      <c r="BR68" s="2"/>
+      <c r="BS68" s="2"/>
+      <c r="BT68" s="2"/>
+      <c r="BU68" s="2"/>
+      <c r="BV68" s="2"/>
+      <c r="BW68" s="2"/>
+      <c r="BX68" s="2"/>
+      <c r="BY68" s="2"/>
+      <c r="BZ68" s="2"/>
+      <c r="CA68" s="2"/>
+      <c r="CB68" s="2"/>
+      <c r="CC68" s="2"/>
+      <c r="CD68" s="2"/>
+      <c r="CE68" s="2"/>
+      <c r="CF68" s="2"/>
+      <c r="CG68" s="2"/>
+      <c r="CH68" s="2"/>
+      <c r="CI68" s="2"/>
+      <c r="CJ68" s="2"/>
+      <c r="CK68" s="2"/>
+      <c r="CL68" s="2"/>
+      <c r="CM68" s="2"/>
+      <c r="CN68" s="2"/>
+      <c r="CO68" s="2"/>
+      <c r="CP68" s="2"/>
+      <c r="CQ68" s="2"/>
+      <c r="CR68" s="2"/>
+      <c r="CS68" s="2"/>
+      <c r="CT68" s="2"/>
+      <c r="CU68" s="2"/>
+      <c r="CV68" s="2"/>
+      <c r="CW68" s="2"/>
+      <c r="CX68" s="2"/>
+      <c r="CY68" s="2"/>
+      <c r="CZ68" s="2"/>
+      <c r="DA68" s="2"/>
+      <c r="DB68" s="2"/>
+      <c r="DC68" s="2"/>
+      <c r="DD68" s="2"/>
+      <c r="DE68" s="2"/>
+      <c r="DF68" s="2"/>
+    </row>
+    <row r="69" spans="1:110" x14ac:dyDescent="0.8">
+      <c r="A69" s="281" t="s">
+        <v>126</v>
+      </c>
+      <c r="B69" s="290">
+        <v>46122</v>
+      </c>
+      <c r="C69" s="232" t="s">
+        <v>83</v>
+      </c>
+      <c r="D69" s="326">
+        <v>1</v>
+      </c>
+      <c r="E69" s="435" t="s">
+        <v>151</v>
+      </c>
+      <c r="F69" s="233"/>
+      <c r="G69" s="234" t="s">
+        <v>0</v>
+      </c>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" s="2"/>
+      <c r="Q69" s="2"/>
+      <c r="R69" s="2"/>
+      <c r="S69" s="2"/>
+      <c r="T69" s="2"/>
+      <c r="U69" s="2"/>
+      <c r="V69" s="2"/>
+      <c r="W69" s="2"/>
+      <c r="X69" s="2"/>
+      <c r="Y69" s="2"/>
+      <c r="Z69" s="2"/>
+      <c r="AA69" s="2"/>
+      <c r="AB69" s="2"/>
+      <c r="AC69" s="2"/>
+      <c r="AD69" s="2"/>
+      <c r="AE69" s="2"/>
+      <c r="AF69" s="2"/>
+      <c r="AG69" s="2"/>
+      <c r="AH69" s="2"/>
+      <c r="AI69" s="2"/>
+      <c r="AJ69" s="2"/>
+      <c r="AK69" s="2"/>
+      <c r="AL69" s="2"/>
+      <c r="AM69" s="2"/>
+      <c r="AN69" s="2"/>
+      <c r="AO69" s="2"/>
+      <c r="AP69" s="2"/>
+      <c r="AQ69" s="2"/>
+      <c r="AR69" s="2"/>
+      <c r="AS69" s="2"/>
+      <c r="AT69" s="2"/>
+      <c r="AU69" s="2"/>
+      <c r="AV69" s="2"/>
+      <c r="AW69" s="2"/>
+      <c r="AX69" s="2"/>
+      <c r="AY69" s="2"/>
+      <c r="AZ69" s="2"/>
+      <c r="BA69" s="150"/>
+      <c r="BB69" s="299"/>
+      <c r="BC69" s="300"/>
+      <c r="BD69" s="301"/>
+      <c r="BE69" s="302"/>
+      <c r="BF69" s="303"/>
+      <c r="BG69" s="304"/>
+      <c r="BH69" s="330" t="s">
+        <v>180</v>
+      </c>
+      <c r="BI69" s="433"/>
+      <c r="BJ69" s="433"/>
+      <c r="BK69" s="433"/>
+      <c r="BL69" s="433"/>
+      <c r="BM69" s="433"/>
+      <c r="BN69" s="433"/>
+      <c r="BO69" s="433"/>
+      <c r="BP69" s="2"/>
+      <c r="BQ69" s="2"/>
+      <c r="BR69" s="2"/>
+      <c r="BS69" s="2"/>
+      <c r="BT69" s="2"/>
+      <c r="BU69" s="2"/>
+      <c r="BV69" s="2"/>
+      <c r="BW69" s="2"/>
+      <c r="BX69" s="2"/>
+      <c r="BY69" s="2"/>
+      <c r="BZ69" s="2"/>
+      <c r="CA69" s="2"/>
+      <c r="CB69" s="2"/>
+      <c r="CC69" s="2"/>
+      <c r="CD69" s="2"/>
+      <c r="CE69" s="2"/>
+      <c r="CF69" s="2"/>
+      <c r="CG69" s="2"/>
+      <c r="CH69" s="2"/>
+      <c r="CI69" s="2"/>
+      <c r="CJ69" s="2"/>
+      <c r="CK69" s="2"/>
+      <c r="CL69" s="2"/>
+      <c r="CM69" s="2"/>
+      <c r="CN69" s="2"/>
+      <c r="CO69" s="2"/>
+      <c r="CP69" s="2"/>
+      <c r="CQ69" s="2"/>
+      <c r="CR69" s="2"/>
+      <c r="CS69" s="2"/>
+      <c r="CT69" s="2"/>
+      <c r="CU69" s="2"/>
+      <c r="CV69" s="2"/>
+      <c r="CW69" s="2"/>
+      <c r="CX69" s="2"/>
+      <c r="CY69" s="2"/>
+      <c r="CZ69" s="2"/>
+      <c r="DA69" s="2"/>
+      <c r="DB69" s="2"/>
+      <c r="DC69" s="2"/>
+      <c r="DD69" s="2"/>
+      <c r="DE69" s="2"/>
+      <c r="DF69" s="2"/>
+    </row>
+    <row r="70" spans="1:110" x14ac:dyDescent="0.8">
+      <c r="A70" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B70" s="291">
+        <v>46129</v>
+      </c>
+      <c r="C70" s="431">
+        <v>46134</v>
+      </c>
+      <c r="D70" s="235"/>
+      <c r="E70" s="235"/>
+      <c r="F70" s="236"/>
+      <c r="G70" s="237" t="s">
+        <v>0</v>
+      </c>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
+      <c r="R70" s="2"/>
+      <c r="S70" s="2"/>
+      <c r="T70" s="2"/>
+      <c r="U70" s="2"/>
+      <c r="V70" s="2"/>
+      <c r="W70" s="2"/>
+      <c r="X70" s="2"/>
+      <c r="Y70" s="2"/>
+      <c r="Z70" s="2"/>
+      <c r="AA70" s="2"/>
+      <c r="AB70" s="2"/>
+      <c r="AC70" s="2"/>
+      <c r="AD70" s="2"/>
+      <c r="AE70" s="2"/>
+      <c r="AF70" s="2"/>
+      <c r="AG70" s="2"/>
+      <c r="AH70" s="2"/>
+      <c r="AI70" s="2"/>
+      <c r="AJ70" s="2"/>
+      <c r="AK70" s="2"/>
+      <c r="AL70" s="2"/>
+      <c r="AM70" s="2"/>
+      <c r="AN70" s="2"/>
+      <c r="AO70" s="2"/>
+      <c r="AP70" s="2"/>
+      <c r="AQ70" s="2"/>
+      <c r="AR70" s="2"/>
+      <c r="AS70" s="2"/>
+      <c r="AT70" s="2"/>
+      <c r="AU70" s="2"/>
+      <c r="AV70" s="2"/>
+      <c r="AW70" s="2"/>
+      <c r="AX70" s="2"/>
+      <c r="AY70" s="2"/>
+      <c r="AZ70" s="2"/>
+      <c r="BA70" s="2"/>
+      <c r="BB70" s="2"/>
+      <c r="BC70" s="2"/>
+      <c r="BD70" s="2"/>
+      <c r="BE70" s="305"/>
+      <c r="BF70" s="306"/>
+      <c r="BG70" s="307"/>
+      <c r="BH70" s="308"/>
+      <c r="BI70" s="309"/>
+      <c r="BJ70" s="310"/>
+      <c r="BK70" s="311"/>
+      <c r="BL70" s="312"/>
+      <c r="BM70" s="313"/>
+      <c r="BN70" s="2"/>
+      <c r="BO70" s="329" t="s">
+        <v>195</v>
+      </c>
+      <c r="BP70" s="329"/>
+      <c r="BQ70" s="329"/>
+      <c r="BR70" s="329"/>
+      <c r="BS70" s="329"/>
+      <c r="BT70" s="434"/>
+      <c r="BU70" s="434"/>
+      <c r="BV70" s="2"/>
+      <c r="BW70" s="2"/>
+      <c r="BX70" s="2"/>
+      <c r="BY70" s="2"/>
+      <c r="BZ70" s="2"/>
+      <c r="CA70" s="2"/>
+      <c r="CB70" s="2"/>
+      <c r="CC70" s="2"/>
+      <c r="CD70" s="2"/>
+      <c r="CE70" s="2"/>
+      <c r="CF70" s="2"/>
+      <c r="CG70" s="2"/>
+      <c r="CH70" s="2"/>
+      <c r="CI70" s="2"/>
+      <c r="CJ70" s="2"/>
+      <c r="CK70" s="2"/>
+      <c r="CL70" s="2"/>
+      <c r="CM70" s="2"/>
+      <c r="CN70" s="2"/>
+      <c r="CO70" s="2"/>
+      <c r="CP70" s="2"/>
+      <c r="CQ70" s="2"/>
+      <c r="CR70" s="2"/>
+      <c r="CS70" s="2"/>
+      <c r="CT70" s="2"/>
+      <c r="CU70" s="2"/>
+      <c r="CV70" s="2"/>
+      <c r="CW70" s="2"/>
+      <c r="CX70" s="2"/>
+      <c r="CY70" s="2"/>
+      <c r="CZ70" s="2"/>
+      <c r="DA70" s="2"/>
+      <c r="DB70" s="2"/>
+      <c r="DC70" s="2"/>
+      <c r="DD70" s="2"/>
+      <c r="DE70" s="2"/>
+      <c r="DF70" s="2"/>
+    </row>
+    <row r="71" spans="1:110" x14ac:dyDescent="0.8">
+      <c r="A71" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B71" s="291">
+        <v>46129</v>
+      </c>
+      <c r="C71" s="235" t="s">
+        <v>85</v>
+      </c>
+      <c r="D71" s="235"/>
+      <c r="E71" s="235"/>
+      <c r="F71" s="236"/>
+      <c r="G71" s="237"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2"/>
+      <c r="R71" s="2"/>
+      <c r="S71" s="2"/>
+      <c r="T71" s="2"/>
+      <c r="U71" s="2"/>
+      <c r="V71" s="2"/>
+      <c r="W71" s="2"/>
+      <c r="X71" s="2"/>
+      <c r="Y71" s="2"/>
+      <c r="Z71" s="2"/>
+      <c r="AA71" s="2"/>
+      <c r="AB71" s="2"/>
+      <c r="AC71" s="2"/>
+      <c r="AD71" s="2"/>
+      <c r="AE71" s="2"/>
+      <c r="AF71" s="2"/>
+      <c r="AG71" s="2"/>
+      <c r="AH71" s="2"/>
+      <c r="AI71" s="2"/>
+      <c r="AJ71" s="2"/>
+      <c r="AK71" s="2"/>
+      <c r="AL71" s="2"/>
+      <c r="AM71" s="2"/>
+      <c r="AN71" s="2"/>
+      <c r="AO71" s="2"/>
+      <c r="AP71" s="2"/>
+      <c r="AQ71" s="2"/>
+      <c r="AR71" s="2"/>
+      <c r="AS71" s="2"/>
+      <c r="AT71" s="2"/>
+      <c r="AU71" s="2"/>
+      <c r="AV71" s="2"/>
+      <c r="AW71" s="2"/>
+      <c r="AX71" s="2"/>
+      <c r="AY71" s="2"/>
+      <c r="AZ71" s="2"/>
+      <c r="BA71" s="2"/>
+      <c r="BB71" s="2"/>
+      <c r="BC71" s="2"/>
+      <c r="BD71" s="2"/>
+      <c r="BE71" s="305"/>
+      <c r="BF71" s="306"/>
+      <c r="BG71" s="307"/>
+      <c r="BH71" s="308"/>
+      <c r="BI71" s="309"/>
+      <c r="BJ71" s="310"/>
+      <c r="BK71" s="311"/>
+      <c r="BL71" s="312"/>
+      <c r="BM71" s="313"/>
+      <c r="BN71" s="2"/>
+      <c r="BO71" s="329" t="s">
+        <v>203</v>
+      </c>
+      <c r="BP71" s="329"/>
+      <c r="BQ71" s="329"/>
+      <c r="BR71" s="329"/>
+      <c r="BS71" s="329"/>
+      <c r="BT71" s="329"/>
+      <c r="BU71" s="329"/>
+      <c r="BV71" s="2"/>
+      <c r="BW71" s="2"/>
+      <c r="BX71" s="2"/>
+      <c r="BY71" s="2"/>
+      <c r="BZ71" s="2"/>
+      <c r="CA71" s="2"/>
+      <c r="CB71" s="2"/>
+      <c r="CC71" s="2"/>
+      <c r="CD71" s="2"/>
+      <c r="CE71" s="2"/>
+      <c r="CF71" s="2"/>
+      <c r="CG71" s="2"/>
+      <c r="CH71" s="2"/>
+      <c r="CI71" s="2"/>
+      <c r="CJ71" s="2"/>
+      <c r="CK71" s="2"/>
+      <c r="CL71" s="2"/>
+      <c r="CM71" s="2"/>
+      <c r="CN71" s="2"/>
+      <c r="CO71" s="2"/>
+      <c r="CP71" s="2"/>
+      <c r="CQ71" s="2"/>
+      <c r="CR71" s="2"/>
+      <c r="CS71" s="2"/>
+      <c r="CT71" s="2"/>
+      <c r="CU71" s="2"/>
+      <c r="CV71" s="2"/>
+      <c r="CW71" s="2"/>
+      <c r="CX71" s="2"/>
+      <c r="CY71" s="2"/>
+      <c r="CZ71" s="2"/>
+      <c r="DA71" s="2"/>
+      <c r="DB71" s="2"/>
+      <c r="DC71" s="2"/>
+      <c r="DD71" s="2"/>
+      <c r="DE71" s="2"/>
+      <c r="DF71" s="2"/>
+    </row>
+    <row r="72" spans="1:110" x14ac:dyDescent="0.8">
+      <c r="A72" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B72" s="291">
+        <v>46129</v>
+      </c>
+      <c r="C72" s="235" t="s">
+        <v>85</v>
+      </c>
+      <c r="D72" s="235"/>
+      <c r="E72" s="235"/>
+      <c r="F72" s="236"/>
+      <c r="G72" s="237"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2"/>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" s="2"/>
+      <c r="Q72" s="2"/>
+      <c r="R72" s="2"/>
+      <c r="S72" s="2"/>
+      <c r="T72" s="2"/>
+      <c r="U72" s="2"/>
+      <c r="V72" s="2"/>
+      <c r="W72" s="2"/>
+      <c r="X72" s="2"/>
+      <c r="Y72" s="2"/>
+      <c r="Z72" s="2"/>
+      <c r="AA72" s="2"/>
+      <c r="AB72" s="2"/>
+      <c r="AC72" s="2"/>
+      <c r="AD72" s="2"/>
+      <c r="AE72" s="2"/>
+      <c r="AF72" s="2"/>
+      <c r="AG72" s="2"/>
+      <c r="AH72" s="2"/>
+      <c r="AI72" s="2"/>
+      <c r="AJ72" s="2"/>
+      <c r="AK72" s="2"/>
+      <c r="AL72" s="2"/>
+      <c r="AM72" s="2"/>
+      <c r="AN72" s="2"/>
+      <c r="AO72" s="2"/>
+      <c r="AP72" s="2"/>
+      <c r="AQ72" s="2"/>
+      <c r="AR72" s="2"/>
+      <c r="AS72" s="2"/>
+      <c r="AT72" s="2"/>
+      <c r="AU72" s="2"/>
+      <c r="AV72" s="2"/>
+      <c r="AW72" s="2"/>
+      <c r="AX72" s="2"/>
+      <c r="AY72" s="2"/>
+      <c r="AZ72" s="2"/>
+      <c r="BA72" s="2"/>
+      <c r="BB72" s="2"/>
+      <c r="BC72" s="2"/>
+      <c r="BD72" s="2"/>
+      <c r="BE72" s="305"/>
+      <c r="BF72" s="306"/>
+      <c r="BG72" s="307"/>
+      <c r="BH72" s="308"/>
+      <c r="BI72" s="309"/>
+      <c r="BJ72" s="310"/>
+      <c r="BK72" s="311"/>
+      <c r="BL72" s="312"/>
+      <c r="BM72" s="313"/>
+      <c r="BN72" s="2"/>
+      <c r="BO72" s="329" t="s">
+        <v>205</v>
+      </c>
+      <c r="BP72" s="329"/>
+      <c r="BQ72" s="329"/>
+      <c r="BR72" s="329"/>
+      <c r="BS72" s="329"/>
+      <c r="BT72" s="329"/>
+      <c r="BU72" s="329"/>
+      <c r="BV72" s="2"/>
+      <c r="BW72" s="2"/>
+      <c r="BX72" s="2"/>
+      <c r="BY72" s="2"/>
+      <c r="BZ72" s="2"/>
+      <c r="CA72" s="2"/>
+      <c r="CB72" s="2"/>
+      <c r="CC72" s="2"/>
+      <c r="CD72" s="2"/>
+      <c r="CE72" s="2"/>
+      <c r="CF72" s="2"/>
+      <c r="CG72" s="2"/>
+      <c r="CH72" s="2"/>
+      <c r="CI72" s="2"/>
+      <c r="CJ72" s="2"/>
+      <c r="CK72" s="2"/>
+      <c r="CL72" s="2"/>
+      <c r="CM72" s="2"/>
+      <c r="CN72" s="2"/>
+      <c r="CO72" s="2"/>
+      <c r="CP72" s="2"/>
+      <c r="CQ72" s="2"/>
+      <c r="CR72" s="2"/>
+      <c r="CS72" s="2"/>
+      <c r="CT72" s="2"/>
+      <c r="CU72" s="2"/>
+      <c r="CV72" s="2"/>
+      <c r="CW72" s="2"/>
+      <c r="CX72" s="2"/>
+      <c r="CY72" s="2"/>
+      <c r="CZ72" s="2"/>
+      <c r="DA72" s="2"/>
+      <c r="DB72" s="2"/>
+      <c r="DC72" s="2"/>
+      <c r="DD72" s="2"/>
+      <c r="DE72" s="2"/>
+      <c r="DF72" s="2"/>
+    </row>
+    <row r="73" spans="1:110" x14ac:dyDescent="0.8">
+      <c r="A73" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B73" s="291">
+        <v>46129</v>
+      </c>
+      <c r="C73" s="235" t="s">
+        <v>85</v>
+      </c>
+      <c r="D73" s="235"/>
+      <c r="E73" s="235"/>
+      <c r="F73" s="236"/>
+      <c r="G73" s="237"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2"/>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" s="2"/>
+      <c r="Q73" s="2"/>
+      <c r="R73" s="2"/>
+      <c r="S73" s="2"/>
+      <c r="T73" s="2"/>
+      <c r="U73" s="2"/>
+      <c r="V73" s="2"/>
+      <c r="W73" s="2"/>
+      <c r="X73" s="2"/>
+      <c r="Y73" s="2"/>
+      <c r="Z73" s="2"/>
+      <c r="AA73" s="2"/>
+      <c r="AB73" s="2"/>
+      <c r="AC73" s="2"/>
+      <c r="AD73" s="2"/>
+      <c r="AE73" s="2"/>
+      <c r="AF73" s="2"/>
+      <c r="AG73" s="2"/>
+      <c r="AH73" s="2"/>
+      <c r="AI73" s="2"/>
+      <c r="AJ73" s="2"/>
+      <c r="AK73" s="2"/>
+      <c r="AL73" s="2"/>
+      <c r="AM73" s="2"/>
+      <c r="AN73" s="2"/>
+      <c r="AO73" s="2"/>
+      <c r="AP73" s="2"/>
+      <c r="AQ73" s="2"/>
+      <c r="AR73" s="2"/>
+      <c r="AS73" s="2"/>
+      <c r="AT73" s="2"/>
+      <c r="AU73" s="2"/>
+      <c r="AV73" s="2"/>
+      <c r="AW73" s="2"/>
+      <c r="AX73" s="2"/>
+      <c r="AY73" s="2"/>
+      <c r="AZ73" s="2"/>
+      <c r="BA73" s="2"/>
+      <c r="BB73" s="2"/>
+      <c r="BC73" s="2"/>
+      <c r="BD73" s="2"/>
+      <c r="BE73" s="305"/>
+      <c r="BF73" s="306"/>
+      <c r="BG73" s="307"/>
+      <c r="BH73" s="308"/>
+      <c r="BI73" s="309"/>
+      <c r="BJ73" s="310"/>
+      <c r="BK73" s="311"/>
+      <c r="BL73" s="312"/>
+      <c r="BM73" s="313"/>
+      <c r="BN73" s="2"/>
+      <c r="BO73" s="329" t="s">
+        <v>206</v>
+      </c>
+      <c r="BP73" s="329"/>
+      <c r="BQ73" s="329"/>
+      <c r="BR73" s="329"/>
+      <c r="BS73" s="329"/>
+      <c r="BT73" s="329"/>
+      <c r="BU73" s="329"/>
+      <c r="BV73" s="2"/>
+      <c r="BW73" s="2"/>
+      <c r="BX73" s="2"/>
+      <c r="BY73" s="2"/>
+      <c r="BZ73" s="2"/>
+      <c r="CA73" s="2"/>
+      <c r="CB73" s="2"/>
+      <c r="CC73" s="2"/>
+      <c r="CD73" s="2"/>
+      <c r="CE73" s="2"/>
+      <c r="CF73" s="2"/>
+      <c r="CG73" s="2"/>
+      <c r="CH73" s="2"/>
+      <c r="CI73" s="2"/>
+      <c r="CJ73" s="2"/>
+      <c r="CK73" s="2"/>
+      <c r="CL73" s="2"/>
+      <c r="CM73" s="2"/>
+      <c r="CN73" s="2"/>
+      <c r="CO73" s="2"/>
+      <c r="CP73" s="2"/>
+      <c r="CQ73" s="2"/>
+      <c r="CR73" s="2"/>
+      <c r="CS73" s="2"/>
+      <c r="CT73" s="2"/>
+      <c r="CU73" s="2"/>
+      <c r="CV73" s="2"/>
+      <c r="CW73" s="2"/>
+      <c r="CX73" s="2"/>
+      <c r="CY73" s="2"/>
+      <c r="CZ73" s="2"/>
+      <c r="DA73" s="2"/>
+      <c r="DB73" s="2"/>
+      <c r="DC73" s="2"/>
+      <c r="DD73" s="2"/>
+      <c r="DE73" s="2"/>
+      <c r="DF73" s="2"/>
+    </row>
+    <row r="74" spans="1:110" x14ac:dyDescent="0.8">
+      <c r="A74" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B74" s="291">
+        <v>46129</v>
+      </c>
+      <c r="C74" s="235" t="s">
+        <v>85</v>
+      </c>
+      <c r="D74" s="235"/>
+      <c r="E74" s="235"/>
+      <c r="F74" s="236"/>
+      <c r="G74" s="237"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
+      <c r="M74" s="2"/>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" s="2"/>
+      <c r="Q74" s="2"/>
+      <c r="R74" s="2"/>
+      <c r="S74" s="2"/>
+      <c r="T74" s="2"/>
+      <c r="U74" s="2"/>
+      <c r="V74" s="2"/>
+      <c r="W74" s="2"/>
+      <c r="X74" s="2"/>
+      <c r="Y74" s="2"/>
+      <c r="Z74" s="2"/>
+      <c r="AA74" s="2"/>
+      <c r="AB74" s="2"/>
+      <c r="AC74" s="2"/>
+      <c r="AD74" s="2"/>
+      <c r="AE74" s="2"/>
+      <c r="AF74" s="2"/>
+      <c r="AG74" s="2"/>
+      <c r="AH74" s="2"/>
+      <c r="AI74" s="2"/>
+      <c r="AJ74" s="2"/>
+      <c r="AK74" s="2"/>
+      <c r="AL74" s="2"/>
+      <c r="AM74" s="2"/>
+      <c r="AN74" s="2"/>
+      <c r="AO74" s="2"/>
+      <c r="AP74" s="2"/>
+      <c r="AQ74" s="2"/>
+      <c r="AR74" s="2"/>
+      <c r="AS74" s="2"/>
+      <c r="AT74" s="2"/>
+      <c r="AU74" s="2"/>
+      <c r="AV74" s="2"/>
+      <c r="AW74" s="2"/>
+      <c r="AX74" s="2"/>
+      <c r="AY74" s="2"/>
+      <c r="AZ74" s="2"/>
+      <c r="BA74" s="2"/>
+      <c r="BB74" s="2"/>
+      <c r="BC74" s="2"/>
+      <c r="BD74" s="2"/>
+      <c r="BE74" s="305"/>
+      <c r="BF74" s="306"/>
+      <c r="BG74" s="307"/>
+      <c r="BH74" s="308"/>
+      <c r="BI74" s="309"/>
+      <c r="BJ74" s="310"/>
+      <c r="BK74" s="311"/>
+      <c r="BL74" s="312"/>
+      <c r="BM74" s="313"/>
+      <c r="BN74" s="2"/>
+      <c r="BO74" s="329" t="s">
+        <v>207</v>
+      </c>
+      <c r="BP74" s="329"/>
+      <c r="BQ74" s="329"/>
+      <c r="BR74" s="329"/>
+      <c r="BS74" s="329"/>
+      <c r="BT74" s="329"/>
+      <c r="BU74" s="329"/>
+      <c r="BV74" s="2"/>
+      <c r="BW74" s="2"/>
+      <c r="BX74" s="2"/>
+      <c r="BY74" s="2"/>
+      <c r="BZ74" s="2"/>
+      <c r="CA74" s="2"/>
+      <c r="CB74" s="2"/>
+      <c r="CC74" s="2"/>
+      <c r="CD74" s="2"/>
+      <c r="CE74" s="2"/>
+      <c r="CF74" s="2"/>
+      <c r="CG74" s="2"/>
+      <c r="CH74" s="2"/>
+      <c r="CI74" s="2"/>
+      <c r="CJ74" s="2"/>
+      <c r="CK74" s="2"/>
+      <c r="CL74" s="2"/>
+      <c r="CM74" s="2"/>
+      <c r="CN74" s="2"/>
+      <c r="CO74" s="2"/>
+      <c r="CP74" s="2"/>
+      <c r="CQ74" s="2"/>
+      <c r="CR74" s="2"/>
+      <c r="CS74" s="2"/>
+      <c r="CT74" s="2"/>
+      <c r="CU74" s="2"/>
+      <c r="CV74" s="2"/>
+      <c r="CW74" s="2"/>
+      <c r="CX74" s="2"/>
+      <c r="CY74" s="2"/>
+      <c r="CZ74" s="2"/>
+      <c r="DA74" s="2"/>
+      <c r="DB74" s="2"/>
+      <c r="DC74" s="2"/>
+      <c r="DD74" s="2"/>
+      <c r="DE74" s="2"/>
+      <c r="DF74" s="2"/>
+    </row>
+    <row r="75" spans="1:110" x14ac:dyDescent="0.8">
+      <c r="A75" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B75" s="291">
+        <v>46129</v>
+      </c>
+      <c r="C75" s="235" t="s">
+        <v>85</v>
+      </c>
+      <c r="D75" s="238"/>
+      <c r="E75" s="238"/>
+      <c r="F75" s="239"/>
+      <c r="G75" s="240" t="s">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
+      <c r="M75" s="2"/>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" s="2"/>
+      <c r="Q75" s="2"/>
+      <c r="R75" s="2"/>
+      <c r="S75" s="2"/>
+      <c r="T75" s="2"/>
+      <c r="U75" s="2"/>
+      <c r="V75" s="2"/>
+      <c r="W75" s="2"/>
+      <c r="X75" s="2"/>
+      <c r="Y75" s="2"/>
+      <c r="Z75" s="2"/>
+      <c r="AA75" s="2"/>
+      <c r="AB75" s="2"/>
+      <c r="AC75" s="2"/>
+      <c r="AD75" s="2"/>
+      <c r="AE75" s="2"/>
+      <c r="AF75" s="2"/>
+      <c r="AG75" s="2"/>
+      <c r="AH75" s="2"/>
+      <c r="AI75" s="2"/>
+      <c r="AJ75" s="2"/>
+      <c r="AK75" s="2"/>
+      <c r="AL75" s="2"/>
+      <c r="AM75" s="2"/>
+      <c r="AN75" s="2"/>
+      <c r="AO75" s="2"/>
+      <c r="AP75" s="2"/>
+      <c r="AQ75" s="2"/>
+      <c r="AR75" s="2"/>
+      <c r="AS75" s="2"/>
+      <c r="AT75" s="2"/>
+      <c r="AU75" s="2"/>
+      <c r="AV75" s="2"/>
+      <c r="AW75" s="2"/>
+      <c r="AX75" s="2"/>
+      <c r="AY75" s="2"/>
+      <c r="AZ75" s="2"/>
+      <c r="BA75" s="2"/>
+      <c r="BB75" s="2"/>
+      <c r="BC75" s="2"/>
+      <c r="BD75" s="2"/>
+      <c r="BE75" s="2"/>
+      <c r="BF75" s="2"/>
+      <c r="BG75" s="2"/>
+      <c r="BH75" s="2"/>
+      <c r="BI75" s="2"/>
+      <c r="BJ75" s="2"/>
+      <c r="BK75" s="2"/>
+      <c r="BL75" s="314"/>
+      <c r="BM75" s="315"/>
+      <c r="BN75" s="316"/>
+      <c r="BO75" s="329" t="s">
+        <v>208</v>
+      </c>
+      <c r="BP75" s="329"/>
+      <c r="BQ75" s="329"/>
+      <c r="BR75" s="329"/>
+      <c r="BS75" s="329"/>
+      <c r="BT75" s="329"/>
+      <c r="BU75" s="329"/>
+      <c r="BV75" s="317"/>
+      <c r="BW75" s="2"/>
+      <c r="BX75" s="2"/>
+      <c r="BY75" s="2"/>
+      <c r="BZ75" s="2"/>
+      <c r="CA75" s="2"/>
+      <c r="CB75" s="2"/>
+      <c r="CC75" s="2"/>
+      <c r="CD75" s="2"/>
+      <c r="CE75" s="2"/>
+      <c r="CF75" s="2"/>
+      <c r="CG75" s="2"/>
+      <c r="CH75" s="2"/>
+      <c r="CI75" s="2"/>
+      <c r="CJ75" s="2"/>
+      <c r="CK75" s="2"/>
+      <c r="CL75" s="2"/>
+      <c r="CM75" s="2"/>
+      <c r="CN75" s="2"/>
+      <c r="CO75" s="2"/>
+      <c r="CP75" s="2"/>
+      <c r="CQ75" s="2"/>
+      <c r="CR75" s="2"/>
+      <c r="CS75" s="2"/>
+      <c r="CT75" s="2"/>
+      <c r="CU75" s="2"/>
+      <c r="CV75" s="2"/>
+      <c r="CW75" s="2"/>
+      <c r="CX75" s="2"/>
+      <c r="CY75" s="2"/>
+      <c r="CZ75" s="2"/>
+      <c r="DA75" s="2"/>
+      <c r="DB75" s="2"/>
+      <c r="DC75" s="2"/>
+      <c r="DD75" s="2"/>
+      <c r="DE75" s="2"/>
+      <c r="DF75" s="2"/>
+    </row>
+    <row r="76" spans="1:110" x14ac:dyDescent="0.8">
+      <c r="A76" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B76" s="291">
+        <v>46129</v>
+      </c>
+      <c r="C76" s="235" t="s">
+        <v>85</v>
+      </c>
+      <c r="D76" s="238"/>
+      <c r="E76" s="238"/>
+      <c r="F76" s="239"/>
+      <c r="G76" s="240"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" s="2"/>
+      <c r="Q76" s="2"/>
+      <c r="R76" s="2"/>
+      <c r="S76" s="2"/>
+      <c r="T76" s="2"/>
+      <c r="U76" s="2"/>
+      <c r="V76" s="2"/>
+      <c r="W76" s="2"/>
+      <c r="X76" s="2"/>
+      <c r="Y76" s="2"/>
+      <c r="Z76" s="2"/>
+      <c r="AA76" s="2"/>
+      <c r="AB76" s="2"/>
+      <c r="AC76" s="2"/>
+      <c r="AD76" s="2"/>
+      <c r="AE76" s="2"/>
+      <c r="AF76" s="2"/>
+      <c r="AG76" s="2"/>
+      <c r="AH76" s="2"/>
+      <c r="AI76" s="2"/>
+      <c r="AJ76" s="2"/>
+      <c r="AK76" s="2"/>
+      <c r="AL76" s="2"/>
+      <c r="AM76" s="2"/>
+      <c r="AN76" s="2"/>
+      <c r="AO76" s="2"/>
+      <c r="AP76" s="2"/>
+      <c r="AQ76" s="2"/>
+      <c r="AR76" s="2"/>
+      <c r="AS76" s="2"/>
+      <c r="AT76" s="2"/>
+      <c r="AU76" s="2"/>
+      <c r="AV76" s="2"/>
+      <c r="AW76" s="2"/>
+      <c r="AX76" s="2"/>
+      <c r="AY76" s="2"/>
+      <c r="AZ76" s="2"/>
+      <c r="BA76" s="2"/>
+      <c r="BB76" s="2"/>
+      <c r="BC76" s="2"/>
+      <c r="BD76" s="2"/>
+      <c r="BE76" s="2"/>
+      <c r="BF76" s="2"/>
+      <c r="BG76" s="2"/>
+      <c r="BH76" s="2"/>
+      <c r="BI76" s="2"/>
+      <c r="BJ76" s="2"/>
+      <c r="BK76" s="2"/>
+      <c r="BL76" s="314"/>
+      <c r="BM76" s="315"/>
+      <c r="BN76" s="316"/>
+      <c r="BO76" s="329" t="s">
+        <v>211</v>
+      </c>
+      <c r="BP76" s="329"/>
+      <c r="BQ76" s="329"/>
+      <c r="BR76" s="329"/>
+      <c r="BS76" s="329"/>
+      <c r="BT76" s="329"/>
+      <c r="BU76" s="329"/>
+      <c r="BV76" s="317"/>
+      <c r="BW76" s="2"/>
+      <c r="BX76" s="2"/>
+      <c r="BY76" s="2"/>
+      <c r="BZ76" s="2"/>
+      <c r="CA76" s="2"/>
+      <c r="CB76" s="2"/>
+      <c r="CC76" s="2"/>
+      <c r="CD76" s="2"/>
+      <c r="CE76" s="2"/>
+      <c r="CF76" s="2"/>
+      <c r="CG76" s="2"/>
+      <c r="CH76" s="2"/>
+      <c r="CI76" s="2"/>
+      <c r="CJ76" s="2"/>
+      <c r="CK76" s="2"/>
+      <c r="CL76" s="2"/>
+      <c r="CM76" s="2"/>
+      <c r="CN76" s="2"/>
+      <c r="CO76" s="2"/>
+      <c r="CP76" s="2"/>
+      <c r="CQ76" s="2"/>
+      <c r="CR76" s="2"/>
+      <c r="CS76" s="2"/>
+      <c r="CT76" s="2"/>
+      <c r="CU76" s="2"/>
+      <c r="CV76" s="2"/>
+      <c r="CW76" s="2"/>
+      <c r="CX76" s="2"/>
+      <c r="CY76" s="2"/>
+      <c r="CZ76" s="2"/>
+      <c r="DA76" s="2"/>
+      <c r="DB76" s="2"/>
+      <c r="DC76" s="2"/>
+      <c r="DD76" s="2"/>
+      <c r="DE76" s="2"/>
+      <c r="DF76" s="2"/>
+    </row>
+    <row r="77" spans="1:110" x14ac:dyDescent="0.8">
+      <c r="A77" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B77" s="291">
+        <v>46129</v>
+      </c>
+      <c r="C77" s="235" t="s">
+        <v>85</v>
+      </c>
+      <c r="G77" s="240" t="s">
+        <v>0</v>
+      </c>
+      <c r="AT77" s="2"/>
+      <c r="AU77" s="2"/>
+      <c r="AV77" s="2"/>
+      <c r="AW77" s="2"/>
+      <c r="AX77" s="2"/>
+      <c r="AY77" s="2"/>
+      <c r="AZ77" s="2"/>
+      <c r="BA77" s="2"/>
+      <c r="BB77" s="2"/>
+      <c r="BC77" s="2"/>
+      <c r="BD77" s="2"/>
+      <c r="BE77" s="2"/>
+      <c r="BF77" s="2"/>
+      <c r="BG77" s="2"/>
+      <c r="BH77" s="2"/>
+      <c r="BI77" s="2"/>
+      <c r="BJ77" s="2"/>
+      <c r="BK77" s="2"/>
+      <c r="BL77" s="150"/>
+      <c r="BM77" s="318"/>
+      <c r="BN77" s="319"/>
+      <c r="BO77" s="329" t="s">
+        <v>181</v>
+      </c>
+      <c r="BP77" s="329"/>
+      <c r="BQ77" s="329"/>
+      <c r="BR77" s="329"/>
+      <c r="BS77" s="329"/>
+      <c r="BT77" s="329"/>
+      <c r="BU77" s="329"/>
+      <c r="BV77" s="320"/>
+      <c r="BW77" s="2"/>
+      <c r="BX77" s="2"/>
+      <c r="BY77" s="2"/>
+      <c r="BZ77" s="2"/>
+      <c r="CA77" s="2"/>
+      <c r="CB77" s="2"/>
+      <c r="CC77" s="2"/>
+      <c r="CD77" s="2"/>
+      <c r="CE77" s="2"/>
+      <c r="CF77" s="2"/>
+      <c r="CG77" s="2"/>
+      <c r="CH77" s="2"/>
+      <c r="CI77" s="2"/>
+      <c r="CJ77" s="2"/>
+      <c r="CK77" s="2"/>
+      <c r="CL77" s="2"/>
+      <c r="CM77" s="2"/>
+      <c r="CN77" s="2"/>
+      <c r="CO77" s="2"/>
+      <c r="CP77" s="2"/>
+      <c r="CQ77" s="2"/>
+      <c r="CR77" s="2"/>
+      <c r="CS77" s="2"/>
+      <c r="CT77" s="2"/>
+      <c r="CU77" s="2"/>
+      <c r="CV77" s="2"/>
+      <c r="CW77" s="2"/>
+      <c r="CX77" s="2"/>
+      <c r="CY77" s="2"/>
+      <c r="CZ77" s="2"/>
+      <c r="DA77" s="2"/>
+      <c r="DB77" s="2"/>
+      <c r="DC77" s="2"/>
+      <c r="DD77" s="2"/>
+      <c r="DE77" s="2"/>
+      <c r="DF77" s="2"/>
+    </row>
+    <row r="78" spans="1:110" x14ac:dyDescent="0.8">
+      <c r="A78" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B78" s="291">
+        <v>46129</v>
+      </c>
+      <c r="C78" s="235" t="s">
+        <v>85</v>
+      </c>
+      <c r="BO78" s="329" t="s">
+        <v>212</v>
+      </c>
+      <c r="BP78" s="329"/>
+      <c r="BQ78" s="329"/>
+      <c r="BR78" s="329"/>
+      <c r="BS78" s="329"/>
+      <c r="BT78" s="329"/>
+      <c r="BU78" s="329"/>
+    </row>
   </sheetData>
-  <mergeCells count="67">
-    <mergeCell ref="BH58:BO58"/>
-    <mergeCell ref="BO67:BU67"/>
-    <mergeCell ref="BH63:BO63"/>
-    <mergeCell ref="BH62:BO62"/>
-    <mergeCell ref="BH61:BO61"/>
-    <mergeCell ref="BH60:BO60"/>
-    <mergeCell ref="BH59:BO59"/>
-    <mergeCell ref="BA54:BH54"/>
-    <mergeCell ref="BA56:BH56"/>
-    <mergeCell ref="BA55:BH55"/>
-    <mergeCell ref="BA57:BH57"/>
-    <mergeCell ref="BA52:BH52"/>
-    <mergeCell ref="BA49:BH49"/>
-    <mergeCell ref="BA50:BH50"/>
-    <mergeCell ref="BA51:BH51"/>
-    <mergeCell ref="BA53:BH53"/>
-    <mergeCell ref="BO65:BU65"/>
-    <mergeCell ref="BO66:BU66"/>
-    <mergeCell ref="BH64:BO64"/>
-    <mergeCell ref="AT38:BA38"/>
-    <mergeCell ref="BA39:BH39"/>
-    <mergeCell ref="BA40:BH40"/>
-    <mergeCell ref="BA41:BH41"/>
-    <mergeCell ref="BA42:BH42"/>
-    <mergeCell ref="BA43:BH43"/>
-    <mergeCell ref="BA44:BH44"/>
-    <mergeCell ref="BA45:BH45"/>
-    <mergeCell ref="BA46:BH46"/>
-    <mergeCell ref="BA47:BH47"/>
-    <mergeCell ref="BA48:BH48"/>
-    <mergeCell ref="AT36:BA36"/>
-    <mergeCell ref="AT35:BA35"/>
-    <mergeCell ref="AT37:BA37"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="P13:R13"/>
-    <mergeCell ref="R15:Y15"/>
-    <mergeCell ref="R16:Y16"/>
-    <mergeCell ref="AE33:AL33"/>
-    <mergeCell ref="AO33:AT33"/>
-    <mergeCell ref="AO34:AT34"/>
-    <mergeCell ref="P10:R10"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="H2:S2"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="R17:Y17"/>
-    <mergeCell ref="AF28:AM28"/>
-    <mergeCell ref="AF29:AM29"/>
-    <mergeCell ref="AF32:AM32"/>
-    <mergeCell ref="AF30:AM30"/>
+  <mergeCells count="78">
+    <mergeCell ref="BO78:BU78"/>
     <mergeCell ref="AF31:AM31"/>
     <mergeCell ref="CC2:DF2"/>
     <mergeCell ref="Y24:AF24"/>
@@ -14362,11 +15522,71 @@
     <mergeCell ref="AY2:CB2"/>
     <mergeCell ref="K7:R7"/>
     <mergeCell ref="P8:R8"/>
+    <mergeCell ref="P10:R10"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="H2:S2"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="R17:Y17"/>
     <mergeCell ref="P9:R9"/>
+    <mergeCell ref="BA47:BH47"/>
+    <mergeCell ref="AT36:BA36"/>
+    <mergeCell ref="AT35:BA35"/>
+    <mergeCell ref="AT37:BA37"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="P13:R13"/>
+    <mergeCell ref="R15:Y15"/>
+    <mergeCell ref="R16:Y16"/>
+    <mergeCell ref="AE33:AL33"/>
+    <mergeCell ref="AO33:AT33"/>
+    <mergeCell ref="AO34:AT34"/>
+    <mergeCell ref="AF28:AM28"/>
+    <mergeCell ref="AF29:AM29"/>
+    <mergeCell ref="AF32:AM32"/>
+    <mergeCell ref="AF30:AM30"/>
+    <mergeCell ref="BA42:BH42"/>
+    <mergeCell ref="BA43:BH43"/>
+    <mergeCell ref="BA44:BH44"/>
+    <mergeCell ref="BA45:BH45"/>
+    <mergeCell ref="BA46:BH46"/>
+    <mergeCell ref="BA38:BH38"/>
+    <mergeCell ref="BA39:BH39"/>
+    <mergeCell ref="BA40:BH40"/>
+    <mergeCell ref="BA41:BH41"/>
+    <mergeCell ref="BA48:BH48"/>
+    <mergeCell ref="BA49:BH49"/>
+    <mergeCell ref="BA50:BH50"/>
+    <mergeCell ref="BA52:BH52"/>
+    <mergeCell ref="BH69:BO69"/>
+    <mergeCell ref="BO70:BS70"/>
+    <mergeCell ref="BH62:BO62"/>
+    <mergeCell ref="BH63:BO63"/>
+    <mergeCell ref="BH64:BO64"/>
+    <mergeCell ref="BH65:BO65"/>
+    <mergeCell ref="BH66:BO66"/>
+    <mergeCell ref="BH67:BO67"/>
+    <mergeCell ref="BH68:BO68"/>
+    <mergeCell ref="BA53:BH53"/>
+    <mergeCell ref="BA55:BH55"/>
+    <mergeCell ref="BA54:BH54"/>
+    <mergeCell ref="BA56:BH56"/>
+    <mergeCell ref="BA51:BH51"/>
+    <mergeCell ref="BH57:BO57"/>
+    <mergeCell ref="BO77:BU77"/>
+    <mergeCell ref="BH61:BO61"/>
+    <mergeCell ref="BH60:BO60"/>
+    <mergeCell ref="BH59:BO59"/>
+    <mergeCell ref="BH58:BO58"/>
+    <mergeCell ref="BO75:BU75"/>
+    <mergeCell ref="BO71:BU71"/>
+    <mergeCell ref="BO72:BU72"/>
+    <mergeCell ref="BO73:BU73"/>
+    <mergeCell ref="BO74:BU74"/>
+    <mergeCell ref="BO76:BU76"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="G1:DF4 A1:C4 G5 I5:DF5 G6:I6 G8:DF10 X7:DF7 G7:J7 A8:C10 B7 B5:C5 A13:C13 A12 B15:C15 A11:B11 G23:DF23 S16:DF16 A14 A17:C17 A16:B16 G14:O14 S14:DF14 A23 G18:DF18 G21:Q21 S21:DF21 G15:Q17 S17:DF17 S6:DF6 A21:C21 C6 G33:AD33 B26:C26 G26:X26 AG26:DF26 A33 G64:AS66 G32:AC32 AQ32:DF32 S15:DF15 AT67:BJ67 AF33:AN33 AU33:DF33 G34:AJ34 B34:C34 B40 G11:DF13 BB38:DF38 G38:AS38 AT39:AZ39 BT39:DF39 AT40:AZ40 G39:AS40 A65 C65 BS40:DF40 AT64:AZ64 BQ64:DF64 AT65:BD65 BV65:DF65 AT66:BK66 BW66:DF66 CA67:DF67" numberStoredAsText="1"/>
+    <ignoredError sqref="G1:DF4 A1:C4 G5 I5:DF5 G6:I6 G8:DF10 X7:DF7 G7:J7 A8:C10 B7 B5:C5 A13:C13 A12 B15:C15 A11:B11 G23:DF23 S16:DF16 A14 A17:C17 A16:B16 G14:O14 S14:DF14 A23 G18:DF18 G21:Q21 S21:DF21 G15:Q17 S17:DF17 S6:DF6 A21:C21 C6 G33:AD33 B26:C26 G26:X26 AG26:DF26 A33 G32:AC32 AQ32:DF32 S15:DF15 AT77:BJ77 AF33:AN33 AU33:DF33 G34:AJ34 B34:C34 B39 G11:DF13 BT38:DF38 G38:AZ39 A70 BS39:DF39 AT69:AZ69 BQ69:DF69 AT70:BD70 BV70:DF70 G75:BK75 BW75:DF75 CA77:DF77 G69:AS70" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Documentation/GanntChart/BattleNationsGanntChart.xlsx
+++ b/Documentation/GanntChart/BattleNationsGanntChart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jreig\git\BattleNations\Documentation\GanntChart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{34C683D4-32F6-4647-8681-0B1E686158EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142F7CFD-1580-4713-AC11-3E3E6C5B1251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="212">
   <si>
     <t/>
   </si>
@@ -287,9 +287,6 @@
     <t>17-Apr-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Update whatever requests we get from customer </t>
-  </si>
-  <si>
     <t>24-Apr-2026</t>
   </si>
   <si>
@@ -482,9 +479,6 @@
     <t>Completed by</t>
   </si>
   <si>
-    <t>Max</t>
-  </si>
-  <si>
     <t>JD</t>
   </si>
   <si>
@@ -554,12 +548,6 @@
     <t>Look through all files javadocs + polish anywhere needed</t>
   </si>
   <si>
-    <t>Time to complete: 2 hours</t>
-  </si>
-  <si>
-    <t>Prepare for final Presentation</t>
-  </si>
-  <si>
     <t>Display Player owed region percentages on region display (10-Apr-26 - 17-Apr-26)</t>
   </si>
   <si>
@@ -578,9 +566,6 @@
     <t>Prepare for Customer Presentation  (10-Apr-26 - 17-Apr-26)</t>
   </si>
   <si>
-    <t>Prepare for final Presentation (17-Apr-26 - 24-Apr-26)</t>
-  </si>
-  <si>
     <t>MAX</t>
   </si>
   <si>
@@ -620,9 +605,6 @@
     <t>Add Test Section To game Manual</t>
   </si>
   <si>
-    <t>Update whatever requests we get from customer (17-Apr-26 - 22-Apr-26)</t>
-  </si>
-  <si>
     <t>Polish Game + Visuals  (10-Apr-26 - 17-Apr-26)</t>
   </si>
   <si>
@@ -665,20 +647,35 @@
     <t>Add Flow Charts to game Manual</t>
   </si>
   <si>
-    <t xml:space="preserve">Add Images to Game Manual Where Appropriate </t>
-  </si>
-  <si>
     <t>Add Images to Game Manual Where Appropriate (17-Apr-26 - 24-Apr-26)</t>
   </si>
   <si>
     <t>Write Final Test for NeighborService Class (17-Apr-26 - 24-Apr-26)</t>
+  </si>
+  <si>
+    <t>Need max to fix his flow charts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Update Customer Requests </t>
+  </si>
+  <si>
+    <t>Update Customer Requests  (17-Apr-26 - 22-Apr-26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add &amp; resize Images to Game Manual Where Appropriate </t>
+  </si>
+  <si>
+    <t>Prepare for Final Presentation</t>
+  </si>
+  <si>
+    <t>Prepare For Final Presentation (22-Apr-26 - 27-Apr-26)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="356" x14ac:knownFonts="1">
+  <fonts count="353" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2803,30 +2800,12 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="149">
+  <fills count="150">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3711,7 +3690,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4681,24 +4666,12 @@
     <xf numFmtId="0" fontId="349" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="352" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="353" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="354" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="291" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="146" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="290" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4711,22 +4684,73 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="355" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="352" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="15" fontId="344" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="344" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="148" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="350" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="146" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="331" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="145" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="311" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="322" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="145" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="219" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="220" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="221" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="222" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="223" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="224" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="225" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="295" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4827,8 +4851,14 @@
     <xf numFmtId="0" fontId="282" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="283" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="284" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="145" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="160" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="172" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4857,30 +4887,6 @@
     <xf numFmtId="0" fontId="126" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="219" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="220" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="221" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="222" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="223" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="224" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="225" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="145" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4986,41 +4992,20 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="160" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="344" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="311" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="146" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="146" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="331" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="148" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="331" fillId="146" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="149" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5368,7 +5353,7 @@
     <col min="2" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="13.1640625" customWidth="1"/>
     <col min="5" max="5" width="17.70703125" customWidth="1"/>
-    <col min="6" max="6" width="10.95703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="3.33203125" customWidth="1"/>
     <col min="9" max="9" width="8.5" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" hidden="1" customWidth="1"/>
@@ -5495,13 +5480,13 @@
       <c r="DF1" s="2"/>
     </row>
     <row r="2" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A2" s="376" t="s">
+      <c r="A2" s="391" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="377" t="s">
+      <c r="B2" s="392" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="377" t="s">
+      <c r="C2" s="392" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="11"/>
@@ -5510,313 +5495,313 @@
       <c r="G2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="378" t="s">
+      <c r="H2" s="393" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="377" t="s">
+      <c r="I2" s="392" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="377" t="s">
+      <c r="J2" s="392" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="377" t="s">
+      <c r="K2" s="392" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="377" t="s">
+      <c r="L2" s="392" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="377" t="s">
+      <c r="M2" s="392" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="377" t="s">
+      <c r="N2" s="392" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="377" t="s">
+      <c r="O2" s="392" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="377" t="s">
+      <c r="P2" s="392" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="377" t="s">
+      <c r="Q2" s="392" t="s">
         <v>2</v>
       </c>
-      <c r="R2" s="377" t="s">
+      <c r="R2" s="392" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="377" t="s">
+      <c r="S2" s="392" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="423" t="s">
+      <c r="T2" s="430" t="s">
         <v>3</v>
       </c>
-      <c r="U2" s="377" t="s">
+      <c r="U2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="V2" s="377" t="s">
+      <c r="V2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="W2" s="377" t="s">
+      <c r="W2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="X2" s="377" t="s">
+      <c r="X2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="Y2" s="377" t="s">
+      <c r="Y2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="Z2" s="377" t="s">
+      <c r="Z2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AA2" s="377" t="s">
+      <c r="AA2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AB2" s="377" t="s">
+      <c r="AB2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="377" t="s">
+      <c r="AC2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AD2" s="377" t="s">
+      <c r="AD2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AE2" s="377" t="s">
+      <c r="AE2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AF2" s="377" t="s">
+      <c r="AF2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AG2" s="377" t="s">
+      <c r="AG2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AH2" s="377" t="s">
+      <c r="AH2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AI2" s="377" t="s">
+      <c r="AI2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AJ2" s="377" t="s">
+      <c r="AJ2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AK2" s="377" t="s">
+      <c r="AK2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AL2" s="377" t="s">
+      <c r="AL2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AM2" s="377" t="s">
+      <c r="AM2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AN2" s="377" t="s">
+      <c r="AN2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AO2" s="377" t="s">
+      <c r="AO2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AP2" s="377" t="s">
+      <c r="AP2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AQ2" s="377" t="s">
+      <c r="AQ2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AR2" s="377" t="s">
+      <c r="AR2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AS2" s="377" t="s">
+      <c r="AS2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AT2" s="377" t="s">
+      <c r="AT2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AU2" s="377" t="s">
+      <c r="AU2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AV2" s="377" t="s">
+      <c r="AV2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AW2" s="377" t="s">
+      <c r="AW2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AX2" s="377" t="s">
+      <c r="AX2" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="AY2" s="424" t="s">
+      <c r="AY2" s="431" t="s">
         <v>4</v>
       </c>
-      <c r="AZ2" s="377" t="s">
+      <c r="AZ2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BA2" s="377" t="s">
+      <c r="BA2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BB2" s="377" t="s">
+      <c r="BB2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BC2" s="377" t="s">
+      <c r="BC2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BD2" s="377" t="s">
+      <c r="BD2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BE2" s="377" t="s">
+      <c r="BE2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BF2" s="377" t="s">
+      <c r="BF2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BG2" s="377" t="s">
+      <c r="BG2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BH2" s="377" t="s">
+      <c r="BH2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BI2" s="377" t="s">
+      <c r="BI2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BJ2" s="377" t="s">
+      <c r="BJ2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BK2" s="377" t="s">
+      <c r="BK2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BL2" s="377" t="s">
+      <c r="BL2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BM2" s="377" t="s">
+      <c r="BM2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BN2" s="377" t="s">
+      <c r="BN2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BO2" s="377" t="s">
+      <c r="BO2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BP2" s="377" t="s">
+      <c r="BP2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BQ2" s="377" t="s">
+      <c r="BQ2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BR2" s="377" t="s">
+      <c r="BR2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BS2" s="377" t="s">
+      <c r="BS2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BT2" s="377" t="s">
+      <c r="BT2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BU2" s="377" t="s">
+      <c r="BU2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BV2" s="377" t="s">
+      <c r="BV2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BW2" s="377" t="s">
+      <c r="BW2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BX2" s="377" t="s">
+      <c r="BX2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BY2" s="377" t="s">
+      <c r="BY2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="BZ2" s="377" t="s">
+      <c r="BZ2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="CA2" s="377" t="s">
+      <c r="CA2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="CB2" s="377" t="s">
+      <c r="CB2" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="CC2" s="390" t="s">
+      <c r="CC2" s="397" t="s">
         <v>5</v>
       </c>
-      <c r="CD2" s="377" t="s">
+      <c r="CD2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CE2" s="377" t="s">
+      <c r="CE2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CF2" s="377" t="s">
+      <c r="CF2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CG2" s="377" t="s">
+      <c r="CG2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CH2" s="377" t="s">
+      <c r="CH2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CI2" s="377" t="s">
+      <c r="CI2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CJ2" s="377" t="s">
+      <c r="CJ2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CK2" s="377" t="s">
+      <c r="CK2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CL2" s="377" t="s">
+      <c r="CL2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CM2" s="377" t="s">
+      <c r="CM2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CN2" s="377" t="s">
+      <c r="CN2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CO2" s="377" t="s">
+      <c r="CO2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CP2" s="377" t="s">
+      <c r="CP2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CQ2" s="377" t="s">
+      <c r="CQ2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CR2" s="377" t="s">
+      <c r="CR2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CS2" s="377" t="s">
+      <c r="CS2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CT2" s="377" t="s">
+      <c r="CT2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CU2" s="377" t="s">
+      <c r="CU2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CV2" s="377" t="s">
+      <c r="CV2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CW2" s="377" t="s">
+      <c r="CW2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CX2" s="377" t="s">
+      <c r="CX2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CY2" s="377" t="s">
+      <c r="CY2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="CZ2" s="377" t="s">
+      <c r="CZ2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="DA2" s="377" t="s">
+      <c r="DA2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="DB2" s="377" t="s">
+      <c r="DB2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="DC2" s="377" t="s">
+      <c r="DC2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="DD2" s="377" t="s">
+      <c r="DD2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="DE2" s="377" t="s">
+      <c r="DE2" s="392" t="s">
         <v>5</v>
       </c>
-      <c r="DF2" s="377" t="s">
+      <c r="DF2" s="392" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5831,13 +5816,13 @@
         <v>7</v>
       </c>
       <c r="D3" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="17" t="s">
         <v>86</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>87</v>
       </c>
       <c r="G3" s="18" t="s">
         <v>0</v>
@@ -6276,7 +6261,7 @@
     </row>
     <row r="5" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A5" s="281" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B5" s="129" t="s">
         <v>40</v>
@@ -6287,23 +6272,23 @@
       <c r="D5" s="131">
         <v>1</v>
       </c>
-      <c r="E5" s="326" t="s">
-        <v>149</v>
+      <c r="E5" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F5" s="132"/>
       <c r="G5" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="H5" s="333" t="s">
-        <v>88</v>
-      </c>
-      <c r="I5" s="379" t="s">
+      <c r="H5" s="336" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="394" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="380" t="s">
+      <c r="J5" s="395" t="s">
         <v>42</v>
       </c>
-      <c r="K5" s="381" t="s">
+      <c r="K5" s="396" t="s">
         <v>42</v>
       </c>
       <c r="L5" s="2"/>
@@ -6408,7 +6393,7 @@
     </row>
     <row r="6" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A6" s="281" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B6" s="250">
         <v>46073</v>
@@ -6419,8 +6404,8 @@
       <c r="D6" s="135">
         <v>1</v>
       </c>
-      <c r="E6" s="326" t="s">
-        <v>150</v>
+      <c r="E6" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F6" s="136"/>
       <c r="G6" s="137" t="s">
@@ -6430,15 +6415,15 @@
       <c r="I6" s="2"/>
       <c r="J6" s="150"/>
       <c r="K6" s="330" t="s">
-        <v>96</v>
-      </c>
-      <c r="L6" s="421"/>
-      <c r="M6" s="421"/>
-      <c r="N6" s="421"/>
-      <c r="O6" s="421"/>
-      <c r="P6" s="421"/>
-      <c r="Q6" s="421"/>
-      <c r="R6" s="421"/>
+        <v>95</v>
+      </c>
+      <c r="L6" s="428"/>
+      <c r="M6" s="428"/>
+      <c r="N6" s="428"/>
+      <c r="O6" s="428"/>
+      <c r="P6" s="428"/>
+      <c r="Q6" s="428"/>
+      <c r="R6" s="428"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
@@ -6534,7 +6519,7 @@
     </row>
     <row r="7" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A7" s="281" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B7" s="142" t="s">
         <v>41</v>
@@ -6545,8 +6530,8 @@
       <c r="D7" s="143">
         <v>1</v>
       </c>
-      <c r="E7" s="326" t="s">
-        <v>150</v>
+      <c r="E7" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F7" s="144"/>
       <c r="G7" s="145" t="s">
@@ -6556,7 +6541,7 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="330" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L7" s="330"/>
       <c r="M7" s="330"/>
@@ -6671,8 +6656,8 @@
       <c r="D8" s="159">
         <v>1</v>
       </c>
-      <c r="E8" s="326" t="s">
-        <v>150</v>
+      <c r="E8" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F8" s="160"/>
       <c r="G8" s="161" t="s">
@@ -6686,13 +6671,13 @@
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="425" t="s">
+      <c r="P8" s="385" t="s">
         <v>49</v>
       </c>
-      <c r="Q8" s="426" t="s">
+      <c r="Q8" s="386" t="s">
         <v>49</v>
       </c>
-      <c r="R8" s="427" t="s">
+      <c r="R8" s="387" t="s">
         <v>49</v>
       </c>
       <c r="S8" s="2"/>
@@ -6801,8 +6786,8 @@
       <c r="D9" s="164">
         <v>1</v>
       </c>
-      <c r="E9" s="326" t="s">
-        <v>150</v>
+      <c r="E9" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F9" s="165"/>
       <c r="G9" s="166" t="s">
@@ -6816,13 +6801,13 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="428" t="s">
+      <c r="P9" s="344" t="s">
         <v>51</v>
       </c>
-      <c r="Q9" s="429" t="s">
+      <c r="Q9" s="345" t="s">
         <v>51</v>
       </c>
-      <c r="R9" s="430" t="s">
+      <c r="R9" s="346" t="s">
         <v>51</v>
       </c>
       <c r="S9" s="2"/>
@@ -6931,8 +6916,8 @@
       <c r="D10" s="169">
         <v>1</v>
       </c>
-      <c r="E10" s="326" t="s">
-        <v>150</v>
+      <c r="E10" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F10" s="170"/>
       <c r="G10" s="171" t="s">
@@ -6946,13 +6931,13 @@
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="373" t="s">
+      <c r="P10" s="388" t="s">
         <v>53</v>
       </c>
-      <c r="Q10" s="374" t="s">
+      <c r="Q10" s="389" t="s">
         <v>53</v>
       </c>
-      <c r="R10" s="375" t="s">
+      <c r="R10" s="390" t="s">
         <v>53</v>
       </c>
       <c r="S10" s="2"/>
@@ -7061,8 +7046,8 @@
       <c r="D11" s="173">
         <v>1</v>
       </c>
-      <c r="E11" s="326" t="s">
-        <v>150</v>
+      <c r="E11" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F11" s="174"/>
       <c r="G11" s="175" t="s">
@@ -7076,13 +7061,13 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="341" t="s">
+      <c r="P11" s="354" t="s">
         <v>56</v>
       </c>
-      <c r="Q11" s="342" t="s">
+      <c r="Q11" s="355" t="s">
         <v>56</v>
       </c>
-      <c r="R11" s="343" t="s">
+      <c r="R11" s="356" t="s">
         <v>56</v>
       </c>
       <c r="S11" s="2"/>
@@ -7191,8 +7176,8 @@
       <c r="D12" s="178">
         <v>1</v>
       </c>
-      <c r="E12" s="326" t="s">
-        <v>150</v>
+      <c r="E12" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F12" s="179"/>
       <c r="G12" s="180" t="s">
@@ -7206,13 +7191,13 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="344" t="s">
+      <c r="P12" s="357" t="s">
         <v>58</v>
       </c>
-      <c r="Q12" s="345" t="s">
+      <c r="Q12" s="358" t="s">
         <v>58</v>
       </c>
-      <c r="R12" s="346" t="s">
+      <c r="R12" s="359" t="s">
         <v>58</v>
       </c>
       <c r="S12" s="2"/>
@@ -7321,8 +7306,8 @@
       <c r="D13" s="183">
         <v>1</v>
       </c>
-      <c r="E13" s="326" t="s">
-        <v>150</v>
+      <c r="E13" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F13" s="184"/>
       <c r="G13" s="185" t="s">
@@ -7336,13 +7321,13 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="347" t="s">
+      <c r="P13" s="360" t="s">
         <v>60</v>
       </c>
-      <c r="Q13" s="348" t="s">
+      <c r="Q13" s="361" t="s">
         <v>60</v>
       </c>
-      <c r="R13" s="349" t="s">
+      <c r="R13" s="362" t="s">
         <v>60</v>
       </c>
       <c r="S13" s="2"/>
@@ -7451,8 +7436,8 @@
       <c r="D14" s="188">
         <v>1</v>
       </c>
-      <c r="E14" s="326" t="s">
-        <v>150</v>
+      <c r="E14" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="189" t="s">
@@ -7469,7 +7454,7 @@
       <c r="P14" s="190"/>
       <c r="Q14" s="191"/>
       <c r="R14" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S14" s="281"/>
       <c r="T14" s="281"/>
@@ -7566,7 +7551,7 @@
     </row>
     <row r="15" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A15" s="281" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B15" s="192" t="s">
         <v>43</v>
@@ -7577,8 +7562,8 @@
       <c r="D15" s="194">
         <v>1</v>
       </c>
-      <c r="E15" s="326" t="s">
-        <v>149</v>
+      <c r="E15" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F15" s="195"/>
       <c r="G15" s="196" t="s">
@@ -7594,28 +7579,28 @@
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
-      <c r="R15" s="333" t="s">
-        <v>92</v>
-      </c>
-      <c r="S15" s="350" t="s">
+      <c r="R15" s="336" t="s">
+        <v>91</v>
+      </c>
+      <c r="S15" s="363" t="s">
         <v>63</v>
       </c>
-      <c r="T15" s="351" t="s">
+      <c r="T15" s="364" t="s">
         <v>63</v>
       </c>
-      <c r="U15" s="352" t="s">
+      <c r="U15" s="365" t="s">
         <v>63</v>
       </c>
-      <c r="V15" s="353" t="s">
+      <c r="V15" s="366" t="s">
         <v>63</v>
       </c>
-      <c r="W15" s="354" t="s">
+      <c r="W15" s="367" t="s">
         <v>63</v>
       </c>
-      <c r="X15" s="355" t="s">
+      <c r="X15" s="368" t="s">
         <v>63</v>
       </c>
-      <c r="Y15" s="356" t="s">
+      <c r="Y15" s="369" t="s">
         <v>63</v>
       </c>
       <c r="Z15" s="2"/>
@@ -7717,8 +7702,8 @@
       <c r="D16" s="198">
         <v>1</v>
       </c>
-      <c r="E16" s="326" t="s">
-        <v>149</v>
+      <c r="E16" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F16" s="199"/>
       <c r="G16" s="200" t="s">
@@ -7734,28 +7719,28 @@
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
-      <c r="R16" s="333" t="s">
-        <v>92</v>
-      </c>
-      <c r="S16" s="357" t="s">
+      <c r="R16" s="336" t="s">
+        <v>91</v>
+      </c>
+      <c r="S16" s="370" t="s">
         <v>65</v>
       </c>
-      <c r="T16" s="358" t="s">
+      <c r="T16" s="371" t="s">
         <v>65</v>
       </c>
-      <c r="U16" s="359" t="s">
+      <c r="U16" s="372" t="s">
         <v>65</v>
       </c>
-      <c r="V16" s="360" t="s">
+      <c r="V16" s="373" t="s">
         <v>65</v>
       </c>
-      <c r="W16" s="361" t="s">
+      <c r="W16" s="374" t="s">
         <v>65</v>
       </c>
-      <c r="X16" s="362" t="s">
+      <c r="X16" s="375" t="s">
         <v>65</v>
       </c>
-      <c r="Y16" s="363" t="s">
+      <c r="Y16" s="376" t="s">
         <v>65</v>
       </c>
       <c r="Z16" s="2"/>
@@ -7857,8 +7842,8 @@
       <c r="D17" s="202">
         <v>1</v>
       </c>
-      <c r="E17" s="326" t="s">
-        <v>149</v>
+      <c r="E17" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F17" s="203"/>
       <c r="G17" s="204" t="s">
@@ -7874,28 +7859,28 @@
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
-      <c r="R17" s="333" t="s">
+      <c r="R17" s="336" t="s">
         <v>67</v>
       </c>
-      <c r="S17" s="382" t="s">
+      <c r="S17" s="337" t="s">
         <v>67</v>
       </c>
-      <c r="T17" s="383" t="s">
+      <c r="T17" s="338" t="s">
         <v>67</v>
       </c>
-      <c r="U17" s="384" t="s">
+      <c r="U17" s="339" t="s">
         <v>67</v>
       </c>
-      <c r="V17" s="385" t="s">
+      <c r="V17" s="340" t="s">
         <v>67</v>
       </c>
-      <c r="W17" s="386" t="s">
+      <c r="W17" s="341" t="s">
         <v>67</v>
       </c>
-      <c r="X17" s="387" t="s">
+      <c r="X17" s="342" t="s">
         <v>67</v>
       </c>
-      <c r="Y17" s="388" t="s">
+      <c r="Y17" s="343" t="s">
         <v>67</v>
       </c>
       <c r="Z17" s="2"/>
@@ -7997,8 +7982,8 @@
       <c r="D18" s="207">
         <v>1</v>
       </c>
-      <c r="E18" s="326" t="s">
-        <v>149</v>
+      <c r="E18" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F18" s="208"/>
       <c r="G18" s="209" t="s">
@@ -8014,28 +7999,28 @@
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
-      <c r="R18" s="392" t="s">
+      <c r="R18" s="399" t="s">
         <v>69</v>
       </c>
-      <c r="S18" s="393" t="s">
+      <c r="S18" s="400" t="s">
         <v>69</v>
       </c>
-      <c r="T18" s="394" t="s">
+      <c r="T18" s="401" t="s">
         <v>69</v>
       </c>
-      <c r="U18" s="395" t="s">
+      <c r="U18" s="402" t="s">
         <v>69</v>
       </c>
-      <c r="V18" s="396" t="s">
+      <c r="V18" s="403" t="s">
         <v>69</v>
       </c>
-      <c r="W18" s="397" t="s">
+      <c r="W18" s="404" t="s">
         <v>69</v>
       </c>
-      <c r="X18" s="398" t="s">
+      <c r="X18" s="405" t="s">
         <v>69</v>
       </c>
-      <c r="Y18" s="399" t="s">
+      <c r="Y18" s="406" t="s">
         <v>69</v>
       </c>
       <c r="Z18" s="2"/>
@@ -8137,8 +8122,8 @@
       <c r="D19" s="147">
         <v>1</v>
       </c>
-      <c r="E19" s="326" t="s">
-        <v>149</v>
+      <c r="E19" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F19" s="148"/>
       <c r="G19" s="149" t="s">
@@ -8154,7 +8139,7 @@
       <c r="O19" s="154"/>
       <c r="P19" s="155"/>
       <c r="R19" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S19" s="259"/>
       <c r="T19" s="259"/>
@@ -8251,7 +8236,7 @@
     </row>
     <row r="20" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A20" s="281" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B20" s="205" t="s">
         <v>43</v>
@@ -8262,8 +8247,8 @@
       <c r="D20" s="207">
         <v>1</v>
       </c>
-      <c r="E20" s="326" t="s">
-        <v>149</v>
+      <c r="E20" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F20" s="208"/>
       <c r="G20" s="209"/>
@@ -8277,16 +8262,16 @@
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
-      <c r="R20" s="407" t="s">
-        <v>95</v>
-      </c>
-      <c r="S20" s="408"/>
-      <c r="T20" s="408"/>
-      <c r="U20" s="408"/>
-      <c r="V20" s="408"/>
-      <c r="W20" s="408"/>
-      <c r="X20" s="408"/>
-      <c r="Y20" s="408"/>
+      <c r="R20" s="414" t="s">
+        <v>94</v>
+      </c>
+      <c r="S20" s="415"/>
+      <c r="T20" s="415"/>
+      <c r="U20" s="415"/>
+      <c r="V20" s="415"/>
+      <c r="W20" s="415"/>
+      <c r="X20" s="415"/>
+      <c r="Y20" s="415"/>
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
       <c r="AB20" s="2"/>
@@ -8386,8 +8371,8 @@
       <c r="D21" s="5">
         <v>1</v>
       </c>
-      <c r="E21" s="326" t="s">
-        <v>149</v>
+      <c r="E21" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="210" t="s">
@@ -8403,28 +8388,28 @@
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
-      <c r="R21" s="333" t="s">
+      <c r="R21" s="336" t="s">
         <v>71</v>
       </c>
-      <c r="S21" s="400" t="s">
+      <c r="S21" s="407" t="s">
         <v>71</v>
       </c>
-      <c r="T21" s="401" t="s">
+      <c r="T21" s="408" t="s">
         <v>71</v>
       </c>
-      <c r="U21" s="402" t="s">
+      <c r="U21" s="409" t="s">
         <v>71</v>
       </c>
-      <c r="V21" s="403" t="s">
+      <c r="V21" s="410" t="s">
         <v>71</v>
       </c>
-      <c r="W21" s="404" t="s">
+      <c r="W21" s="411" t="s">
         <v>71</v>
       </c>
-      <c r="X21" s="405" t="s">
+      <c r="X21" s="412" t="s">
         <v>71</v>
       </c>
-      <c r="Y21" s="406" t="s">
+      <c r="Y21" s="413" t="s">
         <v>71</v>
       </c>
       <c r="Z21" s="2"/>
@@ -8526,8 +8511,8 @@
       <c r="D22" s="139">
         <v>1</v>
       </c>
-      <c r="E22" s="326" t="s">
-        <v>149</v>
+      <c r="E22" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F22" s="140"/>
       <c r="G22" s="141" t="s">
@@ -8545,12 +8530,12 @@
       <c r="Q22" s="247"/>
       <c r="R22" s="248"/>
       <c r="S22" s="330" t="s">
-        <v>104</v>
-      </c>
-      <c r="T22" s="422"/>
-      <c r="U22" s="422"/>
-      <c r="V22" s="422"/>
-      <c r="W22" s="422"/>
+        <v>103</v>
+      </c>
+      <c r="T22" s="429"/>
+      <c r="U22" s="429"/>
+      <c r="V22" s="429"/>
+      <c r="W22" s="429"/>
       <c r="X22" s="2"/>
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
@@ -8652,8 +8637,8 @@
       <c r="D23" s="251">
         <v>1</v>
       </c>
-      <c r="E23" s="326" t="s">
-        <v>150</v>
+      <c r="E23" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="212" t="s">
@@ -8672,40 +8657,40 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
-      <c r="U23" s="409" t="s">
+      <c r="U23" s="416" t="s">
         <v>74</v>
       </c>
-      <c r="V23" s="410" t="s">
+      <c r="V23" s="417" t="s">
         <v>74</v>
       </c>
-      <c r="W23" s="411" t="s">
+      <c r="W23" s="418" t="s">
         <v>74</v>
       </c>
-      <c r="X23" s="412" t="s">
+      <c r="X23" s="419" t="s">
         <v>74</v>
       </c>
-      <c r="Y23" s="413" t="s">
+      <c r="Y23" s="420" t="s">
         <v>74</v>
       </c>
-      <c r="Z23" s="414" t="s">
+      <c r="Z23" s="421" t="s">
         <v>74</v>
       </c>
-      <c r="AA23" s="415" t="s">
+      <c r="AA23" s="422" t="s">
         <v>74</v>
       </c>
-      <c r="AB23" s="416" t="s">
+      <c r="AB23" s="423" t="s">
         <v>74</v>
       </c>
-      <c r="AC23" s="417" t="s">
+      <c r="AC23" s="424" t="s">
         <v>74</v>
       </c>
-      <c r="AD23" s="418" t="s">
+      <c r="AD23" s="425" t="s">
         <v>74</v>
       </c>
-      <c r="AE23" s="419" t="s">
+      <c r="AE23" s="426" t="s">
         <v>74</v>
       </c>
-      <c r="AF23" s="420" t="s">
+      <c r="AF23" s="427" t="s">
         <v>74</v>
       </c>
       <c r="AG23" s="2"/>
@@ -8789,7 +8774,7 @@
     </row>
     <row r="24" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A24" s="281" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B24" s="213" t="s">
         <v>62</v>
@@ -8800,8 +8785,8 @@
       <c r="D24" s="251">
         <v>1</v>
       </c>
-      <c r="E24" s="326" t="s">
-        <v>150</v>
+      <c r="E24" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="212"/>
@@ -8823,15 +8808,15 @@
       <c r="W24" s="255"/>
       <c r="X24" s="256"/>
       <c r="Y24" s="330" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z24" s="391"/>
-      <c r="AA24" s="391"/>
-      <c r="AB24" s="391"/>
-      <c r="AC24" s="391"/>
-      <c r="AD24" s="391"/>
-      <c r="AE24" s="391"/>
-      <c r="AF24" s="391"/>
+        <v>102</v>
+      </c>
+      <c r="Z24" s="398"/>
+      <c r="AA24" s="398"/>
+      <c r="AB24" s="398"/>
+      <c r="AC24" s="398"/>
+      <c r="AD24" s="398"/>
+      <c r="AE24" s="398"/>
+      <c r="AF24" s="398"/>
       <c r="AG24" s="2"/>
       <c r="AH24" s="2"/>
       <c r="AI24" s="2"/>
@@ -8913,7 +8898,7 @@
     </row>
     <row r="25" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A25" s="281" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B25" s="213" t="s">
         <v>62</v>
@@ -8924,8 +8909,8 @@
       <c r="D25" s="251">
         <v>1</v>
       </c>
-      <c r="E25" s="326" t="s">
-        <v>149</v>
+      <c r="E25" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F25" s="211"/>
       <c r="G25" s="212"/>
@@ -8947,15 +8932,15 @@
       <c r="W25" s="255"/>
       <c r="X25" s="256"/>
       <c r="Y25" s="330" t="s">
-        <v>105</v>
-      </c>
-      <c r="Z25" s="391"/>
-      <c r="AA25" s="391"/>
-      <c r="AB25" s="391"/>
-      <c r="AC25" s="391"/>
-      <c r="AD25" s="391"/>
-      <c r="AE25" s="391"/>
-      <c r="AF25" s="391"/>
+        <v>104</v>
+      </c>
+      <c r="Z25" s="398"/>
+      <c r="AA25" s="398"/>
+      <c r="AB25" s="398"/>
+      <c r="AC25" s="398"/>
+      <c r="AD25" s="398"/>
+      <c r="AE25" s="398"/>
+      <c r="AF25" s="398"/>
       <c r="AG25" s="2"/>
       <c r="AH25" s="2"/>
       <c r="AI25" s="2"/>
@@ -9037,7 +9022,7 @@
     </row>
     <row r="26" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A26" s="281" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B26" s="213" t="s">
         <v>62</v>
@@ -9048,8 +9033,8 @@
       <c r="D26" s="251">
         <v>1</v>
       </c>
-      <c r="E26" s="326" t="s">
-        <v>150</v>
+      <c r="E26" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F26" s="215"/>
       <c r="G26" s="216" t="s">
@@ -9073,15 +9058,15 @@
       <c r="W26" s="2"/>
       <c r="X26" s="2"/>
       <c r="Y26" s="330" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z26" s="391"/>
-      <c r="AA26" s="391"/>
-      <c r="AB26" s="391"/>
-      <c r="AC26" s="391"/>
-      <c r="AD26" s="391"/>
-      <c r="AE26" s="391"/>
-      <c r="AF26" s="391"/>
+        <v>107</v>
+      </c>
+      <c r="Z26" s="398"/>
+      <c r="AA26" s="398"/>
+      <c r="AB26" s="398"/>
+      <c r="AC26" s="398"/>
+      <c r="AD26" s="398"/>
+      <c r="AE26" s="398"/>
+      <c r="AF26" s="398"/>
       <c r="AG26" s="2"/>
       <c r="AH26" s="2"/>
       <c r="AI26" s="2"/>
@@ -9163,7 +9148,7 @@
     </row>
     <row r="27" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A27" s="281" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B27" s="213" t="s">
         <v>62</v>
@@ -9174,8 +9159,8 @@
       <c r="D27" s="251">
         <v>1</v>
       </c>
-      <c r="E27" s="326" t="s">
-        <v>150</v>
+      <c r="E27" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F27" s="215"/>
       <c r="G27" s="216" t="s">
@@ -9198,16 +9183,16 @@
       <c r="V27" s="2"/>
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
-      <c r="AF27" s="389" t="s">
-        <v>109</v>
-      </c>
-      <c r="AG27" s="389"/>
-      <c r="AH27" s="389"/>
-      <c r="AI27" s="389"/>
-      <c r="AJ27" s="389"/>
-      <c r="AK27" s="389"/>
-      <c r="AL27" s="389"/>
-      <c r="AM27" s="389"/>
+      <c r="AF27" s="335" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG27" s="335"/>
+      <c r="AH27" s="335"/>
+      <c r="AI27" s="335"/>
+      <c r="AJ27" s="335"/>
+      <c r="AK27" s="335"/>
+      <c r="AL27" s="335"/>
+      <c r="AM27" s="335"/>
       <c r="AN27" s="263"/>
       <c r="AO27" s="2"/>
       <c r="AP27" s="2"/>
@@ -9282,7 +9267,7 @@
     </row>
     <row r="28" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A28" s="281" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B28" s="214" t="s">
         <v>73</v>
@@ -9293,8 +9278,8 @@
       <c r="D28" s="251">
         <v>1</v>
       </c>
-      <c r="E28" s="326" t="s">
-        <v>150</v>
+      <c r="E28" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F28" s="215"/>
       <c r="G28" s="216"/>
@@ -9322,16 +9307,16 @@
       <c r="AC28" s="263"/>
       <c r="AD28" s="263"/>
       <c r="AE28" s="263"/>
-      <c r="AF28" s="389" t="s">
-        <v>110</v>
-      </c>
-      <c r="AG28" s="389"/>
-      <c r="AH28" s="389"/>
-      <c r="AI28" s="389"/>
-      <c r="AJ28" s="389"/>
-      <c r="AK28" s="389"/>
-      <c r="AL28" s="389"/>
-      <c r="AM28" s="389"/>
+      <c r="AF28" s="335" t="s">
+        <v>109</v>
+      </c>
+      <c r="AG28" s="335"/>
+      <c r="AH28" s="335"/>
+      <c r="AI28" s="335"/>
+      <c r="AJ28" s="335"/>
+      <c r="AK28" s="335"/>
+      <c r="AL28" s="335"/>
+      <c r="AM28" s="335"/>
       <c r="AN28" s="2"/>
       <c r="AO28" s="2"/>
       <c r="AP28" s="2"/>
@@ -9406,7 +9391,7 @@
     </row>
     <row r="29" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A29" s="281" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B29" s="214" t="s">
         <v>73</v>
@@ -9417,8 +9402,8 @@
       <c r="D29" s="251">
         <v>1</v>
       </c>
-      <c r="E29" s="326" t="s">
-        <v>150</v>
+      <c r="E29" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F29" s="215"/>
       <c r="G29" s="216"/>
@@ -9446,16 +9431,16 @@
       <c r="AC29" s="267"/>
       <c r="AD29" s="268"/>
       <c r="AE29" s="269"/>
-      <c r="AF29" s="389" t="s">
-        <v>111</v>
-      </c>
-      <c r="AG29" s="389"/>
-      <c r="AH29" s="389"/>
-      <c r="AI29" s="389"/>
-      <c r="AJ29" s="389"/>
-      <c r="AK29" s="389"/>
-      <c r="AL29" s="389"/>
-      <c r="AM29" s="389"/>
+      <c r="AF29" s="335" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG29" s="335"/>
+      <c r="AH29" s="335"/>
+      <c r="AI29" s="335"/>
+      <c r="AJ29" s="335"/>
+      <c r="AK29" s="335"/>
+      <c r="AL29" s="335"/>
+      <c r="AM29" s="335"/>
       <c r="AN29" s="2"/>
       <c r="AO29" s="2"/>
       <c r="AP29" s="2"/>
@@ -9530,7 +9515,7 @@
     </row>
     <row r="30" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A30" s="281" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B30" s="214" t="s">
         <v>73</v>
@@ -9541,8 +9526,8 @@
       <c r="D30" s="251">
         <v>1</v>
       </c>
-      <c r="E30" s="326" t="s">
-        <v>149</v>
+      <c r="E30" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F30" s="215"/>
       <c r="G30" s="216"/>
@@ -9570,16 +9555,16 @@
       <c r="AC30" s="267"/>
       <c r="AD30" s="268"/>
       <c r="AE30" s="269"/>
-      <c r="AF30" s="389" t="s">
-        <v>114</v>
-      </c>
-      <c r="AG30" s="389"/>
-      <c r="AH30" s="389"/>
-      <c r="AI30" s="389"/>
-      <c r="AJ30" s="389"/>
-      <c r="AK30" s="389"/>
-      <c r="AL30" s="389"/>
-      <c r="AM30" s="389"/>
+      <c r="AF30" s="335" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG30" s="335"/>
+      <c r="AH30" s="335"/>
+      <c r="AI30" s="335"/>
+      <c r="AJ30" s="335"/>
+      <c r="AK30" s="335"/>
+      <c r="AL30" s="335"/>
+      <c r="AM30" s="335"/>
       <c r="AN30" s="2"/>
       <c r="AO30" s="2"/>
       <c r="AP30" s="2"/>
@@ -9654,7 +9639,7 @@
     </row>
     <row r="31" spans="1:110" ht="17.5" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A31" s="281" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B31" s="214" t="s">
         <v>73</v>
@@ -9665,8 +9650,8 @@
       <c r="D31" s="251">
         <v>1</v>
       </c>
-      <c r="E31" s="326" t="s">
-        <v>149</v>
+      <c r="E31" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F31" s="217"/>
       <c r="G31" s="218" t="s">
@@ -9696,16 +9681,16 @@
       <c r="AC31" s="2"/>
       <c r="AD31" s="272"/>
       <c r="AE31" s="273"/>
-      <c r="AF31" s="389" t="s">
-        <v>115</v>
-      </c>
-      <c r="AG31" s="389"/>
-      <c r="AH31" s="389"/>
-      <c r="AI31" s="389"/>
-      <c r="AJ31" s="389"/>
-      <c r="AK31" s="389"/>
-      <c r="AL31" s="389"/>
-      <c r="AM31" s="389"/>
+      <c r="AF31" s="335" t="s">
+        <v>114</v>
+      </c>
+      <c r="AG31" s="335"/>
+      <c r="AH31" s="335"/>
+      <c r="AI31" s="335"/>
+      <c r="AJ31" s="335"/>
+      <c r="AK31" s="335"/>
+      <c r="AL31" s="335"/>
+      <c r="AM31" s="335"/>
       <c r="AN31" s="2"/>
       <c r="AO31" s="2"/>
       <c r="AP31" s="2"/>
@@ -9780,7 +9765,7 @@
     </row>
     <row r="32" spans="1:110" ht="17.5" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A32" s="281" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B32" s="214" t="s">
         <v>73</v>
@@ -9791,8 +9776,8 @@
       <c r="D32" s="251">
         <v>1</v>
       </c>
-      <c r="E32" s="326" t="s">
-        <v>149</v>
+      <c r="E32" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F32" s="217"/>
       <c r="G32" s="218" t="s">
@@ -9822,16 +9807,16 @@
       <c r="AC32" s="2"/>
       <c r="AD32" s="272"/>
       <c r="AE32" s="273"/>
-      <c r="AF32" s="389" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG32" s="389"/>
-      <c r="AH32" s="389"/>
-      <c r="AI32" s="389"/>
-      <c r="AJ32" s="389"/>
-      <c r="AK32" s="389"/>
-      <c r="AL32" s="389"/>
-      <c r="AM32" s="389"/>
+      <c r="AF32" s="335" t="s">
+        <v>116</v>
+      </c>
+      <c r="AG32" s="335"/>
+      <c r="AH32" s="335"/>
+      <c r="AI32" s="335"/>
+      <c r="AJ32" s="335"/>
+      <c r="AK32" s="335"/>
+      <c r="AL32" s="335"/>
+      <c r="AM32" s="335"/>
       <c r="AN32" s="2"/>
       <c r="AO32" s="2"/>
       <c r="AP32" s="2"/>
@@ -9917,8 +9902,8 @@
       <c r="D33" s="274">
         <v>1</v>
       </c>
-      <c r="E33" s="326" t="s">
-        <v>151</v>
+      <c r="E33" s="322" t="s">
+        <v>149</v>
       </c>
       <c r="F33" s="219"/>
       <c r="G33" s="220" t="s">
@@ -9947,38 +9932,38 @@
       <c r="AB33" s="2"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="2"/>
-      <c r="AE33" s="364"/>
-      <c r="AF33" s="365" t="s">
+      <c r="AE33" s="377"/>
+      <c r="AF33" s="378" t="s">
         <v>77</v>
       </c>
-      <c r="AG33" s="366" t="s">
+      <c r="AG33" s="379" t="s">
         <v>77</v>
       </c>
-      <c r="AH33" s="367" t="s">
+      <c r="AH33" s="380" t="s">
         <v>77</v>
       </c>
-      <c r="AI33" s="368" t="s">
+      <c r="AI33" s="381" t="s">
         <v>77</v>
       </c>
-      <c r="AJ33" s="369" t="s">
+      <c r="AJ33" s="382" t="s">
         <v>77</v>
       </c>
-      <c r="AK33" s="370" t="s">
+      <c r="AK33" s="383" t="s">
         <v>77</v>
       </c>
-      <c r="AL33" s="371" t="s">
+      <c r="AL33" s="384" t="s">
         <v>77</v>
       </c>
       <c r="AM33" s="281"/>
       <c r="AN33" s="281"/>
-      <c r="AO33" s="372" t="s">
-        <v>119</v>
-      </c>
-      <c r="AP33" s="372"/>
-      <c r="AQ33" s="372"/>
-      <c r="AR33" s="372"/>
-      <c r="AS33" s="372"/>
-      <c r="AT33" s="372"/>
+      <c r="AO33" s="332" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP33" s="332"/>
+      <c r="AQ33" s="332"/>
+      <c r="AR33" s="332"/>
+      <c r="AS33" s="332"/>
+      <c r="AT33" s="332"/>
       <c r="AU33" s="2"/>
       <c r="AV33" s="2"/>
       <c r="AW33" s="2"/>
@@ -10046,7 +10031,7 @@
     </row>
     <row r="34" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A34" s="281" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B34" s="221" t="s">
         <v>75</v>
@@ -10057,8 +10042,8 @@
       <c r="D34" s="278">
         <v>1</v>
       </c>
-      <c r="E34" s="326" t="s">
-        <v>151</v>
+      <c r="E34" s="322" t="s">
+        <v>149</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="224" t="s">
@@ -10095,16 +10080,16 @@
       <c r="AJ34" s="2"/>
       <c r="AK34" s="275"/>
       <c r="AL34" s="276"/>
-      <c r="AM34" s="324"/>
-      <c r="AN34" s="325"/>
-      <c r="AO34" s="372" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP34" s="372"/>
-      <c r="AQ34" s="372"/>
-      <c r="AR34" s="372"/>
-      <c r="AS34" s="372"/>
-      <c r="AT34" s="372"/>
+      <c r="AM34" s="320"/>
+      <c r="AN34" s="321"/>
+      <c r="AO34" s="332" t="s">
+        <v>127</v>
+      </c>
+      <c r="AP34" s="332"/>
+      <c r="AQ34" s="332"/>
+      <c r="AR34" s="332"/>
+      <c r="AS34" s="332"/>
+      <c r="AT34" s="332"/>
       <c r="AU34" s="2"/>
       <c r="AV34" s="2"/>
       <c r="AW34" s="2"/>
@@ -10183,8 +10168,8 @@
       <c r="D35" s="278">
         <v>1</v>
       </c>
-      <c r="E35" s="326" t="s">
-        <v>150</v>
+      <c r="E35" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F35" s="223"/>
       <c r="G35" s="224"/>
@@ -10220,34 +10205,34 @@
       <c r="AK35" s="275"/>
       <c r="AL35" s="276"/>
       <c r="AM35" s="277"/>
-      <c r="AN35" s="321"/>
-      <c r="AO35" s="322"/>
-      <c r="AP35" s="322"/>
-      <c r="AQ35" s="322"/>
-      <c r="AR35" s="322"/>
-      <c r="AS35" s="322"/>
-      <c r="AT35" s="333" t="s">
-        <v>120</v>
-      </c>
-      <c r="AU35" s="334" t="s">
+      <c r="AN35" s="318"/>
+      <c r="AO35" s="319"/>
+      <c r="AP35" s="319"/>
+      <c r="AQ35" s="319"/>
+      <c r="AR35" s="319"/>
+      <c r="AS35" s="319"/>
+      <c r="AT35" s="336" t="s">
+        <v>119</v>
+      </c>
+      <c r="AU35" s="347" t="s">
         <v>81</v>
       </c>
-      <c r="AV35" s="335" t="s">
+      <c r="AV35" s="348" t="s">
         <v>81</v>
       </c>
-      <c r="AW35" s="336" t="s">
+      <c r="AW35" s="349" t="s">
         <v>81</v>
       </c>
-      <c r="AX35" s="337" t="s">
+      <c r="AX35" s="350" t="s">
         <v>81</v>
       </c>
-      <c r="AY35" s="338" t="s">
+      <c r="AY35" s="351" t="s">
         <v>81</v>
       </c>
-      <c r="AZ35" s="339" t="s">
+      <c r="AZ35" s="352" t="s">
         <v>81</v>
       </c>
-      <c r="BA35" s="340" t="s">
+      <c r="BA35" s="353" t="s">
         <v>81</v>
       </c>
       <c r="BB35" s="2"/>
@@ -10310,7 +10295,7 @@
     </row>
     <row r="36" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A36" s="281" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B36" s="225" t="s">
         <v>79</v>
@@ -10321,8 +10306,8 @@
       <c r="D36" s="278">
         <v>1</v>
       </c>
-      <c r="E36" s="326" t="s">
-        <v>150</v>
+      <c r="E36" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F36" s="227"/>
       <c r="G36" s="228"/>
@@ -10364,28 +10349,28 @@
       <c r="AQ36" s="2"/>
       <c r="AR36" s="2"/>
       <c r="AS36" s="2"/>
-      <c r="AT36" s="333" t="s">
-        <v>124</v>
-      </c>
-      <c r="AU36" s="334" t="s">
+      <c r="AT36" s="336" t="s">
+        <v>123</v>
+      </c>
+      <c r="AU36" s="347" t="s">
         <v>81</v>
       </c>
-      <c r="AV36" s="335" t="s">
+      <c r="AV36" s="348" t="s">
         <v>81</v>
       </c>
-      <c r="AW36" s="336" t="s">
+      <c r="AW36" s="349" t="s">
         <v>81</v>
       </c>
-      <c r="AX36" s="337" t="s">
+      <c r="AX36" s="350" t="s">
         <v>81</v>
       </c>
-      <c r="AY36" s="338" t="s">
+      <c r="AY36" s="351" t="s">
         <v>81</v>
       </c>
-      <c r="AZ36" s="339" t="s">
+      <c r="AZ36" s="352" t="s">
         <v>81</v>
       </c>
-      <c r="BA36" s="340" t="s">
+      <c r="BA36" s="353" t="s">
         <v>81</v>
       </c>
       <c r="BB36" s="2"/>
@@ -10448,7 +10433,7 @@
     </row>
     <row r="37" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A37" s="281" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B37" s="225" t="s">
         <v>79</v>
@@ -10459,8 +10444,8 @@
       <c r="D37" s="278">
         <v>1</v>
       </c>
-      <c r="E37" s="326" t="s">
-        <v>149</v>
+      <c r="E37" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F37" s="227"/>
       <c r="G37" s="228"/>
@@ -10502,28 +10487,28 @@
       <c r="AQ37" s="2"/>
       <c r="AR37" s="2"/>
       <c r="AS37" s="2"/>
-      <c r="AT37" s="333" t="s">
-        <v>123</v>
-      </c>
-      <c r="AU37" s="334" t="s">
+      <c r="AT37" s="336" t="s">
+        <v>122</v>
+      </c>
+      <c r="AU37" s="347" t="s">
         <v>81</v>
       </c>
-      <c r="AV37" s="335" t="s">
+      <c r="AV37" s="348" t="s">
         <v>81</v>
       </c>
-      <c r="AW37" s="336" t="s">
+      <c r="AW37" s="349" t="s">
         <v>81</v>
       </c>
-      <c r="AX37" s="337" t="s">
+      <c r="AX37" s="350" t="s">
         <v>81</v>
       </c>
-      <c r="AY37" s="338" t="s">
+      <c r="AY37" s="351" t="s">
         <v>81</v>
       </c>
-      <c r="AZ37" s="339" t="s">
+      <c r="AZ37" s="352" t="s">
         <v>81</v>
       </c>
-      <c r="BA37" s="340" t="s">
+      <c r="BA37" s="353" t="s">
         <v>81</v>
       </c>
       <c r="BB37" s="2"/>
@@ -10586,7 +10571,7 @@
     </row>
     <row r="38" spans="1:110" ht="19.5" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A38" s="281" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B38" s="230" t="s">
         <v>80</v>
@@ -10597,8 +10582,8 @@
       <c r="D38" s="282">
         <v>0.75</v>
       </c>
-      <c r="E38" s="326" t="s">
-        <v>149</v>
+      <c r="E38" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="229" t="s">
@@ -10650,15 +10635,15 @@
       <c r="AY38" s="2"/>
       <c r="AZ38" s="2"/>
       <c r="BA38" s="330" t="s">
-        <v>147</v>
-      </c>
-      <c r="BB38" s="432"/>
-      <c r="BC38" s="432"/>
-      <c r="BD38" s="432"/>
-      <c r="BE38" s="432"/>
-      <c r="BF38" s="432"/>
-      <c r="BG38" s="432"/>
-      <c r="BH38" s="432"/>
+        <v>146</v>
+      </c>
+      <c r="BB38" s="333"/>
+      <c r="BC38" s="333"/>
+      <c r="BD38" s="333"/>
+      <c r="BE38" s="333"/>
+      <c r="BF38" s="333"/>
+      <c r="BG38" s="333"/>
+      <c r="BH38" s="333"/>
       <c r="BI38" s="283"/>
       <c r="BJ38" s="284"/>
       <c r="BK38" s="285"/>
@@ -10712,7 +10697,7 @@
     </row>
     <row r="39" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A39" s="281" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B39" s="230" t="s">
         <v>80</v>
@@ -10723,8 +10708,8 @@
       <c r="D39" s="280">
         <v>1</v>
       </c>
-      <c r="E39" s="326" t="s">
-        <v>149</v>
+      <c r="E39" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F39" s="6"/>
       <c r="G39" s="231" t="s">
@@ -10776,15 +10761,15 @@
       <c r="AY39" s="2"/>
       <c r="AZ39" s="2"/>
       <c r="BA39" s="330" t="s">
-        <v>125</v>
-      </c>
-      <c r="BB39" s="332"/>
-      <c r="BC39" s="332"/>
-      <c r="BD39" s="332"/>
-      <c r="BE39" s="332"/>
-      <c r="BF39" s="332"/>
-      <c r="BG39" s="332"/>
-      <c r="BH39" s="332"/>
+        <v>124</v>
+      </c>
+      <c r="BB39" s="334"/>
+      <c r="BC39" s="334"/>
+      <c r="BD39" s="334"/>
+      <c r="BE39" s="334"/>
+      <c r="BF39" s="334"/>
+      <c r="BG39" s="334"/>
+      <c r="BH39" s="334"/>
       <c r="BI39" s="292"/>
       <c r="BJ39" s="293"/>
       <c r="BK39" s="294"/>
@@ -10838,7 +10823,7 @@
     </row>
     <row r="40" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A40" s="281" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B40" s="230" t="s">
         <v>80</v>
@@ -10849,8 +10834,8 @@
       <c r="D40" s="280">
         <v>1</v>
       </c>
-      <c r="E40" s="326" t="s">
-        <v>150</v>
+      <c r="E40" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="231"/>
@@ -10900,7 +10885,7 @@
       <c r="AY40" s="2"/>
       <c r="AZ40" s="2"/>
       <c r="BA40" s="330" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="BB40" s="330"/>
       <c r="BC40" s="330"/>
@@ -10962,7 +10947,7 @@
     </row>
     <row r="41" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A41" s="281" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B41" s="230" t="s">
         <v>80</v>
@@ -10973,8 +10958,8 @@
       <c r="D41" s="280">
         <v>1</v>
       </c>
-      <c r="E41" s="326" t="s">
-        <v>150</v>
+      <c r="E41" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="231"/>
@@ -11024,7 +11009,7 @@
       <c r="AY41" s="2"/>
       <c r="AZ41" s="2"/>
       <c r="BA41" s="330" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="BB41" s="330"/>
       <c r="BC41" s="330"/>
@@ -11086,7 +11071,7 @@
     </row>
     <row r="42" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A42" s="281" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B42" s="230" t="s">
         <v>80</v>
@@ -11097,8 +11082,8 @@
       <c r="D42" s="280">
         <v>1</v>
       </c>
-      <c r="E42" s="326" t="s">
-        <v>150</v>
+      <c r="E42" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="231"/>
@@ -11148,7 +11133,7 @@
       <c r="AY42" s="2"/>
       <c r="AZ42" s="2"/>
       <c r="BA42" s="330" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="BB42" s="330"/>
       <c r="BC42" s="330"/>
@@ -11210,7 +11195,7 @@
     </row>
     <row r="43" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A43" s="281" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B43" s="230" t="s">
         <v>80</v>
@@ -11221,8 +11206,8 @@
       <c r="D43" s="280">
         <v>1</v>
       </c>
-      <c r="E43" s="326" t="s">
-        <v>150</v>
+      <c r="E43" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="231"/>
@@ -11272,7 +11257,7 @@
       <c r="AY43" s="2"/>
       <c r="AZ43" s="2"/>
       <c r="BA43" s="330" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="BB43" s="330"/>
       <c r="BC43" s="330"/>
@@ -11334,7 +11319,7 @@
     </row>
     <row r="44" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A44" s="281" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B44" s="230" t="s">
         <v>80</v>
@@ -11345,8 +11330,8 @@
       <c r="D44" s="280">
         <v>1</v>
       </c>
-      <c r="E44" s="326" t="s">
-        <v>149</v>
+      <c r="E44" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="231"/>
@@ -11396,7 +11381,7 @@
       <c r="AY44" s="2"/>
       <c r="AZ44" s="2"/>
       <c r="BA44" s="330" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="BB44" s="330"/>
       <c r="BC44" s="330"/>
@@ -11458,7 +11443,7 @@
     </row>
     <row r="45" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A45" s="281" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B45" s="230" t="s">
         <v>80</v>
@@ -11469,8 +11454,8 @@
       <c r="D45" s="280">
         <v>1</v>
       </c>
-      <c r="E45" s="326" t="s">
-        <v>150</v>
+      <c r="E45" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="231"/>
@@ -11520,7 +11505,7 @@
       <c r="AY45" s="2"/>
       <c r="AZ45" s="2"/>
       <c r="BA45" s="330" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="BB45" s="330"/>
       <c r="BC45" s="330"/>
@@ -11582,7 +11567,7 @@
     </row>
     <row r="46" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A46" s="281" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B46" s="230" t="s">
         <v>80</v>
@@ -11593,8 +11578,8 @@
       <c r="D46" s="280">
         <v>1</v>
       </c>
-      <c r="E46" s="326" t="s">
-        <v>149</v>
+      <c r="E46" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F46" s="6"/>
       <c r="G46" s="231"/>
@@ -11644,7 +11629,7 @@
       <c r="AY46" s="2"/>
       <c r="AZ46" s="2"/>
       <c r="BA46" s="330" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="BB46" s="330"/>
       <c r="BC46" s="330"/>
@@ -11706,7 +11691,7 @@
     </row>
     <row r="47" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A47" s="281" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B47" s="230" t="s">
         <v>80</v>
@@ -11717,8 +11702,8 @@
       <c r="D47" s="280">
         <v>1</v>
       </c>
-      <c r="E47" s="326" t="s">
-        <v>150</v>
+      <c r="E47" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="231"/>
@@ -11768,7 +11753,7 @@
       <c r="AY47" s="2"/>
       <c r="AZ47" s="2"/>
       <c r="BA47" s="330" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="BB47" s="330"/>
       <c r="BC47" s="330"/>
@@ -11830,7 +11815,7 @@
     </row>
     <row r="48" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A48" s="281" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B48" s="230" t="s">
         <v>80</v>
@@ -11841,8 +11826,8 @@
       <c r="D48" s="280">
         <v>1</v>
       </c>
-      <c r="E48" s="326" t="s">
-        <v>150</v>
+      <c r="E48" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="231"/>
@@ -11892,7 +11877,7 @@
       <c r="AY48" s="2"/>
       <c r="AZ48" s="2"/>
       <c r="BA48" s="330" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="BB48" s="330"/>
       <c r="BC48" s="330"/>
@@ -11954,7 +11939,7 @@
     </row>
     <row r="49" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A49" s="281" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B49" s="230" t="s">
         <v>80</v>
@@ -11965,8 +11950,8 @@
       <c r="D49" s="280">
         <v>1</v>
       </c>
-      <c r="E49" s="326" t="s">
-        <v>149</v>
+      <c r="E49" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="231"/>
@@ -12016,7 +12001,7 @@
       <c r="AY49" s="2"/>
       <c r="AZ49" s="2"/>
       <c r="BA49" s="330" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="BB49" s="330"/>
       <c r="BC49" s="330"/>
@@ -12078,7 +12063,7 @@
     </row>
     <row r="50" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A50" s="281" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B50" s="230" t="s">
         <v>80</v>
@@ -12089,8 +12074,8 @@
       <c r="D50" s="280">
         <v>1</v>
       </c>
-      <c r="E50" s="326" t="s">
-        <v>150</v>
+      <c r="E50" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="231"/>
@@ -12140,7 +12125,7 @@
       <c r="AY50" s="2"/>
       <c r="AZ50" s="2"/>
       <c r="BA50" s="330" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="BB50" s="330"/>
       <c r="BC50" s="330"/>
@@ -12202,7 +12187,7 @@
     </row>
     <row r="51" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A51" s="281" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B51" s="230" t="s">
         <v>80</v>
@@ -12213,8 +12198,8 @@
       <c r="D51" s="280">
         <v>1</v>
       </c>
-      <c r="E51" s="326" t="s">
-        <v>149</v>
+      <c r="E51" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="231"/>
@@ -12264,7 +12249,7 @@
       <c r="AY51" s="2"/>
       <c r="AZ51" s="2"/>
       <c r="BA51" s="330" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="BB51" s="330"/>
       <c r="BC51" s="330"/>
@@ -12326,7 +12311,7 @@
     </row>
     <row r="52" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A52" s="281" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B52" s="230" t="s">
         <v>80</v>
@@ -12337,8 +12322,8 @@
       <c r="D52" s="280">
         <v>1</v>
       </c>
-      <c r="E52" s="326" t="s">
-        <v>149</v>
+      <c r="E52" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="231"/>
@@ -12388,7 +12373,7 @@
       <c r="AY52" s="2"/>
       <c r="AZ52" s="2"/>
       <c r="BA52" s="330" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="BB52" s="330"/>
       <c r="BC52" s="330"/>
@@ -12450,7 +12435,7 @@
     </row>
     <row r="53" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A53" s="281" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B53" s="230" t="s">
         <v>80</v>
@@ -12461,8 +12446,8 @@
       <c r="D53" s="280">
         <v>1</v>
       </c>
-      <c r="E53" s="326" t="s">
-        <v>150</v>
+      <c r="E53" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="231"/>
@@ -12512,7 +12497,7 @@
       <c r="AY53" s="2"/>
       <c r="AZ53" s="2"/>
       <c r="BA53" s="330" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="BB53" s="330"/>
       <c r="BC53" s="330"/>
@@ -12574,7 +12559,7 @@
     </row>
     <row r="54" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A54" s="281" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B54" s="230" t="s">
         <v>80</v>
@@ -12585,8 +12570,8 @@
       <c r="D54" s="280">
         <v>1</v>
       </c>
-      <c r="E54" s="326" t="s">
-        <v>150</v>
+      <c r="E54" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="231"/>
@@ -12636,7 +12621,7 @@
       <c r="AY54" s="2"/>
       <c r="AZ54" s="2"/>
       <c r="BA54" s="330" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="BB54" s="330"/>
       <c r="BC54" s="330"/>
@@ -12698,7 +12683,7 @@
     </row>
     <row r="55" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A55" s="281" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B55" s="230" t="s">
         <v>80</v>
@@ -12709,8 +12694,8 @@
       <c r="D55" s="280">
         <v>1</v>
       </c>
-      <c r="E55" s="326" t="s">
-        <v>151</v>
+      <c r="E55" s="322" t="s">
+        <v>149</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="231"/>
@@ -12760,7 +12745,7 @@
       <c r="AY55" s="2"/>
       <c r="AZ55" s="2"/>
       <c r="BA55" s="330" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="BB55" s="330"/>
       <c r="BC55" s="330"/>
@@ -12822,7 +12807,7 @@
     </row>
     <row r="56" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A56" s="281" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B56" s="230" t="s">
         <v>80</v>
@@ -12833,8 +12818,8 @@
       <c r="D56" s="280">
         <v>1</v>
       </c>
-      <c r="E56" s="326" t="s">
-        <v>150</v>
+      <c r="E56" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="231"/>
@@ -12884,7 +12869,7 @@
       <c r="AY56" s="2"/>
       <c r="AZ56" s="2"/>
       <c r="BA56" s="330" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="BB56" s="330"/>
       <c r="BC56" s="330"/>
@@ -12946,7 +12931,7 @@
     </row>
     <row r="57" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A57" s="281" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B57" s="290">
         <v>46122</v>
@@ -12957,8 +12942,8 @@
       <c r="D57" s="280">
         <v>1</v>
       </c>
-      <c r="E57" s="326" t="s">
-        <v>150</v>
+      <c r="E57" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="231"/>
@@ -13007,24 +12992,24 @@
       <c r="AX57" s="2"/>
       <c r="AY57" s="2"/>
       <c r="AZ57" s="2"/>
-      <c r="BA57" s="327"/>
-      <c r="BB57" s="327"/>
-      <c r="BC57" s="327"/>
-      <c r="BD57" s="327"/>
-      <c r="BE57" s="327"/>
-      <c r="BF57" s="327"/>
-      <c r="BG57" s="327"/>
+      <c r="BA57" s="323"/>
+      <c r="BB57" s="323"/>
+      <c r="BC57" s="323"/>
+      <c r="BD57" s="323"/>
+      <c r="BE57" s="323"/>
+      <c r="BF57" s="323"/>
+      <c r="BG57" s="323"/>
       <c r="BH57" s="330" t="s">
-        <v>175</v>
-      </c>
-      <c r="BI57" s="433"/>
-      <c r="BJ57" s="433"/>
-      <c r="BK57" s="433"/>
-      <c r="BL57" s="433"/>
-      <c r="BM57" s="433"/>
-      <c r="BN57" s="433"/>
-      <c r="BO57" s="433"/>
-      <c r="BP57" s="328"/>
+        <v>171</v>
+      </c>
+      <c r="BI57" s="331"/>
+      <c r="BJ57" s="331"/>
+      <c r="BK57" s="331"/>
+      <c r="BL57" s="331"/>
+      <c r="BM57" s="331"/>
+      <c r="BN57" s="331"/>
+      <c r="BO57" s="331"/>
+      <c r="BP57" s="324"/>
       <c r="BQ57" s="2"/>
       <c r="BR57" s="2"/>
       <c r="BS57" s="2"/>
@@ -13070,7 +13055,7 @@
     </row>
     <row r="58" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A58" s="281" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B58" s="290">
         <v>46122</v>
@@ -13081,8 +13066,8 @@
       <c r="D58" s="280">
         <v>1</v>
       </c>
-      <c r="E58" s="326" t="s">
-        <v>150</v>
+      <c r="E58" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="231"/>
@@ -13131,23 +13116,23 @@
       <c r="AX58" s="2"/>
       <c r="AY58" s="2"/>
       <c r="AZ58" s="2"/>
-      <c r="BA58" s="327"/>
-      <c r="BB58" s="327"/>
-      <c r="BC58" s="327"/>
-      <c r="BD58" s="327"/>
-      <c r="BE58" s="327"/>
-      <c r="BF58" s="327"/>
-      <c r="BG58" s="327"/>
+      <c r="BA58" s="323"/>
+      <c r="BB58" s="323"/>
+      <c r="BC58" s="323"/>
+      <c r="BD58" s="323"/>
+      <c r="BE58" s="323"/>
+      <c r="BF58" s="323"/>
+      <c r="BG58" s="323"/>
       <c r="BH58" s="330" t="s">
-        <v>176</v>
-      </c>
-      <c r="BI58" s="433"/>
-      <c r="BJ58" s="433"/>
-      <c r="BK58" s="433"/>
-      <c r="BL58" s="433"/>
-      <c r="BM58" s="433"/>
-      <c r="BN58" s="433"/>
-      <c r="BO58" s="433"/>
+        <v>172</v>
+      </c>
+      <c r="BI58" s="331"/>
+      <c r="BJ58" s="331"/>
+      <c r="BK58" s="331"/>
+      <c r="BL58" s="331"/>
+      <c r="BM58" s="331"/>
+      <c r="BN58" s="331"/>
+      <c r="BO58" s="331"/>
       <c r="BP58" s="2"/>
       <c r="BQ58" s="2"/>
       <c r="BR58" s="2"/>
@@ -13194,7 +13179,7 @@
     </row>
     <row r="59" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A59" s="281" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B59" s="290">
         <v>46122</v>
@@ -13205,8 +13190,8 @@
       <c r="D59" s="280">
         <v>1</v>
       </c>
-      <c r="E59" s="326" t="s">
-        <v>150</v>
+      <c r="E59" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="231"/>
@@ -13255,23 +13240,23 @@
       <c r="AX59" s="2"/>
       <c r="AY59" s="2"/>
       <c r="AZ59" s="2"/>
-      <c r="BA59" s="327"/>
-      <c r="BB59" s="327"/>
-      <c r="BC59" s="327"/>
-      <c r="BD59" s="327"/>
-      <c r="BE59" s="327"/>
-      <c r="BF59" s="327"/>
-      <c r="BG59" s="327"/>
+      <c r="BA59" s="323"/>
+      <c r="BB59" s="323"/>
+      <c r="BC59" s="323"/>
+      <c r="BD59" s="323"/>
+      <c r="BE59" s="323"/>
+      <c r="BF59" s="323"/>
+      <c r="BG59" s="323"/>
       <c r="BH59" s="330" t="s">
-        <v>177</v>
-      </c>
-      <c r="BI59" s="433"/>
-      <c r="BJ59" s="433"/>
-      <c r="BK59" s="433"/>
-      <c r="BL59" s="433"/>
-      <c r="BM59" s="433"/>
-      <c r="BN59" s="433"/>
-      <c r="BO59" s="433"/>
+        <v>173</v>
+      </c>
+      <c r="BI59" s="331"/>
+      <c r="BJ59" s="331"/>
+      <c r="BK59" s="331"/>
+      <c r="BL59" s="331"/>
+      <c r="BM59" s="331"/>
+      <c r="BN59" s="331"/>
+      <c r="BO59" s="331"/>
       <c r="BP59" s="2"/>
       <c r="BQ59" s="2"/>
       <c r="BR59" s="2"/>
@@ -13318,7 +13303,7 @@
     </row>
     <row r="60" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A60" s="281" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B60" s="290">
         <v>46122</v>
@@ -13329,8 +13314,8 @@
       <c r="D60" s="280">
         <v>1</v>
       </c>
-      <c r="E60" s="326" t="s">
-        <v>182</v>
+      <c r="E60" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" s="231"/>
@@ -13379,23 +13364,23 @@
       <c r="AX60" s="2"/>
       <c r="AY60" s="2"/>
       <c r="AZ60" s="2"/>
-      <c r="BA60" s="327"/>
-      <c r="BB60" s="327"/>
-      <c r="BC60" s="327"/>
-      <c r="BD60" s="327"/>
-      <c r="BE60" s="327"/>
-      <c r="BF60" s="327"/>
-      <c r="BG60" s="327"/>
+      <c r="BA60" s="323"/>
+      <c r="BB60" s="323"/>
+      <c r="BC60" s="323"/>
+      <c r="BD60" s="323"/>
+      <c r="BE60" s="323"/>
+      <c r="BF60" s="323"/>
+      <c r="BG60" s="323"/>
       <c r="BH60" s="330" t="s">
-        <v>178</v>
-      </c>
-      <c r="BI60" s="433"/>
-      <c r="BJ60" s="433"/>
-      <c r="BK60" s="433"/>
-      <c r="BL60" s="433"/>
-      <c r="BM60" s="433"/>
-      <c r="BN60" s="433"/>
-      <c r="BO60" s="433"/>
+        <v>174</v>
+      </c>
+      <c r="BI60" s="331"/>
+      <c r="BJ60" s="331"/>
+      <c r="BK60" s="331"/>
+      <c r="BL60" s="331"/>
+      <c r="BM60" s="331"/>
+      <c r="BN60" s="331"/>
+      <c r="BO60" s="331"/>
       <c r="BP60" s="2"/>
       <c r="BQ60" s="2"/>
       <c r="BR60" s="2"/>
@@ -13441,8 +13426,8 @@
       <c r="DF60" s="2"/>
     </row>
     <row r="61" spans="1:110" ht="53.25" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A61" s="323" t="s">
-        <v>172</v>
+      <c r="A61" s="281" t="s">
+        <v>170</v>
       </c>
       <c r="B61" s="290">
         <v>46122</v>
@@ -13451,12 +13436,12 @@
         <v>83</v>
       </c>
       <c r="D61" s="280">
-        <v>0.95</v>
-      </c>
-      <c r="E61" s="326"/>
-      <c r="F61" s="6" t="s">
-        <v>173</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E61" s="322" t="s">
+        <v>149</v>
+      </c>
+      <c r="F61" s="6"/>
       <c r="G61" s="231"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -13503,23 +13488,23 @@
       <c r="AX61" s="2"/>
       <c r="AY61" s="2"/>
       <c r="AZ61" s="2"/>
-      <c r="BA61" s="327"/>
-      <c r="BB61" s="327"/>
-      <c r="BC61" s="327"/>
-      <c r="BD61" s="327"/>
-      <c r="BE61" s="327"/>
-      <c r="BF61" s="327"/>
-      <c r="BG61" s="327"/>
-      <c r="BH61" s="331" t="s">
-        <v>179</v>
-      </c>
-      <c r="BI61" s="436"/>
-      <c r="BJ61" s="436"/>
-      <c r="BK61" s="436"/>
-      <c r="BL61" s="436"/>
-      <c r="BM61" s="436"/>
-      <c r="BN61" s="436"/>
-      <c r="BO61" s="436"/>
+      <c r="BA61" s="323"/>
+      <c r="BB61" s="323"/>
+      <c r="BC61" s="323"/>
+      <c r="BD61" s="323"/>
+      <c r="BE61" s="323"/>
+      <c r="BF61" s="323"/>
+      <c r="BG61" s="323"/>
+      <c r="BH61" s="330" t="s">
+        <v>175</v>
+      </c>
+      <c r="BI61" s="331"/>
+      <c r="BJ61" s="331"/>
+      <c r="BK61" s="331"/>
+      <c r="BL61" s="331"/>
+      <c r="BM61" s="331"/>
+      <c r="BN61" s="331"/>
+      <c r="BO61" s="331"/>
       <c r="BP61" s="2"/>
       <c r="BQ61" s="2"/>
       <c r="BR61" s="2"/>
@@ -13577,8 +13562,8 @@
       <c r="D62" s="280">
         <v>1</v>
       </c>
-      <c r="E62" s="326" t="s">
-        <v>151</v>
+      <c r="E62" s="322" t="s">
+        <v>149</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="231"/>
@@ -13627,15 +13612,15 @@
       <c r="AX62" s="2"/>
       <c r="AY62" s="2"/>
       <c r="AZ62" s="2"/>
-      <c r="BA62" s="327"/>
-      <c r="BB62" s="327"/>
-      <c r="BC62" s="327"/>
-      <c r="BD62" s="327"/>
-      <c r="BE62" s="327"/>
-      <c r="BF62" s="327"/>
-      <c r="BG62" s="327"/>
+      <c r="BA62" s="323"/>
+      <c r="BB62" s="323"/>
+      <c r="BC62" s="323"/>
+      <c r="BD62" s="323"/>
+      <c r="BE62" s="323"/>
+      <c r="BF62" s="323"/>
+      <c r="BG62" s="323"/>
       <c r="BH62" s="330" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="BI62" s="330"/>
       <c r="BJ62" s="330"/>
@@ -13690,7 +13675,7 @@
     </row>
     <row r="63" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A63" s="281" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B63" s="290">
         <v>46122</v>
@@ -13701,8 +13686,8 @@
       <c r="D63" s="280">
         <v>1</v>
       </c>
-      <c r="E63" s="326" t="s">
-        <v>150</v>
+      <c r="E63" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="231"/>
@@ -13751,15 +13736,15 @@
       <c r="AX63" s="2"/>
       <c r="AY63" s="2"/>
       <c r="AZ63" s="2"/>
-      <c r="BA63" s="327"/>
-      <c r="BB63" s="327"/>
-      <c r="BC63" s="327"/>
-      <c r="BD63" s="327"/>
-      <c r="BE63" s="327"/>
-      <c r="BF63" s="327"/>
-      <c r="BG63" s="327"/>
+      <c r="BA63" s="323"/>
+      <c r="BB63" s="323"/>
+      <c r="BC63" s="323"/>
+      <c r="BD63" s="323"/>
+      <c r="BE63" s="323"/>
+      <c r="BF63" s="323"/>
+      <c r="BG63" s="323"/>
       <c r="BH63" s="330" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="BI63" s="330"/>
       <c r="BJ63" s="330"/>
@@ -13814,7 +13799,7 @@
     </row>
     <row r="64" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A64" s="281" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B64" s="290">
         <v>46122</v>
@@ -13825,8 +13810,8 @@
       <c r="D64" s="280">
         <v>1</v>
       </c>
-      <c r="E64" s="326" t="s">
-        <v>150</v>
+      <c r="E64" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F64" s="6"/>
       <c r="G64" s="231"/>
@@ -13875,15 +13860,15 @@
       <c r="AX64" s="2"/>
       <c r="AY64" s="2"/>
       <c r="AZ64" s="2"/>
-      <c r="BA64" s="327"/>
-      <c r="BB64" s="327"/>
-      <c r="BC64" s="327"/>
-      <c r="BD64" s="327"/>
-      <c r="BE64" s="327"/>
-      <c r="BF64" s="327"/>
-      <c r="BG64" s="327"/>
+      <c r="BA64" s="323"/>
+      <c r="BB64" s="323"/>
+      <c r="BC64" s="323"/>
+      <c r="BD64" s="323"/>
+      <c r="BE64" s="323"/>
+      <c r="BF64" s="323"/>
+      <c r="BG64" s="323"/>
       <c r="BH64" s="330" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="BI64" s="330"/>
       <c r="BJ64" s="330"/>
@@ -13938,7 +13923,7 @@
     </row>
     <row r="65" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A65" s="281" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B65" s="290">
         <v>46122</v>
@@ -13949,8 +13934,8 @@
       <c r="D65" s="280">
         <v>1</v>
       </c>
-      <c r="E65" s="326" t="s">
-        <v>150</v>
+      <c r="E65" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="231"/>
@@ -13999,15 +13984,15 @@
       <c r="AX65" s="2"/>
       <c r="AY65" s="2"/>
       <c r="AZ65" s="2"/>
-      <c r="BA65" s="327"/>
-      <c r="BB65" s="327"/>
-      <c r="BC65" s="327"/>
-      <c r="BD65" s="327"/>
-      <c r="BE65" s="327"/>
-      <c r="BF65" s="327"/>
-      <c r="BG65" s="327"/>
+      <c r="BA65" s="323"/>
+      <c r="BB65" s="323"/>
+      <c r="BC65" s="323"/>
+      <c r="BD65" s="323"/>
+      <c r="BE65" s="323"/>
+      <c r="BF65" s="323"/>
+      <c r="BG65" s="323"/>
       <c r="BH65" s="330" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="BI65" s="330"/>
       <c r="BJ65" s="330"/>
@@ -14062,7 +14047,7 @@
     </row>
     <row r="66" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A66" s="281" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B66" s="290">
         <v>46122</v>
@@ -14073,8 +14058,8 @@
       <c r="D66" s="280">
         <v>1</v>
       </c>
-      <c r="E66" s="326" t="s">
-        <v>150</v>
+      <c r="E66" s="322" t="s">
+        <v>148</v>
       </c>
       <c r="F66" s="6"/>
       <c r="G66" s="231"/>
@@ -14123,15 +14108,15 @@
       <c r="AX66" s="2"/>
       <c r="AY66" s="2"/>
       <c r="AZ66" s="2"/>
-      <c r="BA66" s="327"/>
-      <c r="BB66" s="327"/>
-      <c r="BC66" s="327"/>
-      <c r="BD66" s="327"/>
-      <c r="BE66" s="327"/>
-      <c r="BF66" s="327"/>
-      <c r="BG66" s="327"/>
+      <c r="BA66" s="323"/>
+      <c r="BB66" s="323"/>
+      <c r="BC66" s="323"/>
+      <c r="BD66" s="323"/>
+      <c r="BE66" s="323"/>
+      <c r="BF66" s="323"/>
+      <c r="BG66" s="323"/>
       <c r="BH66" s="330" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="BI66" s="330"/>
       <c r="BJ66" s="330"/>
@@ -14186,7 +14171,7 @@
     </row>
     <row r="67" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A67" s="281" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B67" s="290">
         <v>46122</v>
@@ -14197,8 +14182,8 @@
       <c r="D67" s="280">
         <v>1</v>
       </c>
-      <c r="E67" s="326" t="s">
-        <v>182</v>
+      <c r="E67" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="231"/>
@@ -14247,15 +14232,15 @@
       <c r="AX67" s="2"/>
       <c r="AY67" s="2"/>
       <c r="AZ67" s="2"/>
-      <c r="BA67" s="327"/>
-      <c r="BB67" s="327"/>
-      <c r="BC67" s="327"/>
-      <c r="BD67" s="327"/>
-      <c r="BE67" s="327"/>
-      <c r="BF67" s="327"/>
-      <c r="BG67" s="327"/>
+      <c r="BA67" s="323"/>
+      <c r="BB67" s="323"/>
+      <c r="BC67" s="323"/>
+      <c r="BD67" s="323"/>
+      <c r="BE67" s="323"/>
+      <c r="BF67" s="323"/>
+      <c r="BG67" s="323"/>
       <c r="BH67" s="330" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="BI67" s="330"/>
       <c r="BJ67" s="330"/>
@@ -14310,7 +14295,7 @@
     </row>
     <row r="68" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A68" s="281" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B68" s="290">
         <v>46122</v>
@@ -14321,8 +14306,8 @@
       <c r="D68" s="280">
         <v>1</v>
       </c>
-      <c r="E68" s="326" t="s">
-        <v>182</v>
+      <c r="E68" s="322" t="s">
+        <v>177</v>
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="231"/>
@@ -14371,15 +14356,15 @@
       <c r="AX68" s="2"/>
       <c r="AY68" s="2"/>
       <c r="AZ68" s="2"/>
-      <c r="BA68" s="327"/>
-      <c r="BB68" s="327"/>
-      <c r="BC68" s="327"/>
-      <c r="BD68" s="327"/>
-      <c r="BE68" s="327"/>
-      <c r="BF68" s="327"/>
-      <c r="BG68" s="327"/>
+      <c r="BA68" s="323"/>
+      <c r="BB68" s="323"/>
+      <c r="BC68" s="323"/>
+      <c r="BD68" s="323"/>
+      <c r="BE68" s="323"/>
+      <c r="BF68" s="323"/>
+      <c r="BG68" s="323"/>
       <c r="BH68" s="330" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="BI68" s="330"/>
       <c r="BJ68" s="330"/>
@@ -14434,7 +14419,7 @@
     </row>
     <row r="69" spans="1:110" x14ac:dyDescent="0.8">
       <c r="A69" s="281" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B69" s="290">
         <v>46122</v>
@@ -14442,11 +14427,11 @@
       <c r="C69" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D69" s="326">
+      <c r="D69" s="322">
         <v>1</v>
       </c>
-      <c r="E69" s="435" t="s">
-        <v>151</v>
+      <c r="E69" s="326" t="s">
+        <v>149</v>
       </c>
       <c r="F69" s="233"/>
       <c r="G69" s="234" t="s">
@@ -14505,15 +14490,15 @@
       <c r="BF69" s="303"/>
       <c r="BG69" s="304"/>
       <c r="BH69" s="330" t="s">
-        <v>180</v>
-      </c>
-      <c r="BI69" s="433"/>
-      <c r="BJ69" s="433"/>
-      <c r="BK69" s="433"/>
-      <c r="BL69" s="433"/>
-      <c r="BM69" s="433"/>
-      <c r="BN69" s="433"/>
-      <c r="BO69" s="433"/>
+        <v>176</v>
+      </c>
+      <c r="BI69" s="331"/>
+      <c r="BJ69" s="331"/>
+      <c r="BK69" s="331"/>
+      <c r="BL69" s="331"/>
+      <c r="BM69" s="331"/>
+      <c r="BN69" s="331"/>
+      <c r="BO69" s="331"/>
       <c r="BP69" s="2"/>
       <c r="BQ69" s="2"/>
       <c r="BR69" s="2"/>
@@ -14559,17 +14544,21 @@
       <c r="DF69" s="2"/>
     </row>
     <row r="70" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A70" s="2" t="s">
-        <v>84</v>
+      <c r="A70" s="281" t="s">
+        <v>207</v>
       </c>
       <c r="B70" s="291">
         <v>46129</v>
       </c>
-      <c r="C70" s="431">
+      <c r="C70" s="325">
         <v>46134</v>
       </c>
-      <c r="D70" s="235"/>
-      <c r="E70" s="235"/>
+      <c r="D70" s="327">
+        <v>1</v>
+      </c>
+      <c r="E70" s="326" t="s">
+        <v>149</v>
+      </c>
       <c r="F70" s="236"/>
       <c r="G70" s="237" t="s">
         <v>0</v>
@@ -14633,15 +14622,15 @@
       <c r="BL70" s="312"/>
       <c r="BM70" s="313"/>
       <c r="BN70" s="2"/>
-      <c r="BO70" s="329" t="s">
-        <v>195</v>
-      </c>
-      <c r="BP70" s="329"/>
-      <c r="BQ70" s="329"/>
-      <c r="BR70" s="329"/>
-      <c r="BS70" s="329"/>
-      <c r="BT70" s="434"/>
-      <c r="BU70" s="434"/>
+      <c r="BO70" s="332" t="s">
+        <v>208</v>
+      </c>
+      <c r="BP70" s="332"/>
+      <c r="BQ70" s="332"/>
+      <c r="BR70" s="332"/>
+      <c r="BS70" s="332"/>
+      <c r="BT70" s="2"/>
+      <c r="BU70" s="2"/>
       <c r="BV70" s="2"/>
       <c r="BW70" s="2"/>
       <c r="BX70" s="2"/>
@@ -14680,19 +14669,25 @@
       <c r="DE70" s="2"/>
       <c r="DF70" s="2"/>
     </row>
-    <row r="71" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A71" s="2" t="s">
-        <v>209</v>
+    <row r="71" spans="1:110" ht="48" x14ac:dyDescent="0.8">
+      <c r="A71" s="328" t="s">
+        <v>203</v>
       </c>
       <c r="B71" s="291">
         <v>46129</v>
       </c>
       <c r="C71" s="235" t="s">
-        <v>85</v>
-      </c>
-      <c r="D71" s="235"/>
-      <c r="E71" s="235"/>
-      <c r="F71" s="236"/>
+        <v>84</v>
+      </c>
+      <c r="D71" s="327">
+        <v>0</v>
+      </c>
+      <c r="E71" s="326" t="s">
+        <v>177</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>206</v>
+      </c>
       <c r="G71" s="237"/>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
@@ -14753,15 +14748,15 @@
       <c r="BL71" s="312"/>
       <c r="BM71" s="313"/>
       <c r="BN71" s="2"/>
-      <c r="BO71" s="329" t="s">
-        <v>203</v>
-      </c>
-      <c r="BP71" s="329"/>
-      <c r="BQ71" s="329"/>
-      <c r="BR71" s="329"/>
-      <c r="BS71" s="329"/>
-      <c r="BT71" s="329"/>
-      <c r="BU71" s="329"/>
+      <c r="BO71" s="434" t="s">
+        <v>197</v>
+      </c>
+      <c r="BP71" s="434"/>
+      <c r="BQ71" s="434"/>
+      <c r="BR71" s="434"/>
+      <c r="BS71" s="434"/>
+      <c r="BT71" s="434"/>
+      <c r="BU71" s="434"/>
       <c r="BV71" s="2"/>
       <c r="BW71" s="2"/>
       <c r="BX71" s="2"/>
@@ -14801,17 +14796,21 @@
       <c r="DF71" s="2"/>
     </row>
     <row r="72" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A72" s="2" t="s">
-        <v>204</v>
+      <c r="A72" s="281" t="s">
+        <v>198</v>
       </c>
       <c r="B72" s="291">
         <v>46129</v>
       </c>
       <c r="C72" s="235" t="s">
-        <v>85</v>
-      </c>
-      <c r="D72" s="235"/>
-      <c r="E72" s="235"/>
+        <v>84</v>
+      </c>
+      <c r="D72" s="327">
+        <v>1</v>
+      </c>
+      <c r="E72" s="326" t="s">
+        <v>148</v>
+      </c>
       <c r="F72" s="236"/>
       <c r="G72" s="237"/>
       <c r="H72" s="2"/>
@@ -14873,15 +14872,15 @@
       <c r="BL72" s="312"/>
       <c r="BM72" s="313"/>
       <c r="BN72" s="2"/>
-      <c r="BO72" s="329" t="s">
-        <v>205</v>
-      </c>
-      <c r="BP72" s="329"/>
-      <c r="BQ72" s="329"/>
-      <c r="BR72" s="329"/>
-      <c r="BS72" s="329"/>
-      <c r="BT72" s="329"/>
-      <c r="BU72" s="329"/>
+      <c r="BO72" s="332" t="s">
+        <v>199</v>
+      </c>
+      <c r="BP72" s="332"/>
+      <c r="BQ72" s="332"/>
+      <c r="BR72" s="332"/>
+      <c r="BS72" s="332"/>
+      <c r="BT72" s="332"/>
+      <c r="BU72" s="332"/>
       <c r="BV72" s="2"/>
       <c r="BW72" s="2"/>
       <c r="BX72" s="2"/>
@@ -14921,17 +14920,21 @@
       <c r="DF72" s="2"/>
     </row>
     <row r="73" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A73" s="2" t="s">
-        <v>194</v>
+      <c r="A73" s="281" t="s">
+        <v>189</v>
       </c>
       <c r="B73" s="291">
         <v>46129</v>
       </c>
       <c r="C73" s="235" t="s">
-        <v>85</v>
-      </c>
-      <c r="D73" s="235"/>
-      <c r="E73" s="235"/>
+        <v>84</v>
+      </c>
+      <c r="D73" s="327">
+        <v>1</v>
+      </c>
+      <c r="E73" s="326" t="s">
+        <v>148</v>
+      </c>
       <c r="F73" s="236"/>
       <c r="G73" s="237"/>
       <c r="H73" s="2"/>
@@ -14993,15 +14996,15 @@
       <c r="BL73" s="312"/>
       <c r="BM73" s="313"/>
       <c r="BN73" s="2"/>
-      <c r="BO73" s="329" t="s">
-        <v>206</v>
-      </c>
-      <c r="BP73" s="329"/>
-      <c r="BQ73" s="329"/>
-      <c r="BR73" s="329"/>
-      <c r="BS73" s="329"/>
-      <c r="BT73" s="329"/>
-      <c r="BU73" s="329"/>
+      <c r="BO73" s="332" t="s">
+        <v>200</v>
+      </c>
+      <c r="BP73" s="332"/>
+      <c r="BQ73" s="332"/>
+      <c r="BR73" s="332"/>
+      <c r="BS73" s="332"/>
+      <c r="BT73" s="332"/>
+      <c r="BU73" s="332"/>
       <c r="BV73" s="2"/>
       <c r="BW73" s="2"/>
       <c r="BX73" s="2"/>
@@ -15041,17 +15044,21 @@
       <c r="DF73" s="2"/>
     </row>
     <row r="74" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A74" s="2" t="s">
-        <v>193</v>
+      <c r="A74" s="281" t="s">
+        <v>188</v>
       </c>
       <c r="B74" s="291">
         <v>46129</v>
       </c>
       <c r="C74" s="235" t="s">
-        <v>85</v>
-      </c>
-      <c r="D74" s="235"/>
-      <c r="E74" s="235"/>
+        <v>84</v>
+      </c>
+      <c r="D74" s="327">
+        <v>1</v>
+      </c>
+      <c r="E74" s="326" t="s">
+        <v>148</v>
+      </c>
       <c r="F74" s="236"/>
       <c r="G74" s="237"/>
       <c r="H74" s="2"/>
@@ -15113,15 +15120,15 @@
       <c r="BL74" s="312"/>
       <c r="BM74" s="313"/>
       <c r="BN74" s="2"/>
-      <c r="BO74" s="329" t="s">
-        <v>207</v>
-      </c>
-      <c r="BP74" s="329"/>
-      <c r="BQ74" s="329"/>
-      <c r="BR74" s="329"/>
-      <c r="BS74" s="329"/>
-      <c r="BT74" s="329"/>
-      <c r="BU74" s="329"/>
+      <c r="BO74" s="332" t="s">
+        <v>201</v>
+      </c>
+      <c r="BP74" s="332"/>
+      <c r="BQ74" s="332"/>
+      <c r="BR74" s="332"/>
+      <c r="BS74" s="332"/>
+      <c r="BT74" s="332"/>
+      <c r="BU74" s="332"/>
       <c r="BV74" s="2"/>
       <c r="BW74" s="2"/>
       <c r="BX74" s="2"/>
@@ -15161,17 +15168,21 @@
       <c r="DF74" s="2"/>
     </row>
     <row r="75" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A75" s="2" t="s">
-        <v>192</v>
+      <c r="A75" s="281" t="s">
+        <v>187</v>
       </c>
       <c r="B75" s="291">
         <v>46129</v>
       </c>
       <c r="C75" s="235" t="s">
-        <v>85</v>
-      </c>
-      <c r="D75" s="238"/>
-      <c r="E75" s="238"/>
+        <v>84</v>
+      </c>
+      <c r="D75" s="329">
+        <v>1</v>
+      </c>
+      <c r="E75" s="326" t="s">
+        <v>148</v>
+      </c>
       <c r="F75" s="239"/>
       <c r="G75" s="240" t="s">
         <v>0</v>
@@ -15235,15 +15246,15 @@
       <c r="BL75" s="314"/>
       <c r="BM75" s="315"/>
       <c r="BN75" s="316"/>
-      <c r="BO75" s="329" t="s">
-        <v>208</v>
-      </c>
-      <c r="BP75" s="329"/>
-      <c r="BQ75" s="329"/>
-      <c r="BR75" s="329"/>
-      <c r="BS75" s="329"/>
-      <c r="BT75" s="329"/>
-      <c r="BU75" s="329"/>
+      <c r="BO75" s="332" t="s">
+        <v>202</v>
+      </c>
+      <c r="BP75" s="332"/>
+      <c r="BQ75" s="332"/>
+      <c r="BR75" s="332"/>
+      <c r="BS75" s="332"/>
+      <c r="BT75" s="332"/>
+      <c r="BU75" s="332"/>
       <c r="BV75" s="317"/>
       <c r="BW75" s="2"/>
       <c r="BX75" s="2"/>
@@ -15283,16 +15294,18 @@
       <c r="DF75" s="2"/>
     </row>
     <row r="76" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A76" s="2" t="s">
-        <v>210</v>
+      <c r="A76" s="432" t="s">
+        <v>209</v>
       </c>
       <c r="B76" s="291">
         <v>46129</v>
       </c>
       <c r="C76" s="235" t="s">
-        <v>85</v>
-      </c>
-      <c r="D76" s="238"/>
+        <v>84</v>
+      </c>
+      <c r="D76" s="329">
+        <v>0.75</v>
+      </c>
       <c r="E76" s="238"/>
       <c r="F76" s="239"/>
       <c r="G76" s="240"/>
@@ -15355,15 +15368,15 @@
       <c r="BL76" s="314"/>
       <c r="BM76" s="315"/>
       <c r="BN76" s="316"/>
-      <c r="BO76" s="329" t="s">
-        <v>211</v>
-      </c>
-      <c r="BP76" s="329"/>
-      <c r="BQ76" s="329"/>
-      <c r="BR76" s="329"/>
-      <c r="BS76" s="329"/>
-      <c r="BT76" s="329"/>
-      <c r="BU76" s="329"/>
+      <c r="BO76" s="433" t="s">
+        <v>204</v>
+      </c>
+      <c r="BP76" s="433"/>
+      <c r="BQ76" s="433"/>
+      <c r="BR76" s="433"/>
+      <c r="BS76" s="433"/>
+      <c r="BT76" s="433"/>
+      <c r="BU76" s="433"/>
       <c r="BV76" s="317"/>
       <c r="BW76" s="2"/>
       <c r="BX76" s="2"/>
@@ -15403,109 +15416,54 @@
       <c r="DF76" s="2"/>
     </row>
     <row r="77" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A77" s="2" t="s">
-        <v>174</v>
+      <c r="A77" s="281" t="s">
+        <v>186</v>
       </c>
       <c r="B77" s="291">
         <v>46129</v>
       </c>
       <c r="C77" s="235" t="s">
-        <v>85</v>
-      </c>
-      <c r="G77" s="240" t="s">
-        <v>0</v>
-      </c>
-      <c r="AT77" s="2"/>
-      <c r="AU77" s="2"/>
-      <c r="AV77" s="2"/>
-      <c r="AW77" s="2"/>
-      <c r="AX77" s="2"/>
-      <c r="AY77" s="2"/>
-      <c r="AZ77" s="2"/>
-      <c r="BA77" s="2"/>
-      <c r="BB77" s="2"/>
-      <c r="BC77" s="2"/>
-      <c r="BD77" s="2"/>
-      <c r="BE77" s="2"/>
-      <c r="BF77" s="2"/>
-      <c r="BG77" s="2"/>
-      <c r="BH77" s="2"/>
-      <c r="BI77" s="2"/>
-      <c r="BJ77" s="2"/>
-      <c r="BK77" s="2"/>
-      <c r="BL77" s="150"/>
-      <c r="BM77" s="318"/>
-      <c r="BN77" s="319"/>
-      <c r="BO77" s="329" t="s">
-        <v>181</v>
-      </c>
-      <c r="BP77" s="329"/>
-      <c r="BQ77" s="329"/>
-      <c r="BR77" s="329"/>
-      <c r="BS77" s="329"/>
-      <c r="BT77" s="329"/>
-      <c r="BU77" s="329"/>
-      <c r="BV77" s="320"/>
-      <c r="BW77" s="2"/>
-      <c r="BX77" s="2"/>
-      <c r="BY77" s="2"/>
-      <c r="BZ77" s="2"/>
-      <c r="CA77" s="2"/>
-      <c r="CB77" s="2"/>
-      <c r="CC77" s="2"/>
-      <c r="CD77" s="2"/>
-      <c r="CE77" s="2"/>
-      <c r="CF77" s="2"/>
-      <c r="CG77" s="2"/>
-      <c r="CH77" s="2"/>
-      <c r="CI77" s="2"/>
-      <c r="CJ77" s="2"/>
-      <c r="CK77" s="2"/>
-      <c r="CL77" s="2"/>
-      <c r="CM77" s="2"/>
-      <c r="CN77" s="2"/>
-      <c r="CO77" s="2"/>
-      <c r="CP77" s="2"/>
-      <c r="CQ77" s="2"/>
-      <c r="CR77" s="2"/>
-      <c r="CS77" s="2"/>
-      <c r="CT77" s="2"/>
-      <c r="CU77" s="2"/>
-      <c r="CV77" s="2"/>
-      <c r="CW77" s="2"/>
-      <c r="CX77" s="2"/>
-      <c r="CY77" s="2"/>
-      <c r="CZ77" s="2"/>
-      <c r="DA77" s="2"/>
-      <c r="DB77" s="2"/>
-      <c r="DC77" s="2"/>
-      <c r="DD77" s="2"/>
-      <c r="DE77" s="2"/>
-      <c r="DF77" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="D77" s="327">
+        <v>1</v>
+      </c>
+      <c r="E77" s="326" t="s">
+        <v>148</v>
+      </c>
+      <c r="BO77" s="332" t="s">
+        <v>205</v>
+      </c>
+      <c r="BP77" s="332"/>
+      <c r="BQ77" s="332"/>
+      <c r="BR77" s="332"/>
+      <c r="BS77" s="332"/>
+      <c r="BT77" s="332"/>
+      <c r="BU77" s="332"/>
     </row>
     <row r="78" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A78" s="2" t="s">
-        <v>191</v>
+      <c r="A78" s="435" t="s">
+        <v>210</v>
       </c>
       <c r="B78" s="291">
-        <v>46129</v>
-      </c>
-      <c r="C78" s="235" t="s">
-        <v>85</v>
-      </c>
-      <c r="BO78" s="329" t="s">
-        <v>212</v>
-      </c>
-      <c r="BP78" s="329"/>
-      <c r="BQ78" s="329"/>
-      <c r="BR78" s="329"/>
-      <c r="BS78" s="329"/>
-      <c r="BT78" s="329"/>
-      <c r="BU78" s="329"/>
+        <v>46134</v>
+      </c>
+      <c r="C78" s="291">
+        <v>46139</v>
+      </c>
+      <c r="BT78" s="436" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU78" s="436"/>
+      <c r="BV78" s="436"/>
+      <c r="BW78" s="436"/>
+      <c r="BX78" s="436"/>
+      <c r="BY78" s="436"/>
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="BO78:BU78"/>
+    <mergeCell ref="BT78:BY78"/>
+    <mergeCell ref="BO77:BU77"/>
     <mergeCell ref="AF31:AM31"/>
     <mergeCell ref="CC2:DF2"/>
     <mergeCell ref="Y24:AF24"/>
@@ -15558,6 +15516,13 @@
     <mergeCell ref="BA50:BH50"/>
     <mergeCell ref="BA52:BH52"/>
     <mergeCell ref="BH69:BO69"/>
+    <mergeCell ref="BA53:BH53"/>
+    <mergeCell ref="BA55:BH55"/>
+    <mergeCell ref="BA54:BH54"/>
+    <mergeCell ref="BA56:BH56"/>
+    <mergeCell ref="BA51:BH51"/>
+    <mergeCell ref="BH57:BO57"/>
+    <mergeCell ref="BO76:BU76"/>
     <mergeCell ref="BO70:BS70"/>
     <mergeCell ref="BH62:BO62"/>
     <mergeCell ref="BH63:BO63"/>
@@ -15566,13 +15531,6 @@
     <mergeCell ref="BH66:BO66"/>
     <mergeCell ref="BH67:BO67"/>
     <mergeCell ref="BH68:BO68"/>
-    <mergeCell ref="BA53:BH53"/>
-    <mergeCell ref="BA55:BH55"/>
-    <mergeCell ref="BA54:BH54"/>
-    <mergeCell ref="BA56:BH56"/>
-    <mergeCell ref="BA51:BH51"/>
-    <mergeCell ref="BH57:BO57"/>
-    <mergeCell ref="BO77:BU77"/>
     <mergeCell ref="BH61:BO61"/>
     <mergeCell ref="BH60:BO60"/>
     <mergeCell ref="BH59:BO59"/>
@@ -15582,11 +15540,11 @@
     <mergeCell ref="BO72:BU72"/>
     <mergeCell ref="BO73:BU73"/>
     <mergeCell ref="BO74:BU74"/>
-    <mergeCell ref="BO76:BU76"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="G1:DF4 A1:C4 G5 I5:DF5 G6:I6 G8:DF10 X7:DF7 G7:J7 A8:C10 B7 B5:C5 A13:C13 A12 B15:C15 A11:B11 G23:DF23 S16:DF16 A14 A17:C17 A16:B16 G14:O14 S14:DF14 A23 G18:DF18 G21:Q21 S21:DF21 G15:Q17 S17:DF17 S6:DF6 A21:C21 C6 G33:AD33 B26:C26 G26:X26 AG26:DF26 A33 G32:AC32 AQ32:DF32 S15:DF15 AT77:BJ77 AF33:AN33 AU33:DF33 G34:AJ34 B34:C34 B39 G11:DF13 BT38:DF38 G38:AZ39 A70 BS39:DF39 AT69:AZ69 BQ69:DF69 AT70:BD70 BV70:DF70 G75:BK75 BW75:DF75 CA77:DF77 G69:AS70" numberStoredAsText="1"/>
+    <ignoredError sqref="G1:DF4 A1:C4 G5 I5:DF5 G6:I6 G8:DF10 X7:DF7 G7:J7 A8:C10 B7 B5:C5 A13:C13 A12 B15:C15 A11:B11 G23:DF23 S16:DF16 A14 A17:C17 A16:B16 G14:O14 S14:DF14 A23 G18:DF18 G21:Q21 S21:DF21 G15:Q17 S17:DF17 S6:DF6 A21:C21 C6 G33:AD33 B26:C26 G26:X26 AG26:DF26 A33 G32:AC32 AQ32:DF32 S15:DF15 AF33:AN33 AU33:DF33 G34:AJ34 B34:C34 B39 G11:DF13 BT38:DF38 G38:AZ39 BS39:DF39 AT69:AZ69 BQ69:DF69 AT70:BD70 BV70:DF70 G75:BK75 BW75:DF75 G69:AS70" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Documentation/GanntChart/BattleNationsGanntChart.xlsx
+++ b/Documentation/GanntChart/BattleNationsGanntChart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jreig\git\BattleNations\Documentation\GanntChart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142F7CFD-1580-4713-AC11-3E3E6C5B1251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE83680C-E18C-44B9-97EB-D158884B7034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="215">
   <si>
     <t/>
   </si>
@@ -669,13 +669,22 @@
   </si>
   <si>
     <t>Prepare For Final Presentation (22-Apr-26 - 27-Apr-26)</t>
+  </si>
+  <si>
+    <t>Need to add code snippits</t>
+  </si>
+  <si>
+    <t>Finalize user manual</t>
+  </si>
+  <si>
+    <t>Finalize User Manual (22-Apr-26 - 27-Apr-26)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="353" x14ac:knownFonts="1">
+  <fonts count="354" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2803,6 +2812,12 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="150">
@@ -3713,7 +3728,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="437">
+  <cellXfs count="436">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4427,9 +4442,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="350" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="350" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="351" fillId="144" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4702,25 +4714,163 @@
     <xf numFmtId="9" fontId="350" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="146" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="149" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="145" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="145" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="331" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="253" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="145" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="229" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="231" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="232" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="233" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="234" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="235" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="236" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="240" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="241" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="242" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="243" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="244" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="245" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="246" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="145" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="311" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="229" fillId="145" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="322" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="249" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="250" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="251" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="252" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="253" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="254" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="255" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="256" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="257" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="258" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="259" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="260" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="145" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="141" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="219" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4851,149 +5001,14 @@
     <xf numFmtId="0" fontId="282" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="283" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="284" fillId="147" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="160" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="173" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="174" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="311" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="322" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="331" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="253" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="229" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="230" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="231" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="232" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="233" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="234" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="235" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="236" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="240" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="241" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="242" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="243" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="244" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="245" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="246" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="145" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="229" fillId="145" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="249" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="250" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="251" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="252" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="253" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="254" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="255" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="256" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="257" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="258" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="259" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="260" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="146" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="146" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5001,11 +5016,8 @@
     <xf numFmtId="0" fontId="0" fillId="148" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="149" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="353" fillId="145" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5346,7 +5358,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DF78"/>
+  <dimension ref="A1:DF79"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.8"/>
   <cols>
     <col min="1" max="1" width="52.83203125" customWidth="1"/>
@@ -5480,13 +5492,13 @@
       <c r="DF1" s="2"/>
     </row>
     <row r="2" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A2" s="391" t="s">
+      <c r="A2" s="377" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="392" t="s">
+      <c r="B2" s="334" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="392" t="s">
+      <c r="C2" s="334" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="11"/>
@@ -5495,313 +5507,313 @@
       <c r="G2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="393" t="s">
+      <c r="H2" s="378" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="392" t="s">
+      <c r="I2" s="334" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="392" t="s">
+      <c r="J2" s="334" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="392" t="s">
+      <c r="K2" s="334" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="392" t="s">
+      <c r="L2" s="334" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="392" t="s">
+      <c r="M2" s="334" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="392" t="s">
+      <c r="N2" s="334" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="392" t="s">
+      <c r="O2" s="334" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="392" t="s">
+      <c r="P2" s="334" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="392" t="s">
+      <c r="Q2" s="334" t="s">
         <v>2</v>
       </c>
-      <c r="R2" s="392" t="s">
+      <c r="R2" s="334" t="s">
         <v>2</v>
       </c>
-      <c r="S2" s="392" t="s">
+      <c r="S2" s="334" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="430" t="s">
+      <c r="T2" s="369" t="s">
         <v>3</v>
       </c>
-      <c r="U2" s="392" t="s">
+      <c r="U2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="V2" s="392" t="s">
+      <c r="V2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="W2" s="392" t="s">
+      <c r="W2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="X2" s="392" t="s">
+      <c r="X2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="Y2" s="392" t="s">
+      <c r="Y2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="Z2" s="392" t="s">
+      <c r="Z2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AA2" s="392" t="s">
+      <c r="AA2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AB2" s="392" t="s">
+      <c r="AB2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="392" t="s">
+      <c r="AC2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AD2" s="392" t="s">
+      <c r="AD2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AE2" s="392" t="s">
+      <c r="AE2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AF2" s="392" t="s">
+      <c r="AF2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AG2" s="392" t="s">
+      <c r="AG2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AH2" s="392" t="s">
+      <c r="AH2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AI2" s="392" t="s">
+      <c r="AI2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AJ2" s="392" t="s">
+      <c r="AJ2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AK2" s="392" t="s">
+      <c r="AK2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AL2" s="392" t="s">
+      <c r="AL2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AM2" s="392" t="s">
+      <c r="AM2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AN2" s="392" t="s">
+      <c r="AN2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AO2" s="392" t="s">
+      <c r="AO2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AP2" s="392" t="s">
+      <c r="AP2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AQ2" s="392" t="s">
+      <c r="AQ2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AR2" s="392" t="s">
+      <c r="AR2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AS2" s="392" t="s">
+      <c r="AS2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AT2" s="392" t="s">
+      <c r="AT2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AU2" s="392" t="s">
+      <c r="AU2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AV2" s="392" t="s">
+      <c r="AV2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AW2" s="392" t="s">
+      <c r="AW2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AX2" s="392" t="s">
+      <c r="AX2" s="334" t="s">
         <v>3</v>
       </c>
-      <c r="AY2" s="431" t="s">
+      <c r="AY2" s="370" t="s">
         <v>4</v>
       </c>
-      <c r="AZ2" s="392" t="s">
+      <c r="AZ2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BA2" s="392" t="s">
+      <c r="BA2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BB2" s="392" t="s">
+      <c r="BB2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BC2" s="392" t="s">
+      <c r="BC2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BD2" s="392" t="s">
+      <c r="BD2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BE2" s="392" t="s">
+      <c r="BE2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BF2" s="392" t="s">
+      <c r="BF2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BG2" s="392" t="s">
+      <c r="BG2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BH2" s="392" t="s">
+      <c r="BH2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BI2" s="392" t="s">
+      <c r="BI2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BJ2" s="392" t="s">
+      <c r="BJ2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BK2" s="392" t="s">
+      <c r="BK2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BL2" s="392" t="s">
+      <c r="BL2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BM2" s="392" t="s">
+      <c r="BM2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BN2" s="392" t="s">
+      <c r="BN2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BO2" s="392" t="s">
+      <c r="BO2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BP2" s="392" t="s">
+      <c r="BP2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BQ2" s="392" t="s">
+      <c r="BQ2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BR2" s="392" t="s">
+      <c r="BR2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BS2" s="392" t="s">
+      <c r="BS2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BT2" s="392" t="s">
+      <c r="BT2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BU2" s="392" t="s">
+      <c r="BU2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BV2" s="392" t="s">
+      <c r="BV2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BW2" s="392" t="s">
+      <c r="BW2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BX2" s="392" t="s">
+      <c r="BX2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BY2" s="392" t="s">
+      <c r="BY2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="BZ2" s="392" t="s">
+      <c r="BZ2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="CA2" s="392" t="s">
+      <c r="CA2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="CB2" s="392" t="s">
+      <c r="CB2" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="CC2" s="397" t="s">
+      <c r="CC2" s="333" t="s">
         <v>5</v>
       </c>
-      <c r="CD2" s="392" t="s">
+      <c r="CD2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CE2" s="392" t="s">
+      <c r="CE2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CF2" s="392" t="s">
+      <c r="CF2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CG2" s="392" t="s">
+      <c r="CG2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CH2" s="392" t="s">
+      <c r="CH2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CI2" s="392" t="s">
+      <c r="CI2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CJ2" s="392" t="s">
+      <c r="CJ2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CK2" s="392" t="s">
+      <c r="CK2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CL2" s="392" t="s">
+      <c r="CL2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CM2" s="392" t="s">
+      <c r="CM2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CN2" s="392" t="s">
+      <c r="CN2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CO2" s="392" t="s">
+      <c r="CO2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CP2" s="392" t="s">
+      <c r="CP2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CQ2" s="392" t="s">
+      <c r="CQ2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CR2" s="392" t="s">
+      <c r="CR2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CS2" s="392" t="s">
+      <c r="CS2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CT2" s="392" t="s">
+      <c r="CT2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CU2" s="392" t="s">
+      <c r="CU2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CV2" s="392" t="s">
+      <c r="CV2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CW2" s="392" t="s">
+      <c r="CW2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CX2" s="392" t="s">
+      <c r="CX2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CY2" s="392" t="s">
+      <c r="CY2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="CZ2" s="392" t="s">
+      <c r="CZ2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="DA2" s="392" t="s">
+      <c r="DA2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="DB2" s="392" t="s">
+      <c r="DB2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="DC2" s="392" t="s">
+      <c r="DC2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="DD2" s="392" t="s">
+      <c r="DD2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="DE2" s="392" t="s">
+      <c r="DE2" s="334" t="s">
         <v>5</v>
       </c>
-      <c r="DF2" s="392" t="s">
+      <c r="DF2" s="334" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6260,7 +6272,7 @@
       <c r="DF4" s="2"/>
     </row>
     <row r="5" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A5" s="281" t="s">
+      <c r="A5" s="280" t="s">
         <v>90</v>
       </c>
       <c r="B5" s="129" t="s">
@@ -6272,23 +6284,23 @@
       <c r="D5" s="131">
         <v>1</v>
       </c>
-      <c r="E5" s="322" t="s">
+      <c r="E5" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F5" s="132"/>
       <c r="G5" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="H5" s="336" t="s">
+      <c r="H5" s="345" t="s">
         <v>87</v>
       </c>
-      <c r="I5" s="394" t="s">
+      <c r="I5" s="379" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="395" t="s">
+      <c r="J5" s="380" t="s">
         <v>42</v>
       </c>
-      <c r="K5" s="396" t="s">
+      <c r="K5" s="381" t="s">
         <v>42</v>
       </c>
       <c r="L5" s="2"/>
@@ -6392,10 +6404,10 @@
       <c r="DF5" s="2"/>
     </row>
     <row r="6" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A6" s="281" t="s">
+      <c r="A6" s="280" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="250">
+      <c r="B6" s="249">
         <v>46073</v>
       </c>
       <c r="C6" s="134" t="s">
@@ -6404,7 +6416,7 @@
       <c r="D6" s="135">
         <v>1</v>
       </c>
-      <c r="E6" s="322" t="s">
+      <c r="E6" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F6" s="136"/>
@@ -6414,16 +6426,16 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="150"/>
-      <c r="K6" s="330" t="s">
+      <c r="K6" s="335" t="s">
         <v>95</v>
       </c>
-      <c r="L6" s="428"/>
-      <c r="M6" s="428"/>
-      <c r="N6" s="428"/>
-      <c r="O6" s="428"/>
-      <c r="P6" s="428"/>
-      <c r="Q6" s="428"/>
-      <c r="R6" s="428"/>
+      <c r="L6" s="367"/>
+      <c r="M6" s="367"/>
+      <c r="N6" s="367"/>
+      <c r="O6" s="367"/>
+      <c r="P6" s="367"/>
+      <c r="Q6" s="367"/>
+      <c r="R6" s="367"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
@@ -6518,19 +6530,19 @@
       <c r="DF6" s="2"/>
     </row>
     <row r="7" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A7" s="281" t="s">
+      <c r="A7" s="280" t="s">
         <v>88</v>
       </c>
       <c r="B7" s="142" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="249">
+      <c r="C7" s="248">
         <v>46108</v>
       </c>
       <c r="D7" s="143">
         <v>1</v>
       </c>
-      <c r="E7" s="322" t="s">
+      <c r="E7" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F7" s="144"/>
@@ -6540,16 +6552,16 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
-      <c r="K7" s="330" t="s">
+      <c r="K7" s="335" t="s">
         <v>96</v>
       </c>
-      <c r="L7" s="330"/>
-      <c r="M7" s="330"/>
-      <c r="N7" s="330"/>
-      <c r="O7" s="330"/>
-      <c r="P7" s="330"/>
-      <c r="Q7" s="330"/>
-      <c r="R7" s="330"/>
+      <c r="L7" s="335"/>
+      <c r="M7" s="335"/>
+      <c r="N7" s="335"/>
+      <c r="O7" s="335"/>
+      <c r="P7" s="335"/>
+      <c r="Q7" s="335"/>
+      <c r="R7" s="335"/>
       <c r="S7" s="150"/>
       <c r="T7" s="150"/>
       <c r="U7" s="2"/>
@@ -6644,7 +6656,7 @@
       <c r="DF7" s="2"/>
     </row>
     <row r="8" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A8" s="281" t="s">
+      <c r="A8" s="280" t="s">
         <v>47</v>
       </c>
       <c r="B8" s="157" t="s">
@@ -6656,7 +6668,7 @@
       <c r="D8" s="159">
         <v>1</v>
       </c>
-      <c r="E8" s="322" t="s">
+      <c r="E8" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F8" s="160"/>
@@ -6671,13 +6683,13 @@
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="385" t="s">
+      <c r="P8" s="371" t="s">
         <v>49</v>
       </c>
-      <c r="Q8" s="386" t="s">
+      <c r="Q8" s="372" t="s">
         <v>49</v>
       </c>
-      <c r="R8" s="387" t="s">
+      <c r="R8" s="373" t="s">
         <v>49</v>
       </c>
       <c r="S8" s="2"/>
@@ -6774,7 +6786,7 @@
       <c r="DF8" s="2"/>
     </row>
     <row r="9" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A9" s="281" t="s">
+      <c r="A9" s="280" t="s">
         <v>50</v>
       </c>
       <c r="B9" s="162" t="s">
@@ -6786,7 +6798,7 @@
       <c r="D9" s="164">
         <v>1</v>
       </c>
-      <c r="E9" s="322" t="s">
+      <c r="E9" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F9" s="165"/>
@@ -6801,13 +6813,13 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="344" t="s">
+      <c r="P9" s="389" t="s">
         <v>51</v>
       </c>
-      <c r="Q9" s="345" t="s">
+      <c r="Q9" s="390" t="s">
         <v>51</v>
       </c>
-      <c r="R9" s="346" t="s">
+      <c r="R9" s="391" t="s">
         <v>51</v>
       </c>
       <c r="S9" s="2"/>
@@ -6904,7 +6916,7 @@
       <c r="DF9" s="2"/>
     </row>
     <row r="10" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A10" s="281" t="s">
+      <c r="A10" s="280" t="s">
         <v>52</v>
       </c>
       <c r="B10" s="167" t="s">
@@ -6916,7 +6928,7 @@
       <c r="D10" s="169">
         <v>1</v>
       </c>
-      <c r="E10" s="322" t="s">
+      <c r="E10" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F10" s="170"/>
@@ -6931,13 +6943,13 @@
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="388" t="s">
+      <c r="P10" s="374" t="s">
         <v>53</v>
       </c>
-      <c r="Q10" s="389" t="s">
+      <c r="Q10" s="375" t="s">
         <v>53</v>
       </c>
-      <c r="R10" s="390" t="s">
+      <c r="R10" s="376" t="s">
         <v>53</v>
       </c>
       <c r="S10" s="2"/>
@@ -7034,7 +7046,7 @@
       <c r="DF10" s="2"/>
     </row>
     <row r="11" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A11" s="281" t="s">
+      <c r="A11" s="280" t="s">
         <v>55</v>
       </c>
       <c r="B11" s="172" t="s">
@@ -7046,7 +7058,7 @@
       <c r="D11" s="173">
         <v>1</v>
       </c>
-      <c r="E11" s="322" t="s">
+      <c r="E11" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F11" s="174"/>
@@ -7061,13 +7073,13 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="354" t="s">
+      <c r="P11" s="399" t="s">
         <v>56</v>
       </c>
-      <c r="Q11" s="355" t="s">
+      <c r="Q11" s="400" t="s">
         <v>56</v>
       </c>
-      <c r="R11" s="356" t="s">
+      <c r="R11" s="401" t="s">
         <v>56</v>
       </c>
       <c r="S11" s="2"/>
@@ -7164,7 +7176,7 @@
       <c r="DF11" s="2"/>
     </row>
     <row r="12" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A12" s="281" t="s">
+      <c r="A12" s="280" t="s">
         <v>57</v>
       </c>
       <c r="B12" s="176" t="s">
@@ -7176,7 +7188,7 @@
       <c r="D12" s="178">
         <v>1</v>
       </c>
-      <c r="E12" s="322" t="s">
+      <c r="E12" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F12" s="179"/>
@@ -7191,13 +7203,13 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="357" t="s">
+      <c r="P12" s="402" t="s">
         <v>58</v>
       </c>
-      <c r="Q12" s="358" t="s">
+      <c r="Q12" s="403" t="s">
         <v>58</v>
       </c>
-      <c r="R12" s="359" t="s">
+      <c r="R12" s="404" t="s">
         <v>58</v>
       </c>
       <c r="S12" s="2"/>
@@ -7294,7 +7306,7 @@
       <c r="DF12" s="2"/>
     </row>
     <row r="13" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A13" s="281" t="s">
+      <c r="A13" s="280" t="s">
         <v>59</v>
       </c>
       <c r="B13" s="181" t="s">
@@ -7306,7 +7318,7 @@
       <c r="D13" s="183">
         <v>1</v>
       </c>
-      <c r="E13" s="322" t="s">
+      <c r="E13" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F13" s="184"/>
@@ -7321,13 +7333,13 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="360" t="s">
+      <c r="P13" s="405" t="s">
         <v>60</v>
       </c>
-      <c r="Q13" s="361" t="s">
+      <c r="Q13" s="406" t="s">
         <v>60</v>
       </c>
-      <c r="R13" s="362" t="s">
+      <c r="R13" s="407" t="s">
         <v>60</v>
       </c>
       <c r="S13" s="2"/>
@@ -7424,7 +7436,7 @@
       <c r="DF13" s="2"/>
     </row>
     <row r="14" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A14" s="281" t="s">
+      <c r="A14" s="280" t="s">
         <v>61</v>
       </c>
       <c r="B14" s="186" t="s">
@@ -7436,7 +7448,7 @@
       <c r="D14" s="188">
         <v>1</v>
       </c>
-      <c r="E14" s="322" t="s">
+      <c r="E14" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F14" s="6"/>
@@ -7456,13 +7468,13 @@
       <c r="R14" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="S14" s="281"/>
-      <c r="T14" s="281"/>
-      <c r="U14" s="281"/>
-      <c r="V14" s="281"/>
-      <c r="W14" s="281"/>
-      <c r="X14" s="281"/>
-      <c r="Y14" s="281"/>
+      <c r="S14" s="280"/>
+      <c r="T14" s="280"/>
+      <c r="U14" s="280"/>
+      <c r="V14" s="280"/>
+      <c r="W14" s="280"/>
+      <c r="X14" s="280"/>
+      <c r="Y14" s="280"/>
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
       <c r="AB14" s="2"/>
@@ -7550,7 +7562,7 @@
       <c r="DF14" s="2"/>
     </row>
     <row r="15" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A15" s="281" t="s">
+      <c r="A15" s="280" t="s">
         <v>117</v>
       </c>
       <c r="B15" s="192" t="s">
@@ -7562,7 +7574,7 @@
       <c r="D15" s="194">
         <v>1</v>
       </c>
-      <c r="E15" s="322" t="s">
+      <c r="E15" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F15" s="195"/>
@@ -7579,28 +7591,28 @@
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
-      <c r="R15" s="336" t="s">
+      <c r="R15" s="345" t="s">
         <v>91</v>
       </c>
-      <c r="S15" s="363" t="s">
+      <c r="S15" s="408" t="s">
         <v>63</v>
       </c>
-      <c r="T15" s="364" t="s">
+      <c r="T15" s="409" t="s">
         <v>63</v>
       </c>
-      <c r="U15" s="365" t="s">
+      <c r="U15" s="410" t="s">
         <v>63</v>
       </c>
-      <c r="V15" s="366" t="s">
+      <c r="V15" s="411" t="s">
         <v>63</v>
       </c>
-      <c r="W15" s="367" t="s">
+      <c r="W15" s="412" t="s">
         <v>63</v>
       </c>
-      <c r="X15" s="368" t="s">
+      <c r="X15" s="413" t="s">
         <v>63</v>
       </c>
-      <c r="Y15" s="369" t="s">
+      <c r="Y15" s="414" t="s">
         <v>63</v>
       </c>
       <c r="Z15" s="2"/>
@@ -7690,7 +7702,7 @@
       <c r="DF15" s="2"/>
     </row>
     <row r="16" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A16" s="281" t="s">
+      <c r="A16" s="280" t="s">
         <v>64</v>
       </c>
       <c r="B16" s="197" t="s">
@@ -7702,7 +7714,7 @@
       <c r="D16" s="198">
         <v>1</v>
       </c>
-      <c r="E16" s="322" t="s">
+      <c r="E16" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F16" s="199"/>
@@ -7719,28 +7731,28 @@
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
-      <c r="R16" s="336" t="s">
+      <c r="R16" s="345" t="s">
         <v>91</v>
       </c>
-      <c r="S16" s="370" t="s">
+      <c r="S16" s="415" t="s">
         <v>65</v>
       </c>
-      <c r="T16" s="371" t="s">
+      <c r="T16" s="416" t="s">
         <v>65</v>
       </c>
-      <c r="U16" s="372" t="s">
+      <c r="U16" s="417" t="s">
         <v>65</v>
       </c>
-      <c r="V16" s="373" t="s">
+      <c r="V16" s="418" t="s">
         <v>65</v>
       </c>
-      <c r="W16" s="374" t="s">
+      <c r="W16" s="419" t="s">
         <v>65</v>
       </c>
-      <c r="X16" s="375" t="s">
+      <c r="X16" s="420" t="s">
         <v>65</v>
       </c>
-      <c r="Y16" s="376" t="s">
+      <c r="Y16" s="421" t="s">
         <v>65</v>
       </c>
       <c r="Z16" s="2"/>
@@ -7830,7 +7842,7 @@
       <c r="DF16" s="2"/>
     </row>
     <row r="17" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A17" s="281" t="s">
+      <c r="A17" s="280" t="s">
         <v>66</v>
       </c>
       <c r="B17" s="201" t="s">
@@ -7842,7 +7854,7 @@
       <c r="D17" s="202">
         <v>1</v>
       </c>
-      <c r="E17" s="322" t="s">
+      <c r="E17" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F17" s="203"/>
@@ -7859,28 +7871,28 @@
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
-      <c r="R17" s="336" t="s">
+      <c r="R17" s="345" t="s">
         <v>67</v>
       </c>
-      <c r="S17" s="337" t="s">
+      <c r="S17" s="382" t="s">
         <v>67</v>
       </c>
-      <c r="T17" s="338" t="s">
+      <c r="T17" s="383" t="s">
         <v>67</v>
       </c>
-      <c r="U17" s="339" t="s">
+      <c r="U17" s="384" t="s">
         <v>67</v>
       </c>
-      <c r="V17" s="340" t="s">
+      <c r="V17" s="385" t="s">
         <v>67</v>
       </c>
-      <c r="W17" s="341" t="s">
+      <c r="W17" s="386" t="s">
         <v>67</v>
       </c>
-      <c r="X17" s="342" t="s">
+      <c r="X17" s="387" t="s">
         <v>67</v>
       </c>
-      <c r="Y17" s="343" t="s">
+      <c r="Y17" s="388" t="s">
         <v>67</v>
       </c>
       <c r="Z17" s="2"/>
@@ -7970,7 +7982,7 @@
       <c r="DF17" s="2"/>
     </row>
     <row r="18" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A18" s="281" t="s">
+      <c r="A18" s="280" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="205" t="s">
@@ -7982,7 +7994,7 @@
       <c r="D18" s="207">
         <v>1</v>
       </c>
-      <c r="E18" s="322" t="s">
+      <c r="E18" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F18" s="208"/>
@@ -7999,28 +8011,28 @@
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
-      <c r="R18" s="399" t="s">
+      <c r="R18" s="337" t="s">
         <v>69</v>
       </c>
-      <c r="S18" s="400" t="s">
+      <c r="S18" s="338" t="s">
         <v>69</v>
       </c>
-      <c r="T18" s="401" t="s">
+      <c r="T18" s="339" t="s">
         <v>69</v>
       </c>
-      <c r="U18" s="402" t="s">
+      <c r="U18" s="340" t="s">
         <v>69</v>
       </c>
-      <c r="V18" s="403" t="s">
+      <c r="V18" s="341" t="s">
         <v>69</v>
       </c>
-      <c r="W18" s="404" t="s">
+      <c r="W18" s="342" t="s">
         <v>69</v>
       </c>
-      <c r="X18" s="405" t="s">
+      <c r="X18" s="343" t="s">
         <v>69</v>
       </c>
-      <c r="Y18" s="406" t="s">
+      <c r="Y18" s="344" t="s">
         <v>69</v>
       </c>
       <c r="Z18" s="2"/>
@@ -8110,19 +8122,19 @@
       <c r="DF18" s="2"/>
     </row>
     <row r="19" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A19" s="281" t="s">
+      <c r="A19" s="280" t="s">
         <v>46</v>
       </c>
       <c r="B19" s="146">
         <v>46080</v>
       </c>
-      <c r="C19" s="262">
+      <c r="C19" s="261">
         <v>46087</v>
       </c>
       <c r="D19" s="147">
         <v>1</v>
       </c>
-      <c r="E19" s="322" t="s">
+      <c r="E19" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F19" s="148"/>
@@ -8141,13 +8153,13 @@
       <c r="R19" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="S19" s="259"/>
-      <c r="T19" s="259"/>
-      <c r="U19" s="259"/>
-      <c r="V19" s="259"/>
-      <c r="W19" s="259"/>
-      <c r="X19" s="260"/>
-      <c r="Y19" s="261"/>
+      <c r="S19" s="258"/>
+      <c r="T19" s="258"/>
+      <c r="U19" s="258"/>
+      <c r="V19" s="258"/>
+      <c r="W19" s="258"/>
+      <c r="X19" s="259"/>
+      <c r="Y19" s="260"/>
       <c r="Z19" s="156"/>
       <c r="AA19" s="2"/>
       <c r="AB19" s="2"/>
@@ -8235,7 +8247,7 @@
       <c r="DF19" s="2"/>
     </row>
     <row r="20" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A20" s="281" t="s">
+      <c r="A20" s="280" t="s">
         <v>93</v>
       </c>
       <c r="B20" s="205" t="s">
@@ -8247,7 +8259,7 @@
       <c r="D20" s="207">
         <v>1</v>
       </c>
-      <c r="E20" s="322" t="s">
+      <c r="E20" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F20" s="208"/>
@@ -8262,16 +8274,16 @@
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
-      <c r="R20" s="414" t="s">
+      <c r="R20" s="353" t="s">
         <v>94</v>
       </c>
-      <c r="S20" s="415"/>
-      <c r="T20" s="415"/>
-      <c r="U20" s="415"/>
-      <c r="V20" s="415"/>
-      <c r="W20" s="415"/>
-      <c r="X20" s="415"/>
-      <c r="Y20" s="415"/>
+      <c r="S20" s="354"/>
+      <c r="T20" s="354"/>
+      <c r="U20" s="354"/>
+      <c r="V20" s="354"/>
+      <c r="W20" s="354"/>
+      <c r="X20" s="354"/>
+      <c r="Y20" s="354"/>
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
       <c r="AB20" s="2"/>
@@ -8359,7 +8371,7 @@
       <c r="DF20" s="2"/>
     </row>
     <row r="21" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A21" s="281" t="s">
+      <c r="A21" s="280" t="s">
         <v>70</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -8371,7 +8383,7 @@
       <c r="D21" s="5">
         <v>1</v>
       </c>
-      <c r="E21" s="322" t="s">
+      <c r="E21" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F21" s="6"/>
@@ -8388,28 +8400,28 @@
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
-      <c r="R21" s="336" t="s">
+      <c r="R21" s="345" t="s">
         <v>71</v>
       </c>
-      <c r="S21" s="407" t="s">
+      <c r="S21" s="346" t="s">
         <v>71</v>
       </c>
-      <c r="T21" s="408" t="s">
+      <c r="T21" s="347" t="s">
         <v>71</v>
       </c>
-      <c r="U21" s="409" t="s">
+      <c r="U21" s="348" t="s">
         <v>71</v>
       </c>
-      <c r="V21" s="410" t="s">
+      <c r="V21" s="349" t="s">
         <v>71</v>
       </c>
-      <c r="W21" s="411" t="s">
+      <c r="W21" s="350" t="s">
         <v>71</v>
       </c>
-      <c r="X21" s="412" t="s">
+      <c r="X21" s="351" t="s">
         <v>71</v>
       </c>
-      <c r="Y21" s="413" t="s">
+      <c r="Y21" s="352" t="s">
         <v>71</v>
       </c>
       <c r="Z21" s="2"/>
@@ -8499,10 +8511,10 @@
       <c r="DF21" s="2"/>
     </row>
     <row r="22" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A22" s="281" t="s">
+      <c r="A22" s="280" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="253">
+      <c r="B22" s="252">
         <v>46080</v>
       </c>
       <c r="C22" s="138" t="s">
@@ -8511,7 +8523,7 @@
       <c r="D22" s="139">
         <v>1</v>
       </c>
-      <c r="E22" s="322" t="s">
+      <c r="E22" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F22" s="140"/>
@@ -8521,21 +8533,21 @@
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="150"/>
-      <c r="K22" s="241"/>
-      <c r="L22" s="242"/>
-      <c r="M22" s="243"/>
-      <c r="N22" s="244"/>
-      <c r="O22" s="245"/>
-      <c r="P22" s="246"/>
-      <c r="Q22" s="247"/>
-      <c r="R22" s="248"/>
-      <c r="S22" s="330" t="s">
+      <c r="K22" s="240"/>
+      <c r="L22" s="241"/>
+      <c r="M22" s="242"/>
+      <c r="N22" s="243"/>
+      <c r="O22" s="244"/>
+      <c r="P22" s="245"/>
+      <c r="Q22" s="246"/>
+      <c r="R22" s="247"/>
+      <c r="S22" s="335" t="s">
         <v>103</v>
       </c>
-      <c r="T22" s="429"/>
-      <c r="U22" s="429"/>
-      <c r="V22" s="429"/>
-      <c r="W22" s="429"/>
+      <c r="T22" s="368"/>
+      <c r="U22" s="368"/>
+      <c r="V22" s="368"/>
+      <c r="W22" s="368"/>
       <c r="X22" s="2"/>
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
@@ -8625,19 +8637,19 @@
       <c r="DF22" s="2"/>
     </row>
     <row r="23" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A23" s="281" t="s">
+      <c r="A23" s="280" t="s">
         <v>72</v>
       </c>
       <c r="B23" s="213" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="252">
+      <c r="C23" s="251">
         <v>46094</v>
       </c>
-      <c r="D23" s="251">
+      <c r="D23" s="250">
         <v>1</v>
       </c>
-      <c r="E23" s="322" t="s">
+      <c r="E23" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F23" s="6"/>
@@ -8657,40 +8669,40 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
-      <c r="U23" s="416" t="s">
+      <c r="U23" s="355" t="s">
         <v>74</v>
       </c>
-      <c r="V23" s="417" t="s">
+      <c r="V23" s="356" t="s">
         <v>74</v>
       </c>
-      <c r="W23" s="418" t="s">
+      <c r="W23" s="357" t="s">
         <v>74</v>
       </c>
-      <c r="X23" s="419" t="s">
+      <c r="X23" s="358" t="s">
         <v>74</v>
       </c>
-      <c r="Y23" s="420" t="s">
+      <c r="Y23" s="359" t="s">
         <v>74</v>
       </c>
-      <c r="Z23" s="421" t="s">
+      <c r="Z23" s="360" t="s">
         <v>74</v>
       </c>
-      <c r="AA23" s="422" t="s">
+      <c r="AA23" s="361" t="s">
         <v>74</v>
       </c>
-      <c r="AB23" s="423" t="s">
+      <c r="AB23" s="362" t="s">
         <v>74</v>
       </c>
-      <c r="AC23" s="424" t="s">
+      <c r="AC23" s="363" t="s">
         <v>74</v>
       </c>
-      <c r="AD23" s="425" t="s">
+      <c r="AD23" s="364" t="s">
         <v>74</v>
       </c>
-      <c r="AE23" s="426" t="s">
+      <c r="AE23" s="365" t="s">
         <v>74</v>
       </c>
-      <c r="AF23" s="427" t="s">
+      <c r="AF23" s="366" t="s">
         <v>74</v>
       </c>
       <c r="AG23" s="2"/>
@@ -8773,7 +8785,7 @@
       <c r="DF23" s="2"/>
     </row>
     <row r="24" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A24" s="281" t="s">
+      <c r="A24" s="280" t="s">
         <v>101</v>
       </c>
       <c r="B24" s="213" t="s">
@@ -8782,10 +8794,10 @@
       <c r="C24" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="251">
+      <c r="D24" s="250">
         <v>1</v>
       </c>
-      <c r="E24" s="322" t="s">
+      <c r="E24" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F24" s="6"/>
@@ -8804,19 +8816,19 @@
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
       <c r="U24" s="150"/>
-      <c r="V24" s="254"/>
-      <c r="W24" s="255"/>
-      <c r="X24" s="256"/>
-      <c r="Y24" s="330" t="s">
+      <c r="V24" s="253"/>
+      <c r="W24" s="254"/>
+      <c r="X24" s="255"/>
+      <c r="Y24" s="335" t="s">
         <v>102</v>
       </c>
-      <c r="Z24" s="398"/>
-      <c r="AA24" s="398"/>
-      <c r="AB24" s="398"/>
-      <c r="AC24" s="398"/>
-      <c r="AD24" s="398"/>
-      <c r="AE24" s="398"/>
-      <c r="AF24" s="398"/>
+      <c r="Z24" s="336"/>
+      <c r="AA24" s="336"/>
+      <c r="AB24" s="336"/>
+      <c r="AC24" s="336"/>
+      <c r="AD24" s="336"/>
+      <c r="AE24" s="336"/>
+      <c r="AF24" s="336"/>
       <c r="AG24" s="2"/>
       <c r="AH24" s="2"/>
       <c r="AI24" s="2"/>
@@ -8897,7 +8909,7 @@
       <c r="DF24" s="2"/>
     </row>
     <row r="25" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A25" s="281" t="s">
+      <c r="A25" s="280" t="s">
         <v>100</v>
       </c>
       <c r="B25" s="213" t="s">
@@ -8906,10 +8918,10 @@
       <c r="C25" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="D25" s="251">
+      <c r="D25" s="250">
         <v>1</v>
       </c>
-      <c r="E25" s="322" t="s">
+      <c r="E25" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F25" s="211"/>
@@ -8927,20 +8939,20 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
-      <c r="U25" s="258"/>
-      <c r="V25" s="254"/>
-      <c r="W25" s="255"/>
-      <c r="X25" s="256"/>
-      <c r="Y25" s="330" t="s">
+      <c r="U25" s="257"/>
+      <c r="V25" s="253"/>
+      <c r="W25" s="254"/>
+      <c r="X25" s="255"/>
+      <c r="Y25" s="335" t="s">
         <v>104</v>
       </c>
-      <c r="Z25" s="398"/>
-      <c r="AA25" s="398"/>
-      <c r="AB25" s="398"/>
-      <c r="AC25" s="398"/>
-      <c r="AD25" s="398"/>
-      <c r="AE25" s="398"/>
-      <c r="AF25" s="398"/>
+      <c r="Z25" s="336"/>
+      <c r="AA25" s="336"/>
+      <c r="AB25" s="336"/>
+      <c r="AC25" s="336"/>
+      <c r="AD25" s="336"/>
+      <c r="AE25" s="336"/>
+      <c r="AF25" s="336"/>
       <c r="AG25" s="2"/>
       <c r="AH25" s="2"/>
       <c r="AI25" s="2"/>
@@ -9021,7 +9033,7 @@
       <c r="DF25" s="2"/>
     </row>
     <row r="26" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A26" s="281" t="s">
+      <c r="A26" s="280" t="s">
         <v>98</v>
       </c>
       <c r="B26" s="213" t="s">
@@ -9030,10 +9042,10 @@
       <c r="C26" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="D26" s="251">
+      <c r="D26" s="250">
         <v>1</v>
       </c>
-      <c r="E26" s="322" t="s">
+      <c r="E26" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F26" s="215"/>
@@ -9057,16 +9069,16 @@
       <c r="V26" s="2"/>
       <c r="W26" s="2"/>
       <c r="X26" s="2"/>
-      <c r="Y26" s="330" t="s">
+      <c r="Y26" s="335" t="s">
         <v>107</v>
       </c>
-      <c r="Z26" s="398"/>
-      <c r="AA26" s="398"/>
-      <c r="AB26" s="398"/>
-      <c r="AC26" s="398"/>
-      <c r="AD26" s="398"/>
-      <c r="AE26" s="398"/>
-      <c r="AF26" s="398"/>
+      <c r="Z26" s="336"/>
+      <c r="AA26" s="336"/>
+      <c r="AB26" s="336"/>
+      <c r="AC26" s="336"/>
+      <c r="AD26" s="336"/>
+      <c r="AE26" s="336"/>
+      <c r="AF26" s="336"/>
       <c r="AG26" s="2"/>
       <c r="AH26" s="2"/>
       <c r="AI26" s="2"/>
@@ -9147,7 +9159,7 @@
       <c r="DF26" s="2"/>
     </row>
     <row r="27" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A27" s="281" t="s">
+      <c r="A27" s="280" t="s">
         <v>99</v>
       </c>
       <c r="B27" s="213" t="s">
@@ -9156,10 +9168,10 @@
       <c r="C27" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="D27" s="251">
+      <c r="D27" s="250">
         <v>1</v>
       </c>
-      <c r="E27" s="322" t="s">
+      <c r="E27" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F27" s="215"/>
@@ -9183,17 +9195,17 @@
       <c r="V27" s="2"/>
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
-      <c r="AF27" s="335" t="s">
+      <c r="AF27" s="332" t="s">
         <v>108</v>
       </c>
-      <c r="AG27" s="335"/>
-      <c r="AH27" s="335"/>
-      <c r="AI27" s="335"/>
-      <c r="AJ27" s="335"/>
-      <c r="AK27" s="335"/>
-      <c r="AL27" s="335"/>
-      <c r="AM27" s="335"/>
-      <c r="AN27" s="263"/>
+      <c r="AG27" s="332"/>
+      <c r="AH27" s="332"/>
+      <c r="AI27" s="332"/>
+      <c r="AJ27" s="332"/>
+      <c r="AK27" s="332"/>
+      <c r="AL27" s="332"/>
+      <c r="AM27" s="332"/>
+      <c r="AN27" s="262"/>
       <c r="AO27" s="2"/>
       <c r="AP27" s="2"/>
       <c r="AQ27" s="2"/>
@@ -9266,19 +9278,19 @@
       <c r="DF27" s="2"/>
     </row>
     <row r="28" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A28" s="281" t="s">
+      <c r="A28" s="280" t="s">
         <v>105</v>
       </c>
       <c r="B28" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="257">
+      <c r="C28" s="256">
         <v>46101</v>
       </c>
-      <c r="D28" s="251">
+      <c r="D28" s="250">
         <v>1</v>
       </c>
-      <c r="E28" s="322" t="s">
+      <c r="E28" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F28" s="215"/>
@@ -9301,22 +9313,22 @@
       <c r="W28" s="2"/>
       <c r="X28" s="2"/>
       <c r="Y28" s="150"/>
-      <c r="Z28" s="263"/>
-      <c r="AA28" s="263"/>
-      <c r="AB28" s="263"/>
-      <c r="AC28" s="263"/>
-      <c r="AD28" s="263"/>
-      <c r="AE28" s="263"/>
-      <c r="AF28" s="335" t="s">
+      <c r="Z28" s="262"/>
+      <c r="AA28" s="262"/>
+      <c r="AB28" s="262"/>
+      <c r="AC28" s="262"/>
+      <c r="AD28" s="262"/>
+      <c r="AE28" s="262"/>
+      <c r="AF28" s="332" t="s">
         <v>109</v>
       </c>
-      <c r="AG28" s="335"/>
-      <c r="AH28" s="335"/>
-      <c r="AI28" s="335"/>
-      <c r="AJ28" s="335"/>
-      <c r="AK28" s="335"/>
-      <c r="AL28" s="335"/>
-      <c r="AM28" s="335"/>
+      <c r="AG28" s="332"/>
+      <c r="AH28" s="332"/>
+      <c r="AI28" s="332"/>
+      <c r="AJ28" s="332"/>
+      <c r="AK28" s="332"/>
+      <c r="AL28" s="332"/>
+      <c r="AM28" s="332"/>
       <c r="AN28" s="2"/>
       <c r="AO28" s="2"/>
       <c r="AP28" s="2"/>
@@ -9390,19 +9402,19 @@
       <c r="DF28" s="2"/>
     </row>
     <row r="29" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A29" s="281" t="s">
+      <c r="A29" s="280" t="s">
         <v>106</v>
       </c>
       <c r="B29" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="257">
+      <c r="C29" s="256">
         <v>46101</v>
       </c>
-      <c r="D29" s="251">
+      <c r="D29" s="250">
         <v>1</v>
       </c>
-      <c r="E29" s="322" t="s">
+      <c r="E29" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F29" s="215"/>
@@ -9425,22 +9437,22 @@
       <c r="W29" s="2"/>
       <c r="X29" s="2"/>
       <c r="Y29" s="150"/>
-      <c r="Z29" s="264"/>
-      <c r="AA29" s="265"/>
-      <c r="AB29" s="266"/>
-      <c r="AC29" s="267"/>
-      <c r="AD29" s="268"/>
-      <c r="AE29" s="269"/>
-      <c r="AF29" s="335" t="s">
+      <c r="Z29" s="263"/>
+      <c r="AA29" s="264"/>
+      <c r="AB29" s="265"/>
+      <c r="AC29" s="266"/>
+      <c r="AD29" s="267"/>
+      <c r="AE29" s="268"/>
+      <c r="AF29" s="332" t="s">
         <v>110</v>
       </c>
-      <c r="AG29" s="335"/>
-      <c r="AH29" s="335"/>
-      <c r="AI29" s="335"/>
-      <c r="AJ29" s="335"/>
-      <c r="AK29" s="335"/>
-      <c r="AL29" s="335"/>
-      <c r="AM29" s="335"/>
+      <c r="AG29" s="332"/>
+      <c r="AH29" s="332"/>
+      <c r="AI29" s="332"/>
+      <c r="AJ29" s="332"/>
+      <c r="AK29" s="332"/>
+      <c r="AL29" s="332"/>
+      <c r="AM29" s="332"/>
       <c r="AN29" s="2"/>
       <c r="AO29" s="2"/>
       <c r="AP29" s="2"/>
@@ -9514,19 +9526,19 @@
       <c r="DF29" s="2"/>
     </row>
     <row r="30" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A30" s="281" t="s">
+      <c r="A30" s="280" t="s">
         <v>111</v>
       </c>
       <c r="B30" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="C30" s="257">
+      <c r="C30" s="256">
         <v>46101</v>
       </c>
-      <c r="D30" s="251">
+      <c r="D30" s="250">
         <v>1</v>
       </c>
-      <c r="E30" s="322" t="s">
+      <c r="E30" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F30" s="215"/>
@@ -9549,22 +9561,22 @@
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
       <c r="Y30" s="150"/>
-      <c r="Z30" s="264"/>
-      <c r="AA30" s="265"/>
-      <c r="AB30" s="266"/>
-      <c r="AC30" s="267"/>
-      <c r="AD30" s="268"/>
-      <c r="AE30" s="269"/>
-      <c r="AF30" s="335" t="s">
+      <c r="Z30" s="263"/>
+      <c r="AA30" s="264"/>
+      <c r="AB30" s="265"/>
+      <c r="AC30" s="266"/>
+      <c r="AD30" s="267"/>
+      <c r="AE30" s="268"/>
+      <c r="AF30" s="332" t="s">
         <v>113</v>
       </c>
-      <c r="AG30" s="335"/>
-      <c r="AH30" s="335"/>
-      <c r="AI30" s="335"/>
-      <c r="AJ30" s="335"/>
-      <c r="AK30" s="335"/>
-      <c r="AL30" s="335"/>
-      <c r="AM30" s="335"/>
+      <c r="AG30" s="332"/>
+      <c r="AH30" s="332"/>
+      <c r="AI30" s="332"/>
+      <c r="AJ30" s="332"/>
+      <c r="AK30" s="332"/>
+      <c r="AL30" s="332"/>
+      <c r="AM30" s="332"/>
       <c r="AN30" s="2"/>
       <c r="AO30" s="2"/>
       <c r="AP30" s="2"/>
@@ -9638,19 +9650,19 @@
       <c r="DF30" s="2"/>
     </row>
     <row r="31" spans="1:110" ht="17.5" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A31" s="281" t="s">
+      <c r="A31" s="280" t="s">
         <v>112</v>
       </c>
       <c r="B31" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="C31" s="257">
+      <c r="C31" s="256">
         <v>46101</v>
       </c>
-      <c r="D31" s="251">
+      <c r="D31" s="250">
         <v>1</v>
       </c>
-      <c r="E31" s="322" t="s">
+      <c r="E31" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F31" s="217"/>
@@ -9679,18 +9691,18 @@
       <c r="AA31" s="2"/>
       <c r="AB31" s="2"/>
       <c r="AC31" s="2"/>
-      <c r="AD31" s="272"/>
-      <c r="AE31" s="273"/>
-      <c r="AF31" s="335" t="s">
+      <c r="AD31" s="271"/>
+      <c r="AE31" s="272"/>
+      <c r="AF31" s="332" t="s">
         <v>114</v>
       </c>
-      <c r="AG31" s="335"/>
-      <c r="AH31" s="335"/>
-      <c r="AI31" s="335"/>
-      <c r="AJ31" s="335"/>
-      <c r="AK31" s="335"/>
-      <c r="AL31" s="335"/>
-      <c r="AM31" s="335"/>
+      <c r="AG31" s="332"/>
+      <c r="AH31" s="332"/>
+      <c r="AI31" s="332"/>
+      <c r="AJ31" s="332"/>
+      <c r="AK31" s="332"/>
+      <c r="AL31" s="332"/>
+      <c r="AM31" s="332"/>
       <c r="AN31" s="2"/>
       <c r="AO31" s="2"/>
       <c r="AP31" s="2"/>
@@ -9764,19 +9776,19 @@
       <c r="DF31" s="2"/>
     </row>
     <row r="32" spans="1:110" ht="17.5" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A32" s="281" t="s">
+      <c r="A32" s="280" t="s">
         <v>115</v>
       </c>
       <c r="B32" s="214" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="257">
+      <c r="C32" s="256">
         <v>46101</v>
       </c>
-      <c r="D32" s="251">
+      <c r="D32" s="250">
         <v>1</v>
       </c>
-      <c r="E32" s="322" t="s">
+      <c r="E32" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F32" s="217"/>
@@ -9805,18 +9817,18 @@
       <c r="AA32" s="2"/>
       <c r="AB32" s="2"/>
       <c r="AC32" s="2"/>
-      <c r="AD32" s="272"/>
-      <c r="AE32" s="273"/>
-      <c r="AF32" s="335" t="s">
+      <c r="AD32" s="271"/>
+      <c r="AE32" s="272"/>
+      <c r="AF32" s="332" t="s">
         <v>116</v>
       </c>
-      <c r="AG32" s="335"/>
-      <c r="AH32" s="335"/>
-      <c r="AI32" s="335"/>
-      <c r="AJ32" s="335"/>
-      <c r="AK32" s="335"/>
-      <c r="AL32" s="335"/>
-      <c r="AM32" s="335"/>
+      <c r="AG32" s="332"/>
+      <c r="AH32" s="332"/>
+      <c r="AI32" s="332"/>
+      <c r="AJ32" s="332"/>
+      <c r="AK32" s="332"/>
+      <c r="AL32" s="332"/>
+      <c r="AM32" s="332"/>
       <c r="AN32" s="2"/>
       <c r="AO32" s="2"/>
       <c r="AP32" s="2"/>
@@ -9890,19 +9902,19 @@
       <c r="DF32" s="2"/>
     </row>
     <row r="33" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A33" s="281" t="s">
+      <c r="A33" s="280" t="s">
         <v>76</v>
       </c>
-      <c r="B33" s="270">
+      <c r="B33" s="269">
         <v>46101</v>
       </c>
-      <c r="C33" s="271">
+      <c r="C33" s="270">
         <v>46108</v>
       </c>
-      <c r="D33" s="274">
+      <c r="D33" s="273">
         <v>1</v>
       </c>
-      <c r="E33" s="322" t="s">
+      <c r="E33" s="321" t="s">
         <v>149</v>
       </c>
       <c r="F33" s="219"/>
@@ -9932,38 +9944,38 @@
       <c r="AB33" s="2"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="2"/>
-      <c r="AE33" s="377"/>
-      <c r="AF33" s="378" t="s">
+      <c r="AE33" s="422"/>
+      <c r="AF33" s="423" t="s">
         <v>77</v>
       </c>
-      <c r="AG33" s="379" t="s">
+      <c r="AG33" s="424" t="s">
         <v>77</v>
       </c>
-      <c r="AH33" s="380" t="s">
+      <c r="AH33" s="425" t="s">
         <v>77</v>
       </c>
-      <c r="AI33" s="381" t="s">
+      <c r="AI33" s="426" t="s">
         <v>77</v>
       </c>
-      <c r="AJ33" s="382" t="s">
+      <c r="AJ33" s="427" t="s">
         <v>77</v>
       </c>
-      <c r="AK33" s="383" t="s">
+      <c r="AK33" s="428" t="s">
         <v>77</v>
       </c>
-      <c r="AL33" s="384" t="s">
+      <c r="AL33" s="429" t="s">
         <v>77</v>
       </c>
-      <c r="AM33" s="281"/>
-      <c r="AN33" s="281"/>
-      <c r="AO33" s="332" t="s">
+      <c r="AM33" s="280"/>
+      <c r="AN33" s="280"/>
+      <c r="AO33" s="331" t="s">
         <v>118</v>
       </c>
-      <c r="AP33" s="332"/>
-      <c r="AQ33" s="332"/>
-      <c r="AR33" s="332"/>
-      <c r="AS33" s="332"/>
-      <c r="AT33" s="332"/>
+      <c r="AP33" s="331"/>
+      <c r="AQ33" s="331"/>
+      <c r="AR33" s="331"/>
+      <c r="AS33" s="331"/>
+      <c r="AT33" s="331"/>
       <c r="AU33" s="2"/>
       <c r="AV33" s="2"/>
       <c r="AW33" s="2"/>
@@ -10030,7 +10042,7 @@
       <c r="DF33" s="2"/>
     </row>
     <row r="34" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A34" s="281" t="s">
+      <c r="A34" s="280" t="s">
         <v>126</v>
       </c>
       <c r="B34" s="221" t="s">
@@ -10039,10 +10051,10 @@
       <c r="C34" s="222" t="s">
         <v>78</v>
       </c>
-      <c r="D34" s="278">
+      <c r="D34" s="277">
         <v>1</v>
       </c>
-      <c r="E34" s="322" t="s">
+      <c r="E34" s="321" t="s">
         <v>149</v>
       </c>
       <c r="F34" s="6"/>
@@ -10078,18 +10090,18 @@
       <c r="AH34" s="2"/>
       <c r="AI34" s="2"/>
       <c r="AJ34" s="2"/>
-      <c r="AK34" s="275"/>
-      <c r="AL34" s="276"/>
-      <c r="AM34" s="320"/>
-      <c r="AN34" s="321"/>
-      <c r="AO34" s="332" t="s">
+      <c r="AK34" s="274"/>
+      <c r="AL34" s="275"/>
+      <c r="AM34" s="319"/>
+      <c r="AN34" s="320"/>
+      <c r="AO34" s="331" t="s">
         <v>127</v>
       </c>
-      <c r="AP34" s="332"/>
-      <c r="AQ34" s="332"/>
-      <c r="AR34" s="332"/>
-      <c r="AS34" s="332"/>
-      <c r="AT34" s="332"/>
+      <c r="AP34" s="331"/>
+      <c r="AQ34" s="331"/>
+      <c r="AR34" s="331"/>
+      <c r="AS34" s="331"/>
+      <c r="AT34" s="331"/>
       <c r="AU34" s="2"/>
       <c r="AV34" s="2"/>
       <c r="AW34" s="2"/>
@@ -10156,7 +10168,7 @@
       <c r="DF34" s="2"/>
     </row>
     <row r="35" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A35" s="281" t="s">
+      <c r="A35" s="280" t="s">
         <v>54</v>
       </c>
       <c r="B35" s="225" t="s">
@@ -10165,10 +10177,10 @@
       <c r="C35" s="226" t="s">
         <v>80</v>
       </c>
-      <c r="D35" s="278">
+      <c r="D35" s="277">
         <v>1</v>
       </c>
-      <c r="E35" s="322" t="s">
+      <c r="E35" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F35" s="223"/>
@@ -10202,37 +10214,37 @@
       <c r="AH35" s="2"/>
       <c r="AI35" s="2"/>
       <c r="AJ35" s="2"/>
-      <c r="AK35" s="275"/>
-      <c r="AL35" s="276"/>
-      <c r="AM35" s="277"/>
-      <c r="AN35" s="318"/>
-      <c r="AO35" s="319"/>
-      <c r="AP35" s="319"/>
-      <c r="AQ35" s="319"/>
-      <c r="AR35" s="319"/>
-      <c r="AS35" s="319"/>
-      <c r="AT35" s="336" t="s">
+      <c r="AK35" s="274"/>
+      <c r="AL35" s="275"/>
+      <c r="AM35" s="276"/>
+      <c r="AN35" s="317"/>
+      <c r="AO35" s="318"/>
+      <c r="AP35" s="318"/>
+      <c r="AQ35" s="318"/>
+      <c r="AR35" s="318"/>
+      <c r="AS35" s="318"/>
+      <c r="AT35" s="345" t="s">
         <v>119</v>
       </c>
-      <c r="AU35" s="347" t="s">
+      <c r="AU35" s="392" t="s">
         <v>81</v>
       </c>
-      <c r="AV35" s="348" t="s">
+      <c r="AV35" s="393" t="s">
         <v>81</v>
       </c>
-      <c r="AW35" s="349" t="s">
+      <c r="AW35" s="394" t="s">
         <v>81</v>
       </c>
-      <c r="AX35" s="350" t="s">
+      <c r="AX35" s="395" t="s">
         <v>81</v>
       </c>
-      <c r="AY35" s="351" t="s">
+      <c r="AY35" s="396" t="s">
         <v>81</v>
       </c>
-      <c r="AZ35" s="352" t="s">
+      <c r="AZ35" s="397" t="s">
         <v>81</v>
       </c>
-      <c r="BA35" s="353" t="s">
+      <c r="BA35" s="398" t="s">
         <v>81</v>
       </c>
       <c r="BB35" s="2"/>
@@ -10294,7 +10306,7 @@
       <c r="DF35" s="2"/>
     </row>
     <row r="36" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A36" s="281" t="s">
+      <c r="A36" s="280" t="s">
         <v>120</v>
       </c>
       <c r="B36" s="225" t="s">
@@ -10303,10 +10315,10 @@
       <c r="C36" s="226" t="s">
         <v>80</v>
       </c>
-      <c r="D36" s="278">
+      <c r="D36" s="277">
         <v>1</v>
       </c>
-      <c r="E36" s="322" t="s">
+      <c r="E36" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F36" s="227"/>
@@ -10349,28 +10361,28 @@
       <c r="AQ36" s="2"/>
       <c r="AR36" s="2"/>
       <c r="AS36" s="2"/>
-      <c r="AT36" s="336" t="s">
+      <c r="AT36" s="345" t="s">
         <v>123</v>
       </c>
-      <c r="AU36" s="347" t="s">
+      <c r="AU36" s="392" t="s">
         <v>81</v>
       </c>
-      <c r="AV36" s="348" t="s">
+      <c r="AV36" s="393" t="s">
         <v>81</v>
       </c>
-      <c r="AW36" s="349" t="s">
+      <c r="AW36" s="394" t="s">
         <v>81</v>
       </c>
-      <c r="AX36" s="350" t="s">
+      <c r="AX36" s="395" t="s">
         <v>81</v>
       </c>
-      <c r="AY36" s="351" t="s">
+      <c r="AY36" s="396" t="s">
         <v>81</v>
       </c>
-      <c r="AZ36" s="352" t="s">
+      <c r="AZ36" s="397" t="s">
         <v>81</v>
       </c>
-      <c r="BA36" s="353" t="s">
+      <c r="BA36" s="398" t="s">
         <v>81</v>
       </c>
       <c r="BB36" s="2"/>
@@ -10432,7 +10444,7 @@
       <c r="DF36" s="2"/>
     </row>
     <row r="37" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A37" s="281" t="s">
+      <c r="A37" s="280" t="s">
         <v>121</v>
       </c>
       <c r="B37" s="225" t="s">
@@ -10441,10 +10453,10 @@
       <c r="C37" s="226" t="s">
         <v>80</v>
       </c>
-      <c r="D37" s="278">
+      <c r="D37" s="277">
         <v>1</v>
       </c>
-      <c r="E37" s="322" t="s">
+      <c r="E37" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F37" s="227"/>
@@ -10487,28 +10499,28 @@
       <c r="AQ37" s="2"/>
       <c r="AR37" s="2"/>
       <c r="AS37" s="2"/>
-      <c r="AT37" s="336" t="s">
+      <c r="AT37" s="345" t="s">
         <v>122</v>
       </c>
-      <c r="AU37" s="347" t="s">
+      <c r="AU37" s="392" t="s">
         <v>81</v>
       </c>
-      <c r="AV37" s="348" t="s">
+      <c r="AV37" s="393" t="s">
         <v>81</v>
       </c>
-      <c r="AW37" s="349" t="s">
+      <c r="AW37" s="394" t="s">
         <v>81</v>
       </c>
-      <c r="AX37" s="350" t="s">
+      <c r="AX37" s="395" t="s">
         <v>81</v>
       </c>
-      <c r="AY37" s="351" t="s">
+      <c r="AY37" s="396" t="s">
         <v>81</v>
       </c>
-      <c r="AZ37" s="352" t="s">
+      <c r="AZ37" s="397" t="s">
         <v>81</v>
       </c>
-      <c r="BA37" s="353" t="s">
+      <c r="BA37" s="398" t="s">
         <v>81</v>
       </c>
       <c r="BB37" s="2"/>
@@ -10570,19 +10582,19 @@
       <c r="DF37" s="2"/>
     </row>
     <row r="38" spans="1:110" ht="19.5" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A38" s="281" t="s">
+      <c r="A38" s="280" t="s">
         <v>139</v>
       </c>
       <c r="B38" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="279">
+      <c r="C38" s="278">
         <v>46122</v>
       </c>
-      <c r="D38" s="282">
+      <c r="D38" s="281">
         <v>0.75</v>
       </c>
-      <c r="E38" s="322" t="s">
+      <c r="E38" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F38" s="6"/>
@@ -10634,23 +10646,23 @@
       <c r="AX38" s="2"/>
       <c r="AY38" s="2"/>
       <c r="AZ38" s="2"/>
-      <c r="BA38" s="330" t="s">
+      <c r="BA38" s="335" t="s">
         <v>146</v>
       </c>
-      <c r="BB38" s="333"/>
-      <c r="BC38" s="333"/>
-      <c r="BD38" s="333"/>
-      <c r="BE38" s="333"/>
-      <c r="BF38" s="333"/>
-      <c r="BG38" s="333"/>
-      <c r="BH38" s="333"/>
-      <c r="BI38" s="283"/>
-      <c r="BJ38" s="284"/>
-      <c r="BK38" s="285"/>
-      <c r="BL38" s="286"/>
-      <c r="BM38" s="287"/>
-      <c r="BN38" s="288"/>
-      <c r="BO38" s="289"/>
+      <c r="BB38" s="430"/>
+      <c r="BC38" s="430"/>
+      <c r="BD38" s="430"/>
+      <c r="BE38" s="430"/>
+      <c r="BF38" s="430"/>
+      <c r="BG38" s="430"/>
+      <c r="BH38" s="430"/>
+      <c r="BI38" s="282"/>
+      <c r="BJ38" s="283"/>
+      <c r="BK38" s="284"/>
+      <c r="BL38" s="285"/>
+      <c r="BM38" s="286"/>
+      <c r="BN38" s="287"/>
+      <c r="BO38" s="288"/>
       <c r="BP38" s="2"/>
       <c r="BQ38" s="2"/>
       <c r="BR38" s="2"/>
@@ -10696,19 +10708,19 @@
       <c r="DF38" s="2"/>
     </row>
     <row r="39" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A39" s="281" t="s">
+      <c r="A39" s="280" t="s">
         <v>144</v>
       </c>
       <c r="B39" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="279">
+      <c r="C39" s="278">
         <v>46122</v>
       </c>
-      <c r="D39" s="280">
+      <c r="D39" s="279">
         <v>1</v>
       </c>
-      <c r="E39" s="322" t="s">
+      <c r="E39" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F39" s="6"/>
@@ -10760,23 +10772,23 @@
       <c r="AX39" s="2"/>
       <c r="AY39" s="2"/>
       <c r="AZ39" s="2"/>
-      <c r="BA39" s="330" t="s">
+      <c r="BA39" s="335" t="s">
         <v>124</v>
       </c>
-      <c r="BB39" s="334"/>
-      <c r="BC39" s="334"/>
-      <c r="BD39" s="334"/>
-      <c r="BE39" s="334"/>
-      <c r="BF39" s="334"/>
-      <c r="BG39" s="334"/>
-      <c r="BH39" s="334"/>
-      <c r="BI39" s="292"/>
-      <c r="BJ39" s="293"/>
-      <c r="BK39" s="294"/>
-      <c r="BL39" s="295"/>
-      <c r="BM39" s="296"/>
-      <c r="BN39" s="297"/>
-      <c r="BO39" s="298"/>
+      <c r="BB39" s="431"/>
+      <c r="BC39" s="431"/>
+      <c r="BD39" s="431"/>
+      <c r="BE39" s="431"/>
+      <c r="BF39" s="431"/>
+      <c r="BG39" s="431"/>
+      <c r="BH39" s="431"/>
+      <c r="BI39" s="291"/>
+      <c r="BJ39" s="292"/>
+      <c r="BK39" s="293"/>
+      <c r="BL39" s="294"/>
+      <c r="BM39" s="295"/>
+      <c r="BN39" s="296"/>
+      <c r="BO39" s="297"/>
       <c r="BP39" s="2"/>
       <c r="BQ39" s="2"/>
       <c r="BR39" s="2"/>
@@ -10822,19 +10834,19 @@
       <c r="DF39" s="2"/>
     </row>
     <row r="40" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A40" s="281" t="s">
+      <c r="A40" s="280" t="s">
         <v>128</v>
       </c>
       <c r="B40" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="279">
+      <c r="C40" s="278">
         <v>46122</v>
       </c>
-      <c r="D40" s="280">
+      <c r="D40" s="279">
         <v>1</v>
       </c>
-      <c r="E40" s="322" t="s">
+      <c r="E40" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F40" s="6"/>
@@ -10884,23 +10896,23 @@
       <c r="AX40" s="2"/>
       <c r="AY40" s="2"/>
       <c r="AZ40" s="2"/>
-      <c r="BA40" s="330" t="s">
+      <c r="BA40" s="335" t="s">
         <v>151</v>
       </c>
-      <c r="BB40" s="330"/>
-      <c r="BC40" s="330"/>
-      <c r="BD40" s="330"/>
-      <c r="BE40" s="330"/>
-      <c r="BF40" s="330"/>
-      <c r="BG40" s="330"/>
-      <c r="BH40" s="330"/>
-      <c r="BI40" s="292"/>
-      <c r="BJ40" s="293"/>
-      <c r="BK40" s="294"/>
-      <c r="BL40" s="295"/>
-      <c r="BM40" s="296"/>
-      <c r="BN40" s="297"/>
-      <c r="BO40" s="298"/>
+      <c r="BB40" s="335"/>
+      <c r="BC40" s="335"/>
+      <c r="BD40" s="335"/>
+      <c r="BE40" s="335"/>
+      <c r="BF40" s="335"/>
+      <c r="BG40" s="335"/>
+      <c r="BH40" s="335"/>
+      <c r="BI40" s="291"/>
+      <c r="BJ40" s="292"/>
+      <c r="BK40" s="293"/>
+      <c r="BL40" s="294"/>
+      <c r="BM40" s="295"/>
+      <c r="BN40" s="296"/>
+      <c r="BO40" s="297"/>
       <c r="BP40" s="2"/>
       <c r="BQ40" s="2"/>
       <c r="BR40" s="2"/>
@@ -10946,19 +10958,19 @@
       <c r="DF40" s="2"/>
     </row>
     <row r="41" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A41" s="281" t="s">
+      <c r="A41" s="280" t="s">
         <v>129</v>
       </c>
       <c r="B41" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="279">
+      <c r="C41" s="278">
         <v>46122</v>
       </c>
-      <c r="D41" s="280">
+      <c r="D41" s="279">
         <v>1</v>
       </c>
-      <c r="E41" s="322" t="s">
+      <c r="E41" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F41" s="6"/>
@@ -11008,23 +11020,23 @@
       <c r="AX41" s="2"/>
       <c r="AY41" s="2"/>
       <c r="AZ41" s="2"/>
-      <c r="BA41" s="330" t="s">
+      <c r="BA41" s="335" t="s">
         <v>152</v>
       </c>
-      <c r="BB41" s="330"/>
-      <c r="BC41" s="330"/>
-      <c r="BD41" s="330"/>
-      <c r="BE41" s="330"/>
-      <c r="BF41" s="330"/>
-      <c r="BG41" s="330"/>
-      <c r="BH41" s="330"/>
-      <c r="BI41" s="292"/>
-      <c r="BJ41" s="293"/>
-      <c r="BK41" s="294"/>
-      <c r="BL41" s="295"/>
-      <c r="BM41" s="296"/>
-      <c r="BN41" s="297"/>
-      <c r="BO41" s="298"/>
+      <c r="BB41" s="335"/>
+      <c r="BC41" s="335"/>
+      <c r="BD41" s="335"/>
+      <c r="BE41" s="335"/>
+      <c r="BF41" s="335"/>
+      <c r="BG41" s="335"/>
+      <c r="BH41" s="335"/>
+      <c r="BI41" s="291"/>
+      <c r="BJ41" s="292"/>
+      <c r="BK41" s="293"/>
+      <c r="BL41" s="294"/>
+      <c r="BM41" s="295"/>
+      <c r="BN41" s="296"/>
+      <c r="BO41" s="297"/>
       <c r="BP41" s="2"/>
       <c r="BQ41" s="2"/>
       <c r="BR41" s="2"/>
@@ -11070,19 +11082,19 @@
       <c r="DF41" s="2"/>
     </row>
     <row r="42" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A42" s="281" t="s">
+      <c r="A42" s="280" t="s">
         <v>130</v>
       </c>
       <c r="B42" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C42" s="279">
+      <c r="C42" s="278">
         <v>46122</v>
       </c>
-      <c r="D42" s="280">
+      <c r="D42" s="279">
         <v>1</v>
       </c>
-      <c r="E42" s="322" t="s">
+      <c r="E42" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F42" s="6"/>
@@ -11132,23 +11144,23 @@
       <c r="AX42" s="2"/>
       <c r="AY42" s="2"/>
       <c r="AZ42" s="2"/>
-      <c r="BA42" s="330" t="s">
+      <c r="BA42" s="335" t="s">
         <v>153</v>
       </c>
-      <c r="BB42" s="330"/>
-      <c r="BC42" s="330"/>
-      <c r="BD42" s="330"/>
-      <c r="BE42" s="330"/>
-      <c r="BF42" s="330"/>
-      <c r="BG42" s="330"/>
-      <c r="BH42" s="330"/>
-      <c r="BI42" s="292"/>
-      <c r="BJ42" s="293"/>
-      <c r="BK42" s="294"/>
-      <c r="BL42" s="295"/>
-      <c r="BM42" s="296"/>
-      <c r="BN42" s="297"/>
-      <c r="BO42" s="298"/>
+      <c r="BB42" s="335"/>
+      <c r="BC42" s="335"/>
+      <c r="BD42" s="335"/>
+      <c r="BE42" s="335"/>
+      <c r="BF42" s="335"/>
+      <c r="BG42" s="335"/>
+      <c r="BH42" s="335"/>
+      <c r="BI42" s="291"/>
+      <c r="BJ42" s="292"/>
+      <c r="BK42" s="293"/>
+      <c r="BL42" s="294"/>
+      <c r="BM42" s="295"/>
+      <c r="BN42" s="296"/>
+      <c r="BO42" s="297"/>
       <c r="BP42" s="2"/>
       <c r="BQ42" s="2"/>
       <c r="BR42" s="2"/>
@@ -11194,19 +11206,19 @@
       <c r="DF42" s="2"/>
     </row>
     <row r="43" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A43" s="281" t="s">
+      <c r="A43" s="280" t="s">
         <v>131</v>
       </c>
       <c r="B43" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C43" s="279">
+      <c r="C43" s="278">
         <v>46122</v>
       </c>
-      <c r="D43" s="280">
+      <c r="D43" s="279">
         <v>1</v>
       </c>
-      <c r="E43" s="322" t="s">
+      <c r="E43" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F43" s="6"/>
@@ -11256,23 +11268,23 @@
       <c r="AX43" s="2"/>
       <c r="AY43" s="2"/>
       <c r="AZ43" s="2"/>
-      <c r="BA43" s="330" t="s">
+      <c r="BA43" s="335" t="s">
         <v>154</v>
       </c>
-      <c r="BB43" s="330"/>
-      <c r="BC43" s="330"/>
-      <c r="BD43" s="330"/>
-      <c r="BE43" s="330"/>
-      <c r="BF43" s="330"/>
-      <c r="BG43" s="330"/>
-      <c r="BH43" s="330"/>
-      <c r="BI43" s="292"/>
-      <c r="BJ43" s="293"/>
-      <c r="BK43" s="294"/>
-      <c r="BL43" s="295"/>
-      <c r="BM43" s="296"/>
-      <c r="BN43" s="297"/>
-      <c r="BO43" s="298"/>
+      <c r="BB43" s="335"/>
+      <c r="BC43" s="335"/>
+      <c r="BD43" s="335"/>
+      <c r="BE43" s="335"/>
+      <c r="BF43" s="335"/>
+      <c r="BG43" s="335"/>
+      <c r="BH43" s="335"/>
+      <c r="BI43" s="291"/>
+      <c r="BJ43" s="292"/>
+      <c r="BK43" s="293"/>
+      <c r="BL43" s="294"/>
+      <c r="BM43" s="295"/>
+      <c r="BN43" s="296"/>
+      <c r="BO43" s="297"/>
       <c r="BP43" s="2"/>
       <c r="BQ43" s="2"/>
       <c r="BR43" s="2"/>
@@ -11318,19 +11330,19 @@
       <c r="DF43" s="2"/>
     </row>
     <row r="44" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A44" s="281" t="s">
+      <c r="A44" s="280" t="s">
         <v>132</v>
       </c>
       <c r="B44" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C44" s="279">
+      <c r="C44" s="278">
         <v>46122</v>
       </c>
-      <c r="D44" s="280">
+      <c r="D44" s="279">
         <v>1</v>
       </c>
-      <c r="E44" s="322" t="s">
+      <c r="E44" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F44" s="6"/>
@@ -11380,23 +11392,23 @@
       <c r="AX44" s="2"/>
       <c r="AY44" s="2"/>
       <c r="AZ44" s="2"/>
-      <c r="BA44" s="330" t="s">
+      <c r="BA44" s="335" t="s">
         <v>155</v>
       </c>
-      <c r="BB44" s="330"/>
-      <c r="BC44" s="330"/>
-      <c r="BD44" s="330"/>
-      <c r="BE44" s="330"/>
-      <c r="BF44" s="330"/>
-      <c r="BG44" s="330"/>
-      <c r="BH44" s="330"/>
-      <c r="BI44" s="292"/>
-      <c r="BJ44" s="293"/>
-      <c r="BK44" s="294"/>
-      <c r="BL44" s="295"/>
-      <c r="BM44" s="296"/>
-      <c r="BN44" s="297"/>
-      <c r="BO44" s="298"/>
+      <c r="BB44" s="335"/>
+      <c r="BC44" s="335"/>
+      <c r="BD44" s="335"/>
+      <c r="BE44" s="335"/>
+      <c r="BF44" s="335"/>
+      <c r="BG44" s="335"/>
+      <c r="BH44" s="335"/>
+      <c r="BI44" s="291"/>
+      <c r="BJ44" s="292"/>
+      <c r="BK44" s="293"/>
+      <c r="BL44" s="294"/>
+      <c r="BM44" s="295"/>
+      <c r="BN44" s="296"/>
+      <c r="BO44" s="297"/>
       <c r="BP44" s="2"/>
       <c r="BQ44" s="2"/>
       <c r="BR44" s="2"/>
@@ -11442,19 +11454,19 @@
       <c r="DF44" s="2"/>
     </row>
     <row r="45" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A45" s="281" t="s">
+      <c r="A45" s="280" t="s">
         <v>133</v>
       </c>
       <c r="B45" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C45" s="279">
+      <c r="C45" s="278">
         <v>46122</v>
       </c>
-      <c r="D45" s="280">
+      <c r="D45" s="279">
         <v>1</v>
       </c>
-      <c r="E45" s="322" t="s">
+      <c r="E45" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F45" s="6"/>
@@ -11504,23 +11516,23 @@
       <c r="AX45" s="2"/>
       <c r="AY45" s="2"/>
       <c r="AZ45" s="2"/>
-      <c r="BA45" s="330" t="s">
+      <c r="BA45" s="335" t="s">
         <v>156</v>
       </c>
-      <c r="BB45" s="330"/>
-      <c r="BC45" s="330"/>
-      <c r="BD45" s="330"/>
-      <c r="BE45" s="330"/>
-      <c r="BF45" s="330"/>
-      <c r="BG45" s="330"/>
-      <c r="BH45" s="330"/>
-      <c r="BI45" s="292"/>
-      <c r="BJ45" s="293"/>
-      <c r="BK45" s="294"/>
-      <c r="BL45" s="295"/>
-      <c r="BM45" s="296"/>
-      <c r="BN45" s="297"/>
-      <c r="BO45" s="298"/>
+      <c r="BB45" s="335"/>
+      <c r="BC45" s="335"/>
+      <c r="BD45" s="335"/>
+      <c r="BE45" s="335"/>
+      <c r="BF45" s="335"/>
+      <c r="BG45" s="335"/>
+      <c r="BH45" s="335"/>
+      <c r="BI45" s="291"/>
+      <c r="BJ45" s="292"/>
+      <c r="BK45" s="293"/>
+      <c r="BL45" s="294"/>
+      <c r="BM45" s="295"/>
+      <c r="BN45" s="296"/>
+      <c r="BO45" s="297"/>
       <c r="BP45" s="2"/>
       <c r="BQ45" s="2"/>
       <c r="BR45" s="2"/>
@@ -11566,19 +11578,19 @@
       <c r="DF45" s="2"/>
     </row>
     <row r="46" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A46" s="281" t="s">
+      <c r="A46" s="280" t="s">
         <v>138</v>
       </c>
       <c r="B46" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C46" s="279">
+      <c r="C46" s="278">
         <v>46122</v>
       </c>
-      <c r="D46" s="280">
+      <c r="D46" s="279">
         <v>1</v>
       </c>
-      <c r="E46" s="322" t="s">
+      <c r="E46" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F46" s="6"/>
@@ -11628,23 +11640,23 @@
       <c r="AX46" s="2"/>
       <c r="AY46" s="2"/>
       <c r="AZ46" s="2"/>
-      <c r="BA46" s="330" t="s">
+      <c r="BA46" s="335" t="s">
         <v>157</v>
       </c>
-      <c r="BB46" s="330"/>
-      <c r="BC46" s="330"/>
-      <c r="BD46" s="330"/>
-      <c r="BE46" s="330"/>
-      <c r="BF46" s="330"/>
-      <c r="BG46" s="330"/>
-      <c r="BH46" s="330"/>
-      <c r="BI46" s="292"/>
-      <c r="BJ46" s="293"/>
-      <c r="BK46" s="294"/>
-      <c r="BL46" s="295"/>
-      <c r="BM46" s="296"/>
-      <c r="BN46" s="297"/>
-      <c r="BO46" s="298"/>
+      <c r="BB46" s="335"/>
+      <c r="BC46" s="335"/>
+      <c r="BD46" s="335"/>
+      <c r="BE46" s="335"/>
+      <c r="BF46" s="335"/>
+      <c r="BG46" s="335"/>
+      <c r="BH46" s="335"/>
+      <c r="BI46" s="291"/>
+      <c r="BJ46" s="292"/>
+      <c r="BK46" s="293"/>
+      <c r="BL46" s="294"/>
+      <c r="BM46" s="295"/>
+      <c r="BN46" s="296"/>
+      <c r="BO46" s="297"/>
       <c r="BP46" s="2"/>
       <c r="BQ46" s="2"/>
       <c r="BR46" s="2"/>
@@ -11690,19 +11702,19 @@
       <c r="DF46" s="2"/>
     </row>
     <row r="47" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A47" s="281" t="s">
+      <c r="A47" s="280" t="s">
         <v>134</v>
       </c>
       <c r="B47" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C47" s="279">
+      <c r="C47" s="278">
         <v>46122</v>
       </c>
-      <c r="D47" s="280">
+      <c r="D47" s="279">
         <v>1</v>
       </c>
-      <c r="E47" s="322" t="s">
+      <c r="E47" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F47" s="6"/>
@@ -11752,23 +11764,23 @@
       <c r="AX47" s="2"/>
       <c r="AY47" s="2"/>
       <c r="AZ47" s="2"/>
-      <c r="BA47" s="330" t="s">
+      <c r="BA47" s="335" t="s">
         <v>158</v>
       </c>
-      <c r="BB47" s="330"/>
-      <c r="BC47" s="330"/>
-      <c r="BD47" s="330"/>
-      <c r="BE47" s="330"/>
-      <c r="BF47" s="330"/>
-      <c r="BG47" s="330"/>
-      <c r="BH47" s="330"/>
-      <c r="BI47" s="292"/>
-      <c r="BJ47" s="293"/>
-      <c r="BK47" s="294"/>
-      <c r="BL47" s="295"/>
-      <c r="BM47" s="296"/>
-      <c r="BN47" s="297"/>
-      <c r="BO47" s="298"/>
+      <c r="BB47" s="335"/>
+      <c r="BC47" s="335"/>
+      <c r="BD47" s="335"/>
+      <c r="BE47" s="335"/>
+      <c r="BF47" s="335"/>
+      <c r="BG47" s="335"/>
+      <c r="BH47" s="335"/>
+      <c r="BI47" s="291"/>
+      <c r="BJ47" s="292"/>
+      <c r="BK47" s="293"/>
+      <c r="BL47" s="294"/>
+      <c r="BM47" s="295"/>
+      <c r="BN47" s="296"/>
+      <c r="BO47" s="297"/>
       <c r="BP47" s="2"/>
       <c r="BQ47" s="2"/>
       <c r="BR47" s="2"/>
@@ -11814,19 +11826,19 @@
       <c r="DF47" s="2"/>
     </row>
     <row r="48" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A48" s="281" t="s">
+      <c r="A48" s="280" t="s">
         <v>135</v>
       </c>
       <c r="B48" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C48" s="279">
+      <c r="C48" s="278">
         <v>46122</v>
       </c>
-      <c r="D48" s="280">
+      <c r="D48" s="279">
         <v>1</v>
       </c>
-      <c r="E48" s="322" t="s">
+      <c r="E48" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F48" s="6"/>
@@ -11876,23 +11888,23 @@
       <c r="AX48" s="2"/>
       <c r="AY48" s="2"/>
       <c r="AZ48" s="2"/>
-      <c r="BA48" s="330" t="s">
+      <c r="BA48" s="335" t="s">
         <v>159</v>
       </c>
-      <c r="BB48" s="330"/>
-      <c r="BC48" s="330"/>
-      <c r="BD48" s="330"/>
-      <c r="BE48" s="330"/>
-      <c r="BF48" s="330"/>
-      <c r="BG48" s="330"/>
-      <c r="BH48" s="330"/>
-      <c r="BI48" s="292"/>
-      <c r="BJ48" s="293"/>
-      <c r="BK48" s="294"/>
-      <c r="BL48" s="295"/>
-      <c r="BM48" s="296"/>
-      <c r="BN48" s="297"/>
-      <c r="BO48" s="298"/>
+      <c r="BB48" s="335"/>
+      <c r="BC48" s="335"/>
+      <c r="BD48" s="335"/>
+      <c r="BE48" s="335"/>
+      <c r="BF48" s="335"/>
+      <c r="BG48" s="335"/>
+      <c r="BH48" s="335"/>
+      <c r="BI48" s="291"/>
+      <c r="BJ48" s="292"/>
+      <c r="BK48" s="293"/>
+      <c r="BL48" s="294"/>
+      <c r="BM48" s="295"/>
+      <c r="BN48" s="296"/>
+      <c r="BO48" s="297"/>
       <c r="BP48" s="2"/>
       <c r="BQ48" s="2"/>
       <c r="BR48" s="2"/>
@@ -11938,19 +11950,19 @@
       <c r="DF48" s="2"/>
     </row>
     <row r="49" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A49" s="281" t="s">
+      <c r="A49" s="280" t="s">
         <v>136</v>
       </c>
       <c r="B49" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C49" s="279">
+      <c r="C49" s="278">
         <v>46122</v>
       </c>
-      <c r="D49" s="280">
+      <c r="D49" s="279">
         <v>1</v>
       </c>
-      <c r="E49" s="322" t="s">
+      <c r="E49" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F49" s="6"/>
@@ -12000,23 +12012,23 @@
       <c r="AX49" s="2"/>
       <c r="AY49" s="2"/>
       <c r="AZ49" s="2"/>
-      <c r="BA49" s="330" t="s">
+      <c r="BA49" s="335" t="s">
         <v>160</v>
       </c>
-      <c r="BB49" s="330"/>
-      <c r="BC49" s="330"/>
-      <c r="BD49" s="330"/>
-      <c r="BE49" s="330"/>
-      <c r="BF49" s="330"/>
-      <c r="BG49" s="330"/>
-      <c r="BH49" s="330"/>
-      <c r="BI49" s="292"/>
-      <c r="BJ49" s="293"/>
-      <c r="BK49" s="294"/>
-      <c r="BL49" s="295"/>
-      <c r="BM49" s="296"/>
-      <c r="BN49" s="297"/>
-      <c r="BO49" s="298"/>
+      <c r="BB49" s="335"/>
+      <c r="BC49" s="335"/>
+      <c r="BD49" s="335"/>
+      <c r="BE49" s="335"/>
+      <c r="BF49" s="335"/>
+      <c r="BG49" s="335"/>
+      <c r="BH49" s="335"/>
+      <c r="BI49" s="291"/>
+      <c r="BJ49" s="292"/>
+      <c r="BK49" s="293"/>
+      <c r="BL49" s="294"/>
+      <c r="BM49" s="295"/>
+      <c r="BN49" s="296"/>
+      <c r="BO49" s="297"/>
       <c r="BP49" s="2"/>
       <c r="BQ49" s="2"/>
       <c r="BR49" s="2"/>
@@ -12062,19 +12074,19 @@
       <c r="DF49" s="2"/>
     </row>
     <row r="50" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A50" s="281" t="s">
+      <c r="A50" s="280" t="s">
         <v>137</v>
       </c>
       <c r="B50" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C50" s="279">
+      <c r="C50" s="278">
         <v>46122</v>
       </c>
-      <c r="D50" s="280">
+      <c r="D50" s="279">
         <v>1</v>
       </c>
-      <c r="E50" s="322" t="s">
+      <c r="E50" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F50" s="6"/>
@@ -12124,23 +12136,23 @@
       <c r="AX50" s="2"/>
       <c r="AY50" s="2"/>
       <c r="AZ50" s="2"/>
-      <c r="BA50" s="330" t="s">
+      <c r="BA50" s="335" t="s">
         <v>161</v>
       </c>
-      <c r="BB50" s="330"/>
-      <c r="BC50" s="330"/>
-      <c r="BD50" s="330"/>
-      <c r="BE50" s="330"/>
-      <c r="BF50" s="330"/>
-      <c r="BG50" s="330"/>
-      <c r="BH50" s="330"/>
-      <c r="BI50" s="292"/>
-      <c r="BJ50" s="293"/>
-      <c r="BK50" s="294"/>
-      <c r="BL50" s="295"/>
-      <c r="BM50" s="296"/>
-      <c r="BN50" s="297"/>
-      <c r="BO50" s="298"/>
+      <c r="BB50" s="335"/>
+      <c r="BC50" s="335"/>
+      <c r="BD50" s="335"/>
+      <c r="BE50" s="335"/>
+      <c r="BF50" s="335"/>
+      <c r="BG50" s="335"/>
+      <c r="BH50" s="335"/>
+      <c r="BI50" s="291"/>
+      <c r="BJ50" s="292"/>
+      <c r="BK50" s="293"/>
+      <c r="BL50" s="294"/>
+      <c r="BM50" s="295"/>
+      <c r="BN50" s="296"/>
+      <c r="BO50" s="297"/>
       <c r="BP50" s="2"/>
       <c r="BQ50" s="2"/>
       <c r="BR50" s="2"/>
@@ -12186,19 +12198,19 @@
       <c r="DF50" s="2"/>
     </row>
     <row r="51" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A51" s="281" t="s">
+      <c r="A51" s="280" t="s">
         <v>140</v>
       </c>
       <c r="B51" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C51" s="279">
+      <c r="C51" s="278">
         <v>46122</v>
       </c>
-      <c r="D51" s="280">
+      <c r="D51" s="279">
         <v>1</v>
       </c>
-      <c r="E51" s="322" t="s">
+      <c r="E51" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F51" s="6"/>
@@ -12248,23 +12260,23 @@
       <c r="AX51" s="2"/>
       <c r="AY51" s="2"/>
       <c r="AZ51" s="2"/>
-      <c r="BA51" s="330" t="s">
+      <c r="BA51" s="335" t="s">
         <v>162</v>
       </c>
-      <c r="BB51" s="330"/>
-      <c r="BC51" s="330"/>
-      <c r="BD51" s="330"/>
-      <c r="BE51" s="330"/>
-      <c r="BF51" s="330"/>
-      <c r="BG51" s="330"/>
-      <c r="BH51" s="330"/>
-      <c r="BI51" s="292"/>
-      <c r="BJ51" s="293"/>
-      <c r="BK51" s="294"/>
-      <c r="BL51" s="295"/>
-      <c r="BM51" s="296"/>
-      <c r="BN51" s="297"/>
-      <c r="BO51" s="298"/>
+      <c r="BB51" s="335"/>
+      <c r="BC51" s="335"/>
+      <c r="BD51" s="335"/>
+      <c r="BE51" s="335"/>
+      <c r="BF51" s="335"/>
+      <c r="BG51" s="335"/>
+      <c r="BH51" s="335"/>
+      <c r="BI51" s="291"/>
+      <c r="BJ51" s="292"/>
+      <c r="BK51" s="293"/>
+      <c r="BL51" s="294"/>
+      <c r="BM51" s="295"/>
+      <c r="BN51" s="296"/>
+      <c r="BO51" s="297"/>
       <c r="BP51" s="2"/>
       <c r="BQ51" s="2"/>
       <c r="BR51" s="2"/>
@@ -12310,19 +12322,19 @@
       <c r="DF51" s="2"/>
     </row>
     <row r="52" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A52" s="281" t="s">
+      <c r="A52" s="280" t="s">
         <v>141</v>
       </c>
       <c r="B52" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C52" s="279">
+      <c r="C52" s="278">
         <v>46122</v>
       </c>
-      <c r="D52" s="280">
+      <c r="D52" s="279">
         <v>1</v>
       </c>
-      <c r="E52" s="322" t="s">
+      <c r="E52" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F52" s="6"/>
@@ -12372,23 +12384,23 @@
       <c r="AX52" s="2"/>
       <c r="AY52" s="2"/>
       <c r="AZ52" s="2"/>
-      <c r="BA52" s="330" t="s">
+      <c r="BA52" s="335" t="s">
         <v>163</v>
       </c>
-      <c r="BB52" s="330"/>
-      <c r="BC52" s="330"/>
-      <c r="BD52" s="330"/>
-      <c r="BE52" s="330"/>
-      <c r="BF52" s="330"/>
-      <c r="BG52" s="330"/>
-      <c r="BH52" s="330"/>
-      <c r="BI52" s="292"/>
-      <c r="BJ52" s="293"/>
-      <c r="BK52" s="294"/>
-      <c r="BL52" s="295"/>
-      <c r="BM52" s="296"/>
-      <c r="BN52" s="297"/>
-      <c r="BO52" s="298"/>
+      <c r="BB52" s="335"/>
+      <c r="BC52" s="335"/>
+      <c r="BD52" s="335"/>
+      <c r="BE52" s="335"/>
+      <c r="BF52" s="335"/>
+      <c r="BG52" s="335"/>
+      <c r="BH52" s="335"/>
+      <c r="BI52" s="291"/>
+      <c r="BJ52" s="292"/>
+      <c r="BK52" s="293"/>
+      <c r="BL52" s="294"/>
+      <c r="BM52" s="295"/>
+      <c r="BN52" s="296"/>
+      <c r="BO52" s="297"/>
       <c r="BP52" s="2"/>
       <c r="BQ52" s="2"/>
       <c r="BR52" s="2"/>
@@ -12434,19 +12446,19 @@
       <c r="DF52" s="2"/>
     </row>
     <row r="53" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A53" s="281" t="s">
+      <c r="A53" s="280" t="s">
         <v>142</v>
       </c>
       <c r="B53" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C53" s="279">
+      <c r="C53" s="278">
         <v>46122</v>
       </c>
-      <c r="D53" s="280">
+      <c r="D53" s="279">
         <v>1</v>
       </c>
-      <c r="E53" s="322" t="s">
+      <c r="E53" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F53" s="6"/>
@@ -12496,23 +12508,23 @@
       <c r="AX53" s="2"/>
       <c r="AY53" s="2"/>
       <c r="AZ53" s="2"/>
-      <c r="BA53" s="330" t="s">
+      <c r="BA53" s="335" t="s">
         <v>164</v>
       </c>
-      <c r="BB53" s="330"/>
-      <c r="BC53" s="330"/>
-      <c r="BD53" s="330"/>
-      <c r="BE53" s="330"/>
-      <c r="BF53" s="330"/>
-      <c r="BG53" s="330"/>
-      <c r="BH53" s="330"/>
-      <c r="BI53" s="292"/>
-      <c r="BJ53" s="293"/>
-      <c r="BK53" s="294"/>
-      <c r="BL53" s="295"/>
-      <c r="BM53" s="296"/>
-      <c r="BN53" s="297"/>
-      <c r="BO53" s="298"/>
+      <c r="BB53" s="335"/>
+      <c r="BC53" s="335"/>
+      <c r="BD53" s="335"/>
+      <c r="BE53" s="335"/>
+      <c r="BF53" s="335"/>
+      <c r="BG53" s="335"/>
+      <c r="BH53" s="335"/>
+      <c r="BI53" s="291"/>
+      <c r="BJ53" s="292"/>
+      <c r="BK53" s="293"/>
+      <c r="BL53" s="294"/>
+      <c r="BM53" s="295"/>
+      <c r="BN53" s="296"/>
+      <c r="BO53" s="297"/>
       <c r="BP53" s="2"/>
       <c r="BQ53" s="2"/>
       <c r="BR53" s="2"/>
@@ -12558,19 +12570,19 @@
       <c r="DF53" s="2"/>
     </row>
     <row r="54" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A54" s="281" t="s">
+      <c r="A54" s="280" t="s">
         <v>143</v>
       </c>
       <c r="B54" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C54" s="279">
+      <c r="C54" s="278">
         <v>46122</v>
       </c>
-      <c r="D54" s="280">
+      <c r="D54" s="279">
         <v>1</v>
       </c>
-      <c r="E54" s="322" t="s">
+      <c r="E54" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F54" s="6"/>
@@ -12620,23 +12632,23 @@
       <c r="AX54" s="2"/>
       <c r="AY54" s="2"/>
       <c r="AZ54" s="2"/>
-      <c r="BA54" s="330" t="s">
+      <c r="BA54" s="335" t="s">
         <v>165</v>
       </c>
-      <c r="BB54" s="330"/>
-      <c r="BC54" s="330"/>
-      <c r="BD54" s="330"/>
-      <c r="BE54" s="330"/>
-      <c r="BF54" s="330"/>
-      <c r="BG54" s="330"/>
-      <c r="BH54" s="330"/>
-      <c r="BI54" s="292"/>
-      <c r="BJ54" s="293"/>
-      <c r="BK54" s="294"/>
-      <c r="BL54" s="295"/>
-      <c r="BM54" s="296"/>
-      <c r="BN54" s="297"/>
-      <c r="BO54" s="298"/>
+      <c r="BB54" s="335"/>
+      <c r="BC54" s="335"/>
+      <c r="BD54" s="335"/>
+      <c r="BE54" s="335"/>
+      <c r="BF54" s="335"/>
+      <c r="BG54" s="335"/>
+      <c r="BH54" s="335"/>
+      <c r="BI54" s="291"/>
+      <c r="BJ54" s="292"/>
+      <c r="BK54" s="293"/>
+      <c r="BL54" s="294"/>
+      <c r="BM54" s="295"/>
+      <c r="BN54" s="296"/>
+      <c r="BO54" s="297"/>
       <c r="BP54" s="2"/>
       <c r="BQ54" s="2"/>
       <c r="BR54" s="2"/>
@@ -12682,19 +12694,19 @@
       <c r="DF54" s="2"/>
     </row>
     <row r="55" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A55" s="281" t="s">
+      <c r="A55" s="280" t="s">
         <v>150</v>
       </c>
       <c r="B55" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C55" s="279">
+      <c r="C55" s="278">
         <v>46122</v>
       </c>
-      <c r="D55" s="280">
+      <c r="D55" s="279">
         <v>1</v>
       </c>
-      <c r="E55" s="322" t="s">
+      <c r="E55" s="321" t="s">
         <v>149</v>
       </c>
       <c r="F55" s="6"/>
@@ -12744,23 +12756,23 @@
       <c r="AX55" s="2"/>
       <c r="AY55" s="2"/>
       <c r="AZ55" s="2"/>
-      <c r="BA55" s="330" t="s">
+      <c r="BA55" s="335" t="s">
         <v>166</v>
       </c>
-      <c r="BB55" s="330"/>
-      <c r="BC55" s="330"/>
-      <c r="BD55" s="330"/>
-      <c r="BE55" s="330"/>
-      <c r="BF55" s="330"/>
-      <c r="BG55" s="330"/>
-      <c r="BH55" s="330"/>
-      <c r="BI55" s="292"/>
-      <c r="BJ55" s="293"/>
-      <c r="BK55" s="294"/>
-      <c r="BL55" s="295"/>
-      <c r="BM55" s="296"/>
-      <c r="BN55" s="297"/>
-      <c r="BO55" s="298"/>
+      <c r="BB55" s="335"/>
+      <c r="BC55" s="335"/>
+      <c r="BD55" s="335"/>
+      <c r="BE55" s="335"/>
+      <c r="BF55" s="335"/>
+      <c r="BG55" s="335"/>
+      <c r="BH55" s="335"/>
+      <c r="BI55" s="291"/>
+      <c r="BJ55" s="292"/>
+      <c r="BK55" s="293"/>
+      <c r="BL55" s="294"/>
+      <c r="BM55" s="295"/>
+      <c r="BN55" s="296"/>
+      <c r="BO55" s="297"/>
       <c r="BP55" s="2"/>
       <c r="BQ55" s="2"/>
       <c r="BR55" s="2"/>
@@ -12806,19 +12818,19 @@
       <c r="DF55" s="2"/>
     </row>
     <row r="56" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A56" s="281" t="s">
+      <c r="A56" s="280" t="s">
         <v>145</v>
       </c>
       <c r="B56" s="230" t="s">
         <v>80</v>
       </c>
-      <c r="C56" s="279">
+      <c r="C56" s="278">
         <v>46122</v>
       </c>
-      <c r="D56" s="280">
+      <c r="D56" s="279">
         <v>1</v>
       </c>
-      <c r="E56" s="322" t="s">
+      <c r="E56" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F56" s="6"/>
@@ -12868,23 +12880,23 @@
       <c r="AX56" s="2"/>
       <c r="AY56" s="2"/>
       <c r="AZ56" s="2"/>
-      <c r="BA56" s="330" t="s">
+      <c r="BA56" s="335" t="s">
         <v>167</v>
       </c>
-      <c r="BB56" s="330"/>
-      <c r="BC56" s="330"/>
-      <c r="BD56" s="330"/>
-      <c r="BE56" s="330"/>
-      <c r="BF56" s="330"/>
-      <c r="BG56" s="330"/>
-      <c r="BH56" s="330"/>
-      <c r="BI56" s="292"/>
-      <c r="BJ56" s="293"/>
-      <c r="BK56" s="294"/>
-      <c r="BL56" s="295"/>
-      <c r="BM56" s="296"/>
-      <c r="BN56" s="297"/>
-      <c r="BO56" s="298"/>
+      <c r="BB56" s="335"/>
+      <c r="BC56" s="335"/>
+      <c r="BD56" s="335"/>
+      <c r="BE56" s="335"/>
+      <c r="BF56" s="335"/>
+      <c r="BG56" s="335"/>
+      <c r="BH56" s="335"/>
+      <c r="BI56" s="291"/>
+      <c r="BJ56" s="292"/>
+      <c r="BK56" s="293"/>
+      <c r="BL56" s="294"/>
+      <c r="BM56" s="295"/>
+      <c r="BN56" s="296"/>
+      <c r="BO56" s="297"/>
       <c r="BP56" s="2"/>
       <c r="BQ56" s="2"/>
       <c r="BR56" s="2"/>
@@ -12930,19 +12942,19 @@
       <c r="DF56" s="2"/>
     </row>
     <row r="57" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A57" s="281" t="s">
+      <c r="A57" s="280" t="s">
         <v>168</v>
       </c>
-      <c r="B57" s="290">
+      <c r="B57" s="289">
         <v>46122</v>
       </c>
       <c r="C57" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D57" s="280">
+      <c r="D57" s="279">
         <v>1</v>
       </c>
-      <c r="E57" s="322" t="s">
+      <c r="E57" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F57" s="6"/>
@@ -12992,24 +13004,24 @@
       <c r="AX57" s="2"/>
       <c r="AY57" s="2"/>
       <c r="AZ57" s="2"/>
-      <c r="BA57" s="323"/>
-      <c r="BB57" s="323"/>
-      <c r="BC57" s="323"/>
-      <c r="BD57" s="323"/>
-      <c r="BE57" s="323"/>
-      <c r="BF57" s="323"/>
-      <c r="BG57" s="323"/>
-      <c r="BH57" s="330" t="s">
+      <c r="BA57" s="322"/>
+      <c r="BB57" s="322"/>
+      <c r="BC57" s="322"/>
+      <c r="BD57" s="322"/>
+      <c r="BE57" s="322"/>
+      <c r="BF57" s="322"/>
+      <c r="BG57" s="322"/>
+      <c r="BH57" s="335" t="s">
         <v>171</v>
       </c>
-      <c r="BI57" s="331"/>
-      <c r="BJ57" s="331"/>
-      <c r="BK57" s="331"/>
-      <c r="BL57" s="331"/>
-      <c r="BM57" s="331"/>
-      <c r="BN57" s="331"/>
-      <c r="BO57" s="331"/>
-      <c r="BP57" s="324"/>
+      <c r="BI57" s="432"/>
+      <c r="BJ57" s="432"/>
+      <c r="BK57" s="432"/>
+      <c r="BL57" s="432"/>
+      <c r="BM57" s="432"/>
+      <c r="BN57" s="432"/>
+      <c r="BO57" s="432"/>
+      <c r="BP57" s="323"/>
       <c r="BQ57" s="2"/>
       <c r="BR57" s="2"/>
       <c r="BS57" s="2"/>
@@ -13054,19 +13066,19 @@
       <c r="DF57" s="2"/>
     </row>
     <row r="58" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A58" s="281" t="s">
+      <c r="A58" s="280" t="s">
         <v>169</v>
       </c>
-      <c r="B58" s="290">
+      <c r="B58" s="289">
         <v>46122</v>
       </c>
       <c r="C58" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D58" s="280">
+      <c r="D58" s="279">
         <v>1</v>
       </c>
-      <c r="E58" s="322" t="s">
+      <c r="E58" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F58" s="6"/>
@@ -13116,23 +13128,23 @@
       <c r="AX58" s="2"/>
       <c r="AY58" s="2"/>
       <c r="AZ58" s="2"/>
-      <c r="BA58" s="323"/>
-      <c r="BB58" s="323"/>
-      <c r="BC58" s="323"/>
-      <c r="BD58" s="323"/>
-      <c r="BE58" s="323"/>
-      <c r="BF58" s="323"/>
-      <c r="BG58" s="323"/>
-      <c r="BH58" s="330" t="s">
+      <c r="BA58" s="322"/>
+      <c r="BB58" s="322"/>
+      <c r="BC58" s="322"/>
+      <c r="BD58" s="322"/>
+      <c r="BE58" s="322"/>
+      <c r="BF58" s="322"/>
+      <c r="BG58" s="322"/>
+      <c r="BH58" s="335" t="s">
         <v>172</v>
       </c>
-      <c r="BI58" s="331"/>
-      <c r="BJ58" s="331"/>
-      <c r="BK58" s="331"/>
-      <c r="BL58" s="331"/>
-      <c r="BM58" s="331"/>
-      <c r="BN58" s="331"/>
-      <c r="BO58" s="331"/>
+      <c r="BI58" s="432"/>
+      <c r="BJ58" s="432"/>
+      <c r="BK58" s="432"/>
+      <c r="BL58" s="432"/>
+      <c r="BM58" s="432"/>
+      <c r="BN58" s="432"/>
+      <c r="BO58" s="432"/>
       <c r="BP58" s="2"/>
       <c r="BQ58" s="2"/>
       <c r="BR58" s="2"/>
@@ -13178,19 +13190,19 @@
       <c r="DF58" s="2"/>
     </row>
     <row r="59" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A59" s="281" t="s">
+      <c r="A59" s="280" t="s">
         <v>183</v>
       </c>
-      <c r="B59" s="290">
+      <c r="B59" s="289">
         <v>46122</v>
       </c>
       <c r="C59" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D59" s="280">
+      <c r="D59" s="279">
         <v>1</v>
       </c>
-      <c r="E59" s="322" t="s">
+      <c r="E59" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F59" s="6"/>
@@ -13240,23 +13252,23 @@
       <c r="AX59" s="2"/>
       <c r="AY59" s="2"/>
       <c r="AZ59" s="2"/>
-      <c r="BA59" s="323"/>
-      <c r="BB59" s="323"/>
-      <c r="BC59" s="323"/>
-      <c r="BD59" s="323"/>
-      <c r="BE59" s="323"/>
-      <c r="BF59" s="323"/>
-      <c r="BG59" s="323"/>
-      <c r="BH59" s="330" t="s">
+      <c r="BA59" s="322"/>
+      <c r="BB59" s="322"/>
+      <c r="BC59" s="322"/>
+      <c r="BD59" s="322"/>
+      <c r="BE59" s="322"/>
+      <c r="BF59" s="322"/>
+      <c r="BG59" s="322"/>
+      <c r="BH59" s="335" t="s">
         <v>173</v>
       </c>
-      <c r="BI59" s="331"/>
-      <c r="BJ59" s="331"/>
-      <c r="BK59" s="331"/>
-      <c r="BL59" s="331"/>
-      <c r="BM59" s="331"/>
-      <c r="BN59" s="331"/>
-      <c r="BO59" s="331"/>
+      <c r="BI59" s="432"/>
+      <c r="BJ59" s="432"/>
+      <c r="BK59" s="432"/>
+      <c r="BL59" s="432"/>
+      <c r="BM59" s="432"/>
+      <c r="BN59" s="432"/>
+      <c r="BO59" s="432"/>
       <c r="BP59" s="2"/>
       <c r="BQ59" s="2"/>
       <c r="BR59" s="2"/>
@@ -13302,19 +13314,19 @@
       <c r="DF59" s="2"/>
     </row>
     <row r="60" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A60" s="281" t="s">
+      <c r="A60" s="280" t="s">
         <v>184</v>
       </c>
-      <c r="B60" s="290">
+      <c r="B60" s="289">
         <v>46122</v>
       </c>
       <c r="C60" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D60" s="280">
+      <c r="D60" s="279">
         <v>1</v>
       </c>
-      <c r="E60" s="322" t="s">
+      <c r="E60" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F60" s="6"/>
@@ -13364,23 +13376,23 @@
       <c r="AX60" s="2"/>
       <c r="AY60" s="2"/>
       <c r="AZ60" s="2"/>
-      <c r="BA60" s="323"/>
-      <c r="BB60" s="323"/>
-      <c r="BC60" s="323"/>
-      <c r="BD60" s="323"/>
-      <c r="BE60" s="323"/>
-      <c r="BF60" s="323"/>
-      <c r="BG60" s="323"/>
-      <c r="BH60" s="330" t="s">
+      <c r="BA60" s="322"/>
+      <c r="BB60" s="322"/>
+      <c r="BC60" s="322"/>
+      <c r="BD60" s="322"/>
+      <c r="BE60" s="322"/>
+      <c r="BF60" s="322"/>
+      <c r="BG60" s="322"/>
+      <c r="BH60" s="335" t="s">
         <v>174</v>
       </c>
-      <c r="BI60" s="331"/>
-      <c r="BJ60" s="331"/>
-      <c r="BK60" s="331"/>
-      <c r="BL60" s="331"/>
-      <c r="BM60" s="331"/>
-      <c r="BN60" s="331"/>
-      <c r="BO60" s="331"/>
+      <c r="BI60" s="432"/>
+      <c r="BJ60" s="432"/>
+      <c r="BK60" s="432"/>
+      <c r="BL60" s="432"/>
+      <c r="BM60" s="432"/>
+      <c r="BN60" s="432"/>
+      <c r="BO60" s="432"/>
       <c r="BP60" s="2"/>
       <c r="BQ60" s="2"/>
       <c r="BR60" s="2"/>
@@ -13426,19 +13438,19 @@
       <c r="DF60" s="2"/>
     </row>
     <row r="61" spans="1:110" ht="53.25" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A61" s="281" t="s">
+      <c r="A61" s="280" t="s">
         <v>170</v>
       </c>
-      <c r="B61" s="290">
+      <c r="B61" s="289">
         <v>46122</v>
       </c>
       <c r="C61" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D61" s="280">
+      <c r="D61" s="279">
         <v>1</v>
       </c>
-      <c r="E61" s="322" t="s">
+      <c r="E61" s="321" t="s">
         <v>149</v>
       </c>
       <c r="F61" s="6"/>
@@ -13488,23 +13500,23 @@
       <c r="AX61" s="2"/>
       <c r="AY61" s="2"/>
       <c r="AZ61" s="2"/>
-      <c r="BA61" s="323"/>
-      <c r="BB61" s="323"/>
-      <c r="BC61" s="323"/>
-      <c r="BD61" s="323"/>
-      <c r="BE61" s="323"/>
-      <c r="BF61" s="323"/>
-      <c r="BG61" s="323"/>
-      <c r="BH61" s="330" t="s">
+      <c r="BA61" s="322"/>
+      <c r="BB61" s="322"/>
+      <c r="BC61" s="322"/>
+      <c r="BD61" s="322"/>
+      <c r="BE61" s="322"/>
+      <c r="BF61" s="322"/>
+      <c r="BG61" s="322"/>
+      <c r="BH61" s="335" t="s">
         <v>175</v>
       </c>
-      <c r="BI61" s="331"/>
-      <c r="BJ61" s="331"/>
-      <c r="BK61" s="331"/>
-      <c r="BL61" s="331"/>
-      <c r="BM61" s="331"/>
-      <c r="BN61" s="331"/>
-      <c r="BO61" s="331"/>
+      <c r="BI61" s="432"/>
+      <c r="BJ61" s="432"/>
+      <c r="BK61" s="432"/>
+      <c r="BL61" s="432"/>
+      <c r="BM61" s="432"/>
+      <c r="BN61" s="432"/>
+      <c r="BO61" s="432"/>
       <c r="BP61" s="2"/>
       <c r="BQ61" s="2"/>
       <c r="BR61" s="2"/>
@@ -13550,19 +13562,19 @@
       <c r="DF61" s="2"/>
     </row>
     <row r="62" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A62" s="281" t="s">
+      <c r="A62" s="280" t="s">
         <v>82</v>
       </c>
-      <c r="B62" s="290">
+      <c r="B62" s="289">
         <v>46122</v>
       </c>
       <c r="C62" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D62" s="280">
+      <c r="D62" s="279">
         <v>1</v>
       </c>
-      <c r="E62" s="322" t="s">
+      <c r="E62" s="321" t="s">
         <v>149</v>
       </c>
       <c r="F62" s="6"/>
@@ -13612,23 +13624,23 @@
       <c r="AX62" s="2"/>
       <c r="AY62" s="2"/>
       <c r="AZ62" s="2"/>
-      <c r="BA62" s="323"/>
-      <c r="BB62" s="323"/>
-      <c r="BC62" s="323"/>
-      <c r="BD62" s="323"/>
-      <c r="BE62" s="323"/>
-      <c r="BF62" s="323"/>
-      <c r="BG62" s="323"/>
-      <c r="BH62" s="330" t="s">
+      <c r="BA62" s="322"/>
+      <c r="BB62" s="322"/>
+      <c r="BC62" s="322"/>
+      <c r="BD62" s="322"/>
+      <c r="BE62" s="322"/>
+      <c r="BF62" s="322"/>
+      <c r="BG62" s="322"/>
+      <c r="BH62" s="335" t="s">
         <v>190</v>
       </c>
-      <c r="BI62" s="330"/>
-      <c r="BJ62" s="330"/>
-      <c r="BK62" s="330"/>
-      <c r="BL62" s="330"/>
-      <c r="BM62" s="330"/>
-      <c r="BN62" s="330"/>
-      <c r="BO62" s="330"/>
+      <c r="BI62" s="335"/>
+      <c r="BJ62" s="335"/>
+      <c r="BK62" s="335"/>
+      <c r="BL62" s="335"/>
+      <c r="BM62" s="335"/>
+      <c r="BN62" s="335"/>
+      <c r="BO62" s="335"/>
       <c r="BP62" s="2"/>
       <c r="BQ62" s="2"/>
       <c r="BR62" s="2"/>
@@ -13674,19 +13686,19 @@
       <c r="DF62" s="2"/>
     </row>
     <row r="63" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A63" s="281" t="s">
+      <c r="A63" s="280" t="s">
         <v>181</v>
       </c>
-      <c r="B63" s="290">
+      <c r="B63" s="289">
         <v>46122</v>
       </c>
       <c r="C63" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D63" s="280">
+      <c r="D63" s="279">
         <v>1</v>
       </c>
-      <c r="E63" s="322" t="s">
+      <c r="E63" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F63" s="6"/>
@@ -13736,23 +13748,23 @@
       <c r="AX63" s="2"/>
       <c r="AY63" s="2"/>
       <c r="AZ63" s="2"/>
-      <c r="BA63" s="323"/>
-      <c r="BB63" s="323"/>
-      <c r="BC63" s="323"/>
-      <c r="BD63" s="323"/>
-      <c r="BE63" s="323"/>
-      <c r="BF63" s="323"/>
-      <c r="BG63" s="323"/>
-      <c r="BH63" s="330" t="s">
+      <c r="BA63" s="322"/>
+      <c r="BB63" s="322"/>
+      <c r="BC63" s="322"/>
+      <c r="BD63" s="322"/>
+      <c r="BE63" s="322"/>
+      <c r="BF63" s="322"/>
+      <c r="BG63" s="322"/>
+      <c r="BH63" s="335" t="s">
         <v>191</v>
       </c>
-      <c r="BI63" s="330"/>
-      <c r="BJ63" s="330"/>
-      <c r="BK63" s="330"/>
-      <c r="BL63" s="330"/>
-      <c r="BM63" s="330"/>
-      <c r="BN63" s="330"/>
-      <c r="BO63" s="330"/>
+      <c r="BI63" s="335"/>
+      <c r="BJ63" s="335"/>
+      <c r="BK63" s="335"/>
+      <c r="BL63" s="335"/>
+      <c r="BM63" s="335"/>
+      <c r="BN63" s="335"/>
+      <c r="BO63" s="335"/>
       <c r="BP63" s="2"/>
       <c r="BQ63" s="2"/>
       <c r="BR63" s="2"/>
@@ -13798,19 +13810,19 @@
       <c r="DF63" s="2"/>
     </row>
     <row r="64" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A64" s="281" t="s">
+      <c r="A64" s="280" t="s">
         <v>180</v>
       </c>
-      <c r="B64" s="290">
+      <c r="B64" s="289">
         <v>46122</v>
       </c>
       <c r="C64" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D64" s="280">
+      <c r="D64" s="279">
         <v>1</v>
       </c>
-      <c r="E64" s="322" t="s">
+      <c r="E64" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F64" s="6"/>
@@ -13860,23 +13872,23 @@
       <c r="AX64" s="2"/>
       <c r="AY64" s="2"/>
       <c r="AZ64" s="2"/>
-      <c r="BA64" s="323"/>
-      <c r="BB64" s="323"/>
-      <c r="BC64" s="323"/>
-      <c r="BD64" s="323"/>
-      <c r="BE64" s="323"/>
-      <c r="BF64" s="323"/>
-      <c r="BG64" s="323"/>
-      <c r="BH64" s="330" t="s">
+      <c r="BA64" s="322"/>
+      <c r="BB64" s="322"/>
+      <c r="BC64" s="322"/>
+      <c r="BD64" s="322"/>
+      <c r="BE64" s="322"/>
+      <c r="BF64" s="322"/>
+      <c r="BG64" s="322"/>
+      <c r="BH64" s="335" t="s">
         <v>192</v>
       </c>
-      <c r="BI64" s="330"/>
-      <c r="BJ64" s="330"/>
-      <c r="BK64" s="330"/>
-      <c r="BL64" s="330"/>
-      <c r="BM64" s="330"/>
-      <c r="BN64" s="330"/>
-      <c r="BO64" s="330"/>
+      <c r="BI64" s="335"/>
+      <c r="BJ64" s="335"/>
+      <c r="BK64" s="335"/>
+      <c r="BL64" s="335"/>
+      <c r="BM64" s="335"/>
+      <c r="BN64" s="335"/>
+      <c r="BO64" s="335"/>
       <c r="BP64" s="2"/>
       <c r="BQ64" s="2"/>
       <c r="BR64" s="2"/>
@@ -13922,19 +13934,19 @@
       <c r="DF64" s="2"/>
     </row>
     <row r="65" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A65" s="281" t="s">
+      <c r="A65" s="280" t="s">
         <v>179</v>
       </c>
-      <c r="B65" s="290">
+      <c r="B65" s="289">
         <v>46122</v>
       </c>
       <c r="C65" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D65" s="280">
+      <c r="D65" s="279">
         <v>1</v>
       </c>
-      <c r="E65" s="322" t="s">
+      <c r="E65" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F65" s="6"/>
@@ -13984,23 +13996,23 @@
       <c r="AX65" s="2"/>
       <c r="AY65" s="2"/>
       <c r="AZ65" s="2"/>
-      <c r="BA65" s="323"/>
-      <c r="BB65" s="323"/>
-      <c r="BC65" s="323"/>
-      <c r="BD65" s="323"/>
-      <c r="BE65" s="323"/>
-      <c r="BF65" s="323"/>
-      <c r="BG65" s="323"/>
-      <c r="BH65" s="330" t="s">
+      <c r="BA65" s="322"/>
+      <c r="BB65" s="322"/>
+      <c r="BC65" s="322"/>
+      <c r="BD65" s="322"/>
+      <c r="BE65" s="322"/>
+      <c r="BF65" s="322"/>
+      <c r="BG65" s="322"/>
+      <c r="BH65" s="335" t="s">
         <v>193</v>
       </c>
-      <c r="BI65" s="330"/>
-      <c r="BJ65" s="330"/>
-      <c r="BK65" s="330"/>
-      <c r="BL65" s="330"/>
-      <c r="BM65" s="330"/>
-      <c r="BN65" s="330"/>
-      <c r="BO65" s="330"/>
+      <c r="BI65" s="335"/>
+      <c r="BJ65" s="335"/>
+      <c r="BK65" s="335"/>
+      <c r="BL65" s="335"/>
+      <c r="BM65" s="335"/>
+      <c r="BN65" s="335"/>
+      <c r="BO65" s="335"/>
       <c r="BP65" s="2"/>
       <c r="BQ65" s="2"/>
       <c r="BR65" s="2"/>
@@ -14046,19 +14058,19 @@
       <c r="DF65" s="2"/>
     </row>
     <row r="66" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A66" s="281" t="s">
+      <c r="A66" s="280" t="s">
         <v>178</v>
       </c>
-      <c r="B66" s="290">
+      <c r="B66" s="289">
         <v>46122</v>
       </c>
       <c r="C66" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D66" s="280">
+      <c r="D66" s="279">
         <v>1</v>
       </c>
-      <c r="E66" s="322" t="s">
+      <c r="E66" s="321" t="s">
         <v>148</v>
       </c>
       <c r="F66" s="6"/>
@@ -14108,23 +14120,23 @@
       <c r="AX66" s="2"/>
       <c r="AY66" s="2"/>
       <c r="AZ66" s="2"/>
-      <c r="BA66" s="323"/>
-      <c r="BB66" s="323"/>
-      <c r="BC66" s="323"/>
-      <c r="BD66" s="323"/>
-      <c r="BE66" s="323"/>
-      <c r="BF66" s="323"/>
-      <c r="BG66" s="323"/>
-      <c r="BH66" s="330" t="s">
+      <c r="BA66" s="322"/>
+      <c r="BB66" s="322"/>
+      <c r="BC66" s="322"/>
+      <c r="BD66" s="322"/>
+      <c r="BE66" s="322"/>
+      <c r="BF66" s="322"/>
+      <c r="BG66" s="322"/>
+      <c r="BH66" s="335" t="s">
         <v>194</v>
       </c>
-      <c r="BI66" s="330"/>
-      <c r="BJ66" s="330"/>
-      <c r="BK66" s="330"/>
-      <c r="BL66" s="330"/>
-      <c r="BM66" s="330"/>
-      <c r="BN66" s="330"/>
-      <c r="BO66" s="330"/>
+      <c r="BI66" s="335"/>
+      <c r="BJ66" s="335"/>
+      <c r="BK66" s="335"/>
+      <c r="BL66" s="335"/>
+      <c r="BM66" s="335"/>
+      <c r="BN66" s="335"/>
+      <c r="BO66" s="335"/>
       <c r="BP66" s="2"/>
       <c r="BQ66" s="2"/>
       <c r="BR66" s="2"/>
@@ -14170,19 +14182,19 @@
       <c r="DF66" s="2"/>
     </row>
     <row r="67" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A67" s="281" t="s">
+      <c r="A67" s="280" t="s">
         <v>182</v>
       </c>
-      <c r="B67" s="290">
+      <c r="B67" s="289">
         <v>46122</v>
       </c>
       <c r="C67" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D67" s="280">
+      <c r="D67" s="279">
         <v>1</v>
       </c>
-      <c r="E67" s="322" t="s">
+      <c r="E67" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F67" s="6"/>
@@ -14232,23 +14244,23 @@
       <c r="AX67" s="2"/>
       <c r="AY67" s="2"/>
       <c r="AZ67" s="2"/>
-      <c r="BA67" s="323"/>
-      <c r="BB67" s="323"/>
-      <c r="BC67" s="323"/>
-      <c r="BD67" s="323"/>
-      <c r="BE67" s="323"/>
-      <c r="BF67" s="323"/>
-      <c r="BG67" s="323"/>
-      <c r="BH67" s="330" t="s">
+      <c r="BA67" s="322"/>
+      <c r="BB67" s="322"/>
+      <c r="BC67" s="322"/>
+      <c r="BD67" s="322"/>
+      <c r="BE67" s="322"/>
+      <c r="BF67" s="322"/>
+      <c r="BG67" s="322"/>
+      <c r="BH67" s="335" t="s">
         <v>195</v>
       </c>
-      <c r="BI67" s="330"/>
-      <c r="BJ67" s="330"/>
-      <c r="BK67" s="330"/>
-      <c r="BL67" s="330"/>
-      <c r="BM67" s="330"/>
-      <c r="BN67" s="330"/>
-      <c r="BO67" s="330"/>
+      <c r="BI67" s="335"/>
+      <c r="BJ67" s="335"/>
+      <c r="BK67" s="335"/>
+      <c r="BL67" s="335"/>
+      <c r="BM67" s="335"/>
+      <c r="BN67" s="335"/>
+      <c r="BO67" s="335"/>
       <c r="BP67" s="2"/>
       <c r="BQ67" s="2"/>
       <c r="BR67" s="2"/>
@@ -14294,19 +14306,19 @@
       <c r="DF67" s="2"/>
     </row>
     <row r="68" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A68" s="281" t="s">
+      <c r="A68" s="280" t="s">
         <v>185</v>
       </c>
-      <c r="B68" s="290">
+      <c r="B68" s="289">
         <v>46122</v>
       </c>
       <c r="C68" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D68" s="280">
+      <c r="D68" s="279">
         <v>1</v>
       </c>
-      <c r="E68" s="322" t="s">
+      <c r="E68" s="321" t="s">
         <v>177</v>
       </c>
       <c r="F68" s="6"/>
@@ -14356,23 +14368,23 @@
       <c r="AX68" s="2"/>
       <c r="AY68" s="2"/>
       <c r="AZ68" s="2"/>
-      <c r="BA68" s="323"/>
-      <c r="BB68" s="323"/>
-      <c r="BC68" s="323"/>
-      <c r="BD68" s="323"/>
-      <c r="BE68" s="323"/>
-      <c r="BF68" s="323"/>
-      <c r="BG68" s="323"/>
-      <c r="BH68" s="330" t="s">
+      <c r="BA68" s="322"/>
+      <c r="BB68" s="322"/>
+      <c r="BC68" s="322"/>
+      <c r="BD68" s="322"/>
+      <c r="BE68" s="322"/>
+      <c r="BF68" s="322"/>
+      <c r="BG68" s="322"/>
+      <c r="BH68" s="335" t="s">
         <v>196</v>
       </c>
-      <c r="BI68" s="330"/>
-      <c r="BJ68" s="330"/>
-      <c r="BK68" s="330"/>
-      <c r="BL68" s="330"/>
-      <c r="BM68" s="330"/>
-      <c r="BN68" s="330"/>
-      <c r="BO68" s="330"/>
+      <c r="BI68" s="335"/>
+      <c r="BJ68" s="335"/>
+      <c r="BK68" s="335"/>
+      <c r="BL68" s="335"/>
+      <c r="BM68" s="335"/>
+      <c r="BN68" s="335"/>
+      <c r="BO68" s="335"/>
       <c r="BP68" s="2"/>
       <c r="BQ68" s="2"/>
       <c r="BR68" s="2"/>
@@ -14418,19 +14430,19 @@
       <c r="DF68" s="2"/>
     </row>
     <row r="69" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A69" s="281" t="s">
+      <c r="A69" s="280" t="s">
         <v>125</v>
       </c>
-      <c r="B69" s="290">
+      <c r="B69" s="289">
         <v>46122</v>
       </c>
       <c r="C69" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="D69" s="322">
+      <c r="D69" s="321">
         <v>1</v>
       </c>
-      <c r="E69" s="326" t="s">
+      <c r="E69" s="325" t="s">
         <v>149</v>
       </c>
       <c r="F69" s="233"/>
@@ -14483,22 +14495,22 @@
       <c r="AY69" s="2"/>
       <c r="AZ69" s="2"/>
       <c r="BA69" s="150"/>
-      <c r="BB69" s="299"/>
-      <c r="BC69" s="300"/>
-      <c r="BD69" s="301"/>
-      <c r="BE69" s="302"/>
-      <c r="BF69" s="303"/>
-      <c r="BG69" s="304"/>
-      <c r="BH69" s="330" t="s">
+      <c r="BB69" s="298"/>
+      <c r="BC69" s="299"/>
+      <c r="BD69" s="300"/>
+      <c r="BE69" s="301"/>
+      <c r="BF69" s="302"/>
+      <c r="BG69" s="303"/>
+      <c r="BH69" s="335" t="s">
         <v>176</v>
       </c>
-      <c r="BI69" s="331"/>
-      <c r="BJ69" s="331"/>
-      <c r="BK69" s="331"/>
-      <c r="BL69" s="331"/>
-      <c r="BM69" s="331"/>
-      <c r="BN69" s="331"/>
-      <c r="BO69" s="331"/>
+      <c r="BI69" s="432"/>
+      <c r="BJ69" s="432"/>
+      <c r="BK69" s="432"/>
+      <c r="BL69" s="432"/>
+      <c r="BM69" s="432"/>
+      <c r="BN69" s="432"/>
+      <c r="BO69" s="432"/>
       <c r="BP69" s="2"/>
       <c r="BQ69" s="2"/>
       <c r="BR69" s="2"/>
@@ -14544,19 +14556,19 @@
       <c r="DF69" s="2"/>
     </row>
     <row r="70" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A70" s="281" t="s">
+      <c r="A70" s="280" t="s">
         <v>207</v>
       </c>
-      <c r="B70" s="291">
+      <c r="B70" s="290">
         <v>46129</v>
       </c>
-      <c r="C70" s="325">
+      <c r="C70" s="324">
         <v>46134</v>
       </c>
-      <c r="D70" s="327">
+      <c r="D70" s="326">
         <v>1</v>
       </c>
-      <c r="E70" s="326" t="s">
+      <c r="E70" s="325" t="s">
         <v>149</v>
       </c>
       <c r="F70" s="236"/>
@@ -14612,23 +14624,23 @@
       <c r="BB70" s="2"/>
       <c r="BC70" s="2"/>
       <c r="BD70" s="2"/>
-      <c r="BE70" s="305"/>
-      <c r="BF70" s="306"/>
-      <c r="BG70" s="307"/>
-      <c r="BH70" s="308"/>
-      <c r="BI70" s="309"/>
-      <c r="BJ70" s="310"/>
-      <c r="BK70" s="311"/>
-      <c r="BL70" s="312"/>
-      <c r="BM70" s="313"/>
+      <c r="BE70" s="304"/>
+      <c r="BF70" s="305"/>
+      <c r="BG70" s="306"/>
+      <c r="BH70" s="307"/>
+      <c r="BI70" s="308"/>
+      <c r="BJ70" s="309"/>
+      <c r="BK70" s="310"/>
+      <c r="BL70" s="311"/>
+      <c r="BM70" s="312"/>
       <c r="BN70" s="2"/>
-      <c r="BO70" s="332" t="s">
+      <c r="BO70" s="331" t="s">
         <v>208</v>
       </c>
-      <c r="BP70" s="332"/>
-      <c r="BQ70" s="332"/>
-      <c r="BR70" s="332"/>
-      <c r="BS70" s="332"/>
+      <c r="BP70" s="331"/>
+      <c r="BQ70" s="331"/>
+      <c r="BR70" s="331"/>
+      <c r="BS70" s="331"/>
       <c r="BT70" s="2"/>
       <c r="BU70" s="2"/>
       <c r="BV70" s="2"/>
@@ -14670,19 +14682,19 @@
       <c r="DF70" s="2"/>
     </row>
     <row r="71" spans="1:110" ht="48" x14ac:dyDescent="0.8">
-      <c r="A71" s="328" t="s">
+      <c r="A71" s="327" t="s">
         <v>203</v>
       </c>
-      <c r="B71" s="291">
+      <c r="B71" s="290">
         <v>46129</v>
       </c>
       <c r="C71" s="235" t="s">
         <v>84</v>
       </c>
-      <c r="D71" s="327">
+      <c r="D71" s="326">
         <v>0</v>
       </c>
-      <c r="E71" s="326" t="s">
+      <c r="E71" s="325" t="s">
         <v>177</v>
       </c>
       <c r="F71" s="6" t="s">
@@ -14738,15 +14750,15 @@
       <c r="BB71" s="2"/>
       <c r="BC71" s="2"/>
       <c r="BD71" s="2"/>
-      <c r="BE71" s="305"/>
-      <c r="BF71" s="306"/>
-      <c r="BG71" s="307"/>
-      <c r="BH71" s="308"/>
-      <c r="BI71" s="309"/>
-      <c r="BJ71" s="310"/>
-      <c r="BK71" s="311"/>
-      <c r="BL71" s="312"/>
-      <c r="BM71" s="313"/>
+      <c r="BE71" s="304"/>
+      <c r="BF71" s="305"/>
+      <c r="BG71" s="306"/>
+      <c r="BH71" s="307"/>
+      <c r="BI71" s="308"/>
+      <c r="BJ71" s="309"/>
+      <c r="BK71" s="310"/>
+      <c r="BL71" s="311"/>
+      <c r="BM71" s="312"/>
       <c r="BN71" s="2"/>
       <c r="BO71" s="434" t="s">
         <v>197</v>
@@ -14795,23 +14807,25 @@
       <c r="DE71" s="2"/>
       <c r="DF71" s="2"/>
     </row>
-    <row r="72" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A72" s="281" t="s">
+    <row r="72" spans="1:110" ht="32" x14ac:dyDescent="0.8">
+      <c r="A72" s="329" t="s">
         <v>198</v>
       </c>
-      <c r="B72" s="291">
+      <c r="B72" s="290">
         <v>46129</v>
       </c>
       <c r="C72" s="235" t="s">
         <v>84</v>
       </c>
-      <c r="D72" s="327">
-        <v>1</v>
-      </c>
-      <c r="E72" s="326" t="s">
+      <c r="D72" s="326">
+        <v>0.5</v>
+      </c>
+      <c r="E72" s="325" t="s">
         <v>148</v>
       </c>
-      <c r="F72" s="236"/>
+      <c r="F72" s="6" t="s">
+        <v>212</v>
+      </c>
       <c r="G72" s="237"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
@@ -14862,25 +14876,25 @@
       <c r="BB72" s="2"/>
       <c r="BC72" s="2"/>
       <c r="BD72" s="2"/>
-      <c r="BE72" s="305"/>
-      <c r="BF72" s="306"/>
-      <c r="BG72" s="307"/>
-      <c r="BH72" s="308"/>
-      <c r="BI72" s="309"/>
-      <c r="BJ72" s="310"/>
-      <c r="BK72" s="311"/>
-      <c r="BL72" s="312"/>
-      <c r="BM72" s="313"/>
+      <c r="BE72" s="304"/>
+      <c r="BF72" s="305"/>
+      <c r="BG72" s="306"/>
+      <c r="BH72" s="307"/>
+      <c r="BI72" s="308"/>
+      <c r="BJ72" s="309"/>
+      <c r="BK72" s="310"/>
+      <c r="BL72" s="311"/>
+      <c r="BM72" s="312"/>
       <c r="BN72" s="2"/>
-      <c r="BO72" s="332" t="s">
+      <c r="BO72" s="433" t="s">
         <v>199</v>
       </c>
-      <c r="BP72" s="332"/>
-      <c r="BQ72" s="332"/>
-      <c r="BR72" s="332"/>
-      <c r="BS72" s="332"/>
-      <c r="BT72" s="332"/>
-      <c r="BU72" s="332"/>
+      <c r="BP72" s="433"/>
+      <c r="BQ72" s="433"/>
+      <c r="BR72" s="433"/>
+      <c r="BS72" s="433"/>
+      <c r="BT72" s="433"/>
+      <c r="BU72" s="433"/>
       <c r="BV72" s="2"/>
       <c r="BW72" s="2"/>
       <c r="BX72" s="2"/>
@@ -14920,19 +14934,19 @@
       <c r="DF72" s="2"/>
     </row>
     <row r="73" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A73" s="281" t="s">
+      <c r="A73" s="280" t="s">
         <v>189</v>
       </c>
-      <c r="B73" s="291">
+      <c r="B73" s="290">
         <v>46129</v>
       </c>
       <c r="C73" s="235" t="s">
         <v>84</v>
       </c>
-      <c r="D73" s="327">
+      <c r="D73" s="326">
         <v>1</v>
       </c>
-      <c r="E73" s="326" t="s">
+      <c r="E73" s="325" t="s">
         <v>148</v>
       </c>
       <c r="F73" s="236"/>
@@ -14986,25 +15000,25 @@
       <c r="BB73" s="2"/>
       <c r="BC73" s="2"/>
       <c r="BD73" s="2"/>
-      <c r="BE73" s="305"/>
-      <c r="BF73" s="306"/>
-      <c r="BG73" s="307"/>
-      <c r="BH73" s="308"/>
-      <c r="BI73" s="309"/>
-      <c r="BJ73" s="310"/>
-      <c r="BK73" s="311"/>
-      <c r="BL73" s="312"/>
-      <c r="BM73" s="313"/>
+      <c r="BE73" s="304"/>
+      <c r="BF73" s="305"/>
+      <c r="BG73" s="306"/>
+      <c r="BH73" s="307"/>
+      <c r="BI73" s="308"/>
+      <c r="BJ73" s="309"/>
+      <c r="BK73" s="310"/>
+      <c r="BL73" s="311"/>
+      <c r="BM73" s="312"/>
       <c r="BN73" s="2"/>
-      <c r="BO73" s="332" t="s">
+      <c r="BO73" s="331" t="s">
         <v>200</v>
       </c>
-      <c r="BP73" s="332"/>
-      <c r="BQ73" s="332"/>
-      <c r="BR73" s="332"/>
-      <c r="BS73" s="332"/>
-      <c r="BT73" s="332"/>
-      <c r="BU73" s="332"/>
+      <c r="BP73" s="331"/>
+      <c r="BQ73" s="331"/>
+      <c r="BR73" s="331"/>
+      <c r="BS73" s="331"/>
+      <c r="BT73" s="331"/>
+      <c r="BU73" s="331"/>
       <c r="BV73" s="2"/>
       <c r="BW73" s="2"/>
       <c r="BX73" s="2"/>
@@ -15044,19 +15058,19 @@
       <c r="DF73" s="2"/>
     </row>
     <row r="74" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A74" s="281" t="s">
+      <c r="A74" s="280" t="s">
         <v>188</v>
       </c>
-      <c r="B74" s="291">
+      <c r="B74" s="290">
         <v>46129</v>
       </c>
       <c r="C74" s="235" t="s">
         <v>84</v>
       </c>
-      <c r="D74" s="327">
+      <c r="D74" s="326">
         <v>1</v>
       </c>
-      <c r="E74" s="326" t="s">
+      <c r="E74" s="325" t="s">
         <v>148</v>
       </c>
       <c r="F74" s="236"/>
@@ -15110,25 +15124,25 @@
       <c r="BB74" s="2"/>
       <c r="BC74" s="2"/>
       <c r="BD74" s="2"/>
-      <c r="BE74" s="305"/>
-      <c r="BF74" s="306"/>
-      <c r="BG74" s="307"/>
-      <c r="BH74" s="308"/>
-      <c r="BI74" s="309"/>
-      <c r="BJ74" s="310"/>
-      <c r="BK74" s="311"/>
-      <c r="BL74" s="312"/>
-      <c r="BM74" s="313"/>
+      <c r="BE74" s="304"/>
+      <c r="BF74" s="305"/>
+      <c r="BG74" s="306"/>
+      <c r="BH74" s="307"/>
+      <c r="BI74" s="308"/>
+      <c r="BJ74" s="309"/>
+      <c r="BK74" s="310"/>
+      <c r="BL74" s="311"/>
+      <c r="BM74" s="312"/>
       <c r="BN74" s="2"/>
-      <c r="BO74" s="332" t="s">
+      <c r="BO74" s="331" t="s">
         <v>201</v>
       </c>
-      <c r="BP74" s="332"/>
-      <c r="BQ74" s="332"/>
-      <c r="BR74" s="332"/>
-      <c r="BS74" s="332"/>
-      <c r="BT74" s="332"/>
-      <c r="BU74" s="332"/>
+      <c r="BP74" s="331"/>
+      <c r="BQ74" s="331"/>
+      <c r="BR74" s="331"/>
+      <c r="BS74" s="331"/>
+      <c r="BT74" s="331"/>
+      <c r="BU74" s="331"/>
       <c r="BV74" s="2"/>
       <c r="BW74" s="2"/>
       <c r="BX74" s="2"/>
@@ -15168,23 +15182,23 @@
       <c r="DF74" s="2"/>
     </row>
     <row r="75" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A75" s="281" t="s">
+      <c r="A75" s="435" t="s">
         <v>187</v>
       </c>
-      <c r="B75" s="291">
+      <c r="B75" s="290">
         <v>46129</v>
       </c>
       <c r="C75" s="235" t="s">
         <v>84</v>
       </c>
-      <c r="D75" s="329">
+      <c r="D75" s="328">
         <v>1</v>
       </c>
-      <c r="E75" s="326" t="s">
+      <c r="E75" s="325" t="s">
         <v>148</v>
       </c>
-      <c r="F75" s="239"/>
-      <c r="G75" s="240" t="s">
+      <c r="F75" s="238"/>
+      <c r="G75" s="239" t="s">
         <v>0</v>
       </c>
       <c r="H75" s="2"/>
@@ -15243,19 +15257,19 @@
       <c r="BI75" s="2"/>
       <c r="BJ75" s="2"/>
       <c r="BK75" s="2"/>
-      <c r="BL75" s="314"/>
-      <c r="BM75" s="315"/>
-      <c r="BN75" s="316"/>
-      <c r="BO75" s="332" t="s">
+      <c r="BL75" s="313"/>
+      <c r="BM75" s="314"/>
+      <c r="BN75" s="315"/>
+      <c r="BO75" s="331" t="s">
         <v>202</v>
       </c>
-      <c r="BP75" s="332"/>
-      <c r="BQ75" s="332"/>
-      <c r="BR75" s="332"/>
-      <c r="BS75" s="332"/>
-      <c r="BT75" s="332"/>
-      <c r="BU75" s="332"/>
-      <c r="BV75" s="317"/>
+      <c r="BP75" s="331"/>
+      <c r="BQ75" s="331"/>
+      <c r="BR75" s="331"/>
+      <c r="BS75" s="331"/>
+      <c r="BT75" s="331"/>
+      <c r="BU75" s="331"/>
+      <c r="BV75" s="316"/>
       <c r="BW75" s="2"/>
       <c r="BX75" s="2"/>
       <c r="BY75" s="2"/>
@@ -15294,21 +15308,23 @@
       <c r="DF75" s="2"/>
     </row>
     <row r="76" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A76" s="432" t="s">
+      <c r="A76" s="329" t="s">
         <v>209</v>
       </c>
-      <c r="B76" s="291">
+      <c r="B76" s="290">
         <v>46129</v>
       </c>
       <c r="C76" s="235" t="s">
         <v>84</v>
       </c>
-      <c r="D76" s="329">
+      <c r="D76" s="328">
         <v>0.75</v>
       </c>
-      <c r="E76" s="238"/>
-      <c r="F76" s="239"/>
-      <c r="G76" s="240"/>
+      <c r="E76" s="325" t="s">
+        <v>149</v>
+      </c>
+      <c r="F76" s="238"/>
+      <c r="G76" s="239"/>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
@@ -15365,9 +15381,9 @@
       <c r="BI76" s="2"/>
       <c r="BJ76" s="2"/>
       <c r="BK76" s="2"/>
-      <c r="BL76" s="314"/>
-      <c r="BM76" s="315"/>
-      <c r="BN76" s="316"/>
+      <c r="BL76" s="313"/>
+      <c r="BM76" s="314"/>
+      <c r="BN76" s="315"/>
       <c r="BO76" s="433" t="s">
         <v>204</v>
       </c>
@@ -15377,7 +15393,7 @@
       <c r="BS76" s="433"/>
       <c r="BT76" s="433"/>
       <c r="BU76" s="433"/>
-      <c r="BV76" s="317"/>
+      <c r="BV76" s="316"/>
       <c r="BW76" s="2"/>
       <c r="BX76" s="2"/>
       <c r="BY76" s="2"/>
@@ -15416,52 +15432,140 @@
       <c r="DF76" s="2"/>
     </row>
     <row r="77" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A77" s="281" t="s">
+      <c r="A77" s="280" t="s">
         <v>186</v>
       </c>
-      <c r="B77" s="291">
+      <c r="B77" s="290">
         <v>46129</v>
       </c>
       <c r="C77" s="235" t="s">
         <v>84</v>
       </c>
-      <c r="D77" s="327">
+      <c r="D77" s="326">
         <v>1</v>
       </c>
-      <c r="E77" s="326" t="s">
+      <c r="E77" s="325" t="s">
         <v>148</v>
       </c>
-      <c r="BO77" s="332" t="s">
+      <c r="BO77" s="331" t="s">
         <v>205</v>
       </c>
-      <c r="BP77" s="332"/>
-      <c r="BQ77" s="332"/>
-      <c r="BR77" s="332"/>
-      <c r="BS77" s="332"/>
-      <c r="BT77" s="332"/>
-      <c r="BU77" s="332"/>
+      <c r="BP77" s="331"/>
+      <c r="BQ77" s="331"/>
+      <c r="BR77" s="331"/>
+      <c r="BS77" s="331"/>
+      <c r="BT77" s="331"/>
+      <c r="BU77" s="331"/>
     </row>
     <row r="78" spans="1:110" x14ac:dyDescent="0.8">
-      <c r="A78" s="435" t="s">
+      <c r="A78" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B78" s="291">
+      <c r="B78" s="290">
         <v>46134</v>
       </c>
-      <c r="C78" s="291">
+      <c r="C78" s="290">
         <v>46139</v>
       </c>
-      <c r="BT78" s="436" t="s">
+      <c r="E78" s="325" t="s">
+        <v>149</v>
+      </c>
+      <c r="BT78" s="330" t="s">
         <v>211</v>
       </c>
-      <c r="BU78" s="436"/>
-      <c r="BV78" s="436"/>
-      <c r="BW78" s="436"/>
-      <c r="BX78" s="436"/>
-      <c r="BY78" s="436"/>
+      <c r="BU78" s="330"/>
+      <c r="BV78" s="330"/>
+      <c r="BW78" s="330"/>
+      <c r="BX78" s="330"/>
+      <c r="BY78" s="330"/>
+    </row>
+    <row r="79" spans="1:110" x14ac:dyDescent="0.8">
+      <c r="A79" t="s">
+        <v>213</v>
+      </c>
+      <c r="B79" s="290">
+        <v>46134</v>
+      </c>
+      <c r="C79" s="290">
+        <v>46139</v>
+      </c>
+      <c r="E79" s="325" t="s">
+        <v>149</v>
+      </c>
+      <c r="BT79" s="330" t="s">
+        <v>214</v>
+      </c>
+      <c r="BU79" s="330"/>
+      <c r="BV79" s="330"/>
+      <c r="BW79" s="330"/>
+      <c r="BX79" s="330"/>
+      <c r="BY79" s="330"/>
     </row>
   </sheetData>
-  <mergeCells count="78">
+  <mergeCells count="79">
+    <mergeCell ref="BT79:BY79"/>
+    <mergeCell ref="BO76:BU76"/>
+    <mergeCell ref="BO70:BS70"/>
+    <mergeCell ref="BH62:BO62"/>
+    <mergeCell ref="BH63:BO63"/>
+    <mergeCell ref="BH64:BO64"/>
+    <mergeCell ref="BH65:BO65"/>
+    <mergeCell ref="BH66:BO66"/>
+    <mergeCell ref="BH67:BO67"/>
+    <mergeCell ref="BH68:BO68"/>
+    <mergeCell ref="BO75:BU75"/>
+    <mergeCell ref="BO71:BU71"/>
+    <mergeCell ref="BO72:BU72"/>
+    <mergeCell ref="BO73:BU73"/>
+    <mergeCell ref="BO74:BU74"/>
+    <mergeCell ref="BA48:BH48"/>
+    <mergeCell ref="BA49:BH49"/>
+    <mergeCell ref="BA50:BH50"/>
+    <mergeCell ref="BA52:BH52"/>
+    <mergeCell ref="BH69:BO69"/>
+    <mergeCell ref="BA53:BH53"/>
+    <mergeCell ref="BA55:BH55"/>
+    <mergeCell ref="BA54:BH54"/>
+    <mergeCell ref="BA56:BH56"/>
+    <mergeCell ref="BA51:BH51"/>
+    <mergeCell ref="BH57:BO57"/>
+    <mergeCell ref="BH61:BO61"/>
+    <mergeCell ref="BH60:BO60"/>
+    <mergeCell ref="BH59:BO59"/>
+    <mergeCell ref="BH58:BO58"/>
+    <mergeCell ref="BA45:BH45"/>
+    <mergeCell ref="BA46:BH46"/>
+    <mergeCell ref="BA38:BH38"/>
+    <mergeCell ref="BA39:BH39"/>
+    <mergeCell ref="BA40:BH40"/>
+    <mergeCell ref="BA41:BH41"/>
+    <mergeCell ref="AF32:AM32"/>
+    <mergeCell ref="AF30:AM30"/>
+    <mergeCell ref="BA42:BH42"/>
+    <mergeCell ref="BA43:BH43"/>
+    <mergeCell ref="BA44:BH44"/>
+    <mergeCell ref="R17:Y17"/>
+    <mergeCell ref="P9:R9"/>
+    <mergeCell ref="BA47:BH47"/>
+    <mergeCell ref="AT36:BA36"/>
+    <mergeCell ref="AT35:BA35"/>
+    <mergeCell ref="AT37:BA37"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="P13:R13"/>
+    <mergeCell ref="R15:Y15"/>
+    <mergeCell ref="R16:Y16"/>
+    <mergeCell ref="AE33:AL33"/>
+    <mergeCell ref="AO33:AT33"/>
+    <mergeCell ref="AO34:AT34"/>
+    <mergeCell ref="AF28:AM28"/>
+    <mergeCell ref="AF29:AM29"/>
+    <mergeCell ref="K7:R7"/>
+    <mergeCell ref="P8:R8"/>
+    <mergeCell ref="P10:R10"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="H2:S2"/>
+    <mergeCell ref="H5:K5"/>
     <mergeCell ref="BT78:BY78"/>
     <mergeCell ref="BO77:BU77"/>
     <mergeCell ref="AF31:AM31"/>
@@ -15478,68 +15582,6 @@
     <mergeCell ref="S22:W22"/>
     <mergeCell ref="T2:AX2"/>
     <mergeCell ref="AY2:CB2"/>
-    <mergeCell ref="K7:R7"/>
-    <mergeCell ref="P8:R8"/>
-    <mergeCell ref="P10:R10"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="H2:S2"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="R17:Y17"/>
-    <mergeCell ref="P9:R9"/>
-    <mergeCell ref="BA47:BH47"/>
-    <mergeCell ref="AT36:BA36"/>
-    <mergeCell ref="AT35:BA35"/>
-    <mergeCell ref="AT37:BA37"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="P13:R13"/>
-    <mergeCell ref="R15:Y15"/>
-    <mergeCell ref="R16:Y16"/>
-    <mergeCell ref="AE33:AL33"/>
-    <mergeCell ref="AO33:AT33"/>
-    <mergeCell ref="AO34:AT34"/>
-    <mergeCell ref="AF28:AM28"/>
-    <mergeCell ref="AF29:AM29"/>
-    <mergeCell ref="AF32:AM32"/>
-    <mergeCell ref="AF30:AM30"/>
-    <mergeCell ref="BA42:BH42"/>
-    <mergeCell ref="BA43:BH43"/>
-    <mergeCell ref="BA44:BH44"/>
-    <mergeCell ref="BA45:BH45"/>
-    <mergeCell ref="BA46:BH46"/>
-    <mergeCell ref="BA38:BH38"/>
-    <mergeCell ref="BA39:BH39"/>
-    <mergeCell ref="BA40:BH40"/>
-    <mergeCell ref="BA41:BH41"/>
-    <mergeCell ref="BA48:BH48"/>
-    <mergeCell ref="BA49:BH49"/>
-    <mergeCell ref="BA50:BH50"/>
-    <mergeCell ref="BA52:BH52"/>
-    <mergeCell ref="BH69:BO69"/>
-    <mergeCell ref="BA53:BH53"/>
-    <mergeCell ref="BA55:BH55"/>
-    <mergeCell ref="BA54:BH54"/>
-    <mergeCell ref="BA56:BH56"/>
-    <mergeCell ref="BA51:BH51"/>
-    <mergeCell ref="BH57:BO57"/>
-    <mergeCell ref="BO76:BU76"/>
-    <mergeCell ref="BO70:BS70"/>
-    <mergeCell ref="BH62:BO62"/>
-    <mergeCell ref="BH63:BO63"/>
-    <mergeCell ref="BH64:BO64"/>
-    <mergeCell ref="BH65:BO65"/>
-    <mergeCell ref="BH66:BO66"/>
-    <mergeCell ref="BH67:BO67"/>
-    <mergeCell ref="BH68:BO68"/>
-    <mergeCell ref="BH61:BO61"/>
-    <mergeCell ref="BH60:BO60"/>
-    <mergeCell ref="BH59:BO59"/>
-    <mergeCell ref="BH58:BO58"/>
-    <mergeCell ref="BO75:BU75"/>
-    <mergeCell ref="BO71:BU71"/>
-    <mergeCell ref="BO72:BU72"/>
-    <mergeCell ref="BO73:BU73"/>
-    <mergeCell ref="BO74:BU74"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
